--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1cf3487e497644f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R242ac835ca714518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R9f7b39f2442e48e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R79887e37706647f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R147403299fa443fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1c002432162c4d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rb81b1f27cf2d49eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf1a546e02fc64072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5113ae3026174d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rf45a7e9ed09e4e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R83068b30977b4544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R998ebf0e1436479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Ra65cf24e2c5c4691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Ra0adf47a99854822"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,7 +375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd78accfe435647b7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2ddc1dcb445d44bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -676,8 +676,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:f>COUNTIF('Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -712,8 +711,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:f>IF(B5=0,0,AVERAGE('Loop Tracker'!$S$2:$S$21))</x:f>
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -761,12 +759,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A13,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
-        <x:f>IF(B13=0,0,C13/B13)</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F13" s="29" t="str"/>
       <x:c r="G13" s="29" t="str"/>
@@ -865,7 +861,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7632b52c9eba4a85"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44d34abe412a47dc"/>
 </x:worksheet>
 </file>
 
@@ -1051,7 +1047,7 @@
         <x:v>Manifest covers expected MEG/EEG/log file families; ambiguous rows are explicit.</x:v>
       </x:c>
       <x:c r="K3" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
         <x:v>P0</x:v>
@@ -1071,14 +1067,14 @@
       <x:c r="Q3" s="14" t="str">
         <x:v>Harden `manifest-from-paths` and produce a manifest summary with explicit unknowns rather than guessing.</x:v>
       </x:c>
-      <x:c r="R3" s="14" t="str"/>
+      <x:c r="R3" s="14" t="str">
+        <x:v>Manifest v1 closed on 2026-06-29. Rows now include family/warnings, optional sizes, and raw/log pairing summaries.</x:v>
+      </x:c>
       <x:c r="S3" s="16" t="n">
-        <x:f>IF(K3="Done",1,IF(K3="Review",0.8,IF(K3="In Progress",0.5,IF(K3="Blocked",0.2,IF(K3="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="T3" s="14" t="str">
-        <x:f>IF(K3="Blocked","Fix blocker",IF(K3="Review","Review/merge",IF(AND(L3="P0",K3="Not Started"),"Next candidate",IF(K3="Done","Closed","Normal"))))</x:f>
-        <x:v>Next candidate</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="68" customHeight="1">
@@ -1139,7 +1135,6 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T4" s="14" t="str">
-        <x:f>IF(K4="Blocked","Fix blocker",IF(K4="Review","Review/merge",IF(AND(L4="P0",K4="Not Started"),"Next candidate",IF(K4="Done","Closed","Normal"))))</x:f>
         <x:v>Next candidate</x:v>
       </x:c>
     </x:row>
@@ -2245,7 +2240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b075a17310e42bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3167448a87428f"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2338,14 +2333,30 @@
       <x:c r="I2" s="12" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="37" t="str"/>
-      <x:c r="B3" s="12" t="str"/>
-      <x:c r="C3" s="12" t="str"/>
-      <x:c r="D3" s="12" t="str"/>
-      <x:c r="E3" s="12" t="str"/>
-      <x:c r="F3" s="12" t="str"/>
-      <x:c r="G3" s="12" t="str"/>
-      <x:c r="H3" s="12" t="str"/>
+      <x:c r="A3" s="37" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="str">
+        <x:v>Manifest v1 acceptance gate met; proceed to safe tiny-shard selector.</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str">
+        <x:v>docs/LOOP_02_SPANISHBCBL_MANIFEST_V1.md</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="str">
+        <x:v>Loop 3</x:v>
+      </x:c>
       <x:c r="I3" s="12" t="str"/>
     </x:row>
     <x:row r="4">
@@ -4529,7 +4540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb1c476cd3ed4971"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1042f85c7c24895"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4827,7 +4838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc07a4424d7543ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24e6237d915f4676"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5187,7 +5198,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2bda03a0844d28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0cf8adf0114456b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf1a546e02fc64072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5113ae3026174d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rf45a7e9ed09e4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R83068b30977b4544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R998ebf0e1436479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Ra65cf24e2c5c4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Ra0adf47a99854822"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfe26df0f81964c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R20418c70cb104dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R877ec85f4d11466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0e161116c64b4c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rd84c27d3494d4033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R6294ab90f82e431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1a2a08a2b59144f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,7 +375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2ddc1dcb445d44bd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e7ef11e8848463b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -676,7 +676,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -711,7 +711,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -759,10 +759,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="F13" s="29" t="str"/>
       <x:c r="G13" s="29" t="str"/>
@@ -861,7 +861,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44d34abe412a47dc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c67c50aad74f55"/>
 </x:worksheet>
 </file>
 
@@ -1109,7 +1109,7 @@
         <x:v>Dry run prints exact files and size estimate; real download requires explicit confirmation.</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
         <x:v>P0</x:v>
@@ -1129,13 +1129,14 @@
       <x:c r="Q4" s="14" t="str">
         <x:v>Make the tiny selector safety-first: max bytes, max files, dry-run default, and clear planned download report.</x:v>
       </x:c>
-      <x:c r="R4" s="14" t="str"/>
+      <x:c r="R4" s="14" t="str">
+        <x:v>Safe selector closed on 2026-06-29. Plans now include caps, exact paths, known bytes, missing-size warnings, dry-run default, and execute guards.</x:v>
+      </x:c>
       <x:c r="S4" s="16" t="n">
-        <x:f>IF(K4="Done",1,IF(K4="Review",0.8,IF(K4="In Progress",0.5,IF(K4="Blocked",0.2,IF(K4="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="T4" s="14" t="str">
-        <x:v>Next candidate</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
@@ -2240,7 +2241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3167448a87428f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1039633932a6471c"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2360,15 +2361,33 @@
       <x:c r="I3" s="12" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="37" t="str"/>
-      <x:c r="B4" s="12" t="str"/>
-      <x:c r="C4" s="12" t="str"/>
-      <x:c r="D4" s="12" t="str"/>
-      <x:c r="E4" s="12" t="str"/>
-      <x:c r="F4" s="12" t="str"/>
-      <x:c r="G4" s="12" t="str"/>
-      <x:c r="H4" s="12" t="str"/>
-      <x:c r="I4" s="12" t="str"/>
+      <x:c r="A4" s="37" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>Safe tiny-shard selector acceptance gate met; proceed to cache schema v0.</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>docs/LOOP_03_SAFE_TINY_SHARD_SELECTOR.md</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
+        <x:v>Loop 4</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>Download remains dry-run by default; --execute with unknown sizes requires --allow-unknown-size.</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="37" t="str"/>
@@ -4540,7 +4559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1042f85c7c24895"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3140db02fc854dcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4838,7 +4857,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24e6237d915f4676"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ce3c58def9e4ef9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5198,7 +5217,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0cf8adf0114456b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R679de0abe603408f"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfe26df0f81964c7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R20418c70cb104dca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R877ec85f4d11466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0e161116c64b4c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rd84c27d3494d4033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R6294ab90f82e431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1a2a08a2b59144f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfcac1b0d70f84f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R597c9ef5402646ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rfd1e6196e49749a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re70d06af27ef4852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R7741c2a444424ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R5f4a03a2641d429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rddb45056823f4768"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,7 +375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e7ef11e8848463b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf5fa24380384ad5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -676,7 +676,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -711,7 +711,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -759,10 +759,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="F13" s="29" t="str"/>
       <x:c r="G13" s="29" t="str"/>
@@ -861,7 +861,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c67c50aad74f55"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d049b71ada843a5"/>
 </x:worksheet>
 </file>
 
@@ -1171,7 +1171,7 @@
         <x:v>Cache loads with one function; metadata explains every transformation.</x:v>
       </x:c>
       <x:c r="K5" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
         <x:v>P0</x:v>
@@ -1191,14 +1191,14 @@
       <x:c r="Q5" s="14" t="str">
         <x:v>Define the first stable tiny-cache schema and add a `load-cache` smoke command or test.</x:v>
       </x:c>
-      <x:c r="R5" s="14" t="str"/>
+      <x:c r="R5" s="14" t="str">
+        <x:v>Cache schema v0 closed on 2026-06-29. NPZ caches now load through one schema-aware function with validation, transformations, warnings, and sidecar metadata.</x:v>
+      </x:c>
       <x:c r="S5" s="16" t="n">
-        <x:f>IF(K5="Done",1,IF(K5="Review",0.8,IF(K5="In Progress",0.5,IF(K5="Blocked",0.2,IF(K5="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="T5" s="14" t="str">
-        <x:f>IF(K5="Blocked","Fix blocker",IF(K5="Review","Review/merge",IF(AND(L5="P0",K5="Not Started"),"Next candidate",IF(K5="Done","Closed","Normal"))))</x:f>
-        <x:v>Next candidate</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="68" customHeight="1">
@@ -2241,7 +2241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1039633932a6471c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a3ad57be5d44a7e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2390,15 +2390,33 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="37" t="str"/>
-      <x:c r="B5" s="12" t="str"/>
-      <x:c r="C5" s="12" t="str"/>
-      <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str"/>
-      <x:c r="F5" s="12" t="str"/>
-      <x:c r="G5" s="12" t="str"/>
-      <x:c r="H5" s="12" t="str"/>
-      <x:c r="I5" s="12" t="str"/>
+      <x:c r="A5" s="37" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>Cache schema v0 acceptance gate met; proceed to metrics and error reporting.</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>docs/LOOP_04_B2Q_MINI_CACHE_V0.md</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>Loop 5</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>Reports should build on load_npz_cache so synthetic and real caches share one contract.</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="37" t="str"/>
@@ -4559,7 +4577,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3140db02fc854dcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7621c859732e4b83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4857,7 +4875,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ce3c58def9e4ef9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R429d3416b9e94fe4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5217,7 +5235,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R679de0abe603408f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81a5301fedda4da8"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfcac1b0d70f84f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R597c9ef5402646ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rfd1e6196e49749a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re70d06af27ef4852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R7741c2a444424ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R5f4a03a2641d429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rddb45056823f4768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R975438e9ac4e4949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rde18850480c54770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R70fc3841182e4d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re3e7bed03af049e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R4d54396bd75a4b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R33c2c7f3ec1343ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R917cd5c241a7422f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -235,7 +235,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:varyColors val="0"/>
@@ -375,7 +374,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf5fa24380384ad5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17b63114c4fe40d1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -500,9 +499,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -676,7 +675,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -711,7 +710,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>20</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -759,10 +758,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
-        <x:v>0.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="29" t="str"/>
       <x:c r="G13" s="29" t="str"/>
@@ -861,7 +860,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d049b71ada843a5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10a3c80cdf3d4be0"/>
 </x:worksheet>
 </file>
 
@@ -1233,7 +1232,7 @@
         <x:v>Report runs from CLI and writes JSON/Markdown; metric tests pass.</x:v>
       </x:c>
       <x:c r="K6" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L6" s="14" t="str">
         <x:v>P0</x:v>
@@ -1256,11 +1255,11 @@
       <x:c r="R6" s="14" t="str"/>
       <x:c r="S6" s="16" t="n">
         <x:f>IF(K6="Done",1,IF(K6="Review",0.8,IF(K6="In Progress",0.5,IF(K6="Blocked",0.2,IF(K6="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T6" s="14" t="str">
         <x:f>IF(K6="Blocked","Fix blocker",IF(K6="Review","Review/merge",IF(AND(L6="P0",K6="Not Started"),"Next candidate",IF(K6="Done","Closed","Normal"))))</x:f>
-        <x:v>Next candidate</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
@@ -2241,7 +2240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a3ad57be5d44a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeb868de34624230"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2419,15 +2418,33 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="37" t="str"/>
-      <x:c r="B6" s="12" t="str"/>
-      <x:c r="C6" s="12" t="str"/>
-      <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str"/>
-      <x:c r="F6" s="12" t="str"/>
-      <x:c r="G6" s="12" t="str"/>
-      <x:c r="H6" s="12" t="str"/>
-      <x:c r="I6" s="12" t="str"/>
+      <x:c r="A6" s="37" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="str">
+        <x:v>Metrics/error report v1 acceptance gate met; proceed to LM-only / prior-only baseline.</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>docs/LOOP_05_METRICS_ERROR_REPORT_V1.md</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>Loop 6</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>Identity-smoke report verifies plumbing only; no neural/model performance claimed.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="37"/>
@@ -4577,7 +4594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7621c859732e4b83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f4c07f008d48e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4875,7 +4892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R429d3416b9e94fe4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81deadc505b2434a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5235,7 +5252,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81a5301fedda4da8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5820f18be00d4398"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R975438e9ac4e4949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rde18850480c54770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R70fc3841182e4d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re3e7bed03af049e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R4d54396bd75a4b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R33c2c7f3ec1343ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R917cd5c241a7422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0abb75e3a3ea40e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6dc5de27932843d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rcc556fa2d57440b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0ea76e940d5c46e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Red8428aae7b84e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Red28de9d8c2d4929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R4d51a0fece534ac0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -374,7 +374,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17b63114c4fe40d1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R163f203bde9945ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -675,7 +675,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -710,7 +710,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -776,12 +776,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A14,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D14" s="34" t="n">
-        <x:f>IF(B14=0,0,C14/B14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.25</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -860,7 +858,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10a3c80cdf3d4be0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd44fcbfdd24dfa"/>
 </x:worksheet>
 </file>
 
@@ -1294,7 +1292,7 @@
         <x:v>Baseline exists and is reported beside every neural result.</x:v>
       </x:c>
       <x:c r="K7" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
         <x:v>P0</x:v>
@@ -1314,14 +1312,14 @@
       <x:c r="Q7" s="14" t="str">
         <x:v>Implement an intentionally dumb but critical no-brain baseline and wire it into the report.</x:v>
       </x:c>
-      <x:c r="R7" s="14" t="str"/>
+      <x:c r="R7" s="14" t="str">
+        <x:v>Prior-only baseline closed on 2026-07-01. Report warns no neural signal used.</x:v>
+      </x:c>
       <x:c r="S7" s="16" t="n">
-        <x:f>IF(K7="Done",1,IF(K7="Review",0.8,IF(K7="In Progress",0.5,IF(K7="Blocked",0.2,IF(K7="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T7" s="14" t="str">
-        <x:f>IF(K7="Blocked","Fix blocker",IF(K7="Review","Review/merge",IF(AND(L7="P0",K7="Not Started"),"Next candidate",IF(K7="Done","Closed","Normal"))))</x:f>
-        <x:v>Next candidate</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -2240,7 +2238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeb868de34624230"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34087194b6b146d3"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2447,15 +2445,33 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="37"/>
-      <x:c r="B7" s="12"/>
-      <x:c r="C7" s="12"/>
-      <x:c r="D7" s="12"/>
-      <x:c r="E7" s="12"/>
-      <x:c r="F7" s="12"/>
-      <x:c r="G7" s="12"/>
-      <x:c r="H7" s="12"/>
-      <x:c r="I7" s="12"/>
+      <x:c r="A7" s="37" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="str">
+        <x:v>Prior-only baseline acceptance gate met; proceed to template / nearest-centroid baseline.</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="str">
+        <x:v>docs/LOOP_06_LM_PRIOR_BASELINE.md</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>Loop 7</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>No neural signal used; fit-on-eval mode is smoke-only unless separate train labels are supplied.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="37"/>
@@ -4594,7 +4610,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f4c07f008d48e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R522e7cd7d2d84cc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4892,7 +4908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81deadc505b2434a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra845581f9dba454c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5252,7 +5268,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5820f18be00d4398"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ad25d95464a400f"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0abb75e3a3ea40e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6dc5de27932843d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rcc556fa2d57440b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0ea76e940d5c46e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Red8428aae7b84e17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Red28de9d8c2d4929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R4d51a0fece534ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R357ce60614524c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Raf3b2b5f459e4057"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R1bd582fa4d3e4276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R37134cec72c54f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R6a3c57bfb73a480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re427850c1d784bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rabbfba5ac4ef45d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -374,7 +374,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R163f203bde9945ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64943fd6d98c48f8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -675,7 +675,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -710,7 +710,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -776,10 +776,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="34" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -858,7 +858,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd44fcbfdd24dfa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58e5cfbe2ed4fa1"/>
 </x:worksheet>
 </file>
 
@@ -1354,7 +1354,7 @@
         <x:v>Model trains in seconds and produces a baseline report.</x:v>
       </x:c>
       <x:c r="K8" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
         <x:v>P1</x:v>
@@ -1374,14 +1374,14 @@
       <x:c r="Q8" s="14" t="str">
         <x:v>Build a tiny transparent classifier before any neural net. Make it boring and trustworthy.</x:v>
       </x:c>
-      <x:c r="R8" s="14" t="str"/>
+      <x:c r="R8" s="14" t="str">
+        <x:v>Template baseline closed on 2026-07-01. Stratified synthetic holdout report warns synthetic data only.</x:v>
+      </x:c>
       <x:c r="S8" s="16" t="n">
-        <x:f>IF(K8="Done",1,IF(K8="Review",0.8,IF(K8="In Progress",0.5,IF(K8="Blocked",0.2,IF(K8="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T8" s="14" t="str">
-        <x:f>IF(K8="Blocked","Fix blocker",IF(K8="Review","Review/merge",IF(AND(L8="P0",K8="Not Started"),"Next candidate",IF(K8="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
@@ -2238,7 +2238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34087194b6b146d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d7bdf6fdee04ee0"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2474,15 +2474,33 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="37"/>
-      <x:c r="B8" s="12"/>
-      <x:c r="C8" s="12"/>
-      <x:c r="D8" s="12"/>
-      <x:c r="E8" s="12"/>
-      <x:c r="F8" s="12"/>
-      <x:c r="G8" s="12"/>
-      <x:c r="H8" s="12"/>
-      <x:c r="I8" s="12"/>
+      <x:c r="A8" s="37" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str">
+        <x:v>Template / nearest-centroid baseline acceptance gate met; proceed to tiny Conv / EEGNet-style baseline.</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="str">
+        <x:v>docs/LOOP_07_TEMPLATE_BASELINE.md</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>Loop 8</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>Uses neural windows but no deep learning; perfect synthetic score is expected from toy class bumps.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="37"/>
@@ -4610,7 +4628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R522e7cd7d2d84cc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3ab7357e6e7498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4908,7 +4926,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra845581f9dba454c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e8f1d0cda3f43e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5268,7 +5286,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ad25d95464a400f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35fd9d209c014db0"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R357ce60614524c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Raf3b2b5f459e4057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R1bd582fa4d3e4276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R37134cec72c54f56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R6a3c57bfb73a480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re427850c1d784bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rabbfba5ac4ef45d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f30ad2dc11e4567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R48a29ed14bf94656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R408ec8d82d1140f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R4c67b81de88e4dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R09cf2d9ad0b04ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb993434f623f45fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R4d86bceb5ff44faf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -374,7 +374,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64943fd6d98c48f8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref68df1dab004225"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -675,7 +675,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -710,7 +710,7 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>0.35</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
@@ -776,10 +776,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D14" s="34" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -858,7 +858,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58e5cfbe2ed4fa1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ad441ace904208"/>
 </x:worksheet>
 </file>
 
@@ -1416,7 +1416,7 @@
         <x:v>Trains on synthetic data in CI-like smoke mode; real data path documented.</x:v>
       </x:c>
       <x:c r="K9" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L9" s="14" t="str">
         <x:v>P1</x:v>
@@ -1436,14 +1436,14 @@
       <x:c r="Q9" s="14" t="str">
         <x:v>Add a tiny neural baseline without making the package heavy; optional deps and fast smoke test only.</x:v>
       </x:c>
-      <x:c r="R9" s="14" t="str"/>
+      <x:c r="R9" s="14" t="str">
+        <x:v>Tiny Conv baseline closed on 2026-07-01. Torch training smoke is present but skipped locally because the ml extra is not installed.</x:v>
+      </x:c>
       <x:c r="S9" s="16" t="n">
-        <x:f>IF(K9="Done",1,IF(K9="Review",0.8,IF(K9="In Progress",0.5,IF(K9="Blocked",0.2,IF(K9="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T9" s="14" t="str">
-        <x:f>IF(K9="Blocked","Fix blocker",IF(K9="Review","Review/merge",IF(AND(L9="P0",K9="Not Started"),"Next candidate",IF(K9="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
@@ -1504,8 +1504,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T10" s="14" t="str">
-        <x:f>IF(K10="Blocked","Fix blocker",IF(K10="Review","Review/merge",IF(AND(L10="P0",K10="Not Started"),"Next candidate",IF(K10="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:v>Next candidate</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
@@ -2238,7 +2237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d7bdf6fdee04ee0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8ae4d6688e74048"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2503,15 +2502,33 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="37"/>
-      <x:c r="B9" s="12"/>
-      <x:c r="C9" s="12"/>
-      <x:c r="D9" s="12"/>
-      <x:c r="E9" s="12"/>
-      <x:c r="F9" s="12"/>
-      <x:c r="G9" s="12"/>
-      <x:c r="H9" s="12"/>
-      <x:c r="I9" s="12"/>
+      <x:c r="A9" s="37" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str">
+        <x:v>Tiny Conv baseline acceptance gate met for optional-ML scaffold; proceed to CTC character-decoder scaffold.</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="str">
+        <x:v>docs/LOOP_08_TINY_CONV_BASELINE.md</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>Loop 9</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>Torch not installed locally; training smoke tests are present and skipped until .[ml] is available.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="37"/>
@@ -4628,7 +4645,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3ab7357e6e7498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb805d66d2f1943bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4926,7 +4943,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e8f1d0cda3f43e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3be777c7a82740f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5286,7 +5303,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35fd9d209c014db0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf07ab240937446b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f30ad2dc11e4567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R48a29ed14bf94656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R408ec8d82d1140f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R4c67b81de88e4dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R09cf2d9ad0b04ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb993434f623f45fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R4d86bceb5ff44faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra06ca626e5e64370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8ed7e579398a47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc187b7ccb7d24166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R16f4c43d929e49ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R71d0021b44ee47ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1b652dc607be48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R93efe519c1a24e3b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,7 +76,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -160,6 +160,12 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -225,13 +231,11 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>Loops by Phase</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -374,7 +378,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref68df1dab004225"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R54238ab2a7e644ad"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -412,7 +416,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I6" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I19"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -424,12 +429,13 @@
     <x:tableColumn id="8" name="Next Review"/>
     <x:tableColumn id="9" name="Notes"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I9" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I21"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -441,7 +447,7 @@
     <x:tableColumn id="8" name="Owner"/>
     <x:tableColumn id="9" name="Status"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -675,7 +681,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -686,7 +692,6 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="B7" s="36" t="n">
-        <x:f>COUNTIF('Loop Tracker'!$K$2:$K$21,"In Progress")+COUNTIF('Loop Tracker'!$K$2:$K$21,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="29" t="str"/>
@@ -698,7 +703,6 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B8" s="36" t="n">
-        <x:f>COUNTIF('Loop Tracker'!$K$2:$K$21,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
@@ -710,19 +714,21 @@
         <x:v>Average progress</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.905</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="36" t="str">
+    <x:row r="10" ht="130.5" customHeight="1">
+      <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
-      <x:c r="B10" s="36" t="str">
-        <x:v>Only start a new loop when the previous loop has a cache/report/demo or an explicit kill decision.</x:v>
-      </x:c>
+      <x:c r="B10" s="39" t="str">
+        <x:v>Next: Loop 20 NeuroTokenCache v0. Preserve modality, timebase, geometry, masks, split IDs, and provenance.</x:v>
+      </x:c>
+      <x:c r="C10" s="39"/>
+      <x:c r="D10" s="39"/>
       <x:c r="F10" s="29" t="str"/>
       <x:c r="G10" s="29" t="str"/>
       <x:c r="H10" s="29" t="str"/>
@@ -758,9 +764,11 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="n">
+        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A13,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="D13" s="34" t="n">
+        <x:f>AVERAGE('Loop Tracker'!$S$2:$S$6)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="29" t="str"/>
@@ -776,10 +784,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:v>3</x:v>
+        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A14,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="34" t="n">
-        <x:v>0.75</x:v>
+        <x:f>AVERAGE('Loop Tracker'!$S$7:$S$10)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -791,12 +801,11 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A15,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="34" t="n">
-        <x:f>IF(B15=0,0,C15/B15)</x:f>
-        <x:v>0</x:v>
+        <x:f>AVERAGE('Loop Tracker'!$S$11:$S$14)</x:f>
+        <x:v>0.775</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -808,12 +817,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C16" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A16,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D16" s="34" t="n">
-        <x:f>IF(B16=0,0,C16/B16)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -825,12 +832,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C17" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A17,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="34" t="n">
-        <x:f>IF(B17=0,0,C17/B17)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -842,12 +847,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C18" t="n">
-        <x:f>COUNTIFS('Loop Tracker'!$B$2:$B$21,A18,'Loop Tracker'!$K$2:$K$21,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="34" t="n">
-        <x:f>IF(B18=0,0,C18/B18)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -858,7 +861,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ad441ace904208"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8658ef2f3be841cf"/>
 </x:worksheet>
 </file>
 
@@ -1006,10 +1009,12 @@
         <x:v>Synthetic smoke path closed on 2026-06-29. Tests and CLI help passed; real extraction blocked until one explicit .fif/.mat pair is present.</x:v>
       </x:c>
       <x:c r="S2" s="16" t="n">
-        <x:v>100</x:v>
+        <x:f>IF(K2="Done",1,IF(K2="Review",0.8,IF(K2="In Progress",0.5,IF(K2="Blocked",0.2,IF(K2="Parked",0.1,0)))))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T2" s="14" t="str">
-        <x:v>Done</x:v>
+        <x:f>IF(K2="Blocked","Fix blocker",IF(K2="Review","Review/merge",IF(K2="Parked","Parked",IF(AND(L2="P0",K2="Not Started"),"Next candidate",IF(K2="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="68" customHeight="1">
@@ -1068,10 +1073,12 @@
         <x:v>Manifest v1 closed on 2026-06-29. Rows now include family/warnings, optional sizes, and raw/log pairing summaries.</x:v>
       </x:c>
       <x:c r="S3" s="16" t="n">
-        <x:v>100</x:v>
+        <x:f>IF(K3="Done",1,IF(K3="Review",0.8,IF(K3="In Progress",0.5,IF(K3="Blocked",0.2,IF(K3="Parked",0.1,0)))))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T3" s="14" t="str">
-        <x:v>Done</x:v>
+        <x:f>IF(K3="Blocked","Fix blocker",IF(K3="Review","Review/merge",IF(K3="Parked","Parked",IF(AND(L3="P0",K3="Not Started"),"Next candidate",IF(K3="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="68" customHeight="1">
@@ -1130,10 +1137,12 @@
         <x:v>Safe selector closed on 2026-06-29. Plans now include caps, exact paths, known bytes, missing-size warnings, dry-run default, and execute guards.</x:v>
       </x:c>
       <x:c r="S4" s="16" t="n">
-        <x:v>100</x:v>
+        <x:f>IF(K4="Done",1,IF(K4="Review",0.8,IF(K4="In Progress",0.5,IF(K4="Blocked",0.2,IF(K4="Parked",0.1,0)))))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T4" s="14" t="str">
-        <x:v>Done</x:v>
+        <x:f>IF(K4="Blocked","Fix blocker",IF(K4="Review","Review/merge",IF(K4="Parked","Parked",IF(AND(L4="P0",K4="Not Started"),"Next candidate",IF(K4="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
@@ -1192,10 +1201,12 @@
         <x:v>Cache schema v0 closed on 2026-06-29. NPZ caches now load through one schema-aware function with validation, transformations, warnings, and sidecar metadata.</x:v>
       </x:c>
       <x:c r="S5" s="16" t="n">
-        <x:v>100</x:v>
+        <x:f>IF(K5="Done",1,IF(K5="Review",0.8,IF(K5="In Progress",0.5,IF(K5="Blocked",0.2,IF(K5="Parked",0.1,0)))))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T5" s="14" t="str">
-        <x:v>Done</x:v>
+        <x:f>IF(K5="Blocked","Fix blocker",IF(K5="Review","Review/merge",IF(K5="Parked","Parked",IF(AND(L5="P0",K5="Not Started"),"Next candidate",IF(K5="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="68" customHeight="1">
@@ -1256,7 +1267,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T6" s="14" t="str">
-        <x:f>IF(K6="Blocked","Fix blocker",IF(K6="Review","Review/merge",IF(AND(L6="P0",K6="Not Started"),"Next candidate",IF(K6="Done","Closed","Normal"))))</x:f>
+        <x:f>IF(K6="Blocked","Fix blocker",IF(K6="Review","Review/merge",IF(K6="Parked","Parked",IF(AND(L6="P0",K6="Not Started"),"Next candidate",IF(K6="Done","Closed","Normal")))))</x:f>
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
@@ -1316,9 +1327,11 @@
         <x:v>Prior-only baseline closed on 2026-07-01. Report warns no neural signal used.</x:v>
       </x:c>
       <x:c r="S7" s="16" t="n">
+        <x:f>IF(K7="Done",1,IF(K7="Review",0.8,IF(K7="In Progress",0.5,IF(K7="Blocked",0.2,IF(K7="Parked",0.1,0)))))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="T7" s="14" t="str">
+        <x:f>IF(K7="Blocked","Fix blocker",IF(K7="Review","Review/merge",IF(K7="Parked","Parked",IF(AND(L7="P0",K7="Not Started"),"Next candidate",IF(K7="Done","Closed","Normal")))))</x:f>
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
@@ -1378,9 +1391,11 @@
         <x:v>Template baseline closed on 2026-07-01. Stratified synthetic holdout report warns synthetic data only.</x:v>
       </x:c>
       <x:c r="S8" s="16" t="n">
+        <x:f>IF(K8="Done",1,IF(K8="Review",0.8,IF(K8="In Progress",0.5,IF(K8="Blocked",0.2,IF(K8="Parked",0.1,0)))))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="T8" s="14" t="str">
+        <x:f>IF(K8="Blocked","Fix blocker",IF(K8="Review","Review/merge",IF(K8="Parked","Parked",IF(AND(L8="P0",K8="Not Started"),"Next candidate",IF(K8="Done","Closed","Normal")))))</x:f>
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
@@ -1440,13 +1455,15 @@
         <x:v>Tiny Conv baseline closed on 2026-07-01. Torch training smoke is present but skipped locally because the ml extra is not installed.</x:v>
       </x:c>
       <x:c r="S9" s="16" t="n">
+        <x:f>IF(K9="Done",1,IF(K9="Review",0.8,IF(K9="In Progress",0.5,IF(K9="Blocked",0.2,IF(K9="Parked",0.1,0)))))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="T9" s="14" t="str">
+        <x:f>IF(K9="Blocked","Fix blocker",IF(K9="Review","Review/merge",IF(K9="Parked","Parked",IF(AND(L9="P0",K9="Not Started"),"Next candidate",IF(K9="Done","Closed","Normal")))))</x:f>
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="14" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1457,28 +1474,28 @@
         <x:v>CTC Character Decoder Scaffold</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>Can we move from event labels toward sequence decoding without overbuilding?</x:v>
+        <x:v>Can a resource-bounded continuous sentence decoder learn sequence alignment without keystroke timing?</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>Add minimal CTC data interface and model scaffold; train on synthetic sequence data first.</x:v>
+        <x:v>Add a continuous sentence-window cache interface and optional tiny CTC model; prove synthetic training, then run one validated S21 block smoke.</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>CTC feasibility note: what labels/timing are needed.</x:v>
+        <x:v>CTC feasibility and official Brain2Qwerty v2 mapping note, including data, compute, latency, and hardware gaps.</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>Synthetic sequence cache; later real event-aligned cache.</x:v>
+        <x:v>Synthetic sequence data plus validated S21 session-1 block1: 66 trials; 16-channel extraction smoke.</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
-        <x:v>Tiny Conv/Transformer + CTC head scaffold.</x:v>
+        <x:v>Tiny Conv/CTC encoder with padded variable-length sentence batches; CPU-safe smoke defaults.</x:v>
       </x:c>
       <x:c r="I10" s="14" t="str">
-        <x:v>CER; blank-rate; alignment diagnostics.</x:v>
+        <x:v>CER; blank rate; input/target lengths; runtime; peak memory; cache bytes.</x:v>
       </x:c>
       <x:c r="J10" s="14" t="str">
-        <x:v>Synthetic CTC loop works; real-data assumptions are explicit.</x:v>
+        <x:v>Synthetic CTC loop trains; one sentence-level real cache validates shapes and labels; no real decoding-performance claim.</x:v>
       </x:c>
       <x:c r="K10" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L10" s="14" t="str">
         <x:v>P1</x:v>
@@ -1490,24 +1507,27 @@
         <x:v>M</x:v>
       </x:c>
       <x:c r="O10" s="14" t="str">
-        <x:v>Loop 8</x:v>
+        <x:v>Loop 8 plus Loop 8.5 real alignment gate</x:v>
       </x:c>
       <x:c r="P10" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q10" s="14" t="str">
-        <x:v>Create a minimal CTC scaffold that proves the interface, not SOTA accuracy.</x:v>
-      </x:c>
-      <x:c r="R10" s="14" t="str"/>
+        <x:v>Build a CPU-bounded continuous sentence cache and minimal CTC scaffold from the validated S21 block1. Keep Torch optional, preserve the no-brain comparator, and report shape, bytes, runtime, memory, CER, and blank rate.</x:v>
+      </x:c>
+      <x:c r="R10" s="14" t="str">
+        <x:v>Loop 9 closed 2026-07-10: b2q-sentence-cache v0; synthetic CTC 20/20 seeds at CER 0.0 with one training-only restart; prior CER 0.7068; real S21 cache 66x16x617, 1.6 MB, 6.24 sec, about 515 MiB peak RSS. No real model score.</x:v>
+      </x:c>
       <x:c r="S10" s="16" t="n">
         <x:f>IF(K10="Done",1,IF(K10="Review",0.8,IF(K10="In Progress",0.5,IF(K10="Blocked",0.2,IF(K10="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T10" s="14" t="str">
-        <x:v>Next candidate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="68" customHeight="1">
+        <x:f>IF(K10="Blocked","Fix blocker",IF(K10="Review","Review/merge",IF(K10="Parked","Parked",IF(AND(L10="P0",K10="Not Started"),"Next candidate",IF(K10="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="120" customHeight="1">
       <x:c r="A11" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -1524,22 +1544,22 @@
         <x:v>Add experiment runner for 1000/500/250/100/50 Hz or available equivalents.</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>Compression curve: accuracy retained per sampling rate and GB.</x:v>
+        <x:v>Resource curve: cache bytes, timepoints, effective bandwidth, timing grid, signal summaries, and CTC feasibility; no retained-accuracy claim.</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>Synthetic + one real block when possible.</x:v>
+        <x:v>Validated S21 block1, same 16 channels, 100/50/25 Hz; no additional download.</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
-        <x:v>Resample cache generation + baseline eval.</x:v>
+        <x:v>Sequential isolated sentence-cache workers plus strict cross-rate identity and feasibility audit.</x:v>
       </x:c>
       <x:c r="I11" s="14" t="str">
-        <x:v>accuracy retained per GB; extraction time.</x:v>
+        <x:v>cache bytes; runtime; peak RSS; bandwidth; boundary quantization; signal RMS/clamp; stride-one and official v2 CTC margins</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str">
-        <x:v>One report table compares at least 3 sampling rates.</x:v>
+        <x:v>One JSON/Markdown report compares identical 66-row, 16-channel 100/50/25 Hz caches and audits the official temporal contract; no accuracy winner is selected.</x:v>
       </x:c>
       <x:c r="K11" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L11" s="14" t="str">
         <x:v>P1</x:v>
@@ -1551,25 +1571,27 @@
         <x:v>M</x:v>
       </x:c>
       <x:c r="O11" s="14" t="str">
-        <x:v>Loops 4,7</x:v>
+        <x:v>Loop 9 real sentence cache</x:v>
       </x:c>
       <x:c r="P11" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q11" s="14" t="str">
-        <x:v>Run a simple sampling-rate sweep and report accuracy/size/time tradeoffs.</x:v>
-      </x:c>
-      <x:c r="R11" s="14" t="str"/>
+        <x:v>Run isolated one-thread 100/50/25 Hz sentence-cache extraction from validated S21 block1; verify exact identity and report resource, bandwidth, timing, signal, and CTC constraints without training.</x:v>
+      </x:c>
+      <x:c r="R11" s="14" t="str">
+        <x:v>Loop 10 closed 2026-07-10. 100/50/25 Hz caches: 1,663,209 / 846,334 / 431,451 bytes; final run 4.121 / 3.586 / 3.539 sec. Stride-one: all 66/66 feasible. Official v2 kernel16/stride4: 66/66, 66/66, 0/66. No accuracy winner selected.</x:v>
+      </x:c>
       <x:c r="S11" s="16" t="n">
         <x:f>IF(K11="Done",1,IF(K11="Review",0.8,IF(K11="In Progress",0.5,IF(K11="Blocked",0.2,IF(K11="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T11" s="14" t="str">
-        <x:f>IF(K11="Blocked","Fix blocker",IF(K11="Review","Review/merge",IF(AND(L11="P0",K11="Not Started"),"Next candidate",IF(K11="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="68" customHeight="1">
+        <x:f>IF(K11="Blocked","Fix blocker",IF(K11="Review","Review/merge",IF(K11="Parked","Parked",IF(AND(L11="P0",K11="Not Started"),"Next candidate",IF(K11="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="120" customHeight="1">
       <x:c r="A12" s="14" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -1580,28 +1602,28 @@
         <x:v>Channel / Sensor Subset Sweep</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>How many channels are actually needed for useful signal in the tiny loop?</x:v>
+        <x:v>Can explicit geometry-aware channel subsets reduce local input cost while preserving distinct signal proxies?</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>Add channel-picking strategy: all, motor-ish if known, random-k, top-variance.</x:v>
+        <x:v>Add channel geometry provenance and `channel-subset-sweep` with spatial-FPS, variance, seeded-random, and file-order strategies plus a 128 MiB cap.</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>Channel ablation report with caveats.</x:v>
+        <x:v>Real S21 channel-subset report anchored to the official v2 random-sensor ablation, with proxy and hardware caveats.</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>Tiny cache with channel metadata.</x:v>
+        <x:v>Validated S21 session-1 block1: 66 sentences, 102 magnetometers, 100 Hz; no additional download.</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
-        <x:v>Feature/channel subset + baseline eval.</x:v>
+        <x:v>Nested 76/51/25/16/8-channel subsets using spatial FPS, same-block post-scaling variance, seed-17 random, and first-order controls.</x:v>
       </x:c>
       <x:c r="I12" s="14" t="str">
-        <x:v>accuracy retained per channel count; size reduction.</x:v>
+        <x:v>cache bytes; runtime/RSS; marginal variance share; mean/max spatial coverage; set overlap; exact trial/text/timing identity; no decoder score</x:v>
       </x:c>
       <x:c r="J12" s="14" t="str">
-        <x:v>At least 3 channel settings are comparable from the same split.</x:v>
+        <x:v>One finite-geometry 102-mag base and 20 subset caches stay under 128 MiB, preserve exact identity and signal slices, and yield candidates without claiming an accuracy winner.</x:v>
       </x:c>
       <x:c r="K12" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L12" s="14" t="str">
         <x:v>P1</x:v>
@@ -1613,22 +1635,24 @@
         <x:v>M</x:v>
       </x:c>
       <x:c r="O12" s="14" t="str">
-        <x:v>Loop 10</x:v>
+        <x:v>Loop 10 100 Hz cache plus validated S21 raw geometry</x:v>
       </x:c>
       <x:c r="P12" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q12" s="14" t="str">
-        <x:v>Implement channel subset sweeps using explicit strategies and honest caveats.</x:v>
-      </x:c>
-      <x:c r="R12" s="14" t="str"/>
+        <x:v>Extract one 102-magnetometer 100 Hz S21 base cache with geometry before preload. Run nested 76/51/25/16/8 spatial-FPS, variance, random, and first-order subsets under 128 MiB; report resources, proxy metrics, overlaps, and exact identity without an accuracy or OPM claim.</x:v>
+      </x:c>
+      <x:c r="R12" s="14" t="str">
+        <x:v>Closed 2026-07-10. Base 66x102x617: 10,602,568 B, 12.004 s, 1,679,278,080 B peak RSS. Sweep: 3.492 s and 73,683,875 B. At 16 channels, FPS mean/max coverage was 34.9/69.8 mm with 14.8% variance share; variance was 56.6/140.3 mm with 21.3%; first-order was 102.2/219.3 mm. Exact identities passed; no accuracy winner.</x:v>
+      </x:c>
       <x:c r="S12" s="16" t="n">
         <x:f>IF(K12="Done",1,IF(K12="Review",0.8,IF(K12="In Progress",0.5,IF(K12="Blocked",0.2,IF(K12="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T12" s="14" t="str">
-        <x:f>IF(K12="Blocked","Fix blocker",IF(K12="Review","Review/merge",IF(AND(L12="P0",K12="Not Started"),"Next candidate",IF(K12="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:f>IF(K12="Blocked","Fix blocker",IF(K12="Review","Review/merge",IF(K12="Parked","Parked",IF(AND(L12="P0",K12="Not Started"),"Next candidate",IF(K12="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
@@ -1642,28 +1666,28 @@
         <x:v>Precision + Storage Sweep</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>Can we shrink caches by changing representation before losing too much signal?</x:v>
+        <x:v>Can we reduce local cache and load cost while bounding signal distortion before any decoder test?</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>Add cache writer variants: float32, float16, optional int8 quantized, compressed NPZ.</x:v>
+        <x:v>Add a representation runner for float32, float16, and calibrated integer/serialization variants without changing the sentence-cache contract.</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>Storage report: MB, load time, metric deltas.</x:v>
+        <x:v>Storage/distortion report covering bytes, encode/load time, reconstruction error, saturation, and proof limits.</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>B2Q-mini cache.</x:v>
+        <x:v>Fixed Loop 11 102-mag base plus 16-channel FPS and variance candidate caches; no new download.</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
-        <x:v>Precision and serialization variants.</x:v>
+        <x:v>Deterministic encode/decode variants over identical arrays; no model training.</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>MB per minute/event; accuracy delta; load time.</x:v>
+        <x:v>bytes; compression ratio; encode/load time; reconstruction RMSE/max error; saturation; exact metadata identity</x:v>
       </x:c>
       <x:c r="J13" s="14" t="str">
-        <x:v>Report shows at least 3 storage variants with reproducible commands.</x:v>
+        <x:v>At least three representations preserve schema and trial identity, stay within an explicit output cap, and report distortion without declaring retained decoder accuracy.</x:v>
       </x:c>
       <x:c r="K13" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L13" s="14" t="str">
         <x:v>P1</x:v>
@@ -1675,22 +1699,24 @@
         <x:v>M</x:v>
       </x:c>
       <x:c r="O13" s="14" t="str">
-        <x:v>Loop 10</x:v>
+        <x:v>Loop 11 geometry-aware subset caches</x:v>
       </x:c>
       <x:c r="P13" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q13" s="14" t="str">
-        <x:v>Compare cache precision/storage formats and produce a size-versus-score report.</x:v>
-      </x:c>
-      <x:c r="R13" s="14" t="str"/>
+        <x:v>On fixed Loop 11 base, FPS-16, and variance-16 caches, compare float32, float16, and calibrated integer/serialization variants. Record bytes, encode/load time, reconstruction RMSE/max error, saturation, and metadata identity; do not train or call a format accuracy-preserving.</x:v>
+      </x:c>
+      <x:c r="R13" s="14" t="str">
+        <x:v>Closed 2026-07-10. Five encodings across base/FPS-16/variance-16 produced 15 exact-identity artifacts in 34.4 MiB. Qint16 was 49.84% smaller with worst relative RMSE 0.003693%; qint8 was 80.75% smaller with worst relative RMSE 0.9531%. No clipping or decoder accuracy claim; float32 remains default.</x:v>
+      </x:c>
       <x:c r="S13" s="16" t="n">
         <x:f>IF(K13="Done",1,IF(K13="Review",0.8,IF(K13="In Progress",0.5,IF(K13="Blocked",0.2,IF(K13="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T13" s="14" t="str">
-        <x:f>IF(K13="Blocked","Fix blocker",IF(K13="Review","Review/merge",IF(AND(L13="P0",K13="Not Started"),"Next candidate",IF(K13="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:f>IF(K13="Blocked","Fix blocker",IF(K13="Review","Review/merge",IF(K13="Parked","Parked",IF(AND(L13="P0",K13="Not Started"),"Next candidate",IF(K13="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
@@ -1701,31 +1727,31 @@
         <x:v>Compression</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>Zarr / Lazy Cache Backend</x:v>
+        <x:v>Measured Lazy-Backend Gate</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>When NPZ becomes awkward, can we stream chunks without rewriting the whole system?</x:v>
+        <x:v>Is current NPZ complete/partial access materially limiting enough to justify another backend?</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>Add optional Zarr backend behind same cache interface.</x:v>
+        <x:v>Add an isolated NPZ access benchmark with explicit thresholds and only build another backend after a failed gate.</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>Backend comparison note: NPZ vs Zarr for tiny/medium data.</x:v>
+        <x:v>Backend decision note separating relative partial-read inefficiency from absolute local cost, including a no-build outcome.</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>Synthetic + tiny cache.</x:v>
+        <x:v>Nine fixed Loop 11/12 real caches; no raw FIF read, new data download, or signal-cache write.</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str">
-        <x:v>Chunked array storage; lazy loading.</x:v>
+        <x:v>Fresh one-thread workers for full, 1-row, and 8-row standard/packed NPZ access with exact decoded hashes.</x:v>
       </x:c>
       <x:c r="I14" s="14" t="str">
-        <x:v>load time; random access time; file count; cache size.</x:v>
+        <x:v>full/partial median time; peak RSS; compressed bytes; exact identity; implementation overhead</x:v>
       </x:c>
       <x:c r="J14" s="14" t="str">
-        <x:v>Zarr is optional; NPZ remains default; same training interface works.</x:v>
+        <x:v>A backend is built only after a failed declared gate; otherwise NPZ stays default with durable revisit triggers.</x:v>
       </x:c>
       <x:c r="K14" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Parked</x:v>
       </x:c>
       <x:c r="L14" s="14" t="str">
         <x:v>P2</x:v>
@@ -1743,19 +1769,21 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q14" s="14" t="str">
-        <x:v>Add Zarr as an optional backend only after NPZ is stable; do not break the simple path.</x:v>
-      </x:c>
-      <x:c r="R14" s="14" t="str"/>
+        <x:v>Run the bounded NPZ access gate first. Record relative inefficiency and absolute time/memory/size separately; add no backend without a failed measured gate and exact semantic-parity plan.</x:v>
+      </x:c>
+      <x:c r="R14" s="14" t="str">
+        <x:v>Closed 2026-07-10 as Parked. 9/9 caches passed exact hashes and all budgets. Largest 10.1 MiB; slowest full/partial 60.386/53.634 ms; highest worker RSS 140.6 MiB. One-row member amplification is 66x, but absolute cost is below budget. Zarr was not installed; proceed to Loop 14.</x:v>
+      </x:c>
       <x:c r="S14" s="16" t="n">
         <x:f>IF(K14="Done",1,IF(K14="Review",0.8,IF(K14="In Progress",0.5,IF(K14="Blocked",0.2,IF(K14="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="T14" s="14" t="str">
-        <x:f>IF(K14="Blocked","Fix blocker",IF(K14="Review","Review/merge",IF(AND(L14="P0",K14="Not Started"),"Next candidate",IF(K14="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="68" customHeight="1">
+        <x:f>IF(K14="Blocked","Fix blocker",IF(K14="Review","Review/merge",IF(K14="Parked","Parked",IF(AND(L14="P0",K14="Not Started"),"Next candidate",IF(K14="Done","Closed","Normal")))))</x:f>
+        <x:v>Parked</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="132" customHeight="1">
       <x:c r="A15" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -1766,28 +1794,28 @@
         <x:v>Split Protocol v1</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>Are we accidentally evaluating on data that is too similar to training?</x:v>
+        <x:v>Are repeated sentence texts or fit-on-eval transformations leaking information into validation/test results?</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>Add explicit split types: event, sentence, session, subject where metadata permits.</x:v>
+        <x:v>Add deterministic sentence-text train/validation/test membership, explicit event/session/subject capability labels, membership hashes, and leakage validation.</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>Evaluation protocol note and leakage checklist.</x:v>
+        <x:v>Protocol note mapping the official v2 80/10/10 text-group principle to inspectable local metadata and documenting stricter session/subject gates.</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>Tiny cache + manifest metadata.</x:v>
+        <x:v>Synthetic fixtures plus current 66-row S21 cache for plumbing only; no new download and no session/subject generalization claim.</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>Deterministic splits and seed tracking.</x:v>
+        <x:v>Pure-Python deterministic grouping, duplicate-text containment, train-only fitting rules, and report-level refusal of unsupported split claims.</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>gap between random/event/session splits.</x:v>
+        <x:v>partition counts; group overlap; membership hash; unavailable metadata; fit-scope violations</x:v>
       </x:c>
       <x:c r="J15" s="14" t="str">
-        <x:v>Every report names the split type; leakage risks are visible.</x:v>
+        <x:v>Every report names algorithm/version/group key; duplicate text never crosses partitions; unsupported session/subject splits fail or report unavailable; train-only fit scope is auditable.</x:v>
       </x:c>
       <x:c r="K15" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
         <x:v>P0</x:v>
@@ -1799,25 +1827,27 @@
         <x:v>S</x:v>
       </x:c>
       <x:c r="O15" s="14" t="str">
-        <x:v>Loops 4-7</x:v>
+        <x:v>Loops 4-13</x:v>
       </x:c>
       <x:c r="P15" s="14" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="Q15" s="14" t="str">
-        <x:v>Make split type explicit and impossible to ignore in every training/eval report.</x:v>
-      </x:c>
-      <x:c r="R15" s="14" t="str"/>
+        <x:v>Keep the strict 55/6/5 membership and five source test rows frozen. The capped second-session gate is resolved by Loop 15; do not retune Loop 14 on either holdout.</x:v>
+      </x:c>
+      <x:c r="R15" s="14" t="str">
+        <x:v>Closed 2026-07-10. Train-only scaler and exact report binding passed. Prior/tiny source-test CER 0.953488/0.947674 remained near-null. The second-session requirement is now resolved in Loop 15, whose fixed model fails transfer.</x:v>
+      </x:c>
       <x:c r="S15" s="16" t="n">
         <x:f>IF(K15="Done",1,IF(K15="Review",0.8,IF(K15="In Progress",0.5,IF(K15="Blocked",0.2,IF(K15="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T15" s="14" t="str">
-        <x:f>IF(K15="Blocked","Fix blocker",IF(K15="Review","Review/merge",IF(AND(L15="P0",K15="Not Started"),"Next candidate",IF(K15="Done","Closed","Normal"))))</x:f>
-        <x:v>Next candidate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="68" customHeight="1">
+        <x:f>IF(K15="Blocked","Fix blocker",IF(K15="Review","Review/merge",IF(K15="Parked","Parked",IF(AND(L15="P0",K15="Not Started"),"Next candidate",IF(K15="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="210" customHeight="1">
       <x:c r="A16" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -1831,25 +1861,25 @@
         <x:v>Can a tiny subject/session adapter improve stability without retraining everything?</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>Add per-channel normalization, session normalization, and simple adapter hooks.</x:v>
+        <x:v>Zero-parameter robust channel-affine adapter and bounded synthetic gate runner.</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>Adaptation note: what changed, what stayed fixed, how many examples used.</x:v>
+        <x:v>Primary-source adaptation note and synthetic proof protocol with explicit limits.</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>Two sessions/subjects if available; otherwise synthetic domain shift.</x:v>
+        <x:v>Synthetic 96-row adapter gate only; real Stage A source-test and session-2 rows remain frozen.</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
-        <x:v>Normalization + small adapter baseline.</x:v>
+        <x:v>Source-train robust statistics plus unlabeled target-calibration statistics; validation-only adapter selection and one frozen synthetic holdout evaluation.</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
-        <x:v>metric delta vs calibration examples.</x:v>
+        <x:v>Validation/holdout CER gain; paired bootstrap interval; reconstruction MAE; leakage, runtime, memory, storage, and cache checks.</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>Synthetic domain-shift adapter works; real-data path is documented.</x:v>
+        <x:v>Stage A protocol and negative transfer result preserved. Stage B uses a 64/16/16 split, selects only on validation, improves frozen synthetic holdout, and keeps all real holdouts unopened.</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
         <x:v>P2</x:v>
@@ -1867,16 +1897,16 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q16" s="14" t="str">
-        <x:v>Implement the lightest adapter experiment possible: normalization first, learned adapter second.</x:v>
-      </x:c>
-      <x:c r="R16" s="14" t="str"/>
+        <x:v>Close after the synthetic affine gate passes; preserve real S21 holdouts and move calibration-size plus non-diagonal stress tests to Loop 16.</x:v>
+      </x:c>
+      <x:c r="R16" s="14" t="str">
+        <x:v>Stage B closed 2026-07-10. Validation identity/adapted CER 0.327273/0; holdout identity/adapted/prior 0.344828/0/0.577586. Runtime 2.498 s, one thread, 21,354 artifact bytes, zero cache bytes. Synthetic diagonal shift only; no real adapter-benefit claim. Evidence: docs/LOOP_15_STAGE_B_SYNTHETIC_ADAPTER.md</x:v>
+      </x:c>
       <x:c r="S16" s="16" t="n">
-        <x:f>IF(K16="Done",1,IF(K16="Review",0.8,IF(K16="In Progress",0.5,IF(K16="Blocked",0.2,IF(K16="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T16" s="14" t="str">
-        <x:f>IF(K16="Blocked","Fix blocker",IF(K16="Review","Review/merge",IF(AND(L16="P0",K16="Not Started"),"Next candidate",IF(K16="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
@@ -1893,25 +1923,25 @@
         <x:v>How many examples or minutes are needed before performance becomes useful?</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>Add experiment runner varying calibration set size.</x:v>
+        <x:v>Bounded six-size, three-seed calibration curve; multi-view CTC reuse; non-diagonal and time-varying synthetic shifts.</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>Calibration curve report.</x:v>
+        <x:v>Primary-source calibration/drift note with registered selection and explicit failure interpretation.</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>At least one subject/session; synthetic fallback.</x:v>
+        <x:v>Synthetic 96-row source plus independent 48-row unlabeled calibration pool; all real holdouts frozen.</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>Train/adapt with k examples and evaluate held-out.</x:v>
+        <x:v>Validation-only nested 1/2/4/8/16/32-row curve across stationary diagonal, channel mixing, and within-row drift; one post-selection holdout pass.</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>CER/WER or accuracy vs examples/minutes.</x:v>
+        <x:v>CER versus rows/minutes; seed range; paired uncertainty; reconstruction ratio; runtime, RSS, bytes, and leakage checks.</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>Report includes 5+ calibration points or explains why not.</x:v>
+        <x:v>Six sizes and three seeds complete; calibration texts are disjoint; target labels unused; static affine failure under mixing/time drift is reported; no real cache opened.</x:v>
       </x:c>
       <x:c r="K17" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
         <x:v>P2</x:v>
@@ -1929,19 +1959,19 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q17" s="14" t="str">
-        <x:v>Create a calibration curve runner that works on synthetic data and plugs into real caches.</x:v>
-      </x:c>
-      <x:c r="R17" s="14" t="str"/>
+        <x:v>Close as synthetic characterization. Keep robust affine scoped to stationary diagonal drift; require a new synthetic gate for covariance or causal rolling adaptation.</x:v>
+      </x:c>
+      <x:c r="R17" s="14" t="str">
+        <x:v>Closed 2026-07-10. Registered stationary selection: 1 synthetic row/1.26 s; holdout median identity/adapted CER 0.422414/0.232759, with 2 gains and 1 tie. Channel mixing 0.568966/0.862069 and time drift 0.439655/0.603448; all 6 stress seeds harmed. 1.897 s, 1 thread, 158,256 bytes, 0 cache bytes. Evidence: docs/LOOP_16_SYNTHETIC_CALIBRATION_CURVE.md</x:v>
+      </x:c>
       <x:c r="S17" s="16" t="n">
-        <x:f>IF(K17="Done",1,IF(K17="Review",0.8,IF(K17="In Progress",0.5,IF(K17="Blocked",0.2,IF(K17="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T17" s="14" t="str">
-        <x:f>IF(K17="Blocked","Fix blocker",IF(K17="Review","Review/merge",IF(AND(L17="P0",K17="Not Started"),"Next candidate",IF(K17="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="68" customHeight="1">
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="91.5" customHeight="1">
       <x:c r="A18" s="14" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -1961,19 +1991,19 @@
         <x:v>Demo script with limitations copy that avoids mind-reading claims.</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>Synthetic or tiny cache.</x:v>
+        <x:v>Existing compact synthetic/report artifacts first; no new raw-data acquisition.</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
-        <x:v>Interactive visualization.</x:v>
+        <x:v>Local Gradio workflow that reads standardized artifacts and exposes prediction, target, errors, uncertainty, calibration state, and proof posture.</x:v>
       </x:c>
       <x:c r="I18" s="14" t="str">
-        <x:v>time to first demo; explanation clarity.</x:v>
+        <x:v>startup/runtime/RSS; displayed CER/WER; artifact provenance; proof-label completeness; interaction smoke result.</x:v>
       </x:c>
       <x:c r="J18" s="14" t="str">
-        <x:v>Demo runs locally from one command and shows at least one example end-to-end.</x:v>
+        <x:v>One local command renders at least one end-to-end example and never labels the noncausal typed-sentence model as real-time or arbitrary-thought decoding.</x:v>
       </x:c>
       <x:c r="K18" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
         <x:v>P1</x:v>
@@ -1991,19 +2021,21 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q18" s="14" t="str">
-        <x:v>Make a small honest demo: no hype, just signal, prediction, errors, and uncertainty.</x:v>
-      </x:c>
-      <x:c r="R18" s="14" t="str"/>
+        <x:v>Build an honest local Gradio demo from compact existing artifacts. Show signal snippet, target, prediction, CER/WER, uncertainty, calibration state, and proof posture. Keep heavy dependencies optional, measure startup/RSS, and state that the current model is noncausal and typing-task-specific.</x:v>
+      </x:c>
+      <x:c r="R18" s="14" t="str">
+        <x:v>Closed 2026-07-10. Artifact-backed Gradio 6.20 console exposes 19 held-out synthetic examples, signal, target/prediction, CER/WER/keyboard error, aggregate-only real evidence, calibration state, and SHA-256 provenance. Predictive confidence is explicitly unavailable; decoder is noncausal and typing-task-specific. Final startup audit: 1.644 s, 224,837,632-byte peak RSS, 136,734-byte source cache, all 8 checks pass. Desktop/mobile/browser interactions pass with zero console errors. No network fetch, real model run, raw-data access, or new cache. Evidence: docs/LOOP_17_HONEST_LOCAL_DEMO.md</x:v>
+      </x:c>
       <x:c r="S18" s="16" t="n">
         <x:f>IF(K18="Done",1,IF(K18="Review",0.8,IF(K18="In Progress",0.5,IF(K18="Blocked",0.2,IF(K18="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T18" s="14" t="str">
-        <x:f>IF(K18="Blocked","Fix blocker",IF(K18="Review","Review/merge",IF(AND(L18="P0",K18="Not Started"),"Next candidate",IF(K18="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="68" customHeight="1">
+        <x:f>IF(K18="Blocked","Fix blocker",IF(K18="Review","Review/merge",IF(K18="Parked","Parked",IF(AND(L18="P0",K18="Not Started"),"Next candidate",IF(K18="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="100.5" customHeight="1">
       <x:c r="A19" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -2035,7 +2067,7 @@
         <x:v>At least 3 baselines appear in one leaderboard table.</x:v>
       </x:c>
       <x:c r="K19" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
         <x:v>P1</x:v>
@@ -2055,17 +2087,19 @@
       <x:c r="Q19" s="14" t="str">
         <x:v>Build the experiment report-card format and local leaderboard; make missing metadata obvious.</x:v>
       </x:c>
-      <x:c r="R19" s="14" t="str"/>
+      <x:c r="R19" s="14" t="str">
+        <x:v>Closed 2026-07-10. Versioned artifact-only schema indexes 11 saved runs across 6 exact cohorts and 4 method families. Four within-cohort rankings are authorized; event holdout and fit-on-eval smoke stay unranked, and no global winner exists. All required fields pass; missing SemER, cache hashes, code version, method-specific resources, or uncertainty remain explicit. 247,440 source-report bytes produce 58 deterministic core files and 103,789 total bytes in 0.012 s at 21,643,264-byte peak RSS. Replay is byte-identical outside audit.json. Raw/cache/signal reads, model runs, network fetches, and holdout reopenings are zero. Evidence: docs/LOOP_18_VERSIONED_REPORT_CARDS.md</x:v>
+      </x:c>
       <x:c r="S19" s="16" t="n">
         <x:f>IF(K19="Done",1,IF(K19="Review",0.8,IF(K19="In Progress",0.5,IF(K19="Blocked",0.2,IF(K19="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T19" s="14" t="str">
-        <x:f>IF(K19="Blocked","Fix blocker",IF(K19="Review","Review/merge",IF(AND(L19="P0",K19="Not Started"),"Next candidate",IF(K19="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="68" customHeight="1">
+        <x:f>IF(K19="Blocked","Fix blocker",IF(K19="Review","Review/merge",IF(K19="Parked","Parked",IF(AND(L19="P0",K19="Not Started"),"Next candidate",IF(K19="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="195" customHeight="1">
       <x:c r="A20" s="14" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -2097,7 +2131,7 @@
         <x:v>Bridge is optional and clearly labeled exploratory.</x:v>
       </x:c>
       <x:c r="K20" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
         <x:v>P3</x:v>
@@ -2117,17 +2151,19 @@
       <x:c r="Q20" s="14" t="str">
         <x:v>Explore an EEG adapter only after the core MEG loop is stable; keep claims conservative.</x:v>
       </x:c>
-      <x:c r="R20" s="14" t="str"/>
+      <x:c r="R20" s="14" t="str">
+        <x:v>Closed 2026-07-10. Metadata gate passed 13/13; pinned S7 bundle: 4 files / 94,842,381 bytes. Lazy extraction matched 2,534/2,534 triggers at 2.024 ms median residual and wrote a 12,428,800-byte 2197 x 61 x 25 cache. Template/prior label accuracy: 0.009091/0.122727; paired delta interval [-0.134545,-0.093636]. MOABB parked; no new dependency or full EEG tree; EEG/MEG separate. Evidence: docs/LOOP_19_EEG_BRAINVISION_BRIDGE.md</x:v>
+      </x:c>
       <x:c r="S20" s="16" t="n">
         <x:f>IF(K20="Done",1,IF(K20="Review",0.8,IF(K20="In Progress",0.5,IF(K20="Blocked",0.2,IF(K20="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T20" s="14" t="str">
-        <x:f>IF(K20="Blocked","Fix blocker",IF(K20="Review","Review/merge",IF(AND(L20="P0",K20="Not Started"),"Next candidate",IF(K20="Done","Closed","Normal"))))</x:f>
-        <x:v>Normal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="68" customHeight="1">
+        <x:f>IF(K20="Blocked","Fix blocker",IF(K20="Review","Review/merge",IF(K20="Parked","Parked",IF(AND(L20="P0",K20="Not Started"),"Next candidate",IF(K20="Done","Closed","Normal")))))</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="69" customHeight="1">
       <x:c r="A21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -2177,7 +2213,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="Q21" s="14" t="str">
-        <x:v>Design the neurotoken interface as a small abstraction, not a grand architecture rewrite.</x:v>
+        <x:v>Define NeuroTokenCache v0 as a small modality-aware interface over existing arrays and synthetic embeddings. Preserve timebase, channel geometry, masks, split membership, provenance, and resource accounting; assume no unreleased v2 data and train no larger model.</x:v>
       </x:c>
       <x:c r="R21" s="14" t="str"/>
       <x:c r="S21" s="16" t="n">
@@ -2185,7 +2221,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T21" s="14" t="str">
-        <x:f>IF(K21="Blocked","Fix blocker",IF(K21="Review","Review/merge",IF(AND(L21="P0",K21="Not Started"),"Next candidate",IF(K21="Done","Closed","Normal"))))</x:f>
+        <x:f>IF(K21="Blocked","Fix blocker",IF(K21="Review","Review/merge",IF(K21="Parked","Parked",IF(AND(L21="P0",K21="Not Started"),"Next candidate",IF(K21="Done","Closed","Normal")))))</x:f>
         <x:v>Normal</x:v>
       </x:c>
     </x:row>
@@ -2237,7 +2273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8ae4d6688e74048"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fe018fb8dd74004"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2302,7 +2338,7 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A2" s="37" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2327,9 +2363,9 @@
       <x:c r="H2" s="12" t="str">
         <x:v>Loop 2</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str"/>
-    </x:row>
-    <x:row r="3">
+      <x:c r="I2" s="12"/>
+    </x:row>
+    <x:row r="3" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A3" s="37" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2354,9 +2390,9 @@
       <x:c r="H3" s="12" t="str">
         <x:v>Loop 3</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str"/>
-    </x:row>
-    <x:row r="4">
+      <x:c r="I3" s="12"/>
+    </x:row>
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A4" s="37" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2385,7 +2421,7 @@
         <x:v>Download remains dry-run by default; --execute with unknown sizes requires --allow-unknown-size.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A5" s="37" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2414,7 +2450,7 @@
         <x:v>Reports should build on load_npz_cache so synthetic and real caches share one contract.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="37" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -2443,7 +2479,7 @@
         <x:v>Identity-smoke report verifies plumbing only; no neural/model performance claimed.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A7" s="37" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -2472,7 +2508,7 @@
         <x:v>No neural signal used; fit-on-eval mode is smoke-only unless separate train labels are supplied.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="37" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -2501,7 +2537,7 @@
         <x:v>Uses neural windows but no deep learning; perfect synthetic score is expected from toy class bumps.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="37" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -2530,148 +2566,382 @@
         <x:v>Torch not installed locally; training smoke tests are present and skipped until .[ml] is available.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="37"/>
-      <x:c r="B10" s="12"/>
-      <x:c r="C10" s="12"/>
-      <x:c r="D10" s="12"/>
-      <x:c r="E10" s="12"/>
-      <x:c r="F10" s="12"/>
-      <x:c r="G10" s="12"/>
-      <x:c r="H10" s="12"/>
-      <x:c r="I10" s="12"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="37"/>
-      <x:c r="B11" s="12"/>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12"/>
-      <x:c r="E11" s="12"/>
-      <x:c r="F11" s="12"/>
-      <x:c r="G11" s="12"/>
-      <x:c r="H11" s="12"/>
-      <x:c r="I11" s="12"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="37"/>
-      <x:c r="B12" s="12"/>
-      <x:c r="C12" s="12"/>
-      <x:c r="D12" s="12"/>
-      <x:c r="E12" s="12"/>
-      <x:c r="F12" s="12"/>
-      <x:c r="G12" s="12"/>
-      <x:c r="H12" s="12"/>
-      <x:c r="I12" s="12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="37"/>
-      <x:c r="B13" s="12"/>
-      <x:c r="C13" s="12"/>
-      <x:c r="D13" s="12"/>
-      <x:c r="E13" s="12"/>
-      <x:c r="F13" s="12"/>
-      <x:c r="G13" s="12"/>
-      <x:c r="H13" s="12"/>
-      <x:c r="I13" s="12"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="37"/>
-      <x:c r="B14" s="12"/>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="12"/>
-      <x:c r="E14" s="12"/>
-      <x:c r="F14" s="12"/>
-      <x:c r="G14" s="12"/>
-      <x:c r="H14" s="12"/>
-      <x:c r="I14" s="12"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="37"/>
-      <x:c r="B15" s="12"/>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12"/>
-      <x:c r="E15" s="12"/>
-      <x:c r="F15" s="12"/>
-      <x:c r="G15" s="12"/>
-      <x:c r="H15" s="12"/>
-      <x:c r="I15" s="12"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="37"/>
-      <x:c r="B16" s="12"/>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12"/>
-      <x:c r="E16" s="12"/>
-      <x:c r="F16" s="12"/>
-      <x:c r="G16" s="12"/>
-      <x:c r="H16" s="12"/>
-      <x:c r="I16" s="12"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="37"/>
-      <x:c r="B17" s="12"/>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="12"/>
-      <x:c r="E17" s="12"/>
-      <x:c r="F17" s="12"/>
-      <x:c r="G17" s="12"/>
-      <x:c r="H17" s="12"/>
-      <x:c r="I17" s="12"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="37"/>
-      <x:c r="B18" s="12"/>
-      <x:c r="C18" s="12"/>
-      <x:c r="D18" s="12"/>
-      <x:c r="E18" s="12"/>
-      <x:c r="F18" s="12"/>
-      <x:c r="G18" s="12"/>
-      <x:c r="H18" s="12"/>
-      <x:c r="I18" s="12"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="37"/>
-      <x:c r="B19" s="12"/>
-      <x:c r="C19" s="12"/>
-      <x:c r="D19" s="12"/>
-      <x:c r="E19" s="12"/>
-      <x:c r="F19" s="12"/>
-      <x:c r="G19" s="12"/>
-      <x:c r="H19" s="12"/>
-      <x:c r="I19" s="12"/>
+    <x:row r="10" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A10" s="37" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Proceed to a resource-bounded continuous-sentence CTC scaffold.</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str">
+        <x:v>S21 block1 gives a strict 66/66 identity trial mapping, while the official v2 architecture confirms continuous-window CTC is the next decoder layer.</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
+        <x:v>docs/REAL_DATA_VALIDATION_2026-07-10.md</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>Loop 9</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>Gate cleared for one real block only. Official v2 English data remains embargoed; local work is a SpanishBCBL surrogate, not a reproduction. Sources: https://github.com/facebookresearch/brain2qwerty and https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A11" s="37" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Proceed</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str">
+        <x:v>Sentence-cache v0, synthetic CTC, 20-seed stability, no-brain comparison, and the real S21 resource smoke satisfy Loop 9 without inventing a real model score.</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
+        <x:v>docs/LOOP_09_CONTINUOUS_SENTENCE_CTC.md</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>Loop 10</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>Real cache: 66x16x617, 1.6 MB, 6.24 sec, about 515 MiB peak RSS. Synthetic eval CER 0.0 vs prior CER 0.7068. Next: 100/50/25 Hz extraction sweep.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A12" s="37" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>Proceed without rate selection</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="str">
+        <x:v>The isolated 100/50/25 Hz resource and CTC-length gate is complete; lower rates shrink caches but remove bandwidth, and the official temporal reducer is structurally incompatible with 25 Hz on this block.</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="str">
+        <x:v>docs/LOOP_10_SAMPLING_RATE_SWEEP.md</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>Loop 11</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>Exact 66-row identity at all rates. Cache bytes: 1,663,209 / 846,334 / 431,451. Official v2 kernel16/stride4 feasibility: 66/66, 66/66, 0/66. No accuracy winner. Sources: https://github.com/facebookresearch/brain2qwerty/blob/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2/config/model_config.py and https://github.com/facebookresearch/brain2qwerty/blob/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2/utils.py</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A13" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>Proceed with two sensor-selection candidates; no channel-count winner</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="str">
+        <x:v>The resource/proxy gate passed, but spatial FPS and same-block variance optimize different evidence. Carry both into future held-out decoder evaluation and retain random/first controls.</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="str">
+        <x:v>docs/LOOP_11_CHANNEL_SENSOR_SUBSET_SWEEP.md</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
+        <x:v>Loop 12</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>Base: 102 magnetometers, 66x102x617, 10.1 MiB, 12.004 s, 1.6 GiB peak RSS. Twenty subsets used 70.3 MiB and exact identities passed. Official v2 retrained random 306-to-230/153/76 subsets; this local one-block proxy is not an accuracy reproduction. Sources: https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf and https://github.com/facebookresearch/brain2qwerty/blob/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2/config/model_config.py</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="132" customHeight="1">
+      <x:c r="A14" s="40" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>Proceed with qint16 and qint8 candidates; keep float32 default</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>All 15 representations preserve exact semantic identity with no source values outside the fixed range. Qint16 is the lowest-distortion packed candidate and qint8 is the smallest; no decoder was evaluated.</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>docs/LOOP_12_PRECISION_STORAGE_SWEEP.md</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>Loop 13/14</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>Qint16: 49.84% smaller, worst relative RMSE 0.003693%. Qint8: 80.75% smaller, worst relative RMSE 0.9531%. Packed caches decode to float32, so this is not integer-only inference or retained accuracy. Sources: https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf and https://arxiv.org/abs/1905.12322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="96" customHeight="1">
+      <x:c r="A15" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="str">
+        <x:v>Park optional Zarr; proceed to Loop 14</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="str">
+        <x:v>Nine current real standard/packed caches passed exact decoded-signal identity and declared time, memory, and size budgets. Partial NPZ reads are inefficient but not a material current bottleneck.</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="str">
+        <x:v>docs/LOOP_13_LAZY_BACKEND_GATE.md</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
+        <x:v>Loop 14 / threshold trigger</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
+        <x:v>Largest cache 10.1 MiB; slowest full/partial medians 60.386/53.634 ms; highest worker RSS 140.6 MiB. One-row member amplification 66x. Zarr not installed. Sources: https://numpy.org/doc/stable/reference/generated/numpy.savez_compressed.html and https://zarr-specs.readthedocs.io/en/latest/v3/chunk-grids/regular-grid/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="108" customHeight="1">
+      <x:c r="A16" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>Close strict split protocol; keep tiny CTC conclusion near-null</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="str">
+        <x:v>Train-only scaling and exact report binding pass. Tiny CTC improves by one character edit on five test rows, but poor train fit and a paired interval crossing zero do not show neural advantage.</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>docs/LOOP_14_SPLIT_PROTOCOL_V1.md</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str">
+        <x:v>Capped second-session data gate</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="str">
+        <x:v>55/6/5 rows. Prior/tiny CER 0.953488/0.947674. Delta -0.005814; bootstrap CI [-0.197279, 0.130653]; wins/ties/losses 2/0/3. No session, subject, real-time, or thought-reading claim. Source: https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="112" customHeight="1">
+      <x:c r="A17" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="str">
+        <x:v>Freeze session 2 after the fixed cross-session baseline fails</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="str">
+        <x:v>The complete session-2 acquisition, nonempty-MAT trial map, and frozen source-train scaler pass. The unchanged tiny CTC is materially worse than the no-signal prior, so session 2 is consumed evaluation data rather than an adapter tuning set.</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="str">
+        <x:v>docs/LOOP_15_SAME_SUBJECT_CROSS_SESSION.md</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="str">
+        <x:v>Synthetic adapter gate / pre-registered holdout</x:v>
+      </x:c>
+      <x:c r="I17" s="12" t="str">
+        <x:v>Pinned acquisition: 2,516,384,765 bytes, one worker. MAT gaps [54,58,60]. Source 55 train; 6 validation and 5 test unused. Session-2 rows 63. Tiny/prior CER 0.917949/0.775458; delta +0.142491; paired CI [+0.119386,+0.166069]; wins/ties/losses 3/2/58. Dataset: https://huggingface.co/datasets/bcbl190626/SpanishBCBL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="96" customHeight="1">
+      <x:c r="A18" s="40" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>Close Loop 15 after the bounded synthetic adapter mechanism gate passes</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>A zero-parameter robust channel-affine adapter reverses the registered diagonal gain/offset shift under validation-only selection. This establishes the mechanism and implementation path without reopening real evaluation data.</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>docs/LOOP_15_STAGE_B_SYNTHETIC_ADAPTER.md</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str">
+        <x:v>Loop 16 calibration-size and non-diagonal stress study</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>Synthetic 64/16/16 rows. Validation identity/adapted CER 0.327273/0; holdout identity/adapted/prior 0.344828/0/0.577586; paired interval [-0.408696,-0.286957]. Runtime 2.498 s, one thread, zero cache bytes. No real adapter-benefit claim. Sources: https://arxiv.org/abs/1603.04779 and https://doi.org/10.1109/TBME.2019.2913914</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="96" customHeight="1">
+      <x:c r="A19" s="40" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>Keep robust affine inside its measured stationary-diagonal scope</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>The registered synthetic curve finds a small stationary-diagonal calibration point but static independent-channel statistics harm every channel-mixing and within-row-drift holdout seed.</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>docs/LOOP_16_SYNTHETIC_CALIBRATION_CURVE.md</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str">
+        <x:v>Loop 17 honest demo plus a future synthetic covariance/causal drift gate</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>Six sizes x three seeds x three shifts. Selected 1 synthetic row/1.26 s by median validation rule; stationary holdout identity/adapted CER 0.422414/0.232759 with one tie. Mixing 0.568966/0.862069; time drift 0.439655/0.603448. One thread, 1.897 s, 158,256 bytes, zero cache bytes. Sources: https://doi.org/10.1609/aaai.v30i1.10306 and https://doi.org/10.1186/1687-6180-2012-129</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="37"/>
-      <x:c r="B20" s="12"/>
-      <x:c r="C20" s="12"/>
-      <x:c r="D20" s="12"/>
-      <x:c r="E20" s="12"/>
-      <x:c r="F20" s="12"/>
-      <x:c r="G20" s="12"/>
-      <x:c r="H20" s="12"/>
-      <x:c r="I20" s="12"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="37"/>
-      <x:c r="B21" s="12"/>
-      <x:c r="C21" s="12"/>
-      <x:c r="D21" s="12"/>
-      <x:c r="E21" s="12"/>
-      <x:c r="F21" s="12"/>
-      <x:c r="G21" s="12"/>
-      <x:c r="H21" s="12"/>
-      <x:c r="I21" s="12"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="37"/>
-      <x:c r="B22" s="12"/>
-      <x:c r="C22" s="12"/>
-      <x:c r="D22" s="12"/>
-      <x:c r="E22" s="12"/>
-      <x:c r="F22" s="12"/>
-      <x:c r="G22" s="12"/>
-      <x:c r="H22" s="12"/>
-      <x:c r="I22" s="12"/>
+      <x:c r="A20" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="str">
+        <x:v>Close the honest local demo and proceed to report-card standardization</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="str">
+        <x:v>The console reproduces compact saved artifacts, exposes uncertainty and noncausal scope, and keeps real results aggregate-only. Browser interaction and responsive layout pass without opening either observed real holdout.</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="str">
+        <x:v>docs/LOOP_17_HONEST_LOCAL_DEMO.md</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str">
+        <x:v>Loop 18 leaderboard + report cards</x:v>
+      </x:c>
+      <x:c r="I20" s="12" t="str">
+        <x:v>19 synthetic examples; 27 UI components; 4 callbacks; 1.644 s startup; 224,837,632-byte peak RSS; 136,734-byte source cache. All 8 audit checks pass. 1440x1000 and 390x844 QA pass with no console errors. Gradio remains optional; demo dependency added about 178,756 KiB to the existing environment. Sources: https://www.gradio.app/docs/gradio/blocks and https://facebookresearch.github.io/brain2qwerty/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="94.5" customHeight="1">
+      <x:c r="A21" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="str">
+        <x:v>Rank only inside exact evidence cohorts</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="str">
+        <x:v>Eleven historical runs can be indexed without retraining, but event versus sentence, synthetic versus real, and held-out versus fit-on-eval results are not globally comparable. CER and WER also disagree in the cross-session cohort.</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="str">
+        <x:v>docs/LOOP_18_VERSIONED_REPORT_CARDS.md</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="str">
+        <x:v>Loop 19 bounded EEG bridge discovery gate</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="str">
+        <x:v>11 cards; 6 cohorts; 4 ranked cohorts; 58 deterministic core files; 103,789 bytes; 0.012 s; 21,643,264-byte peak RSS; zero raw/cache/signal reads, model runs, network fetches, or holdout reopenings. Sources: https://research.google/pubs/model-cards-for-model-reporting/ ; https://mlflow.org/docs/latest/tracking/ ; https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="106.5" customHeight="1">
+      <x:c r="A22" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="str">
+        <x:v>Keep a native task-matched EEG bridge; record the first baseline as negative</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="str">
+        <x:v>One pinned 94,842,381-byte BrainVision-plus-MAT bundle validates complete selection, exact trigger-code alignment, lazy extraction, and cache reuse without MOABB. The minimally processed nearest-centroid event classifier is worse than its train-only prior, so bridge success must not become a decoder or hardware claim.</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:v>docs/LOOP_19_EEG_BRAINVISION_BRIDGE.md</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="str">
+        <x:v>Loop 20 modality-aware NeuroTokenCache v0 contract</x:v>
+      </x:c>
+      <x:c r="I22" s="12" t="str">
+        <x:v>2,534/2,534 trigger match; 2.024 ms median residual; 2,197 x 61 x 25 cache; 12,428,800 bytes; template/prior label accuracy 0.009091/0.122727; paired interval [-0.134545,-0.093636]. Sources: https://huggingface.co/datasets/bcbl190626/SpanishBCBL ; https://www.nature.com/articles/s41593-026-02303-2 ; https://github.com/facebookresearch/brain2qwerty/blob/3bf5a4099ca0d23bbe994b2287905760236e56e0/studies/spanishbcbl.py ; https://mne.tools/stable/generated/mne.io.read_raw_brainvision.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="37"/>
@@ -4632,7 +4902,7 @@
       <x:c r="I200" s="12"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="C2:C200">
       <x:formula1>"Proceed,Iterate,Park,Kill"</x:formula1>
     </x:dataValidation>
@@ -4642,10 +4912,16 @@
     <x:dataValidation type="list" sqref="G2:G200">
       <x:formula1>"Cheick,Codex,GPT,TBD"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="F13">
+      <x:formula1>"Yes,No"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G13">
+      <x:formula1>"Cheick,Codex,GPT,TBD"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb805d66d2f1943bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0cdbff58a2049e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4694,7 +4970,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="60" customHeight="1">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="14" t="str">
         <x:v>R1</x:v>
       </x:c>
@@ -4723,7 +4999,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="60" customHeight="1">
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A3" s="14" t="str">
         <x:v>R2</x:v>
       </x:c>
@@ -4752,7 +5028,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="60" customHeight="1">
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="14" t="str">
         <x:v>R3</x:v>
       </x:c>
@@ -4781,7 +5057,7 @@
         <x:v>Watching</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="60" customHeight="1">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="14" t="str">
         <x:v>R4</x:v>
       </x:c>
@@ -4810,7 +5086,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="60" customHeight="1">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="14" t="str">
         <x:v>R5</x:v>
       </x:c>
@@ -4839,7 +5115,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="60" customHeight="1">
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="14" t="str">
         <x:v>R6</x:v>
       </x:c>
@@ -4868,7 +5144,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="60" customHeight="1">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="14" t="str">
         <x:v>R7</x:v>
       </x:c>
@@ -4897,7 +5173,7 @@
         <x:v>Watching</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="60" customHeight="1">
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="14" t="str">
         <x:v>R8</x:v>
       </x:c>
@@ -4905,29 +5181,377 @@
         <x:v>Roadmap</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>Future unreleased data assumptions distort present architecture.</x:v>
+        <x:v>Public Brain2Qwerty v2 code is mistaken for a locally reproduced v2 result while EnglishBCBL data and required GPU scale remain unavailable.</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>Treat SpanishBCBL CTC as a small surrogate; cite the official code commit and data embargo; report compute, data, and latency gaps.</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>A local smoke metric is compared to the v2 paper, or implementation silently assumes EnglishBCBL or multi-GPU hardware.</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A10" s="12" t="str">
+        <x:v>R9</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>Hardware accessibility</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Local CPU success is mistaken for at-home sensor readiness; EEG accuracy loss and OPM shielding requirements are ignored.</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Track compute, sensor modality, shielding, motion, and causal latency as separate gates; cite primary hardware evidence.</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>A demo or roadmap calls the current MEG, EEG, or OPM path consumer-ready.</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>Cheick</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A11" s="12" t="str">
+        <x:v>R10</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>Compression evidence</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Lower sampling or channel counts are presented as retained neural accuracy based on stable scaled RMS or a fit inside one block.</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Require a second block/session split for accuracy; report Nyquist and spatial-information losses; keep resource sweeps score-free.</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>A report uses accuracy-retained language without independent evaluation, or selects a rate/channel count from one block.</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="108" hidden="0" customHeight="1">
+      <x:c r="A12" s="14" t="str">
+        <x:v>R11</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>Sensor selection</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>A geometry or variance proxy selected on one S21 block is mistaken for a generally optimal layout or an OPM-ready hardware design.</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Pre-register FPS and variance candidates; fit variance only on training data; evaluate held-out block/session/subject accuracy; keep modality, shielding, and geometry caveats explicit.</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>A subset is called optimal, accuracy-preserving, anatomical, or OPM-ready without held-out decoding and hardware validation.</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="84" customHeight="1">
+      <x:c r="A13" s="14" t="str">
+        <x:v>R12</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>Precision / storage</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>Low reconstruction error is mistaken for retained decoder accuracy or integer-only local inference.</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Keep float32 as default; evaluate packed candidates on one fixed held-out split; report clipping separately; state that current payloads decode to float32.</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>A report calls a packed cache accuracy-preserving, lower-RAM inference, real-time, or device-ready without a held-out decoder and model-runtime measurement.</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="78" customHeight="1">
+      <x:c r="A14" s="12" t="str">
+        <x:v>R13</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>Backend scaling</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>The parked Zarr decision is misread as a universal format verdict and future NPZ limits go unmonitored.</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="str">
-        <x:v>Use placeholder interfaces only; current loops must run on public/synthetic data.</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>Implementation requires unavailable dataset.</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="str">
-        <x:v>GPT</x:v>
-      </x:c>
-      <x:c r="I9" s="14" t="str">
-        <x:v>Open</x:v>
+      <x:c r="E14" s="12" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>Preserve the Loop 13 thresholds; rerun on larger caches or repeated subarray workflows; require semantic parity before any backend adoption.</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str">
+        <x:v>A cache crosses a size/time/RSS threshold, or training repeatedly reads subarrays while the old park decision is cited as final.</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
+        <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="96" customHeight="1">
+      <x:c r="A15" s="12" t="str">
+        <x:v>R14</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>Evaluation leakage</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="str">
+        <x:v>A valid sentence-membership table is mistaken for a strict evaluation even though scaling or sensor selection used validation/test rows.</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>Require fit_split=train plus matching protocol and semantic-membership hashes; freeze transforms for validation/test; block unsupported session/subject claims.</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
+        <x:v>A report cites strict membership while cache metadata lacks matching train-fit provenance, or aliases are counted as independent people.</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
+        <x:v>Mitigated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="112" customHeight="1">
+      <x:c r="A16" s="12" t="str">
+        <x:v>R15</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>Holdout reuse</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>Architecture, adapters, sensors, or precision are tuned against the five source test rows or observed 63-row session-2 evaluation until a known difference looks meaningful.</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>Freeze both observed holdouts; fit on source train only; select on source validation only; develop adapters on synthetic shift; pre-register the next real comparison and disclose all attempts.</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str">
+        <x:v>A new choice is justified by source-test or session-2 results, repeated holdout runs accumulate, or observed session 2 is described as untouched after tuning.</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="78" customHeight="1">
+      <x:c r="A17" s="14" t="str">
+        <x:v>R16</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>Synthetic validity</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>A diagonal synthetic shift may make robust affine adaptation look unrealistically complete.</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>Run multiple seeds, at least five calibration sizes, unpaired calibration, and non-diagonal or time-varying shifts before any real-data adapter claim.</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str">
+        <x:v>Near-perfect synthetic reconstruction without an untouched real-session benefit result.</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="88" customHeight="1">
+      <x:c r="A18" s="14" t="str">
+        <x:v>R17</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>Adapter scope</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>Automatic static robust-affine adaptation is applied when target drift includes channel mixing or changes within a sentence, worsening decoding relative to identity.</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>Keep identity as the default fallback; identify the shift family on synthetic validation; gate covariance-aware and causal rolling methods separately before any real evaluation.</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>Adapted validation CER exceeds identity, covariance changes remain after scaling, or rolling-window statistics move materially within one sequence.</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="91.5" customHeight="1">
+      <x:c r="A19" s="12" t="str">
+        <x:v>R18</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>Demo interpretation</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="str">
+        <x:v>Perfect synthetic examples or aggregate real metrics are mistaken for a live real-MEG decoder, calibrated confidence, arbitrary-thought reading, or at-home hardware evidence.</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
+        <x:v>Keep the proof strip visible; label examples synthetic and real rows aggregate-only; show confidence as unavailable; expose noncausal/task/hardware boundaries; publish provenance and audit checks.</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str">
+        <x:v>A screenshot, writeup, or downstream report omits synthetic, aggregate-only, noncausal, confidence-unavailable, or typing-task-specific labels.</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="91.5" customHeight="1">
+      <x:c r="A20" s="12" t="str">
+        <x:v>R19</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>Leaderboard comparability</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="str">
+        <x:v>A rank across different tasks, units, splits, subjects, proof postures, or metrics is presented as a global model winner.</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
+        <x:v>Authorize ranks only inside exact cohorts; expose CER, WER, and SemER separately; keep synthetic, real, event, sentence, fit-on-eval, and consumed-holdout evidence distinct; set global winner to null.</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
+        <x:v>A downstream table drops cohort/proof labels, merges event and sentence rows, hides fit-on-eval status, or selects one metric without disclosing disagreement.</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I20" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="99" customHeight="1">
+      <x:c r="A21" s="12" t="str">
+        <x:v>R20</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>EEG interpretation</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="str">
+        <x:v>A trigger-aligned cache or one minimally processed within-session S7 event result is presented as useful brain-to-text, EEG-MEG equivalence, portable sensing, or consumer hardware evidence.</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
+        <x:v>Keep EEG and MEG in separate cohorts; report exact key-label accuracy beside the train-only prior; label CER non-primary for key tokens; require explicit preprocessing plus independent session/subject protocols before any EEG performance or portability claim.</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
+        <x:v>A report cites alignment/cache completion as decoding performance, hides the 0.009091 versus 0.122727 negative result, compares EEG and MEG globally, or mentions at-home/consumer readiness.</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="8">
     <x:dataValidation type="list" sqref="D2:D200">
       <x:formula1>"Low,Medium,High"</x:formula1>
     </x:dataValidation>
@@ -4940,10 +5564,22 @@
     <x:dataValidation type="list" sqref="I2:I200">
       <x:formula1>"Open,Watching,Mitigated,Closed"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="D12">
+      <x:formula1>"Low,Medium,High"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E12">
+      <x:formula1>"Low,Medium,High"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H12">
+      <x:formula1>"Cheick,Codex,GPT,TBD"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I12">
+      <x:formula1>"Open,Watching,Mitigated,Closed"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3be777c7a82740f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2d0d12f208f47f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5176,10 +5812,10 @@
         <x:v>CTC Character Decoder Scaffold</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>Create a minimal CTC scaffold that proves the interface, not SOTA accuracy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+        <x:v>Build a CPU-bounded continuous sentence cache and minimal CTC scaffold from validated S21 block1. Keep Torch optional; preserve the no-brain baseline; report shape, bytes, runtime, memory, CER, and blank rate; make no full-v2 performance claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="84" customHeight="1">
       <x:c r="A11" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -5187,10 +5823,10 @@
         <x:v>Sampling-Rate Sweep</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>Run a simple sampling-rate sweep and report accuracy/size/time tradeoffs.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="58" customHeight="1">
+        <x:v>Run 100/50/25 Hz sentence-cache extraction from validated S21 block1 with identical 16-channel selection. Report bytes, runtime, peak RSS, valid lengths, CTC feasibility, and signal summaries; do not train or claim a real decoder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="96" customHeight="1">
       <x:c r="A12" s="14" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -5198,7 +5834,7 @@
         <x:v>Channel / Sensor Subset Sweep</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>Implement channel subset sweeps using explicit strategies and honest caveats.</x:v>
+        <x:v>Extract one 102-magnetometer 100 Hz S21 base cache with geometry before preload. Run nested 76/51/25/16/8 spatial-FPS, variance, random, and first-order subsets under 128 MiB; report resources, proxy metrics, overlaps, and exact identity without an accuracy or OPM claim.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -5209,7 +5845,7 @@
         <x:v>Precision + Storage Sweep</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Compare cache precision/storage formats and produce a size-versus-score report.</x:v>
+        <x:v>On fixed Loop 11 base, FPS-16, and variance-16 caches, compare float32, float16, and calibrated integer/serialization variants. Record bytes, encode/load time, reconstruction RMSE/max error, saturation, and metadata identity; do not train or call a format accuracy-preserving.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
@@ -5217,13 +5853,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>Zarr / Lazy Cache Backend</x:v>
+        <x:v>Measured Lazy-Backend Gate</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>Add Zarr as an optional backend only after NPZ is stable; do not break the simple path.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="58" customHeight="1">
+        <x:v>Run the bounded NPZ access gate first. Record relative inefficiency and absolute time/memory/size separately; add no backend without a failed measured gate and exact semantic-parity plan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="96" customHeight="1">
       <x:c r="A15" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -5231,10 +5867,10 @@
         <x:v>Split Protocol v1</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Make split type explicit and impossible to ignore in every training/eval report.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="58" customHeight="1">
+        <x:v>Keep the strict 55/6/5 membership and five test rows frozen. Fit every data-dependent transform on train rows, compare neural and no-brain reports with paired uncertainty, and acquire another capped paired session before real adapter or candidate work.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="86" customHeight="1">
       <x:c r="A16" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -5242,7 +5878,7 @@
         <x:v>Normalization + Adapter Baseline</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Implement the lightest adapter experiment possible: normalization first, learned adapter second.</x:v>
+        <x:v>Develop a synthetic domain-shift normalization/adapter gate and use only session-1 train rows for fit plus validation rows for selection. Keep source test and observed session 2 frozen; pre-register any next real comparison.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -5253,7 +5889,7 @@
         <x:v>Calibration Curve Study</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Create a calibration curve runner that works on synthetic data and plugs into real caches.</x:v>
+        <x:v>Build a CPU- and storage-bounded synthetic calibration curve for the robust channel-affine adapter. Use at least five calibration sizes, multiple shift seeds, unpaired target calibration, and one non-diagonal or time-varying shift. Report uncertainty and resource costs, compare against identity, and do not open any real holdout.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
@@ -5264,10 +5900,10 @@
         <x:v>Gradio Demo v1</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Make a small honest demo: no hype, just signal, prediction, errors, and uncertainty.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="58" customHeight="1">
+        <x:v>Build an honest, CPU-bounded Gradio demo from existing compact artifacts. Show a signal snippet, target, prediction, CER/WER, uncertainty, calibration status, and exact proof posture. Measure startup/RSS, keep Gradio optional, and state that the current typed-sentence CTC is noncausal and not arbitrary-thought decoding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="78" customHeight="1">
       <x:c r="A19" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -5275,10 +5911,10 @@
         <x:v>Leaderboard + Report Cards</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Build the experiment report-card format and local leaderboard; make missing metadata obvious.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="58" customHeight="1">
+        <x:v>Build Loop 18 as a local, artifact-only leaderboard. Define one versioned report-card contract for metrics, split/proof posture, comparator, resources, config, cache provenance, and missing-field flags; ingest at least three existing baselines without retraining or reopening observed real holdouts; emit deterministic JSON/Markdown plus one sortable CLI table; test malformed and mixed-version cards; report runtime, RSS, and bytes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="81" customHeight="1">
       <x:c r="A20" s="14" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -5286,10 +5922,10 @@
         <x:v>EEG / MOABB Bridge</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Explore an EEG adapter only after the core MEG loop is stable; keep claims conservative.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="58" customHeight="1">
+        <x:v>Begin Loop 19 with a read-only, bounded EEG/MOABB-style bridge discovery gate. Identify the smallest task-compatible public EEG fixture, exact license, download bytes, optional dependency cost, channel/time/label mapping, and proof boundary before fetching data or adding code. Keep EEG and MEG report-card cohorts separate, default to no download, and define a CPU/storage acceptance gate plus a no-signal comparator.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="91.5" customHeight="1">
       <x:c r="A21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -5297,13 +5933,13 @@
         <x:v>Neurotokens / v2-ready Interface</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Design the neurotoken interface as a small abstraction, not a grand architecture rewrite.</x:v>
+        <x:v>Build Loop 20 as a small modality-aware NeuroTokenCache v0 interface over existing MEG/EEG arrays and synthetic embeddings. Define stable shape, dtype, timebase, channel/sensor geometry, validity mask, modality, split membership, source hashes, transformations, and resource metadata. Add synthetic contract and round-trip tests plus a bounded CLI smoke artifact. Do not assume unreleased Brain2Qwerty v2 data, train a larger model, reopen observed holdouts, or imply that embeddings are learned neurotokens with demonstrated decoding value.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf07ab240937446b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778c358b08734a6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra06ca626e5e64370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8ed7e579398a47c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc187b7ccb7d24166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R16f4c43d929e49ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R71d0021b44ee47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1b652dc607be48a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R93efe519c1a24e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbb4f61033ab24d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R7297a466ab714ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R95a4868c3afb43b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rebbf452a227b47ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R264703610b8e4da7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R39034d051e12461a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rd78c41e4fd454736"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -76,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -166,6 +167,7 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -378,7 +380,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R54238ab2a7e644ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc61b908dfb34164"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -434,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I22"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -681,7 +683,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str"/>
       <x:c r="G6" s="29" t="str"/>
@@ -713,19 +715,19 @@
       <x:c r="A9" s="36" t="str">
         <x:v>Average progress</x:v>
       </x:c>
-      <x:c r="B9" s="34" t="n">
-        <x:v>0.905</x:v>
+      <x:c r="B9" s="41" t="n">
+        <x:v>0.955</x:v>
       </x:c>
       <x:c r="F9" s="29" t="str"/>
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="130.5" customHeight="1">
+    <x:row r="10" ht="142.5" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Next: Loop 20 NeuroTokenCache v0. Preserve modality, timebase, geometry, masks, split IDs, and provenance.</x:v>
+        <x:v>Next: synthetic causal chunk/replay gate. Specify state, right context, flush behavior, equivalence, and measured producer latency before a causal decoder.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -847,10 +849,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="n">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="34" t="n">
-        <x:v>0.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -861,7 +863,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8658ef2f3be841cf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R513b144e86784ece"/>
 </x:worksheet>
 </file>
 
@@ -2163,7 +2165,7 @@
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="69" customHeight="1">
+    <x:row r="21" ht="202.5" customHeight="1">
       <x:c r="A21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -2195,7 +2197,7 @@
         <x:v>No v2-data assumptions; interface can ingest embeddings later.</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
         <x:v>P2</x:v>
@@ -2215,14 +2217,16 @@
       <x:c r="Q21" s="14" t="str">
         <x:v>Define NeuroTokenCache v0 as a small modality-aware interface over existing arrays and synthetic embeddings. Preserve timebase, channel geometry, masks, split membership, provenance, and resource accounting; assume no unreleased v2 data and train no larger model.</x:v>
       </x:c>
-      <x:c r="R21" s="14" t="str"/>
+      <x:c r="R21" s="14" t="str">
+        <x:v>Closed 2026-07-10. NeuroTokenCache v0 stores continuous [items,time,embedding] vectors with masks, timing, source identity, subject/session, modality, geometry availability, strict split/source hashes, resources, and explicit causality boundaries. A target-free synthetic projection wrote 48 x 16 x 32 float32 in 76,646 bytes under a 4-MiB cap; 553 valid frames; exact 37/4/7 split; payload replay SHA-256 82b478948bdcfd5b2d12643f9f912c192a8977c8f0554b9f073171cf6dfe2709. Zero model, training, real-data, or holdout reads. Not learned tokens, decoding value, or end-to-end streaming. Evidence: docs/LOOP_20_NEUROTOKEN_CACHE_V0.md</x:v>
+      </x:c>
       <x:c r="S21" s="16" t="n">
         <x:f>IF(K21="Done",1,IF(K21="Review",0.8,IF(K21="In Progress",0.5,IF(K21="Blocked",0.2,IF(K21="Parked",0.1,0)))))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T21" s="14" t="str">
         <x:f>IF(K21="Blocked","Fix blocker",IF(K21="Review","Review/merge",IF(K21="Parked","Parked",IF(AND(L21="P0",K21="Not Started"),"Next candidate",IF(K21="Done","Closed","Normal")))))</x:f>
-        <x:v>Normal</x:v>
+        <x:v>Closed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2273,7 +2277,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fe018fb8dd74004"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f709087d5f0444c"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2943,16 +2947,34 @@
         <x:v>2,534/2,534 trigger match; 2.024 ms median residual; 2,197 x 61 x 25 cache; 12,428,800 bytes; template/prior label accuracy 0.009091/0.122727; paired interval [-0.134545,-0.093636]. Sources: https://huggingface.co/datasets/bcbl190626/SpanishBCBL ; https://www.nature.com/articles/s41593-026-02303-2 ; https://github.com/facebookresearch/brain2qwerty/blob/3bf5a4099ca0d23bbe994b2287905760236e56e0/studies/spanishbcbl.py ; https://mne.tools/stable/generated/mne.io.read_raw_brainvision.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="37"/>
-      <x:c r="B23" s="12"/>
-      <x:c r="C23" s="12"/>
-      <x:c r="D23" s="12"/>
-      <x:c r="E23" s="12"/>
-      <x:c r="F23" s="12"/>
-      <x:c r="G23" s="12"/>
-      <x:c r="H23" s="12"/>
-      <x:c r="I23" s="12"/>
+    <x:row r="23" ht="118.5" customHeight="1">
+      <x:c r="A23" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>Make neurotokens a continuous interface before making them a model claim</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="str">
+        <x:v>The public v2 encoder exposes time-major frame embeddings, but its reference path is noncausal and its English training data is unavailable. A target-free synthetic projection can validate shape, timing, provenance, split, geometry, resource, and serialization contracts without pretending the vectors are learned or useful for decoding.</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>docs/LOOP_20_NEUROTOKEN_CACHE_V0.md</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="str">
+        <x:v>Synthetic causal chunk/replay contract before a learned encoder or decoder</x:v>
+      </x:c>
+      <x:c r="I23" s="12" t="str">
+        <x:v>48 x 16 x 32 float32; 553 valid frames; 76,646 bytes; 0.09 s; 44,564,480-byte peak RSS; exact 37/4/7 split; exact payload replay; zero model/training/real/holdout reads. Sources: https://github.com/facebookresearch/brain2qwerty/tree/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2 ; https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf ; https://papers.neurips.cc/paper_files/paper/2024/file/a64d53074d011e49af1dfc72c332fe4b-Paper-Datasets_and_Benchmarks_Track.pdf</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="37"/>
@@ -4921,7 +4943,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0cdbff58a2049e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21c8c0895fc54676"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5547,6 +5569,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="106.5" customHeight="1">
+      <x:c r="A22" s="12" t="str">
+        <x:v>R21</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>Neurotoken and streaming interpretation</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="str">
+        <x:v>Synthetic random-projection vectors or producer frame timing are presented as learned brain words, useful neural semantics, a causal decoder, or measured real-time brain-to-text.</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
+        <x:v>Label vectors continuous, synthetic, target-free, and unlearned; keep producer causality, decoder causality, right context, and end-to-end latency separate; require synthetic chunk/replay proof before a causal decoder and a preregistered real cohort before performance claims.</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str">
+        <x:v>A report calls Loop 20 vectors discrete or learned neurotokens, cites the 160-ms frame width as end-to-end latency, or omits that decoder causality and decoding value are untested.</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I22" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -5579,7 +5630,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2d0d12f208f47f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re043617db3814977"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5939,7 +5990,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778c358b08734a6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615e6f9f6bf24f8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbb4f61033ab24d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R7297a466ab714ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R95a4868c3afb43b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rebbf452a227b47ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R264703610b8e4da7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R39034d051e12461a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rd78c41e4fd454736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R951d1fd6a0a14b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re9283ccdbc1c44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R0175fb3bf0384e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R96f3ee232f794904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rdb714919982c4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R5814ee55d1e64af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R84bad1cb6e1845d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -380,7 +380,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc61b908dfb34164"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfb075be4841a4c02"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -436,8 +436,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I23"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -454,7 +454,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C21" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C23" headerRowCount="1" totalsRowCount="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -727,7 +727,7 @@
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Next: synthetic causal chunk/replay gate. Specify state, right context, flush behavior, equivalence, and measured producer latency before a causal decoder.</x:v>
+        <x:v>First roadmap closed. Post-roadmap Loop 21 causal replay passed; next: Loop 22 tiny learned causal encoder on synthetic train/validation/test only.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -863,7 +863,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R513b144e86784ece"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3abeeaa385b4a8f"/>
 </x:worksheet>
 </file>
 
@@ -2277,7 +2277,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f709087d5f0444c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0863ddf29f2a4c4f"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2976,16 +2976,34 @@
         <x:v>48 x 16 x 32 float32; 553 valid frames; 76,646 bytes; 0.09 s; 44,564,480-byte peak RSS; exact 37/4/7 split; exact payload replay; zero model/training/real/holdout reads. Sources: https://github.com/facebookresearch/brain2qwerty/tree/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2 ; https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf ; https://papers.neurips.cc/paper_files/paper/2024/file/a64d53074d011e49af1dfc72c332fe4b-Paper-Datasets_and_Benchmarks_Track.pdf</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="37"/>
-      <x:c r="B24" s="12"/>
-      <x:c r="C24" s="12"/>
-      <x:c r="D24" s="12"/>
-      <x:c r="E24" s="12"/>
-      <x:c r="F24" s="12"/>
-      <x:c r="G24" s="12"/>
-      <x:c r="H24" s="12"/>
-      <x:c r="I24" s="12"/>
+    <x:row r="24" ht="129" customHeight="1">
+      <x:c r="A24" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>Separate causal frame production from transport and text latency</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="str">
+        <x:v>Five registered synthetic chunk schedules preserve one bounded zero-lookahead frame stream, but transport scheduling still adds 0 to 610 ms and no decoder emits text. Producer causality, scheduling delay, decoder emission, and end-to-end latency therefore remain separate proof surfaces.</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:v>docs/LOOP_21_CAUSAL_CHUNK_REPLAY.md</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="str">
+        <x:v>Loop 22 tiny learned causal encoder on synthetic train rows only</x:v>
+      </x:c>
+      <x:c r="I24" s="12" t="str">
+        <x:v>5/5 schedules; 553 frames; exact frame/timestamps; bitwise schedule payload 78dc8b5298064216caa854c884a69834c0959566d9ede903d44ae1cd28562389; max Loop 20 difference 9.536743e-7 under 1e-6 tolerance; zero right context; 300-byte state; 195,520-byte bounded working core; 0.135024 s; 46,301,184-byte peak RSS; no targets/models/training/decoder/real reads. Sources: https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf ; https://ai.meta.com/research/publications/emformer-efficient-memory-transformer-based-acoustic-model-for-low-latency-streaming-speech-recognition/ ; https://research.google/pubs/fastemit-low-latency-streaming-asr-with-sequence-level-emission-regularization/</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="37"/>
@@ -4943,7 +4961,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21c8c0895fc54676"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aeacaaf13b3400d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5598,6 +5616,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="106.5" customHeight="1">
+      <x:c r="A23" s="12" t="str">
+        <x:v>R22</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>Causal and latency claim collapse</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>A zero-lookahead frame producer or low compute RTF is presented as stable incremental text, real-time end-to-end decoding, or responsive local hardware.</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>Report frame availability, right context, scheduler delay, compute time/RTF, decoder emission/revisions, capture/preprocessing, and UI latency separately; do not use a producer benchmark as a text or device claim.</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str">
+        <x:v>A report cites the 160-ms first frame or sub-0.001 compute RTF as text latency while decoder causality, symbol stability, endpointing, or capture-to-render timing remains unavailable.</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I23" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -5630,7 +5677,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re043617db3814977"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf92c8b0b99b04d14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5987,10 +6034,32 @@
         <x:v>Build Loop 20 as a small modality-aware NeuroTokenCache v0 interface over existing MEG/EEG arrays and synthetic embeddings. Define stable shape, dtype, timebase, channel/sensor geometry, validity mask, modality, split membership, source hashes, transformations, and resource metadata. Add synthetic contract and round-trip tests plus a bounded CLI smoke artifact. Do not assume unreleased Brain2Qwerty v2 data, train a larger model, reopen observed holdouts, or imply that embeddings are learned neurotokens with demonstrated decoding value.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="99" customHeight="1">
+      <x:c r="A22" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>Causal NeuroToken Chunk/Replay</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="str">
+        <x:v>Build a synthetic causal replay gate before any learned encoder or decoder. Define zero/right context, bounded mutable state, global frame timestamps, drop-incomplete flush behavior, several adversarial chunk schedules, offline compatibility, schedule-invariant output, scheduler delay, compute RTF, and strict access/resource caps. Do not open target arrays, real neural data, observed holdouts, or claim text/end-to-end latency.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="99" customHeight="1">
+      <x:c r="A23" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>Tiny Learned Causal Encoder</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="str">
+        <x:v>Train one optional-Torch causal encoder on synthetic train rows only, choose stopping/configuration on validation, compare with a no-signal prior, and open a frozen synthetic test once. Preserve Loop 21 chunk/state/timestamp equivalence and enforce parameter, mutable-state, CPU-thread, runtime, RSS, and artifact caps. Do not add a text decoder, language model, real-cache conversion, or observed MEG/EEG evaluation in this gate.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615e6f9f6bf24f8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc84594e9b8cb4abd"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R951d1fd6a0a14b19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re9283ccdbc1c44e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R0175fb3bf0384e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R96f3ee232f794904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rdb714919982c4488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R5814ee55d1e64af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R84bad1cb6e1845d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd28820d48b42426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5cc2f8418b224400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Ra830f236437347e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R92429f2f6afd4eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rc4a6be95cbf94f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb33b1f18dc9e41b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R56302d1939b04154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R363b2beeacb04b31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +25,7 @@
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +47,30 @@
       <x:color rgb="FF7C2D12"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF9A3412"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,15 +92,74 @@
         <x:fgColor rgb="FFFFF7ED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF111827"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF245B85"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EEF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFECACA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="4">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -168,6 +250,82 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -380,7 +538,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfb075be4841a4c02"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R590b3a15feb342b6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -418,8 +576,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -436,8 +593,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I25"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -454,13 +611,30 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C23" headerRowCount="1" totalsRowCount="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C27" headerRowCount="1" totalsRowCount="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
     <x:tableColumn id="3" name="Prompt Seed"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="PracticeTrackTable" displayName="PracticeTrackTable" ref="A4:I14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Gate"/>
+    <x:tableColumn id="3" name="Core Question"/>
+    <x:tableColumn id="4" name="Status"/>
+    <x:tableColumn id="5" name="Deliverable"/>
+    <x:tableColumn id="6" name="Acceptance Boundary"/>
+    <x:tableColumn id="7" name="Depends On"/>
+    <x:tableColumn id="8" name="Proof Posture"/>
+    <x:tableColumn id="9" name="Evidence"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -722,12 +896,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="142.5" customHeight="1">
+    <x:row r="10" ht="93.75" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>First roadmap closed. Post-roadmap Loop 21 causal replay passed; next: Loop 22 tiny learned causal encoder on synthetic train/validation/test only.</x:v>
+        <x:v>RW0 research is done. RW1 metadata-only intake is next. S20 download is blocked. Loop 24 remains a separate preregistration.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -863,7 +1037,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3abeeaa385b4a8f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7d3398cfff4ace"/>
 </x:worksheet>
 </file>
 
@@ -2277,7 +2451,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0863ddf29f2a4c4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f87dd62db2a4984"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3005,49 +3179,121 @@
         <x:v>5/5 schedules; 553 frames; exact frame/timestamps; bitwise schedule payload 78dc8b5298064216caa854c884a69834c0959566d9ede903d44ae1cd28562389; max Loop 20 difference 9.536743e-7 under 1e-6 tolerance; zero right context; 300-byte state; 195,520-byte bounded working core; 0.135024 s; 46,301,184-byte peak RSS; no targets/models/training/decoder/real reads. Sources: https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf ; https://ai.meta.com/research/publications/emformer-efficient-memory-transformer-based-acoustic-model-for-low-latency-streaming-speech-recognition/ ; https://research.google/pubs/fastemit-low-latency-streaming-asr-with-sequence-level-emission-regularization/</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="37"/>
-      <x:c r="B25" s="12"/>
-      <x:c r="C25" s="12"/>
-      <x:c r="D25" s="12"/>
-      <x:c r="E25" s="12"/>
-      <x:c r="F25" s="12"/>
-      <x:c r="G25" s="12"/>
-      <x:c r="H25" s="12"/>
-      <x:c r="I25" s="12"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="37"/>
-      <x:c r="B26" s="12"/>
-      <x:c r="C26" s="12"/>
-      <x:c r="D26" s="12"/>
-      <x:c r="E26" s="12"/>
-      <x:c r="F26" s="12"/>
-      <x:c r="G26" s="12"/>
-      <x:c r="H26" s="12"/>
-      <x:c r="I26" s="12"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="37"/>
-      <x:c r="B27" s="12"/>
-      <x:c r="C27" s="12"/>
-      <x:c r="D27" s="12"/>
-      <x:c r="E27" s="12"/>
-      <x:c r="F27" s="12"/>
-      <x:c r="G27" s="12"/>
-      <x:c r="H27" s="12"/>
-      <x:c r="I27" s="12"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="37"/>
-      <x:c r="B28" s="12"/>
-      <x:c r="C28" s="12"/>
-      <x:c r="D28" s="12"/>
-      <x:c r="E28" s="12"/>
-      <x:c r="F28" s="12"/>
-      <x:c r="G28" s="12"/>
-      <x:c r="H28" s="12"/>
-      <x:c r="I28" s="12"/>
+    <x:row r="25" ht="108.75" customHeight="1">
+      <x:c r="A25" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="str">
+        <x:v>Proceed to a separately preregistered streaming CTC decoder gate</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="str">
+        <x:v>The 1,130-parameter synthetic causal encoder passes its frozen test and all five replay schedules without real data or text decoding.</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="str">
+        <x:v>docs/LOOP_22_TINY_CAUSAL_ENCODER.md</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="str">
+        <x:v>Loop 23</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="str">
+        <x:v>Seed 2203 is consumed. Perfect generated-motif classification is a mechanism check, not neural or text decoding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="108.75" customHeight="1">
+      <x:c r="A26" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="str">
+        <x:v>Park after the frozen exact-sequence gate fails</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="str">
+        <x:v>Validation passes, but the once-opened seed-2303 test reaches 5/8 exact below the required 6/8; every error is one false tail symbol.</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="str">
+        <x:v>docs/LOOP_23_STREAMING_CTC_DECODER.md</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="str">
+        <x:v>Fresh calibration preregistration</x:v>
+      </x:c>
+      <x:c r="I26" s="12" t="str">
+        <x:v>Seed 2303 is consumed. Do not trim, tune, calibrate, or design an endpoint from its outputs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="108.75" customHeight="1">
+      <x:c r="A27" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="n">
+        <x:v>23.5</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>Close supervised synthetic calibration and proceed to Loop 24 preregistration only</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="str">
+        <x:v>One preregistered train-frame blank intercept takes the once-opened seed-2353 test from 7/16 to 16/16 exact with CER 0, nine corrections, and zero regressions.</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>docs/LOOP_23_5_BLANK_INTERCEPT_CALIBRATION.md</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="str">
+        <x:v>Loop 24 preregistration</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="str">
+        <x:v>Seed 2353 is consumed. Replay, calibration, control, bootstrap, access, and resource gates pass; this remains supervised synthetic evidence only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="131.25" customHeight="1">
+      <x:c r="A28" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>RW0</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Add a parallel practice track and keep fresh EEG approval-gated</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>A practical local workflow requires explicit dataset cohorts, sensor modalities, compatibility levels, privacy rules, and authorization boundaries before real intake or device work.</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>docs/REAL_WORLD_PRACTICE_TRACK_RESEARCH.md</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>RW1 metadata-only intake</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="str">
+        <x:v>Eight dataset records and 13 device records are metadata only. S20 session 2 block 2 is an unapproved four-file 96,090,264-byte proposal. No raw, consumed-cache, target, model, training, or download access occurred.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="37"/>
@@ -4961,7 +5207,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aeacaaf13b3400d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f6e7745edb4e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5645,6 +5891,64 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="131.25" customHeight="1">
+      <x:c r="A24" s="12" t="str">
+        <x:v>R23</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>Consumed test reuse</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>A consumed synthetic or real evaluation is reused to select precision candidates, tune decoding, or make a fresh-evidence claim.</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>Freeze seeds 2203, 2303, and 2353 plus S21 session 2 and S7 EEG; require fresh split and one-time access protocols.</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str">
+        <x:v>A new report reads a consumed partition or cites its output as candidate-selection evidence.</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I24" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="131.25" customHeight="1">
+      <x:c r="A25" s="12" t="str">
+        <x:v>R24</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="str">
+        <x:v>Sensitive multimodal misattribution</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="str">
+        <x:v>Eye, hand, microphone, heart, motion, EOG, or wrist-EMG input is exposed, uploaded, or credited to EEG without consent and ablation evidence.</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
+        <x:v>Local-only intake, explicit modality labels, no silent cloud path, and mandatory brain-only, peripheral-only, and combined ablations.</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str">
+        <x:v>A device or report calls behavioral/peripheral data brain activity or lacks a device-only comparator.</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -5677,7 +5981,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf92c8b0b99b04d14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8fea1d7cd7948c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6056,10 +6360,54 @@
         <x:v>Train one optional-Torch causal encoder on synthetic train rows only, choose stopping/configuration on validation, compare with a no-signal prior, and open a frozen synthetic test once. Preserve Loop 21 chunk/state/timestamp equivalence and enforce parameter, mutable-state, CPU-thread, runtime, RSS, and artifact caps. Do not add a text decoder, language model, real-cache conversion, or observed MEG/EEG evaluation in this gate.</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="93.75" customHeight="1">
+      <x:c r="A24" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>Streaming CTC Prefix Decoder</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>Preregister a fresh language-model-free greedy and width-8 prefix CTC gate with exact blank/repeat semantics, partial traces, controls, five-schedule replay, and one conditional frozen test open.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="93.75" customHeight="1">
+      <x:c r="A25" s="12" t="n">
+        <x:v>23.5</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="str">
+        <x:v>Blank Intercept Calibration</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="str">
+        <x:v>Fit exactly one train-frame blank-logit intercept on fresh splits, keep the decoder and symbol logits frozen, require no-harm calibration/control/replay gates, and open the new test once only after validation passes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="93.75" customHeight="1">
+      <x:c r="A26" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="str">
+        <x:v>Local Precision / Runtime Preregistration</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="str">
+        <x:v>Before candidate code, freeze executable numeric paths, fresh selection data, reference outputs, correctness tolerances, runtime/RSS/state/size measurements, resource caps, and a no-rerun rule excluding consumed seeds 2203, 2303, and 2353.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="112.5" customHeight="1">
+      <x:c r="A27" s="12" t="str">
+        <x:v>RW1</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="str">
+        <x:v>Metadata-Only Local Intake</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>Recognize BrainVision, EDF/EDF+, BDF, EEGLAB, FIF, and BIDS synthetic fixtures; validate safe paths, companions, caps, deterministic JSON/Markdown, access counters, and refusal reasons without reading binary signal arrays, labels, targets, or network data.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc84594e9b8cb4abd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6668636792964696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6251,4 +6599,381 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="37.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="31.110000610351562" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28.5" customHeight="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>NeuroDecodeKit Real-World Practice Track</x:v>
+      </x:c>
+      <x:c r="B1" s="44"/>
+      <x:c r="C1" s="44"/>
+      <x:c r="D1" s="44"/>
+      <x:c r="E1" s="44"/>
+      <x:c r="F1" s="44"/>
+      <x:c r="G1" s="44"/>
+      <x:c r="H1" s="44"/>
+      <x:c r="I1" s="44"/>
+    </x:row>
+    <x:row r="2" ht="25.5" customHeight="1">
+      <x:c r="A2" s="48" t="str">
+        <x:v>Parallel to Loop 24. RW0 is metadata evidence; RW4 remains blocked pending explicit approval of the exact S20 packet.</x:v>
+      </x:c>
+      <x:c r="B2" s="48"/>
+      <x:c r="C2" s="48"/>
+      <x:c r="D2" s="48"/>
+      <x:c r="E2" s="48"/>
+      <x:c r="F2" s="48"/>
+      <x:c r="G2" s="48"/>
+      <x:c r="H2" s="48"/>
+      <x:c r="I2" s="48"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="53" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B4" s="53" t="str">
+        <x:v>Gate</x:v>
+      </x:c>
+      <x:c r="C4" s="53" t="str">
+        <x:v>Core Question</x:v>
+      </x:c>
+      <x:c r="D4" s="53" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E4" s="53" t="str">
+        <x:v>Deliverable</x:v>
+      </x:c>
+      <x:c r="F4" s="53" t="str">
+        <x:v>Acceptance Boundary</x:v>
+      </x:c>
+      <x:c r="G4" s="53" t="str">
+        <x:v>Depends On</x:v>
+      </x:c>
+      <x:c r="H4" s="53" t="str">
+        <x:v>Proof Posture</x:v>
+      </x:c>
+      <x:c r="I4" s="53" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="61.5" customHeight="1">
+      <x:c r="A5" s="57" t="str">
+        <x:v>RW0</x:v>
+      </x:c>
+      <x:c r="B5" s="57" t="str">
+        <x:v>Dataset/device research</x:v>
+      </x:c>
+      <x:c r="C5" s="57" t="str">
+        <x:v>Which cohorts, devices, formats, and transports are credible?</x:v>
+      </x:c>
+      <x:c r="D5" s="65" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E5" s="57" t="str">
+        <x:v>Versioned registries, primary-source research, BYO spec, exact fresh-data packet.</x:v>
+      </x:c>
+      <x:c r="F5" s="57" t="str">
+        <x:v>8 datasets, 13 devices, zero signal/consumed/model/target/download access.</x:v>
+      </x:c>
+      <x:c r="G5" s="57" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H5" s="57" t="str">
+        <x:v>Metadata-only research</x:v>
+      </x:c>
+      <x:c r="I5" s="57" t="str">
+        <x:v>docs/REAL_WORLD_PRACTICE_TRACK_RESEARCH.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="61.5" customHeight="1">
+      <x:c r="A6" s="61" t="str">
+        <x:v>RW1</x:v>
+      </x:c>
+      <x:c r="B6" s="61" t="str">
+        <x:v>Local metadata intake</x:v>
+      </x:c>
+      <x:c r="C6" s="61" t="str">
+        <x:v>Can a user identify a local recording without reading signal arrays?</x:v>
+      </x:c>
+      <x:c r="D6" s="66" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="E6" s="61" t="str">
+        <x:v>Dependency-free level-0 scanner, CLI, deterministic JSON/Markdown.</x:v>
+      </x:c>
+      <x:c r="F6" s="61" t="str">
+        <x:v>Synthetic fixtures only; safe paths/companions/caps/refusals; under 4 MiB.</x:v>
+      </x:c>
+      <x:c r="G6" s="61" t="str">
+        <x:v>RW0</x:v>
+      </x:c>
+      <x:c r="H6" s="61" t="str">
+        <x:v>No signal or decoding claim</x:v>
+      </x:c>
+      <x:c r="I6" s="61" t="str">
+        <x:v>docs/BYO_NEURODATA_WORKBENCH_SPEC.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="61.5" customHeight="1">
+      <x:c r="A7" s="57" t="str">
+        <x:v>RW2</x:v>
+      </x:c>
+      <x:c r="B7" s="57" t="str">
+        <x:v>Signal-quality contract</x:v>
+      </x:c>
+      <x:c r="C7" s="57" t="str">
+        <x:v>Can optional readers validate bounded signals, timing, events, and quality?</x:v>
+      </x:c>
+      <x:c r="D7" s="67" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E7" s="57" t="str">
+        <x:v>Lazy MNE/MNE-BIDS readers and frozen quality report.</x:v>
+      </x:c>
+      <x:c r="F7" s="57" t="str">
+        <x:v>No auto-deletion; units/reference/geometry/events and warnings explicit.</x:v>
+      </x:c>
+      <x:c r="G7" s="57" t="str">
+        <x:v>RW1 preregistration</x:v>
+      </x:c>
+      <x:c r="H7" s="57" t="str">
+        <x:v>Signal readability and QC only</x:v>
+      </x:c>
+      <x:c r="I7" s="57" t="str">
+        <x:v>docs/POST_20_ROADMAP.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="61.5" customHeight="1">
+      <x:c r="A8" s="61" t="str">
+        <x:v>RW3</x:v>
+      </x:c>
+      <x:c r="B8" s="61" t="str">
+        <x:v>Replay/live equivalence</x:v>
+      </x:c>
+      <x:c r="C8" s="61" t="str">
+        <x:v>Can offline replay use the exact future live-source chunk contract?</x:v>
+      </x:c>
+      <x:c r="D8" s="68" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E8" s="61" t="str">
+        <x:v>BrainFlow playback/synthetic and LSL timing audit.</x:v>
+      </x:c>
+      <x:c r="F8" s="61" t="str">
+        <x:v>Payload, clock, drop, state, and chunk tolerances frozen before hardware.</x:v>
+      </x:c>
+      <x:c r="G8" s="61" t="str">
+        <x:v>RW2</x:v>
+      </x:c>
+      <x:c r="H8" s="61" t="str">
+        <x:v>Transport/mechanics only</x:v>
+      </x:c>
+      <x:c r="I8" s="61" t="str">
+        <x:v>docs/POST_20_ROADMAP.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="61.5" customHeight="1">
+      <x:c r="A9" s="57" t="str">
+        <x:v>RW4</x:v>
+      </x:c>
+      <x:c r="B9" s="57" t="str">
+        <x:v>Fresh public EEG benchmark</x:v>
+      </x:c>
+      <x:c r="C9" s="57" t="str">
+        <x:v>Does one fresh typing block beat prior and shuffle controls?</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="E9" s="57" t="str">
+        <x:v>One-time S20 event-level aggregate report.</x:v>
+      </x:c>
+      <x:c r="F9" s="57" t="str">
+        <x:v>Explicit approval; exactly 4 files/96,090,264 bytes; no CER/WER.</x:v>
+      </x:c>
+      <x:c r="G9" s="57" t="str">
+        <x:v>User approval + RW2</x:v>
+      </x:c>
+      <x:c r="H9" s="57" t="str">
+        <x:v>Within-recording event evidence at most</x:v>
+      </x:c>
+      <x:c r="I9" s="57" t="str">
+        <x:v>docs/FRESH_EEG_BENCHMARK_S20_APPROVAL_PACKET.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="61.5" customHeight="1">
+      <x:c r="A10" s="61" t="str">
+        <x:v>RW5</x:v>
+      </x:c>
+      <x:c r="B10" s="61" t="str">
+        <x:v>Board-neutral acquisition</x:v>
+      </x:c>
+      <x:c r="C10" s="61" t="str">
+        <x:v>Can one BrainFlow or LSL EEG board pass replay and privacy gates?</x:v>
+      </x:c>
+      <x:c r="D10" s="68" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E10" s="61" t="str">
+        <x:v>One device descriptor and recorded/live comparison.</x:v>
+      </x:c>
+      <x:c r="F10" s="61" t="str">
+        <x:v>Measured raw API, timing, packet loss, consent, and locality.</x:v>
+      </x:c>
+      <x:c r="G10" s="61" t="str">
+        <x:v>RW3</x:v>
+      </x:c>
+      <x:c r="H10" s="61" t="str">
+        <x:v>No portable decoder claim</x:v>
+      </x:c>
+      <x:c r="I10" s="61" t="str">
+        <x:v>registries/devices.v0.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="61.5" customHeight="1">
+      <x:c r="A11" s="57" t="str">
+        <x:v>RW6</x:v>
+      </x:c>
+      <x:c r="B11" s="57" t="str">
+        <x:v>Prompted-typing EEG protocol</x:v>
+      </x:c>
+      <x:c r="C11" s="57" t="str">
+        <x:v>Can task-matched local EEG be collected with synchronized prompts/keys?</x:v>
+      </x:c>
+      <x:c r="D11" s="67" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E11" s="57" t="str">
+        <x:v>Consent, retention, trigger, calibration, and split protocol.</x:v>
+      </x:c>
+      <x:c r="F11" s="57" t="str">
+        <x:v>No collection before ethics, consent, and exact preregistration.</x:v>
+      </x:c>
+      <x:c r="G11" s="57" t="str">
+        <x:v>RW5</x:v>
+      </x:c>
+      <x:c r="H11" s="57" t="str">
+        <x:v>Acquisition protocol only</x:v>
+      </x:c>
+      <x:c r="I11" s="57" t="str">
+        <x:v>docs/POST_20_ROADMAP.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="61.5" customHeight="1">
+      <x:c r="A12" s="61" t="str">
+        <x:v>RW7</x:v>
+      </x:c>
+      <x:c r="B12" s="61" t="str">
+        <x:v>Multimodal ablations</x:v>
+      </x:c>
+      <x:c r="C12" s="61" t="str">
+        <x:v>What comes from EEG versus eye, EOG, EMG, heart, motion, or audio?</x:v>
+      </x:c>
+      <x:c r="D12" s="68" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E12" s="61" t="str">
+        <x:v>Brain-only, peripheral-only, and combined reports.</x:v>
+      </x:c>
+      <x:c r="F12" s="61" t="str">
+        <x:v>Peripheral contribution never credited to EEG; controls mandatory.</x:v>
+      </x:c>
+      <x:c r="G12" s="61" t="str">
+        <x:v>RW5-RW6</x:v>
+      </x:c>
+      <x:c r="H12" s="61" t="str">
+        <x:v>Cohort-specific attribution</x:v>
+      </x:c>
+      <x:c r="I12" s="61" t="str">
+        <x:v>registries/devices.v0.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="61.5" customHeight="1">
+      <x:c r="A13" s="57" t="str">
+        <x:v>RW8</x:v>
+      </x:c>
+      <x:c r="B13" s="57" t="str">
+        <x:v>Local BYO workbench</x:v>
+      </x:c>
+      <x:c r="C13" s="57" t="str">
+        <x:v>Can users inspect, replay, qualify, and report without cloud upload?</x:v>
+      </x:c>
+      <x:c r="D13" s="67" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E13" s="57" t="str">
+        <x:v>Operational local interface with compatibility levels 0-6.</x:v>
+      </x:c>
+      <x:c r="F13" s="57" t="str">
+        <x:v>Unknown input remains inspectable but non-decodable.</x:v>
+      </x:c>
+      <x:c r="G13" s="57" t="str">
+        <x:v>RW1-RW7</x:v>
+      </x:c>
+      <x:c r="H13" s="57" t="str">
+        <x:v>Product capability only</x:v>
+      </x:c>
+      <x:c r="I13" s="57" t="str">
+        <x:v>docs/BYO_NEURODATA_WORKBENCH_SPEC.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="61.5" customHeight="1">
+      <x:c r="A14" s="61" t="str">
+        <x:v>RW9</x:v>
+      </x:c>
+      <x:c r="B14" s="61" t="str">
+        <x:v>Phone/wearable deployment</x:v>
+      </x:c>
+      <x:c r="C14" s="61" t="str">
+        <x:v>Which validated capabilities fit a mobile or wearable envelope?</x:v>
+      </x:c>
+      <x:c r="D14" s="68" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E14" s="61" t="str">
+        <x:v>Measured offline packaging, battery, latency, and privacy gate.</x:v>
+      </x:c>
+      <x:c r="F14" s="61" t="str">
+        <x:v>Requires a qualified device/task/model first.</x:v>
+      </x:c>
+      <x:c r="G14" s="61" t="str">
+        <x:v>RW5-RW8</x:v>
+      </x:c>
+      <x:c r="H14" s="61" t="str">
+        <x:v>No clinical or arbitrary-thought claim</x:v>
+      </x:c>
+      <x:c r="I14" s="61" t="str">
+        <x:v>docs/POST_20_ROADMAP.md</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D14">
+      <x:formula1>"Done,Active,Blocked,Not Started,Parked"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fea261786af43c8"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd28820d48b42426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5cc2f8418b224400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Ra830f236437347e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R92429f2f6afd4eac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rc4a6be95cbf94f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb33b1f18dc9e41b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R56302d1939b04154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R363b2beeacb04b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Red77bff95a384e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rf173094ec2064fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R93dac6de9f7f401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R971711ade9e74b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R34a7a1fd12824b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb068f00d372b4167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8ff9e9c26a8046ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rdc82d3eaf9e44c8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -70,7 +70,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +132,11 @@
         <x:fgColor rgb="FFFECACA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -159,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="70">
+  <x:cellXfs count="71">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -324,6 +329,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -538,7 +546,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R590b3a15feb342b6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab3aa3ba05d04ef7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -576,7 +584,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -611,13 +619,13 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C27" headerRowCount="1" totalsRowCount="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
     <x:tableColumn id="3" name="Prompt Seed"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -901,7 +909,7 @@
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0 research is done. RW1 metadata-only intake is next. S20 download is blocked. Loop 24 remains a separate preregistration.</x:v>
+        <x:v>RW0 and RW1 are done. RW2 quality-contract preregistration is next. S20 remains blocked. Loop 24 remains separate.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1037,7 +1045,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7d3398cfff4ace"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0bba9ed3c0b4745"/>
 </x:worksheet>
 </file>
 
@@ -2451,7 +2459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f87dd62db2a4984"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08a3e0d3ce1454e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3295,16 +3303,34 @@
         <x:v>Eight dataset records and 13 device records are metadata only. S20 session 2 block 2 is an unapproved four-file 96,090,264-byte proposal. No raw, consumed-cache, target, model, training, or download access occurred.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="37"/>
-      <x:c r="B29" s="12"/>
-      <x:c r="C29" s="12"/>
-      <x:c r="D29" s="12"/>
-      <x:c r="E29" s="12"/>
-      <x:c r="F29" s="12"/>
-      <x:c r="G29" s="12"/>
-      <x:c r="H29" s="12"/>
-      <x:c r="I29" s="12"/>
+    <x:row r="29" ht="131.25" customHeight="1">
+      <x:c r="A29" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
+        <x:v>RW1</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="str">
+        <x:v>Close metadata-only local intake at compatibility level 0</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="str">
+        <x:v>Six common format families now produce strict deterministic core reports and measured audit sidecars without binary signal, target, model, training, or network access.</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
+        <x:v>docs/RW1_METADATA_ONLY_LOCAL_INTAKE.md</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="str">
+        <x:v>RW2 preregistration</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="str">
+        <x:v>532-byte synthetic fixture; 11,545 output bytes; 0.001659 s; 21,643,264-byte peak RSS; 11 focused tests; no signal readability or decoding claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="37"/>
@@ -5207,7 +5233,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f6e7745edb4e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd42bc7fae4d41f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5981,7 +6007,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8fea1d7cd7948c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf817273c7de4059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6404,10 +6430,21 @@
         <x:v>Recognize BrainVision, EDF/EDF+, BDF, EEGLAB, FIF, and BIDS synthetic fixtures; validate safe paths, companions, caps, deterministic JSON/Markdown, access counters, and refusal reasons without reading binary signal arrays, labels, targets, or network data.</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="112.5" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>RW2</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>Signal-Quality Contract Preregistration</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Before implementation or signal access, freeze optional reader behavior, bounded samples/channels/time/bytes, units, reference, filters, geometry, events, PSD, warnings, privacy, one-thread resources, synthetic fixtures, and no-auto-deletion rules.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6668636792964696"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c16de9e2f04924"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6631,7 +6668,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0 is metadata evidence; RW4 remains blocked pending explicit approval of the exact S20 packet.</x:v>
+        <x:v>Parallel to Loop 24. RW0 and RW1 are closed; RW2 requires preregistration before any signal read. RW4 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -6700,7 +6737,7 @@
         <x:v>docs/REAL_WORLD_PRACTICE_TRACK_RESEARCH.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="61.5" customHeight="1">
+    <x:row r="6" ht="69" customHeight="1">
       <x:c r="A6" s="61" t="str">
         <x:v>RW1</x:v>
       </x:c>
@@ -6710,14 +6747,14 @@
       <x:c r="C6" s="61" t="str">
         <x:v>Can a user identify a local recording without reading signal arrays?</x:v>
       </x:c>
-      <x:c r="D6" s="66" t="str">
-        <x:v>Active</x:v>
+      <x:c r="D6" s="70" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E6" s="61" t="str">
         <x:v>Dependency-free level-0 scanner, CLI, deterministic JSON/Markdown.</x:v>
       </x:c>
       <x:c r="F6" s="61" t="str">
-        <x:v>Synthetic fixtures only; safe paths/companions/caps/refusals; under 4 MiB.</x:v>
+        <x:v>Closed: 11 focused tests; 532-byte fixture; 11,545 output bytes; zero signal/target/model/network access.</x:v>
       </x:c>
       <x:c r="G6" s="61" t="str">
         <x:v>RW0</x:v>
@@ -6726,7 +6763,7 @@
         <x:v>No signal or decoding claim</x:v>
       </x:c>
       <x:c r="I6" s="61" t="str">
-        <x:v>docs/BYO_NEURODATA_WORKBENCH_SPEC.md</x:v>
+        <x:v>docs/RW1_METADATA_ONLY_LOCAL_INTAKE.md</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="61.5" customHeight="1">
@@ -6973,7 +7010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fea261786af43c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a1a932767b54827"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Red77bff95a384e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rf173094ec2064fcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R93dac6de9f7f401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R971711ade9e74b03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R34a7a1fd12824b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rb068f00d372b4167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8ff9e9c26a8046ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rdc82d3eaf9e44c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1b9e8e2ebbb9427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6f02ee3856f14b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Re8c3fb7ea2db43ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rfeda3a2dab9846f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R153403a09f0545bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R32fc08486d584e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rfd86118987e140cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rceeb00aa684d414d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -70,7 +70,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -137,6 +137,11 @@
         <x:fgColor rgb="FFD1FAE5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -164,7 +169,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="71">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -332,6 +337,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -546,7 +554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab3aa3ba05d04ef7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5176451f4a204eb6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -584,7 +592,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -601,8 +609,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I28"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -619,7 +627,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -909,7 +917,7 @@
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0 and RW1 are done. RW2 quality-contract preregistration is next. S20 remains blocked. Loop 24 remains separate.</x:v>
+        <x:v>RW0/RW1 are done. RW2 preregistration is frozen; synthetic implementation is next. S20 and real reads remain blocked.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1045,7 +1053,7 @@
     <x:mergeCell ref="F5:H13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0bba9ed3c0b4745"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb110dfe4d1a74294"/>
 </x:worksheet>
 </file>
 
@@ -2459,7 +2467,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08a3e0d3ce1454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdbcebc8891b4ca0"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3332,16 +3340,34 @@
         <x:v>532-byte synthetic fixture; 11,545 output bytes; 0.001659 s; 21,643,264-byte peak RSS; 11 focused tests; no signal readability or decoding claim.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="37"/>
-      <x:c r="B30" s="12"/>
-      <x:c r="C30" s="12"/>
-      <x:c r="D30" s="12"/>
-      <x:c r="E30" s="12"/>
-      <x:c r="F30" s="12"/>
-      <x:c r="G30" s="12"/>
-      <x:c r="H30" s="12"/>
-      <x:c r="I30" s="12"/>
+    <x:row r="30" ht="131.25" customHeight="1">
+      <x:c r="A30" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>RW2</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>Freeze bounded signal-quality protocol before implementation</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>Primary-source review exposed BIDS sidecar imports, EEGLAB embedded-array preload risk, and mixed-rate EDF/BDF behavior; bind explicit synthetic-only adapters before code.</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>docs/RW2_SIGNAL_QUALITY_PREREGISTRATION.md</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>RW2 synthetic implementation</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="str">
+        <x:v>Commit eacb231; six adapters; one thread; 32 MiB materialized arrays; 4 MiB/run; 16 MiB fixture/report set; zero real/signal/target/model/training/download access.</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="37"/>
@@ -5233,7 +5259,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd42bc7fae4d41f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a92867ee2d4619"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5975,6 +6001,93 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="88.5" customHeight="1">
+      <x:c r="A26" s="12" t="str">
+        <x:v>R25</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="str">
+        <x:v>Reader bounds</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="str">
+        <x:v>A lazy reader silently preloads a source or mixed-rate EDF/BDF resampling changes bounded values.</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
+        <x:v>Use explicit format readers and arguments; refuse embedded EEGLAB and unproven mixed-rate level 2; assert preload and exact fixture values.</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="str">
+        <x:v>Unexpected preload, memory growth, implicit rate conversion, or value mismatch.</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I26" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="88.5" customHeight="1">
+      <x:c r="A27" s="12" t="str">
+        <x:v>R26</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="str">
+        <x:v>Quality semantics</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>A descriptive warning becomes automatic cleaning or is presented as proof that a real artifact was detected.</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>Keep profile-dependent thresholds unavailable; prove source no-mutation; never delete, interpolate, filter, rereference, or mark bads.</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
+        <x:v>A warning changes source state or is described as a validated real-data diagnosis.</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="88.5" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>R27</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>Signal privacy</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Reports leak absolute paths, participant data, dates, serials, event text/timestamps, exact geometry, or waveform values.</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>Allowlist aggregate fields; redact before serialization; run forbidden-token and waveform/value leakage tests; kill the gate on exposure.</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>Any forbidden identifier, coordinate, annotation, timestamp, or signal value appears in an artifact.</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6007,7 +6120,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf817273c7de4059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd97bda3d179f46cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6441,10 +6554,21 @@
         <x:v>Before implementation or signal access, freeze optional reader behavior, bounded samples/channels/time/bytes, units, reference, filters, geometry, events, PSD, warnings, privacy, one-thread resources, synthetic fixtures, and no-auto-deletion rules.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="123.75" customHeight="1">
+      <x:c r="A29" s="12" t="str">
+        <x:v>RW2-Impl</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
+        <x:v>Synthetic Bounded Signal Quality</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="str">
+        <x:v>Implement commit eacb231 exactly on generated BrainVision, EDF/EDF+, BDF, external-FDT EEGLAB, FIF, and BIDS fixtures. Use explicit lazy optional readers, one thread, bounded windows/arrays/output, strict source binding, redaction and no-mutation checks, descriptive metrics only, exact malformed/refusal tests, and no real/S20/consumed/target/model/training access.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c16de9e2f04924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457de7a18157473c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6668,7 +6792,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0 and RW1 are closed; RW2 requires preregistration before any signal read. RW4 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. RW0/RW1 are closed; RW2 is preregistered and active on synthetic fixtures only. RW4 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -6766,7 +6890,7 @@
         <x:v>docs/RW1_METADATA_ONLY_LOCAL_INTAKE.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="61.5" customHeight="1">
+    <x:row r="7" ht="81" customHeight="1">
       <x:c r="A7" s="57" t="str">
         <x:v>RW2</x:v>
       </x:c>
@@ -6776,23 +6900,23 @@
       <x:c r="C7" s="57" t="str">
         <x:v>Can optional readers validate bounded signals, timing, events, and quality?</x:v>
       </x:c>
-      <x:c r="D7" s="67" t="str">
-        <x:v>Not Started</x:v>
+      <x:c r="D7" s="71" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="E7" s="57" t="str">
-        <x:v>Lazy MNE/MNE-BIDS readers and frozen quality report.</x:v>
+        <x:v>Optional direct MNE adapters, bounded descriptive quality reports, strict validation, and synthetic fixtures.</x:v>
       </x:c>
       <x:c r="F7" s="57" t="str">
-        <x:v>No auto-deletion; units/reference/geometry/events and warnings explicit.</x:v>
+        <x:v>Preregistered at eacb231: six generated formats; one thread; 32-MiB arrays; 4-MiB/run; no real read or auto-cleaning.</x:v>
       </x:c>
       <x:c r="G7" s="57" t="str">
-        <x:v>RW1 preregistration</x:v>
+        <x:v>RW1 + eacb231</x:v>
       </x:c>
       <x:c r="H7" s="57" t="str">
-        <x:v>Signal readability and QC only</x:v>
+        <x:v>Synthetic reader/report mechanics only</x:v>
       </x:c>
       <x:c r="I7" s="57" t="str">
-        <x:v>docs/POST_20_ROADMAP.md</x:v>
+        <x:v>docs/RW2_SIGNAL_QUALITY_PREREGISTRATION.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="61.5" customHeight="1">
@@ -7010,7 +7134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a1a932767b54827"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77068db9a274dc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1b9e8e2ebbb9427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6f02ee3856f14b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Re8c3fb7ea2db43ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rfeda3a2dab9846f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R153403a09f0545bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R32fc08486d584e6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rfd86118987e140cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rceeb00aa684d414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R792995cdda994b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R91cfde5f68284492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R07db33c1cf4d4d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra0dbdbbf8e464567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R6b9812a1b3104237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1de71a20862e4c35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1b5461631fff4608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Reb9e3771ac274104"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -70,7 +70,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -142,6 +142,11 @@
         <x:fgColor rgb="FFFEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -169,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="74">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -341,6 +346,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -554,7 +565,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5176451f4a204eb6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bd1820189b041b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -592,7 +603,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -627,7 +638,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -912,12 +923,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="93.75" customHeight="1">
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0/RW1 are done. RW2 preregistration is frozen; synthetic implementation is next. S20 and real reads remain blocked.</x:v>
+        <x:v>RW0-RW2 closed. Next: preregister RW3 only. No BrainFlow, LSL, live hardware, or real reads. Review the public default branch. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1051,9 +1062,10 @@
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="F4:H4"/>
     <x:mergeCell ref="F5:H13"/>
+    <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb110dfe4d1a74294"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37e6ac99e5874f3d"/>
 </x:worksheet>
 </file>
 
@@ -2467,7 +2479,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdbcebc8891b4ca0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13cc635d5e0447c5"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3369,27 +3381,63 @@
         <x:v>Commit eacb231; six adapters; one thread; 32 MiB materialized arrays; 4 MiB/run; 16 MiB fixture/report set; zero real/signal/target/model/training/download access.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="37"/>
-      <x:c r="B31" s="12"/>
-      <x:c r="C31" s="12"/>
-      <x:c r="D31" s="12"/>
-      <x:c r="E31" s="12"/>
-      <x:c r="F31" s="12"/>
-      <x:c r="G31" s="12"/>
-      <x:c r="H31" s="12"/>
-      <x:c r="I31" s="12"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="37"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="12"/>
-      <x:c r="E32" s="12"/>
-      <x:c r="F32" s="12"/>
-      <x:c r="G32" s="12"/>
-      <x:c r="H32" s="12"/>
-      <x:c r="I32" s="12"/>
+    <x:row r="31" ht="96" customHeight="1">
+      <x:c r="A31" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>RW2</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="str">
+        <x:v>Close exact synthetic compatibility level 2; preregister RW3 only</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
+        <x:v>All 38 authorized fixtures pass, both frozen refusals match, reader opens remain lazy, source/payload hashes are unchanged, and privacy/resource gates pass without real or target access.</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>docs/RW2_SIGNAL_QUALITY_CLOSEOUT.md</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="str">
+        <x:v>RW3 preregistration</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="str">
+        <x:v>Measured FIF: 9 channels, 3 windows, 11,520 values, 92,160 materialized bytes, 76,592 output bytes, 3.839168 s, 150,749,184-byte peak RSS; no real/cache/target/model/training/network access; no real-quality or decoding claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="96" customHeight="1">
+      <x:c r="A32" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>OS1</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Prepare proof-first open-source contribution surface; review public default before release</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>EEG owners need metadata-first contribution paths, maintainers need privacy/security/license controls, and the current public default branch is stale relative to the tested review branch.</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>docs/OPEN_SOURCE_READINESS.md</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>Cheick</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>Review branch and GitHub settings</x:v>
+      </x:c>
+      <x:c r="I32" s="12" t="str">
+        <x:v>Apache-2.0 is provisional for original work; Brain2Qwerty/SpanishBCBL remain separately CC-BY-NC-4.0. History/data/Gitleaks checks pass. Description, topics, labels, issue forms, CI, and contribution docs are prepared.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="37"/>
@@ -5259,7 +5307,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a92867ee2d4619"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b5c674937d41e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6168,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd97bda3d179f46cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb02da44e86428a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6565,10 +6613,21 @@
         <x:v>Implement commit eacb231 exactly on generated BrainVision, EDF/EDF+, BDF, external-FDT EEGLAB, FIF, and BIDS fixtures. Use explicit lazy optional readers, one thread, bounded windows/arrays/output, strict source binding, redaction and no-mutation checks, descriptive metrics only, exact malformed/refusal tests, and no real/S20/consumed/target/model/training access.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="84" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>RW3</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Offline Replay / Live-Source Equivalence Preregistration</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Before installing or using BrainFlow, LSL, or hardware, freeze one versioned chunk/source schema; exact payload, channel, timestamp, clock-correction, packet-loss, ordering, mutable-state, flush, and schedule semantics; synthetic/playback dependency boundaries; privacy and local-only rules; one-thread runtime/RSS/state/output caps; exact replay tolerances; and proceed/park/kill rules. Do not open real/consumed/S20 data, train a model, or claim live, portable, real-time, or decoding support.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457de7a18157473c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65265bb81694174"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6792,7 +6851,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0/RW1 are closed; RW2 is preregistered and active on synthetic fixtures only. RW4 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. RW0-RW2 are closed at exact proof boundaries; RW3 preregistration is next. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -6900,23 +6959,23 @@
       <x:c r="C7" s="57" t="str">
         <x:v>Can optional readers validate bounded signals, timing, events, and quality?</x:v>
       </x:c>
-      <x:c r="D7" s="71" t="str">
-        <x:v>Active</x:v>
+      <x:c r="D7" s="73" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E7" s="57" t="str">
-        <x:v>Optional direct MNE adapters, bounded descriptive quality reports, strict validation, and synthetic fixtures.</x:v>
+        <x:v>Direct optional MNE adapters, deterministic quality JSON/Markdown/audit, strict load/validation, and 40 target-free fixtures.</x:v>
       </x:c>
       <x:c r="F7" s="57" t="str">
-        <x:v>Preregistered at eacb231: six generated formats; one thread; 32-MiB arrays; 4-MiB/run; no real read or auto-cleaning.</x:v>
+        <x:v>Closed: 38 readable fixtures pass; 2 refusals match; 9 focused tests; 76,592-byte FIF report; zero real/cache/target/model/training/network access.</x:v>
       </x:c>
       <x:c r="G7" s="57" t="str">
         <x:v>RW1 + eacb231</x:v>
       </x:c>
       <x:c r="H7" s="57" t="str">
-        <x:v>Synthetic reader/report mechanics only</x:v>
+        <x:v>Synthetic compatibility level 2 only</x:v>
       </x:c>
       <x:c r="I7" s="57" t="str">
-        <x:v>docs/RW2_SIGNAL_QUALITY_PREREGISTRATION.md</x:v>
+        <x:v>docs/RW2_SIGNAL_QUALITY_CLOSEOUT.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="61.5" customHeight="1">
@@ -6933,16 +6992,16 @@
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="E8" s="61" t="str">
-        <x:v>BrainFlow playback/synthetic and LSL timing audit.</x:v>
+        <x:v>Preregister source chunks, playback/synthetic adapter scope, clocks, packet loss, state, schedules, privacy, caps, and stop rules.</x:v>
       </x:c>
       <x:c r="F8" s="61" t="str">
-        <x:v>Payload, clock, drop, state, and chunk tolerances frozen before hardware.</x:v>
+        <x:v>No BrainFlow, LSL, live source, or hardware code before the payload/clock/drop/state/tolerance contract is frozen.</x:v>
       </x:c>
       <x:c r="G8" s="61" t="str">
         <x:v>RW2</x:v>
       </x:c>
       <x:c r="H8" s="61" t="str">
-        <x:v>Transport/mechanics only</x:v>
+        <x:v>Transport protocol only</x:v>
       </x:c>
       <x:c r="I8" s="61" t="str">
         <x:v>docs/POST_20_ROADMAP.md</x:v>
@@ -7134,7 +7193,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77068db9a274dc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fc3c4182a14346"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R792995cdda994b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R91cfde5f68284492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R07db33c1cf4d4d4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra0dbdbbf8e464567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R6b9812a1b3104237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1de71a20862e4c35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1b5461631fff4608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Reb9e3771ac274104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R04aa372e1c444424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6a48b253064e408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc16f1c07c30d4882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R20093182f3964f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rdff799b61b20479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R506e30c2e28e402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R096305ca81f94ceb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rb39cb06c969a4bfc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +25,7 @@
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -69,8 +69,14 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1E3A8A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -147,6 +153,11 @@
         <x:fgColor rgb="FFD1FAE5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -174,7 +185,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -351,6 +362,15 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -565,7 +585,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bd1820189b041b5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R874d726293cb49f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -603,7 +623,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -638,7 +658,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -928,7 +948,7 @@
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0-RW2 closed. Next: preregister RW3 only. No BrainFlow, LSL, live hardware, or real reads. Review the public default branch. RW4/S20 remains blocked.</x:v>
+        <x:v>RW0-RW2 closed. RW3 protocol frozen at c3d1f01; Stage A is not authorized. Review PR #2. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1065,7 +1085,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37e6ac99e5874f3d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R286ae96bb1c741e8"/>
 </x:worksheet>
 </file>
 
@@ -2479,7 +2499,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13cc635d5e0447c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R705b6ba4eb724d47"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3439,16 +3459,34 @@
         <x:v>Apache-2.0 is provisional for original work; Brain2Qwerty/SpanishBCBL remain separately CC-BY-NC-4.0. History/data/Gitleaks checks pass. Description, topics, labels, issue forms, CI, and contribution docs are prepared.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="37"/>
-      <x:c r="B33" s="12"/>
-      <x:c r="C33" s="12"/>
-      <x:c r="D33" s="12"/>
-      <x:c r="E33" s="12"/>
-      <x:c r="F33" s="12"/>
-      <x:c r="G33" s="12"/>
-      <x:c r="H33" s="12"/>
-      <x:c r="I33" s="12"/>
+    <x:row r="33" ht="108" customHeight="1">
+      <x:c r="A33" s="37" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>RW3</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="str">
+        <x:v>Freeze source-chunk and replay-equivalence protocol before code</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="str">
+        <x:v>Primary sources expose regenerated playback time, separate clock correction, destructive timestamp postprocessing, and raw-versus-corrected XDF views; freeze exact semantics before one adapter abstraction.</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>docs/RW3_REPLAY_LIVE_EQUIVALENCE_PREREGISTRATION.md</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
+        <x:v>Review and explicitly authorize Stage A only</x:v>
+      </x:c>
+      <x:c r="I33" s="12" t="str">
+        <x:v>Commit c3d1f01; 5 schedules; 18 future target-free fixture families; 30 refusal IDs; 4 separately gated stages; 7 invariant tests; zero adapter/socket/stream/board/XDF/data/target/model/training access; no runtime or decoding claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37"/>
@@ -5307,7 +5345,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b5c674937d41e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd19a511203c4915"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6168,7 +6206,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb02da44e86428a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra04f5e98b08d4784"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6624,10 +6662,21 @@
         <x:v>Before installing or using BrainFlow, LSL, or hardware, freeze one versioned chunk/source schema; exact payload, channel, timestamp, clock-correction, packet-loss, ordering, mutable-state, flush, and schedule semantics; synthetic/playback dependency boundaries; privacy and local-only rules; one-thread runtime/RSS/state/output caps; exact replay tolerances; and proceed/park/kill rules. Do not open real/consumed/S20 data, train a model, or claim live, portable, real-time, or decoding support.</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="98" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>RW3-Review</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Review Frozen Replay Equivalence Registration</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Review commit c3d1f01, the RW3 primary-source research, preregistration, machine contract, and invariant tests. Confirm five schedules, 18 future fixture families, 30 refusal IDs, four sequential stages, strict timestamp/anomaly/hash/resource/access rules, and the no-runtime/no-decoding boundary. Do not implement Stage A, install BrainFlow/LSL/PyXDF, open sockets or streams, touch hardware or real/consumed data, create targets, run models, or train without separate explicit authorization.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65265bb81694174"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0ef10abfd83481c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6851,7 +6900,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0-RW2 are closed at exact proof boundaries; RW3 preregistration is next. RW4/S20 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. RW0-RW2 are closed; RW3 is preregistered at c3d1f01 with no runtime implementation. Stage A requires separate authorization. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -6978,7 +7027,7 @@
         <x:v>docs/RW2_SIGNAL_QUALITY_CLOSEOUT.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="61.5" customHeight="1">
+    <x:row r="8" ht="112" customHeight="1">
       <x:c r="A8" s="61" t="str">
         <x:v>RW3</x:v>
       </x:c>
@@ -6988,23 +7037,23 @@
       <x:c r="C8" s="61" t="str">
         <x:v>Can offline replay use the exact future live-source chunk contract?</x:v>
       </x:c>
-      <x:c r="D8" s="68" t="str">
-        <x:v>Not Started</x:v>
+      <x:c r="D8" s="76" t="str">
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="E8" s="61" t="str">
-        <x:v>Preregister source chunks, playback/synthetic adapter scope, clocks, packet loss, state, schedules, privacy, caps, and stop rules.</x:v>
+        <x:v>Frozen source-chunk, clock, anomaly, state, hash, privacy, and resource contract; five schedules, 18 future target-free fixtures, 30 refusal IDs, and four gated stages.</x:v>
       </x:c>
       <x:c r="F8" s="61" t="str">
-        <x:v>No BrainFlow, LSL, live source, or hardware code before the payload/clock/drop/state/tolerance contract is frozen.</x:v>
+        <x:v>Registration only at c3d1f01; 7 invariant tests; zero adapters, fixtures, optional imports, sockets, streams, board/XDF/data/model/training access.</x:v>
       </x:c>
       <x:c r="G8" s="61" t="str">
-        <x:v>RW2</x:v>
+        <x:v>RW2 + c3d1f01</x:v>
       </x:c>
       <x:c r="H8" s="61" t="str">
-        <x:v>Transport protocol only</x:v>
+        <x:v>Protocol only; Stage A unapproved</x:v>
       </x:c>
       <x:c r="I8" s="61" t="str">
-        <x:v>docs/POST_20_ROADMAP.md</x:v>
+        <x:v>docs/RW3_REPLAY_LIVE_EQUIVALENCE_PREREGISTRATION.md</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="61.5" customHeight="1">
@@ -7193,7 +7242,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fc3c4182a14346"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reee98a3bc50f4262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R04aa372e1c444424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R6a48b253064e408a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc16f1c07c30d4882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R20093182f3964f28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rdff799b61b20479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R506e30c2e28e402c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R096305ca81f94ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rb39cb06c969a4bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2c35e6bfb69e4427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R335601555183480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R8013336cb3ba4ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8b28ca79fccb4ae9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra2c42adacb1a4139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R434548994d6c4932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Re0c5150f88714daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4d0d2b3d02034f20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,7 +76,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -158,6 +158,11 @@
         <x:fgColor rgb="FFDBEAFE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -185,7 +190,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="78">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -371,6 +376,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -585,7 +593,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R874d726293cb49f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f7797d8ba564556"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -623,7 +631,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -658,7 +666,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -943,12 +951,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="62" customHeight="1">
+    <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0-RW2 closed. RW3 protocol frozen at c3d1f01; Stage A is not authorized. Review PR #2. RW4/S20 remains blocked.</x:v>
+        <x:v>RW0-RW2 closed. RW3 Stage A packet at 163ff2f awaits explicit authorization; no implementation exists. Review PR #2. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1085,7 +1093,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R286ae96bb1c741e8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R439f2b3d955f4bdf"/>
 </x:worksheet>
 </file>
 
@@ -2499,7 +2507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R705b6ba4eb724d47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd53e5cc1b63744bb"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3488,16 +3496,34 @@
         <x:v>Commit c3d1f01; 5 schedules; 18 future target-free fixture families; 30 refusal IDs; 4 separately gated stages; 7 invariant tests; zero adapter/socket/stream/board/XDF/data/target/model/training access; no runtime or decoding claim.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="37"/>
-      <x:c r="B34" s="12"/>
-      <x:c r="C34" s="12"/>
-      <x:c r="D34" s="12"/>
-      <x:c r="E34" s="12"/>
-      <x:c r="F34" s="12"/>
-      <x:c r="G34" s="12"/>
-      <x:c r="H34" s="12"/>
-      <x:c r="I34" s="12"/>
+    <x:row r="34" ht="118" customHeight="1">
+      <x:c r="A34" s="37" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>RW3-A</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Prepare Stage A authorization packet; keep implementation unauthorized</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>The next permission must bind the frozen contract hash, exact 90-case matrix, 30 refusals, caps, forbidden work, and authorization sequence so general continuation cannot become runtime, device, or data access.</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>Explicitly authorize Stage A only, amend, or hold</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="str">
+        <x:v>Commit 163ff2f; machine request authorized_now=false; 10 invariants; zero source chunks, fixtures, adapters, optional imports, sockets, boards, XDF/data/target/model/training access; Stages B-D remain forbidden.</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37"/>
@@ -5345,7 +5371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd19a511203c4915"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb92735a5b7944df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6206,7 +6232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra04f5e98b08d4784"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8dac7305814392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6673,10 +6699,21 @@
         <x:v>Review commit c3d1f01, the RW3 primary-source research, preregistration, machine contract, and invariant tests. Confirm five schedules, 18 future fixture families, 30 refusal IDs, four sequential stages, strict timestamp/anomaly/hash/resource/access rules, and the no-runtime/no-decoding boundary. Do not implement Stage A, install BrainFlow/LSL/PyXDF, open sockets or streams, touch hardware or real/consumed data, create targets, run models, or train without separate explicit authorization.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="118" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>RW3-StageA-Decision</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Decide Stage A Only</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Review docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md and registries/rw3_stage_a_authorization_request.v0.json. Confirm the c3d1f01 contract hash, 90 proposed cases, 30 refusals, one-thread caps, forbidden work, and authorization-only commit sequence. Decide explicitly to authorize Stage A only, amend the packet, or hold. General continuation is not authorization. Do not implement anything; BrainFlow, LSL, PyXDF, sockets, devices, real or consumed data, targets, models, training, and Stages B-D remain unauthorized.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0ef10abfd83481c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4af66e6b99e54673"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6900,7 +6937,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0-RW2 are closed; RW3 is preregistered at c3d1f01 with no runtime implementation. Stage A requires separate authorization. RW4/S20 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. RW0-RW2 are closed. RW3 contract c3d1f01 and Stage A packet 163ff2f are review-ready, but authorized_now is false and no runtime exists. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -7027,7 +7064,7 @@
         <x:v>docs/RW2_SIGNAL_QUALITY_CLOSEOUT.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="112" customHeight="1">
+    <x:row r="8" ht="126" customHeight="1">
       <x:c r="A8" s="61" t="str">
         <x:v>RW3</x:v>
       </x:c>
@@ -7037,23 +7074,23 @@
       <x:c r="C8" s="61" t="str">
         <x:v>Can offline replay use the exact future live-source chunk contract?</x:v>
       </x:c>
-      <x:c r="D8" s="76" t="str">
+      <x:c r="D8" s="77" t="str">
         <x:v>Review</x:v>
       </x:c>
       <x:c r="E8" s="61" t="str">
-        <x:v>Frozen source-chunk, clock, anomaly, state, hash, privacy, and resource contract; five schedules, 18 future target-free fixtures, 30 refusal IDs, and four gated stages.</x:v>
+        <x:v>Frozen contract plus a hash-bound Stage A decision packet: five schedules x 18 future target-free fixtures = 90 cases, all 30 refusal IDs, exact one-thread caps, and an authorization-only commit sequence.</x:v>
       </x:c>
       <x:c r="F8" s="61" t="str">
-        <x:v>Registration only at c3d1f01; 7 invariant tests; zero adapters, fixtures, optional imports, sockets, streams, board/XDF/data/model/training access.</x:v>
+        <x:v>10 contract/request invariants pass; authorized_now is false; zero source chunks, fixtures, CLI additions, optional imports, sockets, streams, boards, XDF/data/target/model/training access.</x:v>
       </x:c>
       <x:c r="G8" s="61" t="str">
-        <x:v>RW2 + c3d1f01</x:v>
+        <x:v>RW2 + c3d1f01 + 163ff2f</x:v>
       </x:c>
       <x:c r="H8" s="61" t="str">
-        <x:v>Protocol only; Stage A unapproved</x:v>
+        <x:v>Decision packet only; Stage A unapproved</x:v>
       </x:c>
       <x:c r="I8" s="61" t="str">
-        <x:v>docs/RW3_REPLAY_LIVE_EQUIVALENCE_PREREGISTRATION.md</x:v>
+        <x:v>docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="61.5" customHeight="1">
@@ -7242,7 +7279,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reee98a3bc50f4262"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912b958147e84b1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2c35e6bfb69e4427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R335601555183480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R8013336cb3ba4ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8b28ca79fccb4ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra2c42adacb1a4139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R434548994d6c4932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Re0c5150f88714daa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4d0d2b3d02034f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd5768105f6924e30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Raffb2b73cbcf4083"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R2a76ee80631e4986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rc6d60f3a72634941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Re2cfea7fa2dc4426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R9ddbffafc8684c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R43e3524ead5b4264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R3595286dda2c46c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -593,7 +593,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f7797d8ba564556"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53bae63a011f4fe7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -666,7 +666,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -951,12 +951,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Next operating rule</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>RW0-RW2 closed. RW3 Stage A packet at 163ff2f awaits explicit authorization; no implementation exists. Review PR #2. RW4/S20 remains blocked.</x:v>
+        <x:v>Loop 24 preregistration 186bb6f and RW3 Stage A packet 163ff2f await separate explicit decisions; neither implementation exists. Review PR #2. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1093,7 +1093,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R439f2b3d955f4bdf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fce81bca42464c"/>
 </x:worksheet>
 </file>
 
@@ -2507,7 +2507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd53e5cc1b63744bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R423ad2958cad428e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3525,16 +3525,34 @@
         <x:v>Commit 163ff2f; machine request authorized_now=false; 10 invariants; zero source chunks, fixtures, adapters, optional imports, sockets, boards, XDF/data/target/model/training access; Stages B-D remain forbidden.</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="37"/>
-      <x:c r="B35" s="12"/>
-      <x:c r="C35" s="12"/>
-      <x:c r="D35" s="12"/>
-      <x:c r="E35" s="12"/>
-      <x:c r="F35" s="12"/>
-      <x:c r="G35" s="12"/>
-      <x:c r="H35" s="12"/>
-      <x:c r="I35" s="12"/>
+    <x:row r="35" ht="90" customHeight="1">
+      <x:c r="A35" s="37" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="str">
+        <x:v>Freeze local precision/runtime before candidate execution</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="str">
+        <x:v>The 1,130-parameter synthetic pipeline is small enough that dtype labels, storage size, warmup, backend choice, and Python overhead can mislead; freeze behavior and resource gates before observing a candidate.</x:v>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
+        <x:v>docs/LOOP_24_PRECISION_RUNTIME_PREREGISTRATION.md</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="str">
+        <x:v>Explicitly authorize Loop 24 only, amend, or hold</x:v>
+      </x:c>
+      <x:c r="I35" s="12" t="str">
+        <x:v>Commit 186bb6f; contract SHA-256 58e9d5407fef9419bc3bb0dc8cd3fa68d36dd238cb636d2f833dd9c5c6c3ae5d; 3 candidates; seeds 2401/2402; 12 balanced selection rounds; 30 refusals; 9 invariants; zero fixture/checkpoint/candidate/inference/training/RW3 access.</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37"/>
@@ -5371,7 +5389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb92735a5b7944df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3881cd5bed8840a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6232,7 +6250,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8dac7305814392"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6caaaeb1f24e90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6677,43 +6695,54 @@
         <x:v>Implement commit eacb231 exactly on generated BrainVision, EDF/EDF+, BDF, external-FDT EEGLAB, FIF, and BIDS fixtures. Use explicit lazy optional readers, one thread, bounded windows/arrays/output, strict source binding, redaction and no-mutation checks, descriptive metrics only, exact malformed/refusal tests, and no real/S20/consumed/target/model/training access.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="84" customHeight="1">
-      <x:c r="A30" t="str">
+    <x:row r="30" ht="126" customHeight="1">
+      <x:c r="A30" s="12" t="str">
         <x:v>RW3</x:v>
       </x:c>
-      <x:c r="B30" t="str">
+      <x:c r="B30" s="12" t="str">
         <x:v>Offline Replay / Live-Source Equivalence Preregistration</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C30" s="12" t="str">
         <x:v>Before installing or using BrainFlow, LSL, or hardware, freeze one versioned chunk/source schema; exact payload, channel, timestamp, clock-correction, packet-loss, ordering, mutable-state, flush, and schedule semantics; synthetic/playback dependency boundaries; privacy and local-only rules; one-thread runtime/RSS/state/output caps; exact replay tolerances; and proceed/park/kill rules. Do not open real/consumed/S20 data, train a model, or claim live, portable, real-time, or decoding support.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="98" customHeight="1">
-      <x:c r="A31" t="str">
+    <x:row r="31" ht="126" customHeight="1">
+      <x:c r="A31" s="12" t="str">
         <x:v>RW3-Review</x:v>
       </x:c>
-      <x:c r="B31" t="str">
+      <x:c r="B31" s="12" t="str">
         <x:v>Review Frozen Replay Equivalence Registration</x:v>
       </x:c>
-      <x:c r="C31" t="str">
+      <x:c r="C31" s="12" t="str">
         <x:v>Review commit c3d1f01, the RW3 primary-source research, preregistration, machine contract, and invariant tests. Confirm five schedules, 18 future fixture families, 30 refusal IDs, four sequential stages, strict timestamp/anomaly/hash/resource/access rules, and the no-runtime/no-decoding boundary. Do not implement Stage A, install BrainFlow/LSL/PyXDF, open sockets or streams, touch hardware or real/consumed data, create targets, run models, or train without separate explicit authorization.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="118" customHeight="1">
-      <x:c r="A32" t="str">
+    <x:row r="32" ht="126" customHeight="1">
+      <x:c r="A32" s="12" t="str">
         <x:v>RW3-StageA-Decision</x:v>
       </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="B32" s="12" t="str">
         <x:v>Decide Stage A Only</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C32" s="12" t="str">
         <x:v>Review docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md and registries/rw3_stage_a_authorization_request.v0.json. Confirm the c3d1f01 contract hash, 90 proposed cases, 30 refusals, one-thread caps, forbidden work, and authorization-only commit sequence. Decide explicitly to authorize Stage A only, amend the packet, or hold. General continuation is not authorization. Do not implement anything; BrainFlow, LSL, PyXDF, sockets, devices, real or consumed data, targets, models, training, and Stages B-D remain unauthorized.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="126" customHeight="1">
+      <x:c r="A33" s="12" t="str">
+        <x:v>Loop24-Decision</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>Decide Local Precision / Runtime Only</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="str">
+        <x:v>Review docs/LOOP_24_PRECISION_RUNTIME_PREREGISTRATION.md and registries/local_precision_runtime_contract.v0.json. Confirm the three exact candidates, frozen hashes, fresh target-free seeds 2401/2402, 12 balanced timing rounds, behavior/resource gates, 30 refusals, and false execution flags. Decide explicitly to use the exact authorization sentence, amend, or hold. General continuation is not authorization. Do not implement a candidate, generate a fixture, load or convert the checkpoint, run inference, benchmark, profile, or measure energy. Do not authorize RW3 Stage A, data access, or model training.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4af66e6b99e54673"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f7d8a8b94c94ed7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6935,9 +6964,9 @@
       <x:c r="H1" s="44"/>
       <x:c r="I1" s="44"/>
     </x:row>
-    <x:row r="2" ht="25.5" customHeight="1">
+    <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. RW0-RW2 are closed. RW3 contract c3d1f01 and Stage A packet 163ff2f are review-ready, but authorized_now is false and no runtime exists. RW4/S20 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. Loop 24 contract 186bb6f and RW3 Stage A packet 163ff2f await separate explicit decisions; all execution/authorization flags are false and no runtime exists. RW4/S20 remains blocked.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -7279,7 +7308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912b958147e84b1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73d55305bd8c45c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd5768105f6924e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Raffb2b73cbcf4083"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R2a76ee80631e4986"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rc6d60f3a72634941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Re2cfea7fa2dc4426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R9ddbffafc8684c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R43e3524ead5b4264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R3595286dda2c46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf1233ac7944e45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re57e319871e14af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R501658a8574e4b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9aead73c39a641a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R584b965739f54b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R40d08a90c6404ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R18ace5416b4b47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc9a2efcb365b487c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -446,7 +446,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Loops by Phase</a:t>
+              <a:t>Original 20 Loops by Phase</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -593,7 +593,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53bae63a011f4fe7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R655bcf13c7c94bb0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -853,7 +853,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="21" t="str">
-        <x:v>NeuroDecodeKit: Post-PR1 20-Loop Tracker</x:v>
+        <x:v>NeuroDecodeKit Roadmap Tracker: Original 20 + Post-Roadmap</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -865,7 +865,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="29" t="str">
-        <x:v>Core rule: keep the loop tiny, honest, measured, and repeatable before adding model complexity.</x:v>
+        <x:v>Core rule: keep each gate tiny, honest, measured, and repeatable. Numbered gates after 20 extend the original roadmap.</x:v>
       </x:c>
       <x:c r="B2" s="29" t="str"/>
       <x:c r="C2" s="29" t="str"/>
@@ -890,7 +890,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="36" t="str">
-        <x:v>Total loops</x:v>
+        <x:v>Original roadmap loops</x:v>
       </x:c>
       <x:c r="B5" s="36" t="n">
         <x:f>COUNTA('Loop Tracker'!$A$2:$A$21)</x:f>
@@ -898,18 +898,19 @@
       </x:c>
       <x:c r="F5" s="29" t="str">
         <x:v>1) Work top-down unless a blocker forces a spike.
-2) Keep each loop small enough for one PR or one experiment note.
-3) Every loop needs an acceptance gate, not vibes.
+2) Keep each gate small enough for one PR or experiment note.
+3) Every gate needs an acceptance boundary.
 4) Add complexity only after a simpler baseline fails.
 5) Never silently download huge neurodata.
-6) Record kill/iterate/proceed decisions in the Decision Log.</x:v>
+6) Record decisions in the Decision Log.
+7) Read 20 as the original roadmap size; use Current numbered gate for the post-roadmap position.</x:v>
       </x:c>
       <x:c r="G5" s="29" t="str"/>
       <x:c r="H5" s="29" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="36" t="str">
-        <x:v>Done</x:v>
+        <x:v>Original completed</x:v>
       </x:c>
       <x:c r="B6" s="36" t="n">
         <x:v>19</x:v>
@@ -920,21 +921,21 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="36" t="str">
-        <x:v>Active</x:v>
+        <x:v>Original parked</x:v>
       </x:c>
       <x:c r="B7" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="29" t="str"/>
       <x:c r="G7" s="29" t="str"/>
       <x:c r="H7" s="29" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="36" t="str">
-        <x:v>Blocked</x:v>
-      </x:c>
-      <x:c r="B8" s="36" t="n">
-        <x:v>0</x:v>
+      <x:c r="A8" s="12" t="str">
+        <x:v>Current numbered gate</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Loop 24 preregistered</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -942,7 +943,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="36" t="str">
-        <x:v>Average progress</x:v>
+        <x:v>Original roadmap progress</x:v>
       </x:c>
       <x:c r="B9" s="41" t="n">
         <x:v>0.955</x:v>
@@ -951,12 +952,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
+    <x:row r="10" ht="84" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>Next operating rule</x:v>
+        <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 24 preregistration 186bb6f and RW3 Stage A packet 163ff2f await separate explicit decisions; neither implementation exists. Review PR #2. RW4/S20 remains blocked.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap only. Loops 21-22 are done, Loop 23 is parked, Loop 23.5 is done, and Loop 24 is preregistered but not authorized. RW3 Stage A is separately unauthorized.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -971,13 +972,13 @@
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="6" t="str">
-        <x:v>Phase</x:v>
+        <x:v>Original phase</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
         <x:v>Loops</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>Done</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>Progress</x:v>
@@ -1093,7 +1094,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fce81bca42464c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a8011a6c0db4b17"/>
 </x:worksheet>
 </file>
 
@@ -2507,7 +2508,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R423ad2958cad428e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642ab09ce8434f64"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -5389,7 +5390,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3881cd5bed8840a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7985ede8ac48ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6250,7 +6251,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6caaaeb1f24e90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3aae485575c440f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6742,7 +6743,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f7d8a8b94c94ed7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85557bf3974747a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7308,7 +7309,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73d55305bd8c45c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bca0cf51f494845"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf1233ac7944e45cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re57e319871e14af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R501658a8574e4b23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9aead73c39a641a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R584b965739f54b10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R40d08a90c6404ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R18ace5416b4b47db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc9a2efcb365b487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdfb0612bac6149bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R666c2c00fe264aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R41e0dd2b772f48a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rbfa8f65597664bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R1d086a245db94d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd336d92b3aa644de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1e86f534998649e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R46af1cd3fe6d4a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R888ca8495f03404c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,12 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -75,8 +77,70 @@
       <x:color rgb="FF1E3A8A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF16324F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF455A64"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF263238"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF16324F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF276A73"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF8A4B08"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF6D4C00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF7A1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:color rgb="FF245C8A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -163,8 +227,38 @@
         <x:fgColor rgb="FFDBEAFE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF16324F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEAF3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF276A73"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="10">
     <x:border/>
     <x:border/>
     <x:border>
@@ -186,11 +280,59 @@
         <x:color rgb="FFD1D5DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB0BEC5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1E5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1E5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1E5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E1E5"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="78">
+  <x:cellXfs count="152">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -381,11 +523,203 @@
     <x:xf numFmtId="0" fontId="8" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="8">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -427,6 +761,50 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1B5E20"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEFD8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A4B08"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8D5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8B1E1E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4D7D7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF455A64"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECEFF1"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -593,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R655bcf13c7c94bb0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bc7bfc1a36c4bd6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -688,6 +1066,31 @@
     <x:tableColumn id="7" name="Depends On"/>
     <x:tableColumn id="8" name="Proof Posture"/>
     <x:tableColumn id="9" name="Evidence"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="NextTwentyLoopsTable" displayName="NextTwentyLoopsTable" ref="A4:P24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:P24"/>
+  <x:tableColumns count="16">
+    <x:tableColumn id="1" name="Loop"/>
+    <x:tableColumn id="2" name="Phase"/>
+    <x:tableColumn id="3" name="Gate"/>
+    <x:tableColumn id="4" name="Priority / Effort"/>
+    <x:tableColumn id="5" name="Core question"/>
+    <x:tableColumn id="6" name="Why high value"/>
+    <x:tableColumn id="7" name="Build + research deliverables"/>
+    <x:tableColumn id="8" name="Data scope + controls"/>
+    <x:tableColumn id="9" name="Primary metrics"/>
+    <x:tableColumn id="10" name="Acceptance + stop rule"/>
+    <x:tableColumn id="11" name="Dependencies"/>
+    <x:tableColumn id="12" name="Authorization boundary"/>
+    <x:tableColumn id="13" name="Resource cap"/>
+    <x:tableColumn id="14" name="Proof posture"/>
+    <x:tableColumn id="15" name="Status"/>
+    <x:tableColumn id="16" name="Primary source URLs"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -853,7 +1256,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="21" t="str">
-        <x:v>NeuroDecodeKit Roadmap Tracker: Original 20 + Post-Roadmap</x:v>
+        <x:v>NeuroDecodeKit Roadmap Tracker: Original 20 + Current Gate + Next 20</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -865,7 +1268,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="29" t="str">
-        <x:v>Core rule: keep each gate tiny, honest, measured, and repeatable. Numbered gates after 20 extend the original roadmap.</x:v>
+        <x:v>Core rule: keep every gate tiny, honest, measured, repeatable, and explicit about what it cannot prove.</x:v>
       </x:c>
       <x:c r="B2" s="29" t="str"/>
       <x:c r="C2" s="29" t="str"/>
@@ -952,12 +1355,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="84" customHeight="1">
+    <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap only. Loops 21-22 are done, Loop 23 is parked, Loop 23.5 is done, and Loop 24 is preregistered but not authorized. RW3 Stage A is separately unauthorized.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 remains preregistered and unauthorized; RW3 Stage A remains separately unauthorized. Loops 25-44 are a planning-only queue on the Loops 25-44 sheet, and every execution flag is false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1094,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a8011a6c0db4b17"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8753ebcdc64a23"/>
 </x:worksheet>
 </file>
 
@@ -2508,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642ab09ce8434f64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6672840ab0be4b91"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -5390,7 +5793,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7985ede8ac48ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a727d5a43b49e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6251,7 +6654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3aae485575c440f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc75f39a821bf4b1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6743,7 +7146,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85557bf3974747a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a7f813ede6044c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7309,7 +7712,1417 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bca0cf51f494845"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d3d437b8a164513"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="52" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="56" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="54" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="31" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="46" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="23" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="81" t="str">
+        <x:v>NeuroDecodeKit Next 20 Loops: 25-44</x:v>
+      </x:c>
+      <x:c r="B1" s="81"/>
+      <x:c r="C1" s="81"/>
+      <x:c r="D1" s="81"/>
+      <x:c r="E1" s="81"/>
+      <x:c r="F1" s="81"/>
+      <x:c r="G1" s="81"/>
+      <x:c r="H1" s="81"/>
+      <x:c r="I1" s="81"/>
+      <x:c r="J1" s="81"/>
+      <x:c r="K1" s="81"/>
+      <x:c r="L1" s="81"/>
+      <x:c r="M1" s="81"/>
+      <x:c r="N1" s="81"/>
+      <x:c r="O1" s="81"/>
+      <x:c r="P1" s="81"/>
+    </x:row>
+    <x:row r="2" ht="44" customHeight="1">
+      <x:c r="A2" s="86" t="str">
+        <x:v>Planning only. Current gate: Loop 24 preregistered. RW3 Stage A is separate. No download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
+      </x:c>
+      <x:c r="B2" s="86"/>
+      <x:c r="C2" s="86"/>
+      <x:c r="D2" s="86"/>
+      <x:c r="E2" s="86"/>
+      <x:c r="F2" s="86"/>
+      <x:c r="G2" s="86"/>
+      <x:c r="H2" s="86"/>
+      <x:c r="I2" s="86"/>
+      <x:c r="J2" s="86"/>
+      <x:c r="K2" s="86"/>
+      <x:c r="L2" s="86"/>
+      <x:c r="M2" s="86"/>
+      <x:c r="N2" s="86"/>
+      <x:c r="O2" s="86"/>
+      <x:c r="P2" s="86"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="98" t="str">
+        <x:v>20 loops | 5 phases | one-thread default | 32 MiB default artifact cap | every row Not Started and execution_authorized=false | source: registries/next_20_loops.v0.json</x:v>
+      </x:c>
+      <x:c r="B3" s="99"/>
+      <x:c r="C3" s="99"/>
+      <x:c r="D3" s="99"/>
+      <x:c r="E3" s="99"/>
+      <x:c r="F3" s="99"/>
+      <x:c r="G3" s="99"/>
+      <x:c r="H3" s="99"/>
+      <x:c r="I3" s="99"/>
+      <x:c r="J3" s="99"/>
+      <x:c r="K3" s="99"/>
+      <x:c r="L3" s="99"/>
+      <x:c r="M3" s="99"/>
+      <x:c r="N3" s="99"/>
+      <x:c r="O3" s="99"/>
+      <x:c r="P3" s="100"/>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
+      <x:c r="A4" s="105" t="str">
+        <x:v>Loop</x:v>
+      </x:c>
+      <x:c r="B4" s="105" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="C4" s="105" t="str">
+        <x:v>Gate</x:v>
+      </x:c>
+      <x:c r="D4" s="105" t="str">
+        <x:v>Priority / Effort</x:v>
+      </x:c>
+      <x:c r="E4" s="105" t="str">
+        <x:v>Core question</x:v>
+      </x:c>
+      <x:c r="F4" s="105" t="str">
+        <x:v>Why high value</x:v>
+      </x:c>
+      <x:c r="G4" s="105" t="str">
+        <x:v>Build + research deliverables</x:v>
+      </x:c>
+      <x:c r="H4" s="105" t="str">
+        <x:v>Data scope + controls</x:v>
+      </x:c>
+      <x:c r="I4" s="105" t="str">
+        <x:v>Primary metrics</x:v>
+      </x:c>
+      <x:c r="J4" s="105" t="str">
+        <x:v>Acceptance + stop rule</x:v>
+      </x:c>
+      <x:c r="K4" s="105" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="L4" s="105" t="str">
+        <x:v>Authorization boundary</x:v>
+      </x:c>
+      <x:c r="M4" s="105" t="str">
+        <x:v>Resource cap</x:v>
+      </x:c>
+      <x:c r="N4" s="105" t="str">
+        <x:v>Proof posture</x:v>
+      </x:c>
+      <x:c r="O4" s="105" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="P4" s="105" t="str">
+        <x:v>Primary source URLs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="138" customHeight="1">
+      <x:c r="A5" s="125" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B5" s="128" t="str">
+        <x:v>P1 - Causal Evidence</x:v>
+      </x:c>
+      <x:c r="C5" s="113" t="str">
+        <x:v>Causal Preprocessing Audit</x:v>
+      </x:c>
+      <x:c r="D5" s="134" t="str">
+        <x:v>P0 / M</x:v>
+      </x:c>
+      <x:c r="E5" s="113" t="str">
+        <x:v>Can every transform before the causal encoder run incrementally without future samples, evaluation-fit statistics, timestamp drift, or chunk-boundary changes?</x:v>
+      </x:c>
+      <x:c r="F5" s="113" t="str">
+        <x:v>A causal model is not causal if filtering, resampling, padding, or normalization leaks future context; this gate protects every later streaming claim.</x:v>
+      </x:c>
+      <x:c r="G5" s="113" t="str">
+        <x:v>Build: Versioned stateful preprocessing contract, offline-versus-stream replay harness, transform provenance, and explicit refusal for noncausal settings.
+Research: Primary-source note on filter delay, resampling event jitter, padding, and train-only normalization semantics.</x:v>
+      </x:c>
+      <x:c r="H5" s="113" t="str">
+        <x:v>Data: Target-free synthetic signals first; any later S21 use is restricted to separately authorized source-train rows and may not open source-test or session-2 evidence.
+Controls:
+- Five or more adversarial chunk schedules including single-sample and boundary splits.
+- Impulse, step, chirp, drift, and end-padding fixtures with future-sample perturbation tests.
+- Offline noncausal reference reported separately and never substituted for the causal path.</x:v>
+      </x:c>
+      <x:c r="I5" s="113" t="str">
+        <x:v>- right-context samples and milliseconds
+- valid-sample and timestamp identity
+- maximum offline-stream payload error
+- schedule hash agreement
+- runtime, peak RSS, input bytes, output bytes, and access counts</x:v>
+      </x:c>
+      <x:c r="J5" s="113" t="str">
+        <x:v>Acceptance: Proceed only if declared right context is zero, every schedule preserves valid samples and timestamps within preregistered tolerances, evaluation-fit/read counters are zero, and resource caps pass.
+Stop: Park any transform that needs future samples or cannot preserve timing; do not widen tolerances after observing a protected row.</x:v>
+      </x:c>
+      <x:c r="K5" s="113" t="str">
+        <x:v>Loops: none
+External: explicit_loop24_proceed_park_or_hold_decision</x:v>
+      </x:c>
+      <x:c r="L5" s="113" t="str">
+        <x:v>Planning only. Fixture generation, real-cache reads, preprocessing execution, and model access require a separate Loop 25 preregistration and authorization.</x:v>
+      </x:c>
+      <x:c r="M5" s="113" t="str">
+        <x:v>One thread, one worker, 32 MiB generated artifacts, 60 seconds per isolated worker, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N5" s="140" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O5" s="146" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P5" s="149" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://mne.tools/stable/generated/mne.filter.resample.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="138" customHeight="1">
+      <x:c r="A6" s="126" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B6" s="129" t="str">
+        <x:v>P1 - Causal Evidence</x:v>
+      </x:c>
+      <x:c r="C6" s="114" t="str">
+        <x:v>Real Validation-Only Encoder Gate</x:v>
+      </x:c>
+      <x:c r="D6" s="135" t="str">
+        <x:v>P0 / L</x:v>
+      </x:c>
+      <x:c r="E6" s="114" t="str">
+        <x:v>Does one fixed, small causal encoder show neural information above no-signal and shuffled controls on source validation without touching any test set?</x:v>
+      </x:c>
+      <x:c r="F6" s="114" t="str">
+        <x:v>The project has strong mechanics but no real neural advantage; this is the first gate that can justify continuing the predictive branch.</x:v>
+      </x:c>
+      <x:c r="G6" s="114" t="str">
+        <x:v>Build: Preregistered tiny architecture, train-only fit path, six-row validation report, uncertainty, control parity, and immutable access ledger.
+Research: Power and identifiability note stating what six validation rows can and cannot establish.</x:v>
+      </x:c>
+      <x:c r="H6" s="114" t="str">
+        <x:v>Data: Only separately authorized S21 source-train and source-validation members; five source-test rows and all session-2 rows stay closed.
+Controls:
+- Same-split no-signal prior.
+- Target permutation fitted on train only.
+- Time-shift and channel-permutation controls chosen before validation opens.
+- Frozen non-neural parameter-count and compute-matched comparator where feasible.</x:v>
+      </x:c>
+      <x:c r="I6" s="114" t="str">
+        <x:v>- CER and exact-sequence accuracy
+- paired item differences and interval
+- control margins
+- parameter count, runtime, peak RSS, and artifact bytes
+- raw, cache, target, model, and training access counts</x:v>
+      </x:c>
+      <x:c r="J6" s="114" t="str">
+        <x:v>Acceptance: Proceed only if the preregistered primary neural-versus-prior margin and all required controls pass on validation with no access violation; this does not authorize source-test opening.
+Stop: If the neural path does not beat the registered controls, park real-model scaling and move to failure analysis without touching test or increasing model size.</x:v>
+      </x:c>
+      <x:c r="K6" s="114" t="str">
+        <x:v>Loops: 25
+External: separate_real_cache_and_training_authorization</x:v>
+      </x:c>
+      <x:c r="L6" s="114" t="str">
+        <x:v>Planning only. Real-cache reads, target access, training, validation opening, and model runs are all unauthorized now.</x:v>
+      </x:c>
+      <x:c r="M6" s="114" t="str">
+        <x:v>One thread, one worker, existing tiny-model class only, 32 MiB generated artifacts, 20 minutes total authorized CPU time, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N6" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O6" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P6" s="150" t="str">
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="138" customHeight="1">
+      <x:c r="A7" s="126" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B7" s="129" t="str">
+        <x:v>P1 - Causal Evidence</x:v>
+      </x:c>
+      <x:c r="C7" s="114" t="str">
+        <x:v>Fresh Holdout Preregistration</x:v>
+      </x:c>
+      <x:c r="D7" s="135" t="str">
+        <x:v>P0 / M</x:v>
+      </x:c>
+      <x:c r="E7" s="114" t="str">
+        <x:v>Which independent participant, session, or task-matched recording can answer the next claim without recycling S21 session-2 or S7 evidence?</x:v>
+      </x:c>
+      <x:c r="F7" s="114" t="str">
+        <x:v>A fresh, hash-bound test is more valuable than another tuned result on already observed data.</x:v>
+      </x:c>
+      <x:c r="G7" s="114" t="str">
+        <x:v>Build: Metadata-only candidate registry, license and byte ledger, exact file plan, split protocol, target-isolation plan, and one-time analysis contract.
+Research: Primary-source dataset and license review separating same-person session, unseen-person, modality, and task claims.</x:v>
+      </x:c>
+      <x:c r="H7" s="114" t="str">
+        <x:v>Data: Metadata and public documentation only; no download, signal read, target read, or remote row preview.
+Controls:
+- Independent identity and sentence-membership audit.
+- Exact no-signal and shuffle comparators frozen before acquisition.
+- One-time test access sequence with physical or cryptographic partition separation.</x:v>
+      </x:c>
+      <x:c r="I7" s="114" t="str">
+        <x:v>- planned files and bytes
+- subjects, sessions, trials, and unique sentence groups
+- license and redistribution status
+- identity-overlap and task-match warnings
+- authorized and unavailable access counters</x:v>
+      </x:c>
+      <x:c r="J7" s="114" t="str">
+        <x:v>Acceptance: Approve a future acquisition packet only if independence, task match, licensing, exact byte cap, split power, and one-time decision rule are explicit; otherwise record no eligible holdout.
+Stop: Hold acquisition if identity, license, task, timing, or byte provenance is ambiguous; never substitute a convenient consumed cohort.</x:v>
+      </x:c>
+      <x:c r="K7" s="114" t="str">
+        <x:v>Loops: none
+External: none</x:v>
+      </x:c>
+      <x:c r="L7" s="114" t="str">
+        <x:v>Metadata research is the only future candidate scope; download or signal access requires a separate exact packet and user authorization.</x:v>
+      </x:c>
+      <x:c r="M7" s="114" t="str">
+        <x:v>Zero downloaded bytes, zero signal reads, one thread, one worker, 8 MiB planning artifacts, and 10 minutes local metadata processing.</x:v>
+      </x:c>
+      <x:c r="N7" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O7" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P7" s="150" t="str">
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="138" customHeight="1">
+      <x:c r="A8" s="126" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="129" t="str">
+        <x:v>P1 - Causal Evidence</x:v>
+      </x:c>
+      <x:c r="C8" s="114" t="str">
+        <x:v>Session And Person Transfer</x:v>
+      </x:c>
+      <x:c r="D8" s="135" t="str">
+        <x:v>P0 / L</x:v>
+      </x:c>
+      <x:c r="E8" s="114" t="str">
+        <x:v>Does the frozen causal system transfer to a genuinely fresh session or person, and how much predeclared calibration is required?</x:v>
+      </x:c>
+      <x:c r="F8" s="114" t="str">
+        <x:v>The existing same-person cross-session result is negative; a fresh one-time test is required before any generalization claim can move.</x:v>
+      </x:c>
+      <x:c r="G8" s="114" t="str">
+        <x:v>Build: Frozen source model, identity-safe adapter protocol, one-time holdout runner, calibration curve, paired controls, and claim-specific report card.
+Research: Transfer taxonomy distinguishing same-session, same-person cross-session, unseen-person zero-shot, and unseen-person calibrated evidence.</x:v>
+      </x:c>
+      <x:c r="H8" s="114" t="str">
+        <x:v>Data: Only a separately acquired and authorized Loop 27 holdout after architecture, preprocessing, adapter, thresholds, and reports are frozen.
+Controls:
+- Train-only no-signal prior evaluated on identical rows.
+- Zero-shot frozen model before any calibration.
+- Calibration-size curve with a physically separate final partition.
+- Identity and repeated-text leakage audit.</x:v>
+      </x:c>
+      <x:c r="I8" s="114" t="str">
+        <x:v>- CER, WER where justified, and exact sequence accuracy
+- neural-minus-prior paired interval
+- zero-shot versus calibrated delta
+- calibration examples, seconds, and compute
+- session/person-specific failure rates</x:v>
+      </x:c>
+      <x:c r="J8" s="114" t="str">
+        <x:v>Acceptance: Promote only the exact same-person or unseen-person claim whose preregistered interval and controls pass on the one-time fresh partition.
+Stop: A failed fresh gate closes that transfer claim; do not tune on the opened holdout or relabel calibrated performance as zero-shot.</x:v>
+      </x:c>
+      <x:c r="K8" s="114" t="str">
+        <x:v>Loops: 25, 26, 27
+External: approved_fresh_holdout_packet, separate_one_time_test_authorization</x:v>
+      </x:c>
+      <x:c r="L8" s="114" t="str">
+        <x:v>Planning only. No fresh acquisition, model run, calibration, or holdout opening is authorized.</x:v>
+      </x:c>
+      <x:c r="M8" s="114" t="str">
+        <x:v>One thread and worker, frozen small model, 32 MiB outputs, preregistered calibration budget, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N8" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O8" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P8" s="150" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/2404.15319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="138" customHeight="1">
+      <x:c r="A9" s="126" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B9" s="129" t="str">
+        <x:v>P2 - Translation And Generalization</x:v>
+      </x:c>
+      <x:c r="C9" s="114" t="str">
+        <x:v>Portable Sensing Translation</x:v>
+      </x:c>
+      <x:c r="D9" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E9" s="114" t="str">
+        <x:v>Which validated requirements survive a move from cryogenic MEG toward OPM-MEG or EEG, and which assumptions break?</x:v>
+      </x:c>
+      <x:c r="F9" s="114" t="str">
+        <x:v>Portability is the product direction users care about, but channel-count ablation is not device qualification.</x:v>
+      </x:c>
+      <x:c r="G9" s="114" t="str">
+        <x:v>Build: Versioned modality requirement matrix covering geometry, reference, units, bandwidth, noise, shielding, timing, compute, and calibration.
+Research: Primary-source OPM-MEG and EEG feasibility review with explicit unavailable fields and partner-data gates.</x:v>
+      </x:c>
+      <x:c r="H9" s="114" t="str">
+        <x:v>Data: Public specifications and existing aggregate evidence only; no device session, new recording, or synthetic claim of modality equivalence.
+Controls:
+- Separate rows for cryogenic MEG, OPM-MEG, scalp EEG, and non-neural wearables.
+- Measured device values distinguished from vendor specifications and unknowns.
+- Random channel ablation explicitly excluded as OPM or EEG evidence.</x:v>
+      </x:c>
+      <x:c r="I9" s="114" t="str">
+        <x:v>- requirement coverage and unavailable-field count
+- sensor count, rate, units, geometry, and clock provenance
+- known versus inferred versus measured status
+- minimum future qualification evidence</x:v>
+      </x:c>
+      <x:c r="J9" s="114" t="str">
+        <x:v>Acceptance: Proceed to a device-specific packet only when one modality has task, timing, geometry, privacy, licensing, and resource requirements that can be measured directly.
+Stop: Do not call a simulated subset, vendor specification, or file-reader success portable decoding.</x:v>
+      </x:c>
+      <x:c r="K9" s="114" t="str">
+        <x:v>Loops: 27
+External: none</x:v>
+      </x:c>
+      <x:c r="L9" s="114" t="str">
+        <x:v>Research and registry planning only; hardware, acquisition, and signal reads require separate authorization.</x:v>
+      </x:c>
+      <x:c r="M9" s="114" t="str">
+        <x:v>Zero hardware sessions, zero downloads, one thread, one worker, and 8 MiB documentation artifacts.</x:v>
+      </x:c>
+      <x:c r="N9" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O9" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P9" s="150" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/2404.15319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="138" customHeight="1">
+      <x:c r="A10" s="126" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="129" t="str">
+        <x:v>P2 - Translation And Generalization</x:v>
+      </x:c>
+      <x:c r="C10" s="114" t="str">
+        <x:v>Local Private Streaming Prototype</x:v>
+      </x:c>
+      <x:c r="D10" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E10" s="114" t="str">
+        <x:v>Can a user inspect incremental hypotheses, revisions, timing, provenance, and refusals locally without confusing replay with live decoding?</x:v>
+      </x:c>
+      <x:c r="F10" s="114" t="str">
+        <x:v>A trustworthy interaction surface exposes latency and uncertainty instead of hiding them behind a final sentence.</x:v>
+      </x:c>
+      <x:c r="G10" s="114" t="str">
+        <x:v>Build: Loopback-only replay UI with partial hypotheses, revision trace, stage clocks, resource telemetry, warnings, and local artifact loading.
+Research: Interaction contract for partial output, abstention, revision, privacy, and replay/live labels.</x:v>
+      </x:c>
+      <x:c r="H10" s="114" t="str">
+        <x:v>Data: Existing synthetic artifacts and aggregate-only real scorecards; no raw real signal, cloud call, socket, or hardware source.
+Controls:
+- Replay badge and source identity visible in every view.
+- No-signal comparator shown beside predictive outputs.
+- Cold start, steady state, scheduling delay, compute delay, and render delay separated.</x:v>
+      </x:c>
+      <x:c r="I10" s="114" t="str">
+        <x:v>- first-token and finalization latency by stage
+- revision count and prefix stability
+- event-loop responsiveness
+- runtime, peak RSS, input and output bytes
+- network, raw, cache, model, and training counters</x:v>
+      </x:c>
+      <x:c r="J10" s="114" t="str">
+        <x:v>Acceptance: Pass only as a local replay interface when all source, causality, latency, unavailable-confidence, and proof labels remain visible and browser QA passes.
+Stop: Park any interface that implies live hardware, real-time text, confidence, or neural success that the loaded artifact does not prove.</x:v>
+      </x:c>
+      <x:c r="K10" s="114" t="str">
+        <x:v>Loops: 25
+External: none</x:v>
+      </x:c>
+      <x:c r="L10" s="114" t="str">
+        <x:v>Planning only. UI implementation and replay execution require a separate bounded Loop 30 authorization; live sources remain outside scope.</x:v>
+      </x:c>
+      <x:c r="M10" s="114" t="str">
+        <x:v>Loopback only, one thread, one worker, 32 MiB temporary artifacts, 1 GiB peak RSS, and no network dependency.</x:v>
+      </x:c>
+      <x:c r="N10" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O10" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P10" s="150" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://labstreaminglayer.readthedocs.io/info/time_synchronization.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="138" customHeight="1">
+      <x:c r="A11" s="126" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B11" s="129" t="str">
+        <x:v>P2 - Translation And Generalization</x:v>
+      </x:c>
+      <x:c r="C11" s="114" t="str">
+        <x:v>Neural Contribution Ablation</x:v>
+      </x:c>
+      <x:c r="D11" s="135" t="str">
+        <x:v>P0 / L</x:v>
+      </x:c>
+      <x:c r="E11" s="114" t="str">
+        <x:v>When a predictive system improves, how much comes from neural signal rather than text priors, timing, sentence lists, or pipeline artifacts?</x:v>
+      </x:c>
+      <x:c r="F11" s="114" t="str">
+        <x:v>This gate prevents autocomplete, prompt memorization, and event timing from being credited to brain activity.</x:v>
+      </x:c>
+      <x:c r="G11" s="114" t="str">
+        <x:v>Build: Hash-bound ablation matrix with full signal, no-signal, shuffled-neural, timing-only, text-prior, and optional neurotoken-drop conditions.
+Research: Neural-contribution estimand and claim language for encoder-only and language-model-assisted systems.</x:v>
+      </x:c>
+      <x:c r="H11" s="114" t="str">
+        <x:v>Data: Future authorized validation data only; no consumed test or target-informed fixture construction.
+Controls:
+- No-signal prior and prompt/sentence-list-only baseline.
+- Within-split temporal, channel, and item permutations fixed before evaluation.
+- Encoder-only and language-model-assisted outputs reported separately.
+- Matched access, preprocessing, parameter, and decoding budgets where feasible.</x:v>
+      </x:c>
+      <x:c r="I11" s="114" t="str">
+        <x:v>- full-minus-ablation CER and WER deltas
+- paired intervals and effect consistency
+- neural-token drop degradation
+- language-prior gain
+- shortcut-control failure count</x:v>
+      </x:c>
+      <x:c r="J11" s="114" t="str">
+        <x:v>Acceptance: Call a neural contribution only if the preregistered full-signal condition beats every required signal-free or corrupted-signal control with the expected direction and no leakage.
+Stop: If a signal-free or shortcut control matches the full path, withhold the neural claim and return to split, confound, or model diagnosis.</x:v>
+      </x:c>
+      <x:c r="K11" s="114" t="str">
+        <x:v>Loops: 26
+External: separate_validation_and_model_authorization</x:v>
+      </x:c>
+      <x:c r="L11" s="114" t="str">
+        <x:v>Planning only. No target, model, validation, or language-model run is authorized.</x:v>
+      </x:c>
+      <x:c r="M11" s="114" t="str">
+        <x:v>One thread, fixed small model, preregistered condition count, 32 MiB artifacts, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N11" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O11" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P11" s="150" t="str">
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="138" customHeight="1">
+      <x:c r="A12" s="126" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="129" t="str">
+        <x:v>P2 - Translation And Generalization</x:v>
+      </x:c>
+      <x:c r="C12" s="114" t="str">
+        <x:v>New-Subject Calibration And Adaptation</x:v>
+      </x:c>
+      <x:c r="D12" s="135" t="str">
+        <x:v>P1 / L</x:v>
+      </x:c>
+      <x:c r="E12" s="114" t="str">
+        <x:v>What is the smallest honest calibration budget that improves a fresh person without training on their final evaluation rows?</x:v>
+      </x:c>
+      <x:c r="F12" s="114" t="str">
+        <x:v>Subject variability is a central barrier, and zero-shot versus calibrated performance must be separated.</x:v>
+      </x:c>
+      <x:c r="G12" s="114" t="str">
+        <x:v>Build: Frozen adapter family, calibration-size schedule, train-only normalization, independent selection and final partitions, and time/compute report.
+Research: Calibration protocol covering unlabeled, label-light, and supervised cases with distinct claims.</x:v>
+      </x:c>
+      <x:c r="H12" s="114" t="str">
+        <x:v>Data: Only a future authorized fresh participant with physically separated calibration, selection, and final partitions.
+Controls:
+- Frozen zero-shot source model.
+- Identity or normalization-only adapter.
+- Same-size signal-free prior and label-permutation control.
+- Multiple registered calibration sizes without final-partition reuse.</x:v>
+      </x:c>
+      <x:c r="I12" s="114" t="str">
+        <x:v>- zero-shot and calibrated CER
+- gain per calibration item and minute
+- calibration compute and wall time
+- no-harm item count
+- selection-to-final generalization</x:v>
+      </x:c>
+      <x:c r="J12" s="114" t="str">
+        <x:v>Acceptance: Promote a calibrated-person claim only when a preselected adapter improves the one-time final partition against zero-shot and prior controls within the declared budget.
+Stop: Do not call calibration zero-shot, do not pick a budget on final data, and park adapters that help validation but harm the final partition.</x:v>
+      </x:c>
+      <x:c r="K12" s="114" t="str">
+        <x:v>Loops: 28, 31
+External: approved_fresh_person_protocol</x:v>
+      </x:c>
+      <x:c r="L12" s="114" t="str">
+        <x:v>Planning only. Participant data, labels, calibration, training, and final evaluation remain unauthorized.</x:v>
+      </x:c>
+      <x:c r="M12" s="114" t="str">
+        <x:v>One thread, one worker, fixed small adapter family, 32 MiB outputs, and preregistered maximum calibration minutes.</x:v>
+      </x:c>
+      <x:c r="N12" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O12" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P12" s="150" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/2404.15319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="138" customHeight="1">
+      <x:c r="A13" s="126" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B13" s="129" t="str">
+        <x:v>P3 - Reliability And Confounds</x:v>
+      </x:c>
+      <x:c r="C13" s="114" t="str">
+        <x:v>Data Scaling And Sample Efficiency</x:v>
+      </x:c>
+      <x:c r="D13" s="135" t="str">
+        <x:v>P1 / L</x:v>
+      </x:c>
+      <x:c r="E13" s="114" t="str">
+        <x:v>Do additional hours and additional unique sentences improve the fixed local encoder, and where does the small-data curve stop paying off?</x:v>
+      </x:c>
+      <x:c r="F13" s="114" t="str">
+        <x:v>Scaling evidence guides acquisition better than guessing whether to collect more repetitions, more sentences, or more people.</x:v>
+      </x:c>
+      <x:c r="G13" s="114" t="str">
+        <x:v>Build: Nested train-prefix runner with fixed validation, unique-sentence and repetition controls, multi-seed uncertainty, and compute ledger.
+Research: Local scaling design that avoids extrapolating Brain2Qwerty v2's 90-hour curve to the tiny SpanishBCBL setting.</x:v>
+      </x:c>
+      <x:c r="H13" s="114" t="str">
+        <x:v>Data: Future authorized train and validation partitions only; no fresh test opening and no larger architecture.
+Controls:
+- Nested subsets preserve participant and sentence membership.
+- Matched total-trial comparison of repeated versus unique sentences.
+- No-signal baseline at every data size.
+- Fixed architecture, optimizer, stopping rule, and seed list.</x:v>
+      </x:c>
+      <x:c r="I13" s="114" t="str">
+        <x:v>- CER versus hours, trials, and unique sentences
+- slope and uncertainty on registered scale
+- neural-minus-prior margin by size
+- training time and energy proxy if available
+- marginal gain per added MiB and minute</x:v>
+      </x:c>
+      <x:c r="J13" s="114" t="str">
+        <x:v>Acceptance: Proceed only if a preregistered monotonic or model-based trend is stable across seeds and remains above the no-signal control; report non-saturation only within observed bounds.
+Stop: Stop the curve when gains disappear, controls fail, or the resource budget is reached; never infer a large-scale law from the bounded local range.</x:v>
+      </x:c>
+      <x:c r="K13" s="114" t="str">
+        <x:v>Loops: 26, 31
+External: separate_bounded_training_authorization</x:v>
+      </x:c>
+      <x:c r="L13" s="114" t="str">
+        <x:v>Planning only. Training prefixes, validation runs, and energy measurements are unauthorized.</x:v>
+      </x:c>
+      <x:c r="M13" s="114" t="str">
+        <x:v>One thread and worker, fixed tiny architecture, at most six train sizes and three seeds if authorized, 32 MiB outputs, and a preregistered CPU-hour cap.</x:v>
+      </x:c>
+      <x:c r="N13" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O13" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P13" s="150" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/2404.15319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="138" customHeight="1">
+      <x:c r="A14" s="126" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B14" s="129" t="str">
+        <x:v>P3 - Reliability And Confounds</x:v>
+      </x:c>
+      <x:c r="C14" s="114" t="str">
+        <x:v>Confidence, Abstention, And Revision</x:v>
+      </x:c>
+      <x:c r="D14" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E14" s="114" t="str">
+        <x:v>Can the system identify when to abstain or delay output without tuning confidence on the final test?</x:v>
+      </x:c>
+      <x:c r="F14" s="114" t="str">
+        <x:v>A decoder that knows when it is unreliable is more useful and safer than one that always emits fluent text.</x:v>
+      </x:c>
+      <x:c r="G14" s="114" t="str">
+        <x:v>Build: Validation-fit confidence contract, risk-coverage report, abstention and revision policy, calibration diagnostics, and user-visible unavailable state.
+Research: Selective-prediction and conformal-risk review mapped to tiny correlated sequence data.</x:v>
+      </x:c>
+      <x:c r="H14" s="114" t="str">
+        <x:v>Data: Synthetic first; any real use requires separate calibration and final partitions and cannot reopen consumed evidence.
+Controls:
+- Confidence-free always-predict baseline.
+- Entropy, margin, stability, and prior-only confidence candidates selected on validation only.
+- Coverage levels fixed before final evaluation.
+- Sequence and item clustering respected in uncertainty estimates.</x:v>
+      </x:c>
+      <x:c r="I14" s="114" t="str">
+        <x:v>- risk-coverage curve and area
+- error rate at registered coverage
+- abstention rate
+- expected calibration error where sample size permits
+- revision count and time-to-stability</x:v>
+      </x:c>
+      <x:c r="J14" s="114" t="str">
+        <x:v>Acceptance: Expose confidence only if higher declared confidence reliably lowers error on an independent partition and the registered coverage-risk rule passes.
+Stop: If confidence does not rank errors or sample size is insufficient, publish confidence as unavailable rather than inventing a score.</x:v>
+      </x:c>
+      <x:c r="K14" s="114" t="str">
+        <x:v>Loops: 30, 31
+External: separate_calibration_evaluation_authorization</x:v>
+      </x:c>
+      <x:c r="L14" s="114" t="str">
+        <x:v>Planning only. No confidence fitting, model inference, or final-partition opening is authorized.</x:v>
+      </x:c>
+      <x:c r="M14" s="114" t="str">
+        <x:v>Dependency-free metrics where possible, one thread, 16 MiB artifacts, and no additional model training.</x:v>
+      </x:c>
+      <x:c r="N14" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O14" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P14" s="150" t="str">
+        <x:v>https://arxiv.org/abs/1705.08500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="138" customHeight="1">
+      <x:c r="A15" s="126" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B15" s="129" t="str">
+        <x:v>P3 - Reliability And Confounds</x:v>
+      </x:c>
+      <x:c r="C15" s="114" t="str">
+        <x:v>Peripheral Confound Firewall</x:v>
+      </x:c>
+      <x:c r="D15" s="135" t="str">
+        <x:v>P0 / L</x:v>
+      </x:c>
+      <x:c r="E15" s="114" t="str">
+        <x:v>Is apparent decoding driven by brain signal, or by keystroke timing, muscle, eye, motion, audio, or prompt leakage?</x:v>
+      </x:c>
+      <x:c r="F15" s="114" t="str">
+        <x:v>Prompted typing strongly recruits motor systems, so a positive score is not enough to establish neural specificity.</x:v>
+      </x:c>
+      <x:c r="G15" s="114" t="str">
+        <x:v>Build: Confound registry, synchronized brain-only/peripheral-only/combined protocol, shortcut audits, and claim-blocking report fields.
+Research: Primary-source confound taxonomy for prompted typing and future no-keypress translation.</x:v>
+      </x:c>
+      <x:c r="H15" s="114" t="str">
+        <x:v>Data: Protocol and synthetic timing fixtures first; real multimodal collection requires separate consent, retention, device, and acquisition authorization.
+Controls:
+- Keystroke timing and key identity without neural samples.
+- Peripheral-only channels including EOG, EMG, motion, microphone, or hand tracking when actually recorded.
+- Brain-only channels with synchronized event structure.
+- Time-shift, channel-drop, and event-jitter controls.</x:v>
+      </x:c>
+      <x:c r="I15" s="114" t="str">
+        <x:v>- brain-only, peripheral-only, combined, and timing-only performance
+- incremental neural contribution
+- shortcut detection rate
+- clock and event alignment residuals
+- unavailable modality count</x:v>
+      </x:c>
+      <x:c r="J15" s="114" t="str">
+        <x:v>Acceptance: A brain-specific claim requires brain-only performance above all preregistered non-brain controls and a positive incremental contribution over the strongest peripheral condition.
+Stop: If peripheral or timing controls explain the result, relabel it as task/peripheral decoding and block a neural claim.</x:v>
+      </x:c>
+      <x:c r="K15" s="114" t="str">
+        <x:v>Loops: 31
+External: separate_multimodal_ethics_and_acquisition_authorization</x:v>
+      </x:c>
+      <x:c r="L15" s="114" t="str">
+        <x:v>Planning only. No peripheral recording, device access, real signal read, or model run is authorized.</x:v>
+      </x:c>
+      <x:c r="M15" s="114" t="str">
+        <x:v>Zero collection now; future packet must set exact files, bytes, retention, one-thread analysis, and 32 MiB derived-artifact cap.</x:v>
+      </x:c>
+      <x:c r="N15" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O15" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P15" s="150" t="str">
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="138" customHeight="1">
+      <x:c r="A16" s="126" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B16" s="129" t="str">
+        <x:v>P3 - Reliability And Confounds</x:v>
+      </x:c>
+      <x:c r="C16" s="114" t="str">
+        <x:v>Geometry And Reference Harmonization</x:v>
+      </x:c>
+      <x:c r="D16" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E16" s="114" t="str">
+        <x:v>Can channel geometry, names, units, reference, and missing sensors be normalized across sessions and devices without erasing provenance?</x:v>
+      </x:c>
+      <x:c r="F16" s="114" t="str">
+        <x:v>Cross-session and cross-device failures can come from coordinate or reference mismatch rather than model capacity.</x:v>
+      </x:c>
+      <x:c r="G16" s="114" t="str">
+        <x:v>Build: Versioned channel ontology, geometry transform ledger, reference/unit converter, missing-channel mask, and roundtrip validation.
+Research: Modality-specific coordinate-frame and referencing requirements with explicit non-equivalence rules.</x:v>
+      </x:c>
+      <x:c r="H16" s="114" t="str">
+        <x:v>Data: Synthetic geometry fixtures and metadata sidecars first; real headers only after separate authorization and without opening signal arrays.
+Controls:
+- Permutation, missing-channel, mirrored-coordinate, wrong-unit, and wrong-reference fixtures.
+- Original and harmonized metadata retained side by side.
+- No accuracy-based channel mapping on evaluation data.</x:v>
+      </x:c>
+      <x:c r="I16" s="114" t="str">
+        <x:v>- matched, missing, duplicate, and ambiguous channel counts
+- coordinate transform residual
+- unit and reference conversion identity
+- geometry availability fraction
+- roundtrip and provenance hashes</x:v>
+      </x:c>
+      <x:c r="J16" s="114" t="str">
+        <x:v>Acceptance: Proceed only when transforms are deterministic, reversible where promised, hash-bound, and refuse ambiguous geometry or reference instead of guessing.
+Stop: Keep geometry unavailable if source coordinates or frames cannot be proven; do not infer device equivalence from channel names alone.</x:v>
+      </x:c>
+      <x:c r="K16" s="114" t="str">
+        <x:v>Loops: 29
+External: none</x:v>
+      </x:c>
+      <x:c r="L16" s="114" t="str">
+        <x:v>Planning only. Synthetic fixture work or real-header inspection requires a separately scoped Loop 36 authorization.</x:v>
+      </x:c>
+      <x:c r="M16" s="114" t="str">
+        <x:v>Dependency-free core, optional MNE only inside adapters, one thread, 16 MiB artifacts, and zero signal-array reads for metadata mode.</x:v>
+      </x:c>
+      <x:c r="N16" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O16" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P16" s="150" t="str">
+        <x:v>https://mne.tools/stable/generated/mne.filter.resample.html
+https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="138" customHeight="1">
+      <x:c r="A17" s="126" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B17" s="129" t="str">
+        <x:v>P4 - Reproducibility And Local Deployment</x:v>
+      </x:c>
+      <x:c r="C17" s="114" t="str">
+        <x:v>BIDS Derivative And Provenance Export</x:v>
+      </x:c>
+      <x:c r="D17" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E17" s="114" t="str">
+        <x:v>Can caches, tokens, reports, and split metadata be exported as inspectable derivatives without copying raw data or losing source identity?</x:v>
+      </x:c>
+      <x:c r="F17" s="114" t="str">
+        <x:v>A standards-aware derivative makes external reproduction easier while preserving the local-first raw-data boundary.</x:v>
+      </x:c>
+      <x:c r="G17" s="114" t="str">
+        <x:v>Build: BIDS-derivative export plan, dataset description, GeneratedBy and SourceDatasets provenance, sidecars, path validator, and no-raw-copy audit.
+Research: BIDS derivative and electrophysiology mapping note identifying standard fields, extension fields, and unsupported claims.</x:v>
+      </x:c>
+      <x:c r="H17" s="114" t="str">
+        <x:v>Data: Tiny synthetic caches and reports only for the interface proof; no real raw file is copied, packaged, or redistributed.
+Controls:
+- Source, configuration, split, payload, and code hashes retained.
+- Path traversal, subject collision, overwrite, and raw-copy refusals.
+- Roundtrip validation from derivative metadata back to source artifact identity.</x:v>
+      </x:c>
+      <x:c r="I17" s="114" t="str">
+        <x:v>- required and unavailable field counts
+- source-to-derivative hash coverage
+- roundtrip identity
+- input, output, and duplicated bytes
+- raw-data copy count</x:v>
+      </x:c>
+      <x:c r="J17" s="114" t="str">
+        <x:v>Acceptance: Pass as a synthetic derivative interface only when provenance is complete, extension fields are namespaced, no raw payload is copied, and all generated files remain under cap.
+Stop: Do not claim BIDS compliance for unsupported fields or invent source metadata; export an explicit warning or refuse.</x:v>
+      </x:c>
+      <x:c r="K17" s="114" t="str">
+        <x:v>Loops: 36
+External: none</x:v>
+      </x:c>
+      <x:c r="L17" s="114" t="str">
+        <x:v>Planning only. Export implementation and generated fixtures require a separate Loop 37 authorization.</x:v>
+      </x:c>
+      <x:c r="M17" s="114" t="str">
+        <x:v>One thread, one worker, dependency-free metadata core, 16 MiB generated derivative tree, and zero real-data bytes.</x:v>
+      </x:c>
+      <x:c r="N17" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O17" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P17" s="150" t="str">
+        <x:v>https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="138" customHeight="1">
+      <x:c r="A18" s="126" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B18" s="129" t="str">
+        <x:v>P4 - Reproducibility And Local Deployment</x:v>
+      </x:c>
+      <x:c r="C18" s="114" t="str">
+        <x:v>Neural Data Privacy And Lifecycle</x:v>
+      </x:c>
+      <x:c r="D18" s="135" t="str">
+        <x:v>P0 / M</x:v>
+      </x:c>
+      <x:c r="E18" s="114" t="str">
+        <x:v>Can the project prove where sensitive recordings and embeddings live, who can access them, and how they are retained or deleted?</x:v>
+      </x:c>
+      <x:c r="F18" s="114" t="str">
+        <x:v>Neural signals and embeddings can carry identity information; local-first behavior needs verifiable lifecycle controls, not just a promise.</x:v>
+      </x:c>
+      <x:c r="G18" s="114" t="str">
+        <x:v>Build: Data inventory, sensitivity labels, local path policy, retention and deletion receipts, redaction scanner, and privacy threat model.
+Research: NIST-aligned privacy risk map plus EEG identity-risk review and contributor guidance.</x:v>
+      </x:c>
+      <x:c r="H18" s="114" t="str">
+        <x:v>Data: Repository metadata and synthetic fixtures only; no identity attack, real embedding export, or participant re-identification experiment.
+Controls:
+- Tracked-history and staged-secret scans.
+- Raw, derived, report, log, temporary, and backup lifecycle paths tested separately.
+- Absolute paths, participant aliases, timestamps, and device serials redacted by default.
+- Deletion receipt verifies expected paths without destructive broad cleanup.</x:v>
+      </x:c>
+      <x:c r="I18" s="114" t="str">
+        <x:v>- sensitive path and field coverage
+- redaction recall on generated fixtures
+- retention-policy violations
+- tracked neural payload bytes
+- verified deletion and unresolved copy counts</x:v>
+      </x:c>
+      <x:c r="J18" s="114" t="str">
+        <x:v>Acceptance: Pass when every artifact class has an owner, location, retention rule, redaction behavior, and verifiable local deletion path, with zero tracked neural payloads.
+Stop: Block data-sharing or release claims when lifecycle ownership, consent, license, or deletion cannot be proven.</x:v>
+      </x:c>
+      <x:c r="K18" s="114" t="str">
+        <x:v>Loops: 37
+External: none</x:v>
+      </x:c>
+      <x:c r="L18" s="114" t="str">
+        <x:v>Planning only. No real identity analysis or destructive cleanup is authorized.</x:v>
+      </x:c>
+      <x:c r="M18" s="114" t="str">
+        <x:v>Standard-library scanners where possible, one thread, one worker, 8 MiB reports, no real signal reads, and no network upload.</x:v>
+      </x:c>
+      <x:c r="N18" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O18" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P18" s="150" t="str">
+        <x:v>https://arxiv.org/abs/2412.09854
+https://www.nist.gov/privacy-framework/privacy-framework</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="138" customHeight="1">
+      <x:c r="A19" s="126" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B19" s="129" t="str">
+        <x:v>P4 - Reproducibility And Local Deployment</x:v>
+      </x:c>
+      <x:c r="C19" s="114" t="str">
+        <x:v>Cross-Machine Reproducibility Matrix</x:v>
+      </x:c>
+      <x:c r="D19" s="135" t="str">
+        <x:v>P0 / M</x:v>
+      </x:c>
+      <x:c r="E19" s="114" t="str">
+        <x:v>Which outputs are bitwise stable across supported Python and operating-system combinations, and which require explicit numerical tolerances?</x:v>
+      </x:c>
+      <x:c r="F19" s="114" t="str">
+        <x:v>Open-source users need to know whether a mismatch is a bug, a backend difference, or an unsupported environment.</x:v>
+      </x:c>
+      <x:c r="G19" s="114" t="str">
+        <x:v>Build: CI matrix, environment manifest, golden semantic hashes, tolerance registry, failure diagnostics, and artifact reproducibility report.
+Research: Reproducibility policy distinguishing semantic identity, numerical compatibility, timing comparison, and environment-specific evidence.</x:v>
+      </x:c>
+      <x:c r="H19" s="114" t="str">
+        <x:v>Data: Dependency-free tests and authorized synthetic fixtures only; no real or consumed cache, target, or model training access.
+Controls:
+- At least macOS and Linux where CI capacity permits.
+- Base and optional-neuro environments kept separate.
+- Bitwise semantic fields tested separately from floating payload tolerances.
+- Tolerance changes require a recorded failing environment and explicit decision.</x:v>
+      </x:c>
+      <x:c r="I19" s="114" t="str">
+        <x:v>- matrix pass rate
+- semantic hash agreement
+- maximum numerical drift
+- runtime and peak RSS by environment
+- artifact and dependency size</x:v>
+      </x:c>
+      <x:c r="J19" s="114" t="str">
+        <x:v>Acceptance: Pass when every supported cell either reproduces the registered contract or fails with an explicit unsupported reason; no tolerance is widened after hidden evaluation access.
+Stop: Do not claim cross-machine reproducibility from one host; quarantine platform-specific drift until diagnosed and documented.</x:v>
+      </x:c>
+      <x:c r="K19" s="114" t="str">
+        <x:v>Loops: 37
+External: ci_capacity_and_optional_environment_review</x:v>
+      </x:c>
+      <x:c r="L19" s="114" t="str">
+        <x:v>Planning only. New matrix jobs, fixtures, and optional installs require a separate bounded Loop 39 change.</x:v>
+      </x:c>
+      <x:c r="M19" s="114" t="str">
+        <x:v>One thread per job, no large cache, 32 MiB job artifacts, and existing CI time limits.</x:v>
+      </x:c>
+      <x:c r="N19" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O19" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P19" s="150" t="str">
+        <x:v>https://arxiv.org/abs/2404.15319
+https://arxiv.org/abs/1810.03993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="138" customHeight="1">
+      <x:c r="A20" s="126" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B20" s="129" t="str">
+        <x:v>P4 - Reproducibility And Local Deployment</x:v>
+      </x:c>
+      <x:c r="C20" s="114" t="str">
+        <x:v>Edge Runtime Packaging Gate</x:v>
+      </x:c>
+      <x:c r="D20" s="135" t="str">
+        <x:v>P2 / L</x:v>
+      </x:c>
+      <x:c r="E20" s="114" t="str">
+        <x:v>Can one already qualified frozen pipeline be packaged for an edge runtime while preserving outputs, state, timestamps, and measured resource behavior?</x:v>
+      </x:c>
+      <x:c r="F20" s="114" t="str">
+        <x:v>Packaging is meaningful only after correctness and local runtime gates; it can then reveal startup, delegate, memory-planning, and operator support constraints.</x:v>
+      </x:c>
+      <x:c r="G20" s="114" t="str">
+        <x:v>Build: Single-backend export contract, operator audit, packaged artifact validator, reference comparison, and startup/runtime/RSS report.
+Research: ExecuTorch or alternative edge-runtime decision note based on supported operators and target platform, not trend appeal.</x:v>
+      </x:c>
+      <x:c r="H20" s="114" t="str">
+        <x:v>Data: Frozen target-free synthetic fixture only; no real data, consumed targets, retraining, or architecture changes.
+Controls:
+- Reference eager path retained.
+- Exact frame, timestamp, decoder trace, and state comparison.
+- Fallback and undelegated operator counts reported.
+- Package size, load time, steady-state time, and peak memory separated.</x:v>
+      </x:c>
+      <x:c r="I20" s="114" t="str">
+        <x:v>- behavioral identity and numerical drift
+- package and tensor bytes
+- startup, producer, decoder, and full-pipeline latency
+- peak RSS and planned memory
+- delegated, fallback, and unsupported operator counts</x:v>
+      </x:c>
+      <x:c r="J20" s="114" t="str">
+        <x:v>Acceptance: Adopt a package only if a previously qualified reference behavior is preserved, unsupported fallback is zero or explicitly accepted, and a preregistered deployment benefit passes.
+Stop: Park packaging if it requires retraining, architecture changes, hidden fallback, or more resources without a measured benefit; do not call desktop packaging portable hardware.</x:v>
+      </x:c>
+      <x:c r="K20" s="114" t="str">
+        <x:v>Loops: 39
+External: explicit_loop24_result_or_hold, separate_edge_runtime_authorization</x:v>
+      </x:c>
+      <x:c r="L20" s="114" t="str">
+        <x:v>Planning only. No export, conversion, optional edge dependency, inference, profiler, or package generation is authorized.</x:v>
+      </x:c>
+      <x:c r="M20" s="114" t="str">
+        <x:v>One backend, one thread, one worker, 32 MiB generated package and reports, 60 seconds per measurement worker, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N20" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O20" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P20" s="150" t="str">
+        <x:v>https://docs.pytorch.org/executorch/stable/index.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="138" customHeight="1">
+      <x:c r="A21" s="126" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B21" s="129" t="str">
+        <x:v>P5 - Live Translation And Release</x:v>
+      </x:c>
+      <x:c r="C21" s="114" t="str">
+        <x:v>RW3 Stream-To-NeuroToken Integration</x:v>
+      </x:c>
+      <x:c r="D21" s="135" t="str">
+        <x:v>P1 / L</x:v>
+      </x:c>
+      <x:c r="E21" s="114" t="str">
+        <x:v>Can an authorized source-chunk replay pass through causal preprocessing into NeuroTokenCache without timestamp, gap, state, or schedule drift?</x:v>
+      </x:c>
+      <x:c r="F21" s="114" t="str">
+        <x:v>This joins the acquisition contract to the model interface while keeping replay mechanics separate from hardware and decoding claims.</x:v>
+      </x:c>
+      <x:c r="G21" s="114" t="str">
+        <x:v>Build: Source-chunk to preprocessing to NeuroToken adapter, resume state, gap propagation, schedule matrix, and end-to-end provenance hashes.
+Research: Clock-domain and latency ledger mapping source, corrected, arrival, preprocessing, token, decoder, and render times.</x:v>
+      </x:c>
+      <x:c r="H21" s="114" t="str">
+        <x:v>Data: Only future authorized target-free RW3 synthetic replay; no BrainFlow, LSL, PyXDF, socket, live source, hardware, or real recording unless separately staged later.
+Controls:
+- Canonical offline path and every authorized chunk schedule.
+- Gap, duplicate, reorder, reconnect, and reset fixtures.
+- Raw, corrected, and arrival clocks kept distinct.
+- Resume from serialized state compared with uninterrupted replay.</x:v>
+      </x:c>
+      <x:c r="I21" s="114" t="str">
+        <x:v>- source, preprocessing, and token semantic hash agreement
+- timestamp and valid-length identity
+- gap and anomaly propagation
+- state bytes and resume identity
+- stage runtime, scheduling delay, peak RSS, and output bytes</x:v>
+      </x:c>
+      <x:c r="J21" s="114" t="str">
+        <x:v>Acceptance: Pass only when every authorized schedule and resume path preserves canonical tokens and provenance, and anomalies remain explicit rather than repaired silently.
+Stop: Any timestamp collapse, silent interpolation, lost anomaly, schedule-dependent token, or state mismatch parks integration before live or device work.</x:v>
+      </x:c>
+      <x:c r="K21" s="114" t="str">
+        <x:v>Loops: 25, 37, 39
+External: explicit_rw3_stage_a_authorization_and_closeout, separate_loop41_authorization</x:v>
+      </x:c>
+      <x:c r="L21" s="114" t="str">
+        <x:v>Planning only. This roadmap does not authorize RW3 Stage A or any adapter, fixture, source-chunk, stream, or token runtime.</x:v>
+      </x:c>
+      <x:c r="M21" s="114" t="str">
+        <x:v>One thread and worker, 32 MiB generated target-free artifacts, 60 seconds per worker, and 1 GiB peak RSS.</x:v>
+      </x:c>
+      <x:c r="N21" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O21" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P21" s="150" t="str">
+        <x:v>https://labstreaminglayer.readthedocs.io/info/time_synchronization.html
+https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="138" customHeight="1">
+      <x:c r="A22" s="126" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B22" s="129" t="str">
+        <x:v>P5 - Live Translation And Release</x:v>
+      </x:c>
+      <x:c r="C22" s="114" t="str">
+        <x:v>One-Device Qualification</x:v>
+      </x:c>
+      <x:c r="D22" s="135" t="str">
+        <x:v>P2 / L</x:v>
+      </x:c>
+      <x:c r="E22" s="114" t="str">
+        <x:v>Can one named device preserve declared channels, units, clocks, packets, and privacy from recorded replay through a bounded local session?</x:v>
+      </x:c>
+      <x:c r="F22" s="114" t="str">
+        <x:v>One measured device is more credible than broad compatibility claims based on SDK imports or vendor tables.</x:v>
+      </x:c>
+      <x:c r="G22" s="114" t="str">
+        <x:v>Build: Device descriptor, consent and locality checklist, recorded-versus-live equivalence packet, loss/reconnect stress report, and compatibility-level decision.
+Research: Device-specific timestamp, unit, reference, geometry, firmware, and data-retention review.</x:v>
+      </x:c>
+      <x:c r="H22" s="114" t="str">
+        <x:v>Data: One separately approved board or headset, one local synthetic or consented non-sensitive qualification session, and no decoding target unless separately approved.
+Controls:
+- SDK synthetic or playback source before physical hardware.
+- Recorded and live paths compared under the same source-chunk contract.
+- Packet loss, reconnect, clock reset, and buffer-drain stress cases.
+- Network-off and local-storage audit.</x:v>
+      </x:c>
+      <x:c r="I22" s="114" t="str">
+        <x:v>- channel, unit, rate, and packet identity
+- clock offset, jitter, gaps, duplicates, and reorder counts
+- capture-to-arrival timing boundary
+- runtime, peak RSS, bytes, and dropped samples
+- privacy and retention violations</x:v>
+      </x:c>
+      <x:c r="J22" s="114" t="str">
+        <x:v>Acceptance: Qualify only the named device, firmware, transport, host, and tested compatibility level; connectivity alone cannot qualify signal quality or decoding.
+Stop: Park physical qualification on ambiguous consent, cloud dependence, hidden timestamps, unstable identity, unsafe retention, or failed replay equivalence.</x:v>
+      </x:c>
+      <x:c r="K22" s="114" t="str">
+        <x:v>Loops: 29, 38, 41
+External: explicit_device_stage_authorization, ethics_consent_and_retention_approval</x:v>
+      </x:c>
+      <x:c r="L22" s="114" t="str">
+        <x:v>Planning only. No SDK import, device discovery, socket, stream, board, hardware, or recording session is authorized.</x:v>
+      </x:c>
+      <x:c r="M22" s="114" t="str">
+        <x:v>One device, one host, one thread for analysis, exact session and byte cap in a future packet, 32 MiB derived artifacts, and no cloud upload.</x:v>
+      </x:c>
+      <x:c r="N22" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O22" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P22" s="150" t="str">
+        <x:v>https://labstreaminglayer.readthedocs.io/info/time_synchronization.html
+https://www.nist.gov/privacy-framework/privacy-framework</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="138" customHeight="1">
+      <x:c r="A23" s="126" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B23" s="129" t="str">
+        <x:v>P5 - Live Translation And Release</x:v>
+      </x:c>
+      <x:c r="C23" s="114" t="str">
+        <x:v>Independent Reproduction Challenge</x:v>
+      </x:c>
+      <x:c r="D23" s="135" t="str">
+        <x:v>P1 / M</x:v>
+      </x:c>
+      <x:c r="E23" s="114" t="str">
+        <x:v>Can an independent contributor reproduce a bounded claim from documented inputs without private guidance or sharing neural recordings?</x:v>
+      </x:c>
+      <x:c r="F23" s="114" t="str">
+        <x:v>Independent reproduction tests the developer experience, evidence contracts, and contribution path more honestly than another maintainer-run demo.</x:v>
+      </x:c>
+      <x:c r="G23" s="114" t="str">
+        <x:v>Build: Challenge packet, fixture manifest, expected semantic checks, environment capture, blinded result card, and discrepancy triage workflow.
+Research: Reproduction protocol distinguishing exact replication, computational reproduction, and extension on contributor-owned data.</x:v>
+      </x:c>
+      <x:c r="H23" s="114" t="str">
+        <x:v>Data: Public code plus tiny synthetic fixtures by default; contributors keep any owned EEG local and submit metadata/aggregate reports only.
+Controls:
+- Maintainer and contributor environments recorded independently.
+- Expected results hidden where needed until submission hash freezes.
+- No private recording, secret, absolute path, or participant identifier in the submission.
+- Negative and failed reproductions retained.</x:v>
+      </x:c>
+      <x:c r="I23" s="114" t="str">
+        <x:v>- semantic and numerical reproduction rate
+- setup time and command count
+- environment and warning completeness
+- discrepancy classes
+- contributor artifact bytes and privacy findings</x:v>
+      </x:c>
+      <x:c r="J23" s="114" t="str">
+        <x:v>Acceptance: Pass when at least one independent environment reproduces the registered artifact contract and a discrepancy, if any, is resolved or documented without moving the claim boundary.
+Stop: Do not promote a result that depends on undocumented maintainer state, private hand edits, leaked data, or an unreviewed tolerance change.</x:v>
+      </x:c>
+      <x:c r="K23" s="114" t="str">
+        <x:v>Loops: 37, 38, 39
+External: community_participant_and_challenge_review</x:v>
+      </x:c>
+      <x:c r="L23" s="114" t="str">
+        <x:v>Planning only. No outreach, external data exchange, or challenge execution is authorized by the roadmap file.</x:v>
+      </x:c>
+      <x:c r="M23" s="114" t="str">
+        <x:v>Tiny public fixtures only, one-thread reference commands, 32 MiB submission cap, and no neural recording upload.</x:v>
+      </x:c>
+      <x:c r="N23" s="141" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O23" s="147" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P23" s="150" t="str">
+        <x:v>https://arxiv.org/abs/2404.15319
+https://arxiv.org/abs/1810.03993
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="138" customHeight="1">
+      <x:c r="A24" s="127" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B24" s="130" t="str">
+        <x:v>P5 - Live Translation And Release</x:v>
+      </x:c>
+      <x:c r="C24" s="115" t="str">
+        <x:v>Claim Promotion And Release Decision</x:v>
+      </x:c>
+      <x:c r="D24" s="136" t="str">
+        <x:v>P0 / M</x:v>
+      </x:c>
+      <x:c r="E24" s="115" t="str">
+        <x:v>Which engineering and scientific claims have earned promotion into a release, and which remain fixture-backed, negative, unavailable, parked, or killed?</x:v>
+      </x:c>
+      <x:c r="F24" s="115" t="str">
+        <x:v>The roadmap should end in an evidence decision, not an accumulation of features or optimistic wording.</x:v>
+      </x:c>
+      <x:c r="G24" s="115" t="str">
+        <x:v>Build: Machine-readable evidence matrix, model and dataset cards, release checklist, claim diff, risk register, and signed proceed, park, or kill decision.
+Research: Release and reporting policy grounded in model cards, datasheets, privacy, licensing, and reproducibility evidence.</x:v>
+      </x:c>
+      <x:c r="H24" s="115" t="str">
+        <x:v>Data: Artifact-only synthesis of closed loop reports; no raw, consumed, target, model, training, device, or network operation.
+Controls:
+- Every claim links to a cohort, split, comparator, uncertainty, resource, and access record.
+- Negative results and unavailable fields remain visible.
+- Engineering capability and scientific performance are stated separately.
+- Clinical, arbitrary-thought, portable-hardware, and real-time claims default to unavailable.</x:v>
+      </x:c>
+      <x:c r="I24" s="115" t="str">
+        <x:v>- claims promoted, parked, killed, and unavailable
+- evidence-card completeness
+- unresolved privacy, license, security, and reproducibility blockers
+- artifact and documentation link integrity
+- release test and CI status</x:v>
+      </x:c>
+      <x:c r="J24" s="115" t="str">
+        <x:v>Acceptance: Release only the subset whose exact evidence cards, licenses, privacy controls, independent reproduction, tests, and claim language pass; all other claims stay explicitly unestablished.
+Stop: Hold the release rather than soften a failed gate, omit a negative comparator, or convert an engineering interface proof into a decoding claim.</x:v>
+      </x:c>
+      <x:c r="K24" s="115" t="str">
+        <x:v>Loops: 38, 39, 43
+External: maintainer_release_decision</x:v>
+      </x:c>
+      <x:c r="L24" s="115" t="str">
+        <x:v>Planning only. The future release decision cannot retroactively authorize or upgrade any earlier experiment.</x:v>
+      </x:c>
+      <x:c r="M24" s="115" t="str">
+        <x:v>Artifact-only review, one thread, one worker, 16 MiB generated reports, zero data/model/training/device access, and complete link/test checks.</x:v>
+      </x:c>
+      <x:c r="N24" s="142" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O24" s="148" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P24" s="151" t="str">
+        <x:v>https://arxiv.org/abs/1810.03993
+https://arxiv.org/abs/1803.09010
+https://www.nist.gov/privacy-framework/privacy-framework</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:P2"/>
+    <x:mergeCell ref="A3:P3"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="O5:O24">
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Parked"/>
+    <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Not Started"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="O5:O24">
+      <x:formula1>'Lists'!$A$2:$A$7</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13187cb046984594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdfb0612bac6149bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R666c2c00fe264aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R41e0dd2b772f48a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rbfa8f65597664bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R1d086a245db94d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd336d92b3aa644de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R1e86f534998649e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R46af1cd3fe6d4a1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R888ca8495f03404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R42a5af0d63a44da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5b7d41fa55a84fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R81461bfe100a4f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R6afdf17f26054df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R329ea3726d9c4d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R4246c86e85204ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R720c9e369e134ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R679be4d6f96540db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R2e3545036f97479d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -770,7 +770,7 @@
         <x:color rgb="FF1B5E20"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEFD8"/>
         </x:patternFill>
       </x:fill>
@@ -781,7 +781,7 @@
         <x:color rgb="FF8A4B08"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8D5"/>
         </x:patternFill>
       </x:fill>
@@ -792,7 +792,7 @@
         <x:color rgb="FF8B1E1E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4D7D7"/>
         </x:patternFill>
       </x:fill>
@@ -803,7 +803,7 @@
         <x:color rgb="FF455A64"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECEFF1"/>
         </x:patternFill>
       </x:fill>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bc7bfc1a36c4bd6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4ea256989e024d39"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1333,12 +1333,12 @@
       <x:c r="G7" s="29" t="str"/>
       <x:c r="H7" s="29" t="str"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 24 preregistered</x:v>
+        <x:v>Loop 24 authorized, no runtime</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1360,7 +1360,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 remains preregistered and unauthorized; RW3 Stage A remains separately unauthorized. Loops 25-44 are a planning-only queue on the Loops 25-44 sheet, and every execution flag is false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 has a separate target-free authorization that takes effect only after its tested commit is pushed; no runtime exists yet. RW3 Stage A remains separately unauthorized. Loops 25-44 remain a planning-only queue and every execution flag is false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8753ebcdc64a23"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8220f52f65f46b1"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6672840ab0be4b91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ec29afa550440e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3958,16 +3958,34 @@
         <x:v>Commit 186bb6f; contract SHA-256 58e9d5407fef9419bc3bb0dc8cd3fa68d36dd238cb636d2f833dd9c5c6c3ae5d; 3 candidates; seeds 2401/2402; 12 balanced selection rounds; 30 refusals; 9 invariants; zero fixture/checkpoint/candidate/inference/training/RW3 access.</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="37"/>
-      <x:c r="B36" s="12"/>
-      <x:c r="C36" s="12"/>
-      <x:c r="D36" s="12"/>
-      <x:c r="E36" s="12"/>
-      <x:c r="F36" s="12"/>
-      <x:c r="G36" s="12"/>
-      <x:c r="H36" s="12"/>
-      <x:c r="I36" s="12"/>
+    <x:row r="36" ht="112" customHeight="1">
+      <x:c r="A36" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>24-AUTH</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>Authorize frozen target-free Loop 24 only; no runtime yet</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
+        <x:v>The user explicitly authorized Loop 24 while mentioning real data and training. Preserve the preregistered experiment by authorizing only its target-free synthetic fixture, frozen checkpoint, three candidates, selection, conditional qualification, reports, and CLI after a tested authorization-only commit is pushed. Route real-data and training ambition to Loops 25-27.</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>docs/LOOP_24_AUTHORIZATION_DECISION.md; registries/loop24_authorization_decision.v0.json</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>Cheick + Codex</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>Push authorization-only commit; confirm CI; execute exact Loop 24</x:v>
+      </x:c>
+      <x:c r="I36" s="12" t="str">
+        <x:v>The immutable 186bb6f contract retains false flags and its original hash. The separate decision permits only target-free fixture generation, frozen checkpoint validation, the three registered candidates, selection, conditional qualification, reports, and CLI work. Real/consumed data, targets, labels, text, training, new models, energy, RW3, devices, hardware, and Loops 25-44 remain false. Authorization-only counters and runtime outputs are zero.</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37"/>
@@ -5793,7 +5811,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a727d5a43b49e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8d2a5507f4444c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6654,7 +6672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc75f39a821bf4b1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91672c34250d49ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7132,21 +7150,21 @@
         <x:v>Review docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md and registries/rw3_stage_a_authorization_request.v0.json. Confirm the c3d1f01 contract hash, 90 proposed cases, 30 refusals, one-thread caps, forbidden work, and authorization-only commit sequence. Decide explicitly to authorize Stage A only, amend the packet, or hold. General continuation is not authorization. Do not implement anything; BrainFlow, LSL, PyXDF, sockets, devices, real or consumed data, targets, models, training, and Stages B-D remain unauthorized.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="126" customHeight="1">
+    <x:row r="33" ht="96" customHeight="1">
       <x:c r="A33" s="12" t="str">
-        <x:v>Loop24-Decision</x:v>
+        <x:v>Loop24-Execute</x:v>
       </x:c>
       <x:c r="B33" s="12" t="str">
-        <x:v>Decide Local Precision / Runtime Only</x:v>
+        <x:v>Implement Authorized Target-Free Precision / Runtime Gate</x:v>
       </x:c>
       <x:c r="C33" s="12" t="str">
-        <x:v>Review docs/LOOP_24_PRECISION_RUNTIME_PREREGISTRATION.md and registries/local_precision_runtime_contract.v0.json. Confirm the three exact candidates, frozen hashes, fresh target-free seeds 2401/2402, 12 balanced timing rounds, behavior/resource gates, 30 refusals, and false execution flags. Decide explicitly to use the exact authorization sentence, amend, or hold. General continuation is not authorization. Do not implement a candidate, generate a fixture, load or convert the checkpoint, run inference, benchmark, profile, or measure energy. Do not authorize RW3 Stage A, data access, or model training.</x:v>
+        <x:v>Only after the authorization-only commit is pushed and CI is green, implement exactly the frozen float32 eager, explicit CPU float16, and dynamic-qint8 QNNPACK candidates; generate target-free seed-2401 selection data; run 12 balanced rounds; freeze the candidate decision; and open seed 2402 once only if a nonreference replacement qualifies. Keep one thread and every cap/counter. Do not access real or consumed data, targets, labels, text, training, energy, RW3, devices, or hardware.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a7f813ede6044c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5b5a16fafac4f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7370,7 +7388,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. Loop 24 contract 186bb6f and RW3 Stage A packet 163ff2f await separate explicit decisions; all execution/authorization flags are false and no runtime exists. RW4/S20 remains blocked.</x:v>
+        <x:v>Parallel to Loop 24. Its contract remains frozen at 186bb6f; a separate target-free authorization is recorded with no runtime yet. RW3 Stage A remains unauthorized at 163ff2f, and RW4/S20 remains blocked. Real data, targets, training, energy, streams, devices, and hardware are not authorized.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -7712,7 +7730,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d3d437b8a164513"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R891009e11fe74ff3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7761,7 +7779,7 @@
     </x:row>
     <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Planning only. Current gate: Loop 24 preregistered. RW3 Stage A is separate. No download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
+        <x:v>Planning only. Current gate: Loop 24 authorized for its exact target-free scope, with no runtime yet. RW3 Stage A is separate. No Loop 25-44 download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -9122,7 +9140,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13187cb046984594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57e89236c1cc43d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R42a5af0d63a44da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R5b7d41fa55a84fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R81461bfe100a4f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R6afdf17f26054df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R329ea3726d9c4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R4246c86e85204ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R720c9e369e134ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R679be4d6f96540db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R2e3545036f97479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R81a04430aee745d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R45293fd42dc348c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R1261d47fa7bc4e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rb3e01c027b074430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R91dc54113ed34043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R6d876237631d4ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rdf4f847f8c9944f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rf68bca0415f948a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R14a1e216c96d45ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4ea256989e024d39"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10192359031a47fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I29"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1044,7 +1044,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -1338,7 +1338,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 24 authorized, no runtime</x:v>
+        <x:v>Loop 24 parked; float32 retained</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1360,7 +1360,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 has a separate target-free authorization that takes effect only after its tested commit is pushed; no runtime exists yet. RW3 Stage A remains separately unauthorized. Loops 25-44 remain a planning-only queue and every execution flag is false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24's frozen target-free run is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A remains unauthorized. Loops 25-44 remain planning-only with execution_authorized=false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8220f52f65f46b1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35b6cb671514a41"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ec29afa550440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f82a249cd094974"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3958,45 +3958,63 @@
         <x:v>Commit 186bb6f; contract SHA-256 58e9d5407fef9419bc3bb0dc8cd3fa68d36dd238cb636d2f833dd9c5c6c3ae5d; 3 candidates; seeds 2401/2402; 12 balanced selection rounds; 30 refusals; 9 invariants; zero fixture/checkpoint/candidate/inference/training/RW3 access.</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="112" customHeight="1">
-      <x:c r="A36" s="37" t="n">
+    <x:row r="36" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A36" s="40" t="n">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="B36" s="12" t="str">
+      <x:c r="B36" s="14" t="str">
         <x:v>24-AUTH</x:v>
       </x:c>
-      <x:c r="C36" s="12" t="str">
+      <x:c r="C36" s="14" t="str">
         <x:v>Authorize frozen target-free Loop 24 only; no runtime yet</x:v>
       </x:c>
-      <x:c r="D36" s="12" t="str">
+      <x:c r="D36" s="14" t="str">
         <x:v>The user explicitly authorized Loop 24 while mentioning real data and training. Preserve the preregistered experiment by authorizing only its target-free synthetic fixture, frozen checkpoint, three candidates, selection, conditional qualification, reports, and CLI after a tested authorization-only commit is pushed. Route real-data and training ambition to Loops 25-27.</x:v>
       </x:c>
-      <x:c r="E36" s="12" t="str">
+      <x:c r="E36" s="14" t="str">
         <x:v>docs/LOOP_24_AUTHORIZATION_DECISION.md; registries/loop24_authorization_decision.v0.json</x:v>
       </x:c>
-      <x:c r="F36" s="12" t="str">
+      <x:c r="F36" s="14" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="G36" s="12" t="str">
+      <x:c r="G36" s="14" t="str">
         <x:v>Cheick + Codex</x:v>
       </x:c>
-      <x:c r="H36" s="12" t="str">
+      <x:c r="H36" s="14" t="str">
         <x:v>Push authorization-only commit; confirm CI; execute exact Loop 24</x:v>
       </x:c>
-      <x:c r="I36" s="12" t="str">
+      <x:c r="I36" s="14" t="str">
         <x:v>The immutable 186bb6f contract retains false flags and its original hash. The separate decision permits only target-free fixture generation, frozen checkpoint validation, the three registered candidates, selection, conditional qualification, reports, and CLI work. Real/consumed data, targets, labels, text, training, new models, energy, RW3, devices, hardware, and Loops 25-44 remain false. Authorization-only counters and runtime outputs are zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="37"/>
-      <x:c r="B37" s="12"/>
-      <x:c r="C37" s="12"/>
-      <x:c r="D37" s="12"/>
-      <x:c r="E37" s="12"/>
-      <x:c r="F37" s="12"/>
-      <x:c r="G37" s="12"/>
-      <x:c r="H37" s="12"/>
-      <x:c r="I37" s="12"/>
+    <x:row r="37" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A37" s="40" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>24-RUN</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="str">
+        <x:v>Park precision candidates; retain float32 reference</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>All 12 balanced timing rounds completed, but total runtime was 65.154951 s against the frozen 60 s cap. Float16 was smaller but slower; dynamic QNNPACK qint8 was smaller but changed behavior and was slower. The protocol therefore requires parking without a rerun.</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>docs/LOOP_24_LOCAL_PRECISION_RUNTIME.md</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H37" s="14" t="str">
+        <x:v>Loop 25 preregistration decision</x:v>
+      </x:c>
+      <x:c r="I37" s="14" t="str">
+        <x:v>Seed 2401 consumed; seed 2402 unopened; float32 retained. Output 125,934 B; fixture + output 262,822 B; max worker RSS 222,248,960 B; no real data, targets, labels, training, energy, RW3, or hardware access.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37"/>
@@ -5811,7 +5829,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8d2a5507f4444c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0b903fe4104e17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6641,6 +6659,35 @@
       </x:c>
       <x:c r="I28" s="12" t="str">
         <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A29" s="14" t="str">
+        <x:v>R28</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>Precision / runtime overclaim</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>A smaller serialized candidate is promoted despite slower full-pipeline runtime, changed behavior, an incomplete timing protocol, or a consumed selection split.</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>Keep the exact behavior, numerical, runtime, state, payload, RSS, and total-runtime gates conjunctive; retain float32 on any failure; require a fresh preregistration before new execution.</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>A report calls float16 or qint8 a replacement, cites payload size as speed, reruns seed 2401, opens seed 2402 without a new authorization, or hides the 65.154951-second cap failure.</x:v>
+      </x:c>
+      <x:c r="H29" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I29" s="14" t="str">
+        <x:v>Watching</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6672,7 +6719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91672c34250d49ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88e5a689bf0c4d8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7150,21 +7197,32 @@
         <x:v>Review docs/RW3_STAGE_A_AUTHORIZATION_PACKET.md and registries/rw3_stage_a_authorization_request.v0.json. Confirm the c3d1f01 contract hash, 90 proposed cases, 30 refusals, one-thread caps, forbidden work, and authorization-only commit sequence. Decide explicitly to authorize Stage A only, amend the packet, or hold. General continuation is not authorization. Do not implement anything; BrainFlow, LSL, PyXDF, sockets, devices, real or consumed data, targets, models, training, and Stages B-D remain unauthorized.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="96" customHeight="1">
-      <x:c r="A33" s="12" t="str">
+    <x:row r="33" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A33" s="14" t="str">
         <x:v>Loop24-Execute</x:v>
       </x:c>
-      <x:c r="B33" s="12" t="str">
-        <x:v>Implement Authorized Target-Free Precision / Runtime Gate</x:v>
-      </x:c>
-      <x:c r="C33" s="12" t="str">
-        <x:v>Only after the authorization-only commit is pushed and CI is green, implement exactly the frozen float32 eager, explicit CPU float16, and dynamic-qint8 QNNPACK candidates; generate target-free seed-2401 selection data; run 12 balanced rounds; freeze the candidate decision; and open seed 2402 once only if a nonreference replacement qualifies. Keep one thread and every cap/counter. Do not access real or consumed data, targets, labels, text, training, energy, RW3, devices, or hardware.</x:v>
+      <x:c r="B33" s="14" t="str">
+        <x:v>Authorized Target-Free Precision / Runtime Gate (Consumed)</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>Historical consumed protocol only. Loop 24 ran once after its authorization-only commit and is now parked. Do not rerun seed 2401 or open seed 2402. Read docs/LOOP_24_LOCAL_PRECISION_RUNTIME.md and make the next action a separate Loop 25 preregistration decision.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" hidden="0" customHeight="1">
+      <x:c r="A34" s="14" t="str">
+        <x:v>Loop25-Decision</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>Preregister Causal Preprocessing Audit</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>Draft Loop 25's causal preprocessing preregistration from the Loop 24 park result. Freeze transform causality, timestamp and valid-sample identity, adversarial chunk schedules, target-free synthetic fixture families, refusal IDs, one-thread resources, and a separate authorization-only commit. Do not generate a fixture, read real or consumed caches, open targets, run a model, train, or execute preprocessing until that decision is explicitly authorized.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5b5a16fafac4f5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce07220506ad44d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7388,7 +7446,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. Its contract remains frozen at 186bb6f; a separate target-free authorization is recorded with no runtime yet. RW3 Stage A remains unauthorized at 163ff2f, and RW4/S20 remains blocked. Real data, targets, training, energy, streams, devices, and hardware are not authorized.</x:v>
+        <x:v>Parallel to Loop 24. Its frozen target-free run is now parked after 65.154951 s exceeded the 60 s cap; float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A remains unauthorized at 163ff2f, and RW4/S20 remains blocked. Real data, targets, training, energy, streams, devices, and hardware are not authorized.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -7730,7 +7788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R891009e11fe74ff3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7a0ffb5648b4a48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7779,7 +7837,7 @@
     </x:row>
     <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Planning only. Current gate: Loop 24 authorized for its exact target-free scope, with no runtime yet. RW3 Stage A is separate. No Loop 25-44 download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
+        <x:v>Planning only. Current gate: Loop 24 is parked after its exact target-free run exceeded the 60-second cap; float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A is separate. No Loop 25-44 download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -9140,7 +9198,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57e89236c1cc43d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81d4a3effe284181"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R81a04430aee745d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R45293fd42dc348c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R1261d47fa7bc4e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rb3e01c027b074430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R91dc54113ed34043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R6d876237631d4ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rdf4f847f8c9944f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rf68bca0415f948a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R14a1e216c96d45ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4c16dcf9bcf4e0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R19ecf83b468041db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R81c0995ef6574e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R181f9faea2014692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra658b34f74324e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1a2522cce51841d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8280e690b23e4ac3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R45140d2c92984bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rf75a048488ac4674"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10192359031a47fb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7f1472f3c7c64031"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I30"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1333,12 +1333,12 @@
       <x:c r="G7" s="29" t="str"/>
       <x:c r="H7" s="29" t="str"/>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="31.5" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 24 parked; float32 retained</x:v>
+        <x:v>Loop 25 preregistered; authorization pending</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1355,12 +1355,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="96" customHeight="1">
+    <x:row r="10" ht="99" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24's frozen target-free run is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A remains unauthorized. Loops 25-44 remain planning-only with execution_authorized=false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. Loop 25 is preregistered at green commit a36d97b; its request is false and seeds 2501/2502 remain unopened. RW3 Stage A remains unauthorized. Loops 26-44 remain planning-only.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35b6cb671514a41"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4fd4b16a5fd4871"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f82a249cd094974"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac693b48ffc44b7b"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4016,16 +4016,34 @@
         <x:v>Seed 2401 consumed; seed 2402 unopened; float32 retained. Output 125,934 B; fixture + output 262,822 B; max worker RSS 222,248,960 B; no real data, targets, labels, training, energy, RW3, or hardware access.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="37"/>
-      <x:c r="B38" s="12"/>
-      <x:c r="C38" s="12"/>
-      <x:c r="D38" s="12"/>
-      <x:c r="E38" s="12"/>
-      <x:c r="F38" s="12"/>
-      <x:c r="G38" s="12"/>
-      <x:c r="H38" s="12"/>
-      <x:c r="I38" s="12"/>
+    <x:row r="38" ht="126" customHeight="1">
+      <x:c r="A38" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>25-REG</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="str">
+        <x:v>Preregister causal preprocessing; keep execution unauthorized</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
+        <x:v>The existing sentence path is offline and future-dependent at filtering, resampling, normalization, and endpoint stages. Freeze one target-free stateful path and every acceptance boundary before creating coefficients or fixtures.</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>docs/LOOP_25_PRIMARY_SOURCE_RESEARCH.md; docs/LOOP_25_CAUSAL_PREPROCESSING_PREREGISTRATION.md; registries/causal_preprocessing_contract.v0.json; docs/LOOP_25_AUTHORIZATION_PACKET.md</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="str">
+        <x:v>Authorize exactly, amend packet, or hold</x:v>
+      </x:c>
+      <x:c r="I38" s="12" t="str">
+        <x:v>Commit a36d97b; CI green; contract SHA-256 42781526225c556d0df54d1b6924fd5d9ecf95578a84c3e3922b6d5c7035050e; 7 schedules; 10 resumes; 3 mutation cuts; 40 refusals; 21 counters; 10 contract + 8 request invariants. authorized_now=false; seeds 2501/2502 unopened; zero runtime/data/target/model/training/RW3/device operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37"/>
@@ -5829,7 +5847,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0b903fe4104e17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R458ed667dfe64244"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6688,6 +6706,35 @@
       </x:c>
       <x:c r="I29" s="14" t="str">
         <x:v>Watching</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="117" customHeight="1">
+      <x:c r="A30" s="12" t="str">
+        <x:v>R29</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>Causal preprocessing</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>Offline zero-phase filtering, future-dependent normalization, endpoint padding, or chunk resets are mislabeled as causal streaming behavior.</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>Require one-pass stateful SOS filtering, phase-locked absolute-index decimation, frozen statistics, and exact schedule/resume/future-mutation checks before any causal claim.</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>An earlier output or state changes when only future samples or chunk boundaries change, or a report hides filter delay as text latency.</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6719,7 +6766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88e5a689bf0c4d8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racd30b423c704bc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7208,21 +7255,21 @@
         <x:v>Historical consumed protocol only. Loop 24 ran once after its authorization-only commit and is now parked. Do not rerun seed 2401 or open seed 2402. Read docs/LOOP_24_LOCAL_PRECISION_RUNTIME.md and make the next action a separate Loop 25 preregistration decision.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="66" hidden="0" customHeight="1">
+    <x:row r="34" ht="126" hidden="0" customHeight="1">
       <x:c r="A34" s="14" t="str">
         <x:v>Loop25-Decision</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Preregister Causal Preprocessing Audit</x:v>
+        <x:v>Decide Frozen Causal Preprocessing Gate</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>Draft Loop 25's causal preprocessing preregistration from the Loop 24 park result. Freeze transform causality, timestamp and valid-sample identity, adversarial chunk schedules, target-free synthetic fixture families, refusal IDs, one-thread resources, and a separate authorization-only commit. Do not generate a fixture, read real or consumed caches, open targets, run a model, train, or execute preprocessing until that decision is explicitly authorized.</x:v>
+        <x:v>Review docs/LOOP_25_AUTHORIZATION_PACKET.md and registries/loop25_authorization_request.v0.json. Confirm green registration commit a36d97b, contract SHA-256 42781526225c556d0df54d1b6924fd5d9ecf95578a84c3e3922b6d5c7035050e, seeds 2501/2502, seven schedules, ten resume cuts, three future-mutation cuts, 40 refusals, 21 counters, the 8 MiB/45-second caps, and every forbidden operation. Decide explicitly to authorize the exact target-free gate, amend the packet, or hold. General continuation is not authorization. Do not implement, generate coefficients or fixtures, open either seed, read data/caches/targets, run models, train, touch RW3, streams, devices, or hardware from this prompt.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce07220506ad44d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a40db3125d4694"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7788,7 +7835,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7a0ffb5648b4a48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfba350fbba1b4e1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7835,9 +7882,9 @@
       <x:c r="O1" s="81"/>
       <x:c r="P1" s="81"/>
     </x:row>
-    <x:row r="2" ht="44" customHeight="1">
+    <x:row r="2" ht="43.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Planning only. Current gate: Loop 24 is parked after its exact target-free run exceeded the 60-second cap; float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A is separate. No Loop 25-44 download, data read, fixture, model, training, stream, board, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 is preregistered at green commit a36d97b and awaits a separate exact authorization decision. Its request is false; seeds 2501/2502 are unopened; no fixture, coefficients, transform, partition, CLI, or runtime exists. Loop 24 is parked, RW3 Stage A is separate, and no data/model/training/stream/device/hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -7855,9 +7902,9 @@
       <x:c r="O2" s="86"/>
       <x:c r="P2" s="86"/>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+    <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | 5 phases | one-thread default | 32 MiB default artifact cap | every row Not Started and execution_authorized=false | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 preregistered | Loops 26-44 Not Started | all 20 execution flags false | one-thread default | Loop 25 cap: 8 MiB / 45 s | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -7925,7 +7972,7 @@
         <x:v>Primary source URLs</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="138" customHeight="1">
+    <x:row r="5" ht="180" customHeight="1">
       <x:c r="A5" s="125" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -7951,8 +7998,8 @@
       <x:c r="H5" s="113" t="str">
         <x:v>Data: Target-free synthetic signals first; any later S21 use is restricted to separately authorized source-train rows and may not open source-test or session-2 evidence.
 Controls:
-- Five or more adversarial chunk schedules including single-sample and boundary splits.
-- Impulse, step, chirp, drift, and end-padding fixtures with future-sample perturbation tests.
+- Seven frozen chunk schedules including whole-item, single-sample, decimation-boundary, frame-boundary, powers-of-two, and seeded-irregular splits.
+- Six target-free signal families, ten resume cuts, and three future-mutation cuts across physically separate seeds 2501 and 2502.
 - Offline noncausal reference reported separately and never substituted for the causal path.</x:v>
       </x:c>
       <x:c r="I5" s="113" t="str">
@@ -7968,19 +8015,19 @@
       </x:c>
       <x:c r="K5" s="113" t="str">
         <x:v>Loops: none
-External: explicit_loop24_proceed_park_or_hold_decision</x:v>
+External: explicit_loop25_authorization_decision</x:v>
       </x:c>
       <x:c r="L5" s="113" t="str">
-        <x:v>Planning only. Fixture generation, real-cache reads, preprocessing execution, and model access require a separate Loop 25 preregistration and authorization.</x:v>
+        <x:v>Preregistered at a36d97b and awaiting a separate exact decision through docs/LOOP_25_AUTHORIZATION_PACKET.md. The request is not authorization; fixture generation, preprocessing execution, data/cache/target/model/training access, RW3, streams, devices, and hardware remain unauthorized.</x:v>
       </x:c>
       <x:c r="M5" s="113" t="str">
-        <x:v>One thread, one worker, 32 MiB generated artifacts, 60 seconds per isolated worker, and 1 GiB peak RSS.</x:v>
+        <x:v>One thread, one worker, 4 MiB fixtures, 16 MiB working arrays, 8 MiB total generated artifacts, 45 seconds internal runtime, 4 KiB mutable state, and 1 GiB peak RSS.</x:v>
       </x:c>
       <x:c r="N5" s="140" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>preregistered_no_implementation_or_execution</x:v>
       </x:c>
       <x:c r="O5" s="146" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="P5" s="149" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -9198,7 +9245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81d4a3effe284181"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R222f9412606749d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4c16dcf9bcf4e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R19ecf83b468041db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R81c0995ef6574e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R181f9faea2014692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra658b34f74324e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1a2522cce51841d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8280e690b23e4ac3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R45140d2c92984bb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rf75a048488ac4674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0c25dd3f202845c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rc67f18f7809d4c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R7235a197a30a47f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R2374940fe0c945c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rfc405dc1db6443f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R95a05bd4512b427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8b8c2a80d03f4258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4801e8487d614c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rb515f2282afb4293"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7f1472f3c7c64031"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c99102139024b1a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I31"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1338,7 +1338,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 25 preregistered; authorization pending</x:v>
+        <x:v>Loop 25 amended v1; authorization pending</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1355,12 +1355,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="99" customHeight="1">
+    <x:row r="10" ht="141" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. Loop 25 is preregistered at green commit a36d97b; its request is false and seeds 2501/2502 remain unopened. RW3 Stage A remains unauthorized. Loops 26-44 remain planning-only.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. Loop 25 v0 was superseded before authorization; amended v1 is green at b6b92d8 with a dedicated anti-alias stage, 65,537 response points, 23 alias probes, 45 refusals, and 23 counters. Its request is false and seeds 2501/2502 remain unopened. RW3 Stage A remains unauthorized. Loops 26-44 remain planning-only.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4fd4b16a5fd4871"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5149618c1b1f4ea9"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac693b48ffc44b7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e6c58713b5e4ed6"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4045,16 +4045,34 @@
         <x:v>Commit a36d97b; CI green; contract SHA-256 42781526225c556d0df54d1b6924fd5d9ecf95578a84c3e3922b6d5c7035050e; 7 schedules; 10 resumes; 3 mutation cuts; 40 refusals; 21 counters; 10 contract + 8 request invariants. authorized_now=false; seeds 2501/2502 unopened; zero runtime/data/target/model/training/RW3/device operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="37"/>
-      <x:c r="B39" s="12"/>
-      <x:c r="C39" s="12"/>
-      <x:c r="D39" s="12"/>
-      <x:c r="E39" s="12"/>
-      <x:c r="F39" s="12"/>
-      <x:c r="G39" s="12"/>
-      <x:c r="H39" s="12"/>
-      <x:c r="I39" s="12"/>
+    <x:row r="39" ht="135" customHeight="1">
+      <x:c r="A39" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
+        <x:v>25-AA</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="str">
+        <x:v>Supersede Loop 25 v0 anti-alias scope before authorization</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="str">
+        <x:v>Pinned Brain2Qwerty uses NeuralSet 0.2.2, whose extractor performs a separate MNE resample after bandpass filtering. V0 checked only 60 Hz at -6 dB and left almost the complete 50-500 Hz folding band unbounded. Amend before any coefficient or seed exists.</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
+        <x:v>docs/LOOP_25_ANTI_ALIAS_AUDIT.md; docs/LOOP_25_CAUSAL_PREPROCESSING_AMENDMENT_1.md; registries/causal_preprocessing_contract.v1.json; docs/LOOP_25_AUTHORIZATION_PACKET_V1.md</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="str">
+        <x:v>Review v1; authorize exactly, amend again, or hold</x:v>
+      </x:c>
+      <x:c r="I39" s="12" t="str">
+        <x:v>Commit b6b92d8; both CI jobs green; contract SHA-256 ecec99a7cc505ec0256c01c3c1e8aeaa05323ab54a71528323fa6d32bd289141; dedicated elliptic anti-alias; 65,537 response points; 23 alias probes; 7 schedules; 10 resumes; 3 mutation cuts; 45 refusals; 23 counters. authorized_now=false; seeds 2501/2502 unopened; zero coefficient/runtime/data/target/model/training/RW3/device operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37"/>
@@ -5847,7 +5865,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R458ed667dfe64244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbafd83858a824306"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6734,6 +6752,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I30" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="126" customHeight="1">
+      <x:c r="A31" s="12" t="str">
+        <x:v>R30</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>Anti-alias completeness</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="str">
+        <x:v>A task low-pass edge or one above-Nyquist probe is mistaken for complete anti-alias protection before 10x decimation, allowing 50-500 Hz source energy to fold into the retained band.</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>Require a separate causal anti-alias SOS, a 65,537-point 0-500 Hz response grid, 23 alias probes, and complete-chain 50-500 Hz attenuation before any fixture array opens.</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
+        <x:v>The dedicated or complete chain exceeds -59.5 dB anywhere in 50-500 Hz, an alias destination is wrong, or a superseded packet is selected.</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6766,7 +6813,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racd30b423c704bc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8036213d44541ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7260,16 +7307,16 @@
         <x:v>Loop25-Decision</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Decide Frozen Causal Preprocessing Gate</x:v>
+        <x:v>Decide Amended Causal Preprocessing Gate v1</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>Review docs/LOOP_25_AUTHORIZATION_PACKET.md and registries/loop25_authorization_request.v0.json. Confirm green registration commit a36d97b, contract SHA-256 42781526225c556d0df54d1b6924fd5d9ecf95578a84c3e3922b6d5c7035050e, seeds 2501/2502, seven schedules, ten resume cuts, three future-mutation cuts, 40 refusals, 21 counters, the 8 MiB/45-second caps, and every forbidden operation. Decide explicitly to authorize the exact target-free gate, amend the packet, or hold. General continuation is not authorization. Do not implement, generate coefficients or fixtures, open either seed, read data/caches/targets, run models, train, touch RW3, streams, devices, or hardware from this prompt.</x:v>
+        <x:v>Review docs/LOOP_25_AUTHORIZATION_PACKET_V1.md and registries/loop25_authorization_request.v1.json. Confirm green amendment b6b92d8, contract SHA-256 ecec99a7cc505ec0256c01c3c1e8aeaa05323ab54a71528323fa6d32bd289141, the dedicated anti-alias stage, 65,537 response points, 23 alias probes, seeds 2501/2502, seven schedules, ten resume cuts, three future-mutation cuts, 45 refusals, 23 counters, and 8 MiB/45-second caps. Decide explicitly to authorize only v1, amend again, or hold. General continuation is not authorization. Do not implement, generate coefficients or fixtures, open either seed, read data/caches/targets, run models, train, touch RW3, streams, devices, or hardware from this prompt.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a40db3125d4694"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59c489db8cfa4fbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7835,7 +7882,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfba350fbba1b4e1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dd0a1bb44444e38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7884,7 +7931,7 @@
     </x:row>
     <x:row r="2" ht="43.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 is preregistered at green commit a36d97b and awaits a separate exact authorization decision. Its request is false; seeds 2501/2502 are unopened; no fixture, coefficients, transform, partition, CLI, or runtime exists. Loop 24 is parked, RW3 Stage A is separate, and no data/model/training/stream/device/hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 is green at b6b92d8 after v0 was superseded before authorization. The v1 request is false; seeds 2501/2502 are unopened; no fixture, coefficient, transform, partition, CLI, or runtime exists. The static full-folding-band gate must pass before seed 2501 opens. Loop 24 is parked, RW3 Stage A is separate, and no data/model/training/stream/device/hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -7904,7 +7951,7 @@
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 preregistered | Loops 26-44 Not Started | all 20 execution flags false | one-thread default | Loop 25 cap: 8 MiB / 45 s | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 amended v1 | Loops 26-44 Not Started | all 20 execution flags false | one-thread default | Loop 25 cap: 8 MiB / 45 s | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -7992,14 +8039,15 @@
         <x:v>A causal model is not causal if filtering, resampling, padding, or normalization leaks future context; this gate protects every later streaming claim.</x:v>
       </x:c>
       <x:c r="G5" s="113" t="str">
-        <x:v>Build: Versioned stateful preprocessing contract, offline-versus-stream replay harness, transform provenance, and explicit refusal for noncausal settings.
-Research: Primary-source note on filter delay, resampling event jitter, padding, and train-only normalization semantics.</x:v>
+        <x:v>Build: Versioned stateful preprocessing contract with a dedicated causal anti-alias SOS stage, phase-locked decimator, replay harness, transform provenance, and fail-closed refusals.
+Research: Pinned Brain2Qwerty-to-NeuralSet-to-MNE source trace plus filter delay, full folding-band, alias-map, resampling jitter, padding, and train-only normalization analysis.</x:v>
       </x:c>
       <x:c r="H5" s="113" t="str">
         <x:v>Data: Target-free synthetic signals first; any later S21 use is restricted to separately authorized source-train rows and may not open source-test or session-2 evidence.
 Controls:
 - Seven frozen chunk schedules including whole-item, single-sample, decimation-boundary, frame-boundary, powers-of-two, and seeded-irregular splits.
 - Six target-free signal families, ten resume cuts, and three future-mutation cuts across physically separate seeds 2501 and 2502.
+- A 65,537-point 0-500 Hz response grid, 23 exact alias source probes, and complete 50-500 Hz folding-band attenuation before any fixture array opens.
 - Offline noncausal reference reported separately and never substituted for the causal path.</x:v>
       </x:c>
       <x:c r="I5" s="113" t="str">
@@ -8007,31 +8055,34 @@
 - valid-sample and timestamp identity
 - maximum offline-stream payload error
 - schedule hash agreement
+- dedicated and complete-chain folding-band attenuation plus alias destination correctness
 - runtime, peak RSS, input bytes, output bytes, and access counts</x:v>
       </x:c>
       <x:c r="J5" s="113" t="str">
-        <x:v>Acceptance: Proceed only if declared right context is zero, every schedule preserves valid samples and timestamps within preregistered tolerances, evaluation-fit/read counters are zero, and resource caps pass.
-Stop: Park any transform that needs future samples or cannot preserve timing; do not widen tolerances after observing a protected row.</x:v>
+        <x:v>Acceptance: Proceed only if the dedicated anti-alias and complete chain pass the full 50-500 Hz folding-band gate before seed access, declared right context is zero, every schedule preserves samples, timestamps, and state, all forbidden counters are zero, and resource caps pass.
+Stop: Park with both seeds unopened if the static filter gate fails; otherwise park any transform that needs future samples or cannot preserve timing, and never widen tolerances after observing a protected row.</x:v>
       </x:c>
       <x:c r="K5" s="113" t="str">
         <x:v>Loops: none
 External: explicit_loop25_authorization_decision</x:v>
       </x:c>
       <x:c r="L5" s="113" t="str">
-        <x:v>Preregistered at a36d97b and awaiting a separate exact decision through docs/LOOP_25_AUTHORIZATION_PACKET.md. The request is not authorization; fixture generation, preprocessing execution, data/cache/target/model/training access, RW3, streams, devices, and hardware remain unauthorized.</x:v>
+        <x:v>Amended at green commit b6b92d8 after the v0 anti-alias scope was superseded before authorization. Await a separate exact decision through docs/LOOP_25_AUTHORIZATION_PACKET_V1.md; the v1 request is false, seeds 2501/2502 are unopened, and coefficients, fixtures, runtime, data/cache/target/model/training access, RW3, streams, devices, and hardware remain unauthorized.</x:v>
       </x:c>
       <x:c r="M5" s="113" t="str">
         <x:v>One thread, one worker, 4 MiB fixtures, 16 MiB working arrays, 8 MiB total generated artifacts, 45 seconds internal runtime, 4 KiB mutable state, and 1 GiB peak RSS.</x:v>
       </x:c>
       <x:c r="N5" s="140" t="str">
-        <x:v>preregistered_no_implementation_or_execution</x:v>
+        <x:v>amended_preregistered_no_implementation_or_execution</x:v>
       </x:c>
       <x:c r="O5" s="146" t="str">
         <x:v>Review</x:v>
       </x:c>
       <x:c r="P5" s="149" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://mne.tools/stable/generated/mne.filter.resample.html</x:v>
+https://github.com/facebookresearch/neuroai/blob/v0.2.2/neuralset-repo/neuralset/extractors/neuro.py#L334-L381
+https://mne.tools/stable/generated/mne.filter.resample.html
+https://docs.scipy.org/doc/scipy-1.14.1/reference/generated/scipy.signal.iirdesign.html</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="138" customHeight="1">
@@ -9245,7 +9296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R222f9412606749d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfc9c8b4bb0d44b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0c25dd3f202845c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rc67f18f7809d4c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R7235a197a30a47f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R2374940fe0c945c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rfc405dc1db6443f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R95a05bd4512b427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8b8c2a80d03f4258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4801e8487d614c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rb515f2282afb4293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R90efdb6614fc405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rd000539bca40496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rf6eb0b18f6834bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R026bc4dd13f24b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R5fe5fa4a582240e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R10cccb20d034426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R32774fd78bbb470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R58f785b5b72241ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R53956edd5380434a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c99102139024b1a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd383f6dc7592446f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I32"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1355,12 +1355,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="141" customHeight="1">
+    <x:row r="10" ht="163.5" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked: 65.154951 s exceeded the 60 s cap, float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. Loop 25 v0 was superseded before authorization; amended v1 is green at b6b92d8 with a dedicated anti-alias stage, 65,537 response points, 23 alias probes, 45 refusals, and 23 counters. Its request is false and seeds 2501/2502 remain unopened. RW3 Stage A remains unauthorized. Loops 26-44 remain planning-only.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked and Loop 25 remains the active numbered decision: amended v1 is green, its request is false, and seeds 2501/2502 are unopened. Loop 26 planning research is complete but execution is Not Started: six validation sentences permit only 64 exact paired assignments, the proposed 2,908-parameter causal CTC and 2,884-parameter linear comparator are recommendations, and no preregistration or authorization sentence exists. Loops 27-44 and RW3 Stage A remain unauthorized.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5149618c1b1f4ea9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dfce7d0221f4e69"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e6c58713b5e4ed6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra623c3c2d2954f60"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4074,16 +4074,34 @@
         <x:v>Commit b6b92d8; both CI jobs green; contract SHA-256 ecec99a7cc505ec0256c01c3c1e8aeaa05323ab54a71528323fa6d32bd289141; dedicated elliptic anti-alias; 65,537 response points; 23 alias probes; 7 schedules; 10 resumes; 3 mutation cuts; 45 refusals; 23 counters. authorized_now=false; seeds 2501/2502 unopened; zero coefficient/runtime/data/target/model/training/RW3/device operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="37"/>
-      <x:c r="B40" s="12"/>
-      <x:c r="C40" s="12"/>
-      <x:c r="D40" s="12"/>
-      <x:c r="E40" s="12"/>
-      <x:c r="F40" s="12"/>
-      <x:c r="G40" s="12"/>
-      <x:c r="H40" s="12"/>
-      <x:c r="I40" s="12"/>
+    <x:row r="40" ht="142.5" customHeight="1">
+      <x:c r="A40" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>26-R1</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>Close Loop 26 planning research without preregistering an experiment</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>Six validation sentences from one person/session support only a coarse source-validation engineering gate. Preserve the 2,908-parameter ceiling, recommend a left-causal padding repair and 2,884-parameter linear comparator, and wait for Loop 25 before freezing thresholds or access.</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md; registries/loop26_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; only then consider a separate Loop 26 preregistration</x:v>
+      </x:c>
+      <x:c r="I40" s="12" t="str">
+        <x:v>Planning only. 64 exact paired assignments; minimum two-sided resolution 0.03125 with six nonzero pairs; 55/6/5 split; source test and session 2 frozen; 14 authorization flags false; zero cache/target/model/training/validation operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37"/>
@@ -5865,7 +5883,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbafd83858a824306"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7b2a4ab97e54a8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6781,6 +6799,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I31" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="138" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>R31</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Six-row validation overclaim</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>A favorable result on six sentences from one person/session is reported as source-test, participant, population, transfer, real-time, or device evidence, or smooth bootstrap output hides the 64-assignment exact resolution.</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>Report all six paired differences and the complete exact null; require all frozen controls; label the unit as sentence instances within one person/session; keep source test and session 2 closed.</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>Any claim exceeds the six named validation rows, any validation item is omitted, a zero/tie is hidden, or protected test/session-2 evidence is opened.</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I32" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6813,7 +6860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8036213d44541ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e206ebf48384e25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7313,10 +7360,21 @@
         <x:v>Review docs/LOOP_25_AUTHORIZATION_PACKET_V1.md and registries/loop25_authorization_request.v1.json. Confirm green amendment b6b92d8, contract SHA-256 ecec99a7cc505ec0256c01c3c1e8aeaa05323ab54a71528323fa6d32bd289141, the dedicated anti-alias stage, 65,537 response points, 23 alias probes, seeds 2501/2502, seven schedules, ten resume cuts, three future-mutation cuts, 45 refusals, 23 counters, and 8 MiB/45-second caps. Decide explicitly to authorize only v1, amend again, or hold. General continuation is not authorization. Do not implement, generate coefficients or fixtures, open either seed, read data/caches/targets, run models, train, touch RW3, streams, devices, or hardware from this prompt.</x:v>
       </x:c>
     </x:row>
+    <x:row r="35" ht="135" customHeight="1">
+      <x:c r="A35" s="12" t="str">
+        <x:v>Loop26-Research</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
+        <x:v>Review Validation Identifiability Before Preregistration</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="str">
+        <x:v>Read docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md and registries/loop26_research_boundary.v0.json. Confirm 55/6/5 source membership, one person/session, 64 paired assignments, the unfrozen 2,908-parameter causal candidate and 2,884-parameter linear comparator, six control families, and 14 false authorization flags. Loop 25 must close first. Do not read caches or targets, run or train a model, open validation, reopen source test or session 2, create an experiment contract, or treat this research packet as authorization.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59c489db8cfa4fbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f84c71ddf4d4029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7882,7 +7940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dd0a1bb44444e38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7a6a79756c04369"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7929,9 +7987,9 @@
       <x:c r="O1" s="81"/>
       <x:c r="P1" s="81"/>
     </x:row>
-    <x:row r="2" ht="43.5" customHeight="1">
+    <x:row r="2" ht="55.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 is green at b6b92d8 after v0 was superseded before authorization. The v1 request is false; seeds 2501/2502 are unopened; no fixture, coefficient, transform, partition, CLI, or runtime exists. The static full-folding-band gate must pass before seed 2501 opens. Loop 24 is parked, RW3 Stage A is separate, and no data/model/training/stream/device/hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision; no coefficient, fixture, seed open, transform, CLI, or runtime exists. Loop 26 planning research now defines the six-row inferential ceiling, a 2,908-parameter left-causal CTC recommendation, a 2,884-parameter linear comparator, and six future controls. Loop 26 remains Not Started, depends on Loop 25, and has no preregistration or authorization sentence. No data, target, model, training, validation, test, session-2, RW3, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -7949,9 +8007,9 @@
       <x:c r="O2" s="86"/>
       <x:c r="P2" s="86"/>
     </x:row>
-    <x:row r="3" ht="25.5" customHeight="1">
+    <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 amended v1 | Loops 26-44 Not Started | all 20 execution flags false | one-thread default | Loop 25 cap: 8 MiB / 45 s | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 amended v1 decision pending | Loop 26 research complete / execution Not Started | Loops 27-44 Not Started | all 20 execution flags false | one-thread default | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8085,7 +8143,7 @@
 https://docs.scipy.org/doc/scipy-1.14.1/reference/generated/scipy.signal.iirdesign.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="138" customHeight="1">
+    <x:row r="6" ht="210" customHeight="1">
       <x:c r="A6" s="126" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -8106,25 +8164,27 @@
       </x:c>
       <x:c r="G6" s="114" t="str">
         <x:v>Build: Preregistered tiny architecture, train-only fit path, six-row validation report, uncertainty, control parity, and immutable access ledger.
-Research: Power and identifiability note stating what six validation rows can and cannot establish.</x:v>
+Research: Completed planning-only power and identifiability note: six paired rows yield 64 exact sign assignments, one-person inference only, and no source-test or transfer claim.
+Packet: docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
         <x:v>Data: Only separately authorized S21 source-train and source-validation members; five source-test rows and all session-2 rows stay closed.
 Controls:
-- Same-split no-signal prior.
-- Target permutation fitted on train only.
-- Time-shift and channel-permutation controls chosen before validation opens.
-- Frozen non-neural parameter-count and compute-matched comparator where feasible.</x:v>
+- Same-split train-only no-signal sentence prior and zero-signal inference.
+- Semantic-ID-derived train-target derangement frozen before targets open.
+- Nonwrapping zero-filled time displacement and channel-name-hash derangements frozen before signal arrays open.
+- A 2,884-parameter linear signal CTC matched against the recommended 2,908-parameter causal candidate.</x:v>
       </x:c>
       <x:c r="I6" s="114" t="str">
-        <x:v>- CER and exact-sequence accuracy
-- paired item differences and interval
-- control margins
+        <x:v>- macro per-sentence CER and corpus CER
+- all six paired item differences and complete 64-assignment exact null
+- exact-sequence accuracy, WER, blank fraction, and wins/ties/losses
+- margin over every signal-free and corrupted-signal control
 - parameter count, runtime, peak RSS, and artifact bytes
 - raw, cache, target, model, and training access counts</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Acceptance: Proceed only if the preregistered primary neural-versus-prior margin and all required controls pass on validation with no access violation; this does not authorize source-test opening.
+        <x:v>Acceptance: A future preregistration may proceed only after Loop 25 closes. A future experiment may proceed only if its frozen primary neural-versus-prior margin and every required control pass on exactly six validation rows with no access violation; this cannot authorize source-test opening.
 Stop: If the neural path does not beat the registered controls, park real-model scaling and move to failure analysis without touching test or increasing model size.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
@@ -8132,20 +8192,26 @@
 External: separate_real_cache_and_training_authorization</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Planning only. Real-cache reads, target access, training, validation opening, and model runs are all unauthorized now.</x:v>
+        <x:v>Planning research is complete, but no experiment preregistration or authorization sentence exists. Real-cache reads, target access, training, validation opening, model runs, test/session-2 access, and Loop 25 execution are unauthorized now.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
-        <x:v>One thread, one worker, existing tiny-model class only, 32 MiB generated artifacts, 20 minutes total authorized CPU time, and 1 GiB peak RSS.</x:v>
+        <x:v>One thread, one worker, at most 2,908 trainable parameters, 32 MiB generated artifacts, 20 minutes total future CPU time across candidate and controls, and 1 GiB peak RSS.</x:v>
       </x:c>
       <x:c r="N6" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete</x:v>
       </x:c>
       <x:c r="O6" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P6" s="150" t="str">
         <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
-https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://github.com/facebookresearch/brain2qwerty/tree/main/brain2qwerty_v2
+https://docs.scipy.org/doc/scipy/reference/generated/scipy.stats.permutation_test.html
+https://docs.scipy.org/doc/scipy/reference/generated/scipy.stats.bootstrap.html
+https://jmlr.org/beta/papers/v11/ojala10a.html
+https://pubmed.ncbi.nlm.nih.gov/28655633/
+https://onlinelibrary.wiley.com/doi/10.1111/jtsa.12638</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="138" customHeight="1">
@@ -9296,7 +9362,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfc9c8b4bb0d44b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21dff73a0d1f411b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R90efdb6614fc405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rd000539bca40496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rf6eb0b18f6834bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R026bc4dd13f24b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R5fe5fa4a582240e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R10cccb20d034426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R32774fd78bbb470c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R58f785b5b72241ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R53956edd5380434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1c10f44730d14172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rb3108f2fab3b445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4978b5026cdc4ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rbcbfbf41ef4042f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R32eb57bae7924213"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1b25ae0d2b544cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R0bfd1196c60c45e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R48d63aa38eee4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R0cf975c8fe1149d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd383f6dc7592446f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17f2976011c54370"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I33"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1355,12 +1355,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="163.5" customHeight="1">
+    <x:row r="10" ht="178.5" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 24 is parked and Loop 25 remains the active numbered decision: amended v1 is green, its request is false, and seeds 2501/2502 are unopened. Loop 26 planning research is complete but execution is Not Started: six validation sentences permit only 64 exact paired assignments, the proposed 2,908-parameter causal CTC and 2,884-parameter linear comparator are recommendations, and no preregistration or authorization sentence exists. Loops 27-44 and RW3 Stage A remain unauthorized.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 25 remains the active numbered decision. Loop 26 planning research is complete but its experiment is Not Started. Loop 27 planning research selected S25 session 2 block 2 as the smallest eligible strict MEG pair: 315 metadata entries -&gt; 23 clean pairs -&gt; 16 eligible -&gt; exactly 2 selected files / 1,009,939,983 bytes. Preregistration is blocked on Loop 25 mechanics, the Loop 26 source model/controls, target isolation, and a Loop 28 final rule. All 18 Loop 27 permissions and all 20 roadmap execution flags are false; no download or payload access occurred.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dfce7d0221f4e69"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c88092bad4f40b6"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra623c3c2d2954f60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37b54a9ff894700"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4103,16 +4103,34 @@
         <x:v>Planning only. 64 exact paired assignments; minimum two-sided resolution 0.03125 with six nonzero pairs; 55/6/5 split; source test and session 2 frozen; 14 authorization flags false; zero cache/target/model/training/validation operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="37"/>
-      <x:c r="B41" s="12"/>
-      <x:c r="C41" s="12"/>
-      <x:c r="D41" s="12"/>
-      <x:c r="E41" s="12"/>
-      <x:c r="F41" s="12"/>
-      <x:c r="G41" s="12"/>
-      <x:c r="H41" s="12"/>
-      <x:c r="I41" s="12"/>
+    <x:row r="41" ht="148.5" customHeight="1">
+      <x:c r="A41" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
+        <x:v>27-R1</x:v>
+      </x:c>
+      <x:c r="C41" s="12" t="str">
+        <x:v>Select S25 metadata for Loop 27 and hold preregistration</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="str">
+        <x:v>A pinned metadata selector found 23 strict MEG pairs and 16 eligible pairs. Select the first eligible pair, S25 session 2 block 2, at exactly 1,009,939,983 bytes. Keep every payload and permission sealed until source-model, control, target-isolation, and final-rule hashes exist.</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
+        <x:v>docs/LOOP_27_PRIMARY_SOURCE_RESEARCH.md; registries/loop27_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H41" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; only after Loop 25/26 evidence exists may Loop 27 preregistration be prepared</x:v>
+      </x:c>
+      <x:c r="I41" s="12" t="str">
+        <x:v>Planning only. S23 officially excluded; S20 is EEG; all 18 permissions false; zero download, local MAT hash, header, signal, target, model, training, final, or backup operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37"/>
@@ -5883,7 +5901,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7b2a4ab97e54a8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racf55277510948bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6828,6 +6846,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I32" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="145.5" customHeight="1">
+      <x:c r="A33" s="12" t="str">
+        <x:v>R32</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>Metadata candidate becomes accidental authorization</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="str">
+        <x:v>A local S25 MAT filename, official payload hash, or 1 GiB cap is treated as permission to hash/open targets, download the FIF, inspect signal, run a model, or silently substitute S18/S24/S22 after failure.</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>Bind 18 false permissions; require source-model/control/target-isolation/final-rule hashes before preregistration; stage acquisition/header/signal/target/final access separately; prohibit automatic backup substitution.</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
+        <x:v>Any S25 content read or download before an exact green authorization-only commit, any candidate-side fitting, or any backup open after protected access.</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I33" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6860,7 +6907,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e206ebf48384e25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd11758ec704a08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7371,10 +7418,21 @@
         <x:v>Read docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md and registries/loop26_research_boundary.v0.json. Confirm 55/6/5 source membership, one person/session, 64 paired assignments, the unfrozen 2,908-parameter causal candidate and 2,884-parameter linear comparator, six control families, and 14 false authorization flags. Loop 25 must close first. Do not read caches or targets, run or train a model, open validation, reopen source test or session 2, create an experiment contract, or treat this research packet as authorization.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="144" customHeight="1">
+      <x:c r="A36" s="12" t="str">
+        <x:v>Loop27-Research</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>Review S25 Holdout Metadata Without Opening It</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>Read docs/LOOP_27_PRIMARY_SOURCE_RESEARCH.md and registries/loop27_research_boundary.v0.json. Confirm 315 MEG metadata entries, 23 strict pairs, 16 eligible pairs, S25 session 2 block 2, two exact files/1,009,939,983 bytes, official S23 exclusion, separate S20 EEG cohort, final-only no-fit recommendation, unavailable channels/trials/overlap/freshness, and 18 false permissions. Do not hash/open the local MAT, download the FIF, inspect a header/signal/target, create a selection/request, run/train a model, open a backup, or treat this research packet as authorization.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f84c71ddf4d4029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e2101b9745441d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7940,7 +7998,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7a6a79756c04369"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42c12f66885e4207"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7987,9 +8045,9 @@
       <x:c r="O1" s="81"/>
       <x:c r="P1" s="81"/>
     </x:row>
-    <x:row r="2" ht="55.5" customHeight="1">
+    <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision; no coefficient, fixture, seed open, transform, CLI, or runtime exists. Loop 26 planning research now defines the six-row inferential ceiling, a 2,908-parameter left-causal CTC recommendation, a 2,884-parameter linear comparator, and six future controls. Loop 26 remains Not Started, depends on Loop 25, and has no preregistration or authorization sentence. No data, target, model, training, validation, test, session-2, RW3, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 planning research selected S25 session 2 block 2 in metadata only: one FIF plus one protected MAT log, exact total 1,009,939,983 bytes under a future 1 GiB cap. The source model, controls, target isolation, and final-only transfer rule are not frozen. No preregistration, request, download, local MAT hash, header, signal, target, model, training, final open, backup, RW3, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8007,9 +8065,9 @@
       <x:c r="O2" s="86"/>
       <x:c r="P2" s="86"/>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
+    <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 amended v1 decision pending | Loop 26 research complete / execution Not Started | Loops 27-44 Not Started | all 20 execution flags false | one-thread default | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loops 28-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8214,7 +8272,7 @@
 https://onlinelibrary.wiley.com/doi/10.1111/jtsa.12638</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="138" customHeight="1">
+    <x:row r="7" ht="225" customHeight="1">
       <x:c r="A7" s="126" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -8235,7 +8293,8 @@
       </x:c>
       <x:c r="G7" s="114" t="str">
         <x:v>Build: Metadata-only candidate registry, license and byte ledger, exact file plan, split protocol, target-isolation plan, and one-time analysis contract.
-Research: Primary-source dataset and license review separating same-person session, unseen-person, modality, and task claims.</x:v>
+Research: Completed metadata-only selection of S25 session 2 block 2 as a 1,009,939,983-byte MEG candidate, with exact payload identities, official exclusions, unavailable fields, and preregistration blockers.
+Packet: docs/LOOP_27_PRIMARY_SOURCE_RESEARCH.md</x:v>
       </x:c>
       <x:c r="H7" s="114" t="str">
         <x:v>Data: Metadata and public documentation only; no download, signal read, target read, or remote row preview.
@@ -8256,17 +8315,17 @@
 Stop: Hold acquisition if identity, license, task, timing, or byte provenance is ambiguous; never substitute a convenient consumed cohort.</x:v>
       </x:c>
       <x:c r="K7" s="114" t="str">
-        <x:v>Loops: none
-External: none</x:v>
+        <x:v>Loops: none for metadata research
+External: none for metadata research</x:v>
       </x:c>
       <x:c r="L7" s="114" t="str">
-        <x:v>Metadata research is the only future candidate scope; download or signal access requires a separate exact packet and user authorization.</x:v>
+        <x:v>Planning research selected S25 metadata only. No preregistration or authorization request exists; download, local log hashing, header/signal/MAT/target access, model/training/final opening, backup substitution, and Loop 28 remain unauthorized.</x:v>
       </x:c>
       <x:c r="M7" s="114" t="str">
         <x:v>Zero downloaded bytes, zero signal reads, one thread, one worker, 8 MiB planning artifacts, and 10 minutes local metadata processing.</x:v>
       </x:c>
       <x:c r="N7" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; candidate=spanishbcbl-meg-s25-session2-block2-v0</x:v>
       </x:c>
       <x:c r="O7" s="147" t="str">
         <x:v>Not Started</x:v>
@@ -9362,7 +9421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21dff73a0d1f411b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b932c427f824987"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1c10f44730d14172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rb3108f2fab3b445f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4978b5026cdc4ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rbcbfbf41ef4042f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R32eb57bae7924213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R1b25ae0d2b544cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R0bfd1196c60c45e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R48d63aa38eee4a64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R0cf975c8fe1149d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb9d5d2564ef54b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8876277b62f24744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rca08e832409f45a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R789565cd69ac4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R02a59fde57c94c04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R941dad77b5af48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R40eb8334ff36455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R1790d3ab11484001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R70fd3bdd3fb64c19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -971,7 +971,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17f2976011c54370"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3835df21652a49e3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1009,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I34"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1044,7 +1044,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -1360,7 +1360,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 25 remains the active numbered decision. Loop 26 planning research is complete but its experiment is Not Started. Loop 27 planning research selected S25 session 2 block 2 as the smallest eligible strict MEG pair: 315 metadata entries -&gt; 23 clean pairs -&gt; 16 eligible -&gt; exactly 2 selected files / 1,009,939,983 bytes. Preregistration is blocked on Loop 25 mechanics, the Loop 26 source model/controls, target isolation, and a Loop 28 final rule. All 18 Loop 27 permissions and all 20 roadmap execution flags are false; no download or payload access occurred.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap. Loop 25 remains the active numbered decision. Loop 26 planning research is complete but its experiment is Not Started. Loop 27 planning research selected S25 session 2 block 2 as the smallest eligible strict MEG pair: 315 metadata entries -&gt; 23 clean pairs -&gt; 16 eligible -&gt; exactly 2 selected files / 1,009,939,983 bytes. Loop 28 planning research now defines a strict T2 zero-shot final-only rule: zero S25 fit/calibration rows, at least 48 final rows, at least 0.05 macro sentence-CER improvement, 65,535 paired assignments plus observed, and strict corruption-control wins. All 21 Loop 28 authorization fields and all 20 roadmap execution flags are false; Loops 25-28 execution remains unauthorized.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1497,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c88092bad4f40b6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b8c97bb5d141de"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37b54a9ff894700"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44903eab5490444c"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4132,16 +4132,34 @@
         <x:v>Planning only. S23 officially excluded; S20 is EEG; all 18 permissions false; zero download, local MAT hash, header, signal, target, model, training, final, or backup operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="37"/>
-      <x:c r="B42" s="12"/>
-      <x:c r="C42" s="12"/>
-      <x:c r="D42" s="12"/>
-      <x:c r="E42" s="12"/>
-      <x:c r="F42" s="12"/>
-      <x:c r="G42" s="12"/>
-      <x:c r="H42" s="12"/>
-      <x:c r="I42" s="12"/>
+    <x:row r="42" ht="132" hidden="0" customHeight="1">
+      <x:c r="A42" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>28-R1</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="str">
+        <x:v>Reserve S25 for strict zero-shot and separate calibration</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
+        <x:v>Brain2Qwerty v2 is continuous-sentence but noncausal. Its joint model includes target participants and its leave-one-out path finetunes on the target, so neither is strict unseen-person zero-shot. Preserve S25's independence by allowing zero target-person fit rows and moving calibrated transfer to a different physical design.</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>docs/LOOP_28_PRIMARY_SOURCE_RESEARCH.md; registries/loop28_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; after Loops 25-27 close, consider a separate Loop 28 preregistration</x:v>
+      </x:c>
+      <x:c r="I42" s="12" t="str">
+        <x:v>Planning only. T0-T3 taxonomy; &gt;=48 final rows; &gt;=0.05 macro-CER advantage; 65,535 paired assignments plus observed; four comparators; 21 authorization flags false; zero S25 payload/target/model/calibration/final operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37"/>
@@ -5901,7 +5919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racf55277510948bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb58cfba5afe64b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6875,6 +6893,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I33" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" hidden="0" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>R33</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Transfer evidence</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Calibrated or transductive behavior is relabeled as strict zero-shot, or one S25 result is presented as population generalization.</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Bind T0-T3 labels, forbid every S25 fit row for T2, keep calibrated transfer physically separate, disclose sentence overlap, require all controls, and cap the claim at one person/session/task.</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>Any target-person statistic, label, adapter, threshold, or update influences T2 before final scoring; calibrated output is called zero-shot; or a single-person result is generalized to a population.</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6907,7 +6954,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd11758ec704a08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd54a2bd88e574a23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7429,10 +7476,21 @@
         <x:v>Read docs/LOOP_27_PRIMARY_SOURCE_RESEARCH.md and registries/loop27_research_boundary.v0.json. Confirm 315 MEG metadata entries, 23 strict pairs, 16 eligible pairs, S25 session 2 block 2, two exact files/1,009,939,983 bytes, official S23 exclusion, separate S20 EEG cohort, final-only no-fit recommendation, unavailable channels/trials/overlap/freshness, and 18 false permissions. Do not hash/open the local MAT, download the FIF, inspect a header/signal/target, create a selection/request, run/train a model, open a backup, or treat this research packet as authorization.</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A37" s="12" t="str">
+        <x:v>Loop28-Research</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
+        <x:v>Review Strict Zero-Shot Transfer Rule</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="str">
+        <x:v>Read docs/LOOP_28_PRIMARY_SOURCE_RESEARCH.md and registries/loop28_research_boundary.v0.json. Confirm Brain2Qwerty v2 is asynchronous but noncausal, its joint and leave-one-out-plus-finetune results are not strict unseen-person zero-shot, the T0-T3 taxonomy, zero S25 fit/calibration rows, &gt;=48 final rows, &gt;=0.05 macro-CER advantage, 65,535 paired assignments plus observed, four comparators, separate calibrated-transfer design, and 21 false permissions. Loop 28 remains Not Started. Do not hash/open/download S25, inspect a header/signal/target, run a model/control, train, calibrate, score final data, open a backup, or treat this research as authorization.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e2101b9745441d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f6d6b17c27840bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7998,7 +8056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42c12f66885e4207"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R552a7aa4f5144988"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8047,7 +8105,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 planning research selected S25 session 2 block 2 in metadata only: one FIF plus one protected MAT log, exact total 1,009,939,983 bytes under a future 1 GiB cap. The source model, controls, target isolation, and final-only transfer rule are not frozen. No preregistration, request, download, local MAT hash, header, signal, target, model, training, final open, backup, RW3, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 planning research selected S25 session 2 block 2 in metadata only: one FIF plus one protected MAT log, exact total 1,009,939,983 bytes under a future 1 GiB cap. Loop 28 planning research defines a strict zero-shot final-only decision rule, but does not freeze the source model, controls, target isolation, staged permissions, or any prediction. No preregistration, request, download, local MAT hash, header, signal, target, model, training, calibration, final open, backup, RW3, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8067,7 +8125,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loops 28-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 28 strict zero-shot research complete / experiment Not Started | Loops 29-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8350,53 +8408,59 @@
         <x:v>P0 / L</x:v>
       </x:c>
       <x:c r="E8" s="114" t="str">
-        <x:v>Does the frozen causal system transfer to a genuinely fresh session or person, and how much predeclared calibration is required?</x:v>
+        <x:v>Does the frozen causal system transfer to one genuinely unseen canonical person without fitting anything to that person?</x:v>
       </x:c>
       <x:c r="F8" s="114" t="str">
-        <x:v>The existing same-person cross-session result is negative; a fresh one-time test is required before any generalization claim can move.</x:v>
+        <x:v>The existing same-person cross-session result is negative, and Brain2Qwerty v2 target-participant finetuning is calibrated rather than strict zero-shot; a fresh one-time T2 test is required before any person-transfer claim can move.</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>Build: Frozen source model, identity-safe adapter protocol, one-time holdout runner, calibration curve, paired controls, and claim-specific report card.
-Research: Transfer taxonomy distinguishing same-session, same-person cross-session, unseen-person zero-shot, and unseen-person calibrated evidence.</x:v>
+        <x:v>Build: Future frozen source-model one-time holdout runner with a source-train-only prior, corruption controls, hash-frozen predictions, and a claim-specific report card. Calibrated adaptation stays physically separate.
+Research: Completed T0-T3 taxonomy, strict zero-shot versus transductive boundary, and one-time S25 final-only rule.
+Packet: docs/LOOP_28_PRIMARY_SOURCE_RESEARCH.md</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Data: Only a separately acquired and authorized Loop 27 holdout after architecture, preprocessing, adapter, thresholds, and reports are frozen.
+        <x:v>Data: Planning research only. A future T2 test may use only a separately acquired and authorized Loop 27 S25 final-only holdout. S25 contributes zero train, validation, calibration, target-wide normalization, subject-embedding, adapter, threshold, or unlabeled-corpus-fit rows.
 Controls:
-- Train-only no-signal prior evaluated on identical rows.
-- Zero-shot frozen model before any calibration.
-- Calibration-size curve with a physically separate final partition.
-- Identity and repeated-text leakage audit.</x:v>
+- Source-train-only no-signal prior.
+- Same checkpoint with exact-zero S25 signal.
+- Frozen channel-name-hash derangement.
+- Frozen nonwrapping zero-filled time displacement.
+- Identity and sentence-overlap audit without plaintext or row cherry-picking.</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>- CER, WER where justified, and exact sequence accuracy
-- neural-minus-prior paired interval
-- zero-shot versus calibrated delta
-- calibration examples, seconds, and compute
-- session/person-specific failure rates</x:v>
+        <x:v>- macro sentence-CER prior-minus-model effect with a 0.05 practical floor
+- one-sided paired p-value from 65,535 frozen assignments plus observed
+- corpus CER, WER where justified, exact sequence accuracy, wins/ties/losses
+- strict candidate-versus-corruption controls
+- identity, overlap, runtime, RSS, bytes, and access counters</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Acceptance: Promote only the exact same-person or unseen-person claim whose preregistered interval and controls pass on the one-time fresh partition.
-Stop: A failed fresh gate closes that transfer claim; do not tune on the opened holdout or relabel calibrated performance as zero-shot.</x:v>
+        <x:v>Acceptance: Support T2 only for this one S25 person/session/task when at least 48 unique final rows remain, macro CER improves by at least 0.05 over the frozen prior, paired p is at most 0.05, every corruption control is strictly worse, and all identity, hash, access, and resource gates pass.
+Stop: Any missing field, tie, threshold miss, control failure, access violation, or cap failure parks T2. Do not tune, calibrate, restart, substitute a backup, or relabel calibrated/transductive performance as zero-shot.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
         <x:v>Loops: 25, 26, 27
 External: approved_fresh_holdout_packet, separate_one_time_test_authorization</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Planning only. No fresh acquisition, model run, calibration, or holdout opening is authorized.</x:v>
+        <x:v>Planning research only. No preregistration or authorization sentence exists; acquisition, local MAT hashing, header/signal/target access, model/control prediction, calibration, final opening, language model, backup, and device work remain unauthorized.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>One thread and worker, frozen small model, 32 MiB outputs, preregistered calibration budget, and 1 GiB peak RSS.</x:v>
+        <x:v>Current research: zero payload bytes, one thread/worker, 8 MiB planning-artifact cap. Future T2: frozen Loop 26 checkpoint only, zero target-person updates and language-model runs, one thread/worker, 32 MiB output cap, 1 GiB RSS; runtime cap awaits measured Loop 26 evidence.</x:v>
       </x:c>
       <x:c r="N8" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; selected_claim=T2_strict_zero_shot; candidate=spanishbcbl-meg-s25-session2-block2-v0</x:v>
       </x:c>
       <x:c r="O8" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P8" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://arxiv.org/abs/2404.15319</x:v>
+https://github.com/facebookresearch/brain2qwerty/tree/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2
+https://arxiv.org/abs/1404.4175
+https://arxiv.org/abs/1805.06427
+https://pubmed.ncbi.nlm.nih.gov/27989847/
+https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="138" customHeight="1">
@@ -9421,7 +9485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b932c427f824987"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52fbd3ebfaa4007"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb9d5d2564ef54b26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8876277b62f24744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rca08e832409f45a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R789565cd69ac4536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R02a59fde57c94c04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R941dad77b5af48f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R40eb8334ff36455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R1790d3ab11484001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R70fd3bdd3fb64c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R083a7b889c094c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rcf3c37c36e6d4877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rd9fd866179b649b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R7bd5e545334945e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R452e2653c0904e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re8904ad509b740ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Ra70df6780cbd4a8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R34a91c98ef294558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R46b2cdff0df5483d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,7 +332,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="152">
+  <x:cellXfs count="153">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -714,6 +714,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -971,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3835df21652a49e3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd58d358a221426f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1009,7 +1012,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1026,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I35"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1355,12 +1358,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="178.5" customHeight="1">
+    <x:row r="10" ht="216" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap. Loop 25 remains the active numbered decision. Loop 26 planning research is complete but its experiment is Not Started. Loop 27 planning research selected S25 session 2 block 2 as the smallest eligible strict MEG pair: 315 metadata entries -&gt; 23 clean pairs -&gt; 16 eligible -&gt; exactly 2 selected files / 1,009,939,983 bytes. Loop 28 planning research now defines a strict T2 zero-shot final-only rule: zero S25 fit/calibration rows, at least 48 final rows, at least 0.05 macro sentence-CER improvement, 65,535 paired assignments plus observed, and strict corruption-control wins. All 21 Loop 28 authorization fields and all 20 roadmap execution flags are false; Loops 25-28 execution remains unauthorized.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, and 29 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls. Its 15 requirements, four profiles, six qualification levels, 12 future packet gates, and 24 authorization flags are machine checked. The 5,000,000,000-byte preferred and 10,000,000,000-byte absolute capacity limits are not download permission. Future S20 plus S25 bundles total 1,106,030,247 bytes; Loop 29 downloaded zero bytes. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1497,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b8c97bb5d141de"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec239fb17cce4d91"/>
 </x:worksheet>
 </file>
 
@@ -2911,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44903eab5490444c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d5b72ffdb234f98"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4161,16 +4164,34 @@
         <x:v>Planning only. T0-T3 taxonomy; &gt;=48 final rows; &gt;=0.05 macro-CER advantage; 65,535 paired assignments plus observed; four comparators; 21 authorization flags false; zero S25 payload/target/model/calibration/final operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="37"/>
-      <x:c r="B43" s="12"/>
-      <x:c r="C43" s="12"/>
-      <x:c r="D43" s="12"/>
-      <x:c r="E43" s="12"/>
-      <x:c r="F43" s="12"/>
-      <x:c r="G43" s="12"/>
-      <x:c r="H43" s="12"/>
-      <x:c r="I43" s="12"/>
+    <x:row r="43" ht="144" customHeight="1">
+      <x:c r="A43" s="152" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B43" s="39" t="str">
+        <x:v>29-R1</x:v>
+      </x:c>
+      <x:c r="C43" s="39" t="str">
+        <x:v>Choose local-first EEG and partner OPM-MEG lanes; hold execution</x:v>
+      </x:c>
+      <x:c r="D43" s="39" t="str">
+        <x:v>Scalp EEG offers the most accessible local acquisition path but has weaker task-matched decoding and stronger reference, placement, motion, and clock risks. OPM-MEG preserves magnetic sensing but still requires specialist shielding, field control, geometry, and motion handling. Keep both lanes separate from cryogenic MEG and peripheral controls.</x:v>
+      </x:c>
+      <x:c r="E43" s="39" t="str">
+        <x:v>docs/LOOP_29_PRIMARY_SOURCE_RESEARCH.md; registries/loop29_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F43" s="39" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G43" s="39" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H43" s="39" t="str">
+        <x:v>Review an exact device or acquisition packet only after its prerequisites and separate authorization exist</x:v>
+      </x:c>
+      <x:c r="I43" s="39" t="str">
+        <x:v>Planning only. 15 requirements; 4 profiles; 6 qualification levels; 12 future packet gates; 24 authorization flags false. Preferred/absolute capacity is 5,000,000,000/10,000,000,000 bytes; S20+S25 total 1,106,030,247 bytes; zero download/data/model/stream/device/hardware operations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37"/>
@@ -5919,7 +5940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb58cfba5afe64b7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f490a3641eb4ae3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6922,6 +6943,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I34" s="12" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="108" customHeight="1">
+      <x:c r="A35" s="39" t="str">
+        <x:v>R34</x:v>
+      </x:c>
+      <x:c r="B35" s="39" t="str">
+        <x:v>Portability and storage overclaim</x:v>
+      </x:c>
+      <x:c r="C35" s="39" t="str">
+        <x:v>A 5-10 GB capacity allowance, cryogenic channel ablation, vendor specification, or at-home acquisition study is treated as download permission or proof of OPM-MEG/EEG text decoding.</x:v>
+      </x:c>
+      <x:c r="D35" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F35" s="39" t="str">
+        <x:v>Keep four modality profiles and six qualification levels separate; bind 24 false permissions; stage S20, S25, device, SDK, stream, and hardware decisions independently; spend storage only on a frozen measured question.</x:v>
+      </x:c>
+      <x:c r="G35" s="39" t="str">
+        <x:v>Any unapproved payload opens, a device is selected from specifications alone, a cryogenic subset is called OPM/EEG evidence, or home recording is called home decoding.</x:v>
+      </x:c>
+      <x:c r="H35" s="39" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I35" s="39" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -6954,7 +7004,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd54a2bd88e574a23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0ab60d29e8b43a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7487,10 +7537,21 @@
         <x:v>Read docs/LOOP_28_PRIMARY_SOURCE_RESEARCH.md and registries/loop28_research_boundary.v0.json. Confirm Brain2Qwerty v2 is asynchronous but noncausal, its joint and leave-one-out-plus-finetune results are not strict unseen-person zero-shot, the T0-T3 taxonomy, zero S25 fit/calibration rows, &gt;=48 final rows, &gt;=0.05 macro-CER advantage, 65,535 paired assignments plus observed, four comparators, separate calibrated-transfer design, and 21 false permissions. Loop 28 remains Not Started. Do not hash/open/download S25, inspect a header/signal/target, run a model/control, train, calibrate, score final data, open a backup, or treat this research as authorization.</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" ht="120" customHeight="1">
+      <x:c r="A38" s="39" t="str">
+        <x:v>Loop29-Research</x:v>
+      </x:c>
+      <x:c r="B38" s="39" t="str">
+        <x:v>Review Portable Sensing Translation Without Executing It</x:v>
+      </x:c>
+      <x:c r="C38" s="39" t="str">
+        <x:v>Read docs/LOOP_29_PRIMARY_SOURCE_RESEARCH.md and registries/loop29_research_boundary.v0.json. Confirm the local-first scalp EEG lane, partner/lab OPM-MEG lane, cryogenic reference, non-neural controls, 15 requirements, four profiles, six qualification levels, 12 packet gates, 24 false permissions, 5,000,000,000-byte preferred and 10,000,000,000-byte absolute capacity limits, and exact 1,106,030,247-byte future S20+S25 allocation. Loop 29 remains Not Started. Storage is not download authorization. Do not open S20/S25 or real headers/signals/targets, run/train a model, select or purchase a device, import an SDK, open a socket/stream, contact a partner, touch hardware, or treat this planning research as portable decoding evidence.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f6d6b17c27840bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcec1fadc745b4c22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8056,7 +8117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R552a7aa4f5144988"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6827e297f16147f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8105,7 +8166,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 planning research selected S25 session 2 block 2 in metadata only: one FIF plus one protected MAT log, exact total 1,009,939,983 bytes under a future 1 GiB cap. Loop 28 planning research defines a strict zero-shot final-only decision rule, but does not freeze the source model, controls, target isolation, staged permissions, or any prediction. No preregistration, request, download, local MAT hash, header, signal, target, model, training, calibration, final open, backup, RW3, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 selected S25 session 2 block 2 in metadata only. Loop 28 defines a strict zero-shot final-only decision rule. Loop 29 planning research now separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls; its experiment remains Not Started. The 5-10 GB capacity envelope is not download permission. No Loop 29 preregistration, request, download, real-data read, model, SDK, stream, device, partner session, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8125,7 +8186,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 28 strict zero-shot research complete / experiment Not Started | Loops 29-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 28 strict zero-shot research complete / experiment Not Started | Loop 29 portability research complete / experiment Not Started | Loops 30-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8463,7 +8524,7 @@
 https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="138" customHeight="1">
+    <x:row r="9" ht="168" customHeight="1">
       <x:c r="A9" s="126" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -8477,51 +8538,65 @@
         <x:v>P1 / M</x:v>
       </x:c>
       <x:c r="E9" s="114" t="str">
-        <x:v>Which validated requirements survive a move from cryogenic MEG toward OPM-MEG or EEG, and which assumptions break?</x:v>
+        <x:v>Which Brain2Qwerty requirements survive translation from cryogenic MEG to OPM-MEG or scalp EEG, which assumptions break, and what is the smallest honest real-data path toward an at-home result?</x:v>
       </x:c>
       <x:c r="F9" s="114" t="str">
-        <x:v>Portability is the product direction users care about, but channel-count ablation is not device qualification.</x:v>
+        <x:v>Accessible sensing is the product direction, but channel-count ablation, vendor specifications, and home recording mechanics are not device qualification or text decoding.</x:v>
       </x:c>
       <x:c r="G9" s="114" t="str">
-        <x:v>Build: Versioned modality requirement matrix covering geometry, reference, units, bandwidth, noise, shielding, timing, compute, and calibration.
-Research: Primary-source OPM-MEG and EEG feasibility review with explicit unavailable fields and partner-data gates.</x:v>
+        <x:v>Build: Future device-specific implementation of the versioned 15-field modality matrix, six-level qualification ladder, and fail-closed packet validator; no runtime exists now.
+Research: Completed primary-source OPM-MEG and EEG review, two-lane decision, storage envelope, and exact S20/S25 result-oriented path.
+Packet: docs/LOOP_29_PRIMARY_SOURCE_RESEARCH.md</x:v>
       </x:c>
       <x:c r="H9" s="114" t="str">
-        <x:v>Data: Public specifications and existing aggregate evidence only; no device session, new recording, or synthetic claim of modality equivalence.
+        <x:v>Data: Public specifications and aggregate evidence only; zero downloads. A future first real-data result may use only the separately approved 96,090,264-byte S20 packet; S25 remains final-only at 1,009,939,983 bytes.
 Controls:
-- Separate rows for cryogenic MEG, OPM-MEG, scalp EEG, and non-neural wearables.
-- Measured device values distinguished from vendor specifications and unknowns.
-- Random channel ablation explicitly excluded as OPM or EEG evidence.</x:v>
+- Separate cryogenic MEG, OPM-MEG, scalp EEG, and non-neural profiles.
+- Distinguish measured values, official specifications, inferences, and unavailable fields.
+- Exclude cryogenic random channel subsets as OPM-MEG or EEG evidence.
+- Keep S20, S25, and any future device recording as separate cohorts and decisions.</x:v>
       </x:c>
       <x:c r="I9" s="114" t="str">
         <x:v>- requirement coverage and unavailable-field count
-- sensor count, rate, units, geometry, and clock provenance
-- known versus inferred versus measured status
-- minimum future qualification evidence</x:v>
+- units, reference, geometry, filters, rate, clocks, packets, and privacy provenance
+- measured versus specified versus unavailable status
+- minimum future qualification level
+- preferred and absolute storage margin after exact bundles
+- protected access and authorization counters</x:v>
       </x:c>
       <x:c r="J9" s="114" t="str">
-        <x:v>Acceptance: Proceed to a device-specific packet only when one modality has task, timing, geometry, privacy, licensing, and resource requirements that can be measured directly.
-Stop: Do not call a simulated subset, vendor specification, or file-reader success portable decoding.</x:v>
+        <x:v>Acceptance: Proceed to a device-specific packet only when one exact configuration has measurable task, units, filters, reference, geometry, clocks, packets, locality, privacy, repeated-session, peripheral-control, license, and resource requirements.
+Stop: Do not call a simulated subset, vendor specification, file read, home-recording study, or S20 research EEG result portable decoding; do not spend unused storage without a measured question.</x:v>
       </x:c>
       <x:c r="K9" s="114" t="str">
         <x:v>Loops: 27
-External: none</x:v>
+External: none for planning; separate exact device or acquisition authorization for execution</x:v>
       </x:c>
       <x:c r="L9" s="114" t="str">
-        <x:v>Research and registry planning only; hardware, acquisition, and signal reads require separate authorization.</x:v>
+        <x:v>Planning research only. The 5-10 GB envelope is capacity permission, not download permission. S20, S25, real/header/signal/target/model/training access, SDKs, streams, purchases, partner sessions, devices, and hardware each require separate authorization.</x:v>
       </x:c>
       <x:c r="M9" s="114" t="str">
-        <x:v>Zero hardware sessions, zero downloads, one thread, one worker, and 8 MiB documentation artifacts.</x:v>
+        <x:v>Current research: zero hardware sessions and downloads, one thread, one worker, and 8 MiB planning artifacts. Future storage: 5,000,000,000 preferred and 10,000,000,000 absolute incremental bytes, with no automatic allocation.</x:v>
       </x:c>
       <x:c r="N9" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; selected_lanes=scalp_EEG_local_first|OPM_MEG_partner_lab</x:v>
       </x:c>
       <x:c r="O9" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P9" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://arxiv.org/abs/2404.15319</x:v>
+https://www.nature.com/articles/s41593-026-02303-2
+https://www.sciencedirect.com/science/article/pii/S1053811921002469
+https://pubmed.ncbi.nlm.nih.gov/39302788/
+https://pubmed.ncbi.nlm.nih.gov/34273527/
+https://pmc.ncbi.nlm.nih.gov/articles/PMC8356471/
+https://mne.tools/stable/auto_tutorials/preprocessing/80_opm_processing.html
+https://pmc.ncbi.nlm.nih.gov/articles/PMC9372279/
+https://pmc.ncbi.nlm.nih.gov/articles/PMC12480468/
+https://bids-specification.readthedocs.io/en/stable/modality-specific-files/electroencephalography.html
+https://docs.openbci.com/Cyton/CytonDataFormat/
+https://brainflow.readthedocs.io/en/stable/DataFormatDesc.html</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="138" customHeight="1">
@@ -9485,7 +9560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52fbd3ebfaa4007"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc461626999b4404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R083a7b889c094c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rcf3c37c36e6d4877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rd9fd866179b649b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R7bd5e545334945e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R452e2653c0904e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re8904ad509b740ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Ra70df6780cbd4a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R34a91c98ef294558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R46b2cdff0df5483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8cff6c16b882478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R911e0908f2664062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rb2a4ba2d9c664fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra342cdde757e4b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra61d4fd75e5a4975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re0524869250349a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R22a9a3983ba44d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R962fbf2e3cd64d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R7c13bb034f8942a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd58d358a221426f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b2a18c6a001408b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1012,7 +1012,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1029,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I36"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1047,7 +1047,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -1358,12 +1358,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="216" customHeight="1">
+    <x:row r="10" ht="225" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, and 29 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls. Its 15 requirements, four profiles, six qualification levels, 12 future packet gates, and 24 authorization flags are machine checked. The 5,000,000,000-byte preferred and 10,000,000,000-byte absolute capacity limits are not download permission. Future S20 plus S25 bundles total 1,106,030,247 bytes; Loop 29 downloaded zero bytes. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, 29, and 30 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls under a capacity-only 5-10 GB envelope. Loop 30 defines a loopback-only target-free replay inspector with four source modes, a 30-field trace, nine clock domains, six latency levels, 18 future gates, 30 refusals, and 30 false authorization flags. No Loop 30 seed, trace, UI, server, browser run, model, stream, live source, or hardware operation exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec239fb17cce4d91"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R708f3fce435a439c"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d5b72ffdb234f98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9e5b9ee15d54859"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4193,16 +4193,34 @@
         <x:v>Planning only. 15 requirements; 4 profiles; 6 qualification levels; 12 future packet gates; 24 authorization flags false. Preferred/absolute capacity is 5,000,000,000/10,000,000,000 bytes; S20+S25 total 1,106,030,247 bytes; zero download/data/model/stream/device/hardware operations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="37"/>
-      <x:c r="B44" s="12"/>
-      <x:c r="C44" s="12"/>
-      <x:c r="D44" s="12"/>
-      <x:c r="E44" s="12"/>
-      <x:c r="F44" s="12"/>
-      <x:c r="G44" s="12"/>
-      <x:c r="H44" s="12"/>
-      <x:c r="I44" s="12"/>
+    <x:row r="44" ht="118" customHeight="1">
+      <x:c r="A44" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>30-R1</x:v>
+      </x:c>
+      <x:c r="C44" s="12" t="str">
+        <x:v>Define a target-free local replay inspector; hold execution</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="str">
+        <x:v>Brain2Qwerty v2 is continuous but whole-sentence and noncausal, Loop 21 proves only a causal producer, and Loop 23 shows that stable zero-revision output can still be wrong. Freeze replay/live, clocks, revision/finalization, confidence, localhost, accessibility, browser, and resource boundaries before any UI or server exists.</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>docs/LOOP_30_PRIMARY_SOURCE_RESEARCH.md; registries/loop30_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H44" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; prepare a separate Loop 30 packet only after its dependency and scope are explicit</x:v>
+      </x:c>
+      <x:c r="I44" s="12" t="str">
+        <x:v>Planning only. 4 source modes; 30 event fields; 9 clocks; 6 latency levels; 18 gates; 30 refusals; 30 authorization flags false. No seed, trace, UI, server, browser, consumed data, model, stream, live source, or hardware operation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37"/>
@@ -5940,7 +5958,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f490a3641eb4ae3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aa4c18b29743be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6972,6 +6990,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I35" s="39" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="104" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>R35</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Replay and latency overclaim</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>A target-free replay, stable partial, localhost label, or within-process timing is presented as live neural decoding, calibrated confidence, correctness, privacy proof, or capture-to-user latency.</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Bind four source modes, nine clock origins, six claim levels, explicit finalization, confidence unavailable, fixed loopback/file/network settings, accessible status, 18 gates, 30 refusals, and browser traffic/long-task QA before implementation.</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>A replay is called live; stability is called confidence/correctness; clocks are subtracted without mapping; external traffic/file exposure occurs; or the UI hides proof, causality, warning, or unavailable labels.</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7004,7 +7051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0ab60d29e8b43a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bf7bdab5f9f4680"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7517,13 +7564,13 @@
     </x:row>
     <x:row r="36" ht="144" customHeight="1">
       <x:c r="A36" s="12" t="str">
-        <x:v>Loop27-Research</x:v>
+        <x:v>Loop30-Research</x:v>
       </x:c>
       <x:c r="B36" s="12" t="str">
-        <x:v>Review S25 Holdout Metadata Without Opening It</x:v>
+        <x:v>Review Target-Free Local Replay Boundary Without Executing It</x:v>
       </x:c>
       <x:c r="C36" s="12" t="str">
-        <x:v>Read docs/LOOP_27_PRIMARY_SOURCE_RESEARCH.md and registries/loop27_research_boundary.v0.json. Confirm 315 MEG metadata entries, 23 strict pairs, 16 eligible pairs, S25 session 2 block 2, two exact files/1,009,939,983 bytes, official S23 exclusion, separate S20 EEG cohort, final-only no-fit recommendation, unavailable channels/trials/overlap/freshness, and 18 false permissions. Do not hash/open the local MAT, download the FIF, inspect a header/signal/target, create a selection/request, run/train a model, open a backup, or treat this research packet as authorization.</x:v>
+        <x:v>Loop 30 planning research only; no execution.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -7548,10 +7595,21 @@
         <x:v>Read docs/LOOP_29_PRIMARY_SOURCE_RESEARCH.md and registries/loop29_research_boundary.v0.json. Confirm the local-first scalp EEG lane, partner/lab OPM-MEG lane, cryogenic reference, non-neural controls, 15 requirements, four profiles, six qualification levels, 12 packet gates, 24 false permissions, 5,000,000,000-byte preferred and 10,000,000,000-byte absolute capacity limits, and exact 1,106,030,247-byte future S20+S25 allocation. Loop 29 remains Not Started. Storage is not download authorization. Do not open S20/S25 or real headers/signals/targets, run/train a model, select or purchase a device, import an SDK, open a socket/stream, contact a partner, touch hardware, or treat this planning research as portable decoding evidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="39" ht="126" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>Loop30-Research</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Review Target-Free Local Replay Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Read docs/LOOP_30_PRIMARY_SOURCE_RESEARCH.md and registries/loop30_research_boundary.v0.json. Confirm four source modes, a new target-free trace only after authorization, 30 event fields, nine clock domains, six latency levels, explicit revisions/finalization, stability not confidence/correctness, fixed 127.0.0.1 privacy settings, accessible status/log semantics, 18 future gates, 30 refusals, and 30 false permissions. Loop 30 remains Not Started. Do not select a seed, generate a trace, reopen Loop 23/24 or S7/S21 artifacts, launch a UI/server/browser, read targets or models, open a socket/stream, touch a device, or treat replay as live/end-to-end neural decoding.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcec1fadc745b4c22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra457e038d1944212"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8117,7 +8175,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6827e297f16147f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e1f5323d0774f52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8166,7 +8224,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 selected S25 session 2 block 2 in metadata only. Loop 28 defines a strict zero-shot final-only decision rule. Loop 29 planning research now separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls; its experiment remains Not Started. The 5-10 GB capacity envelope is not download permission. No Loop 29 preregistration, request, download, real-data read, model, SDK, stream, device, partner session, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 selected S25 metadata only. Loop 28 defines a strict zero-shot final-only rule. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls under a capacity-only 5-10 GB envelope. Loop 30 planning research defines a target-free local replay inspector; its experiment remains Not Started. No Loop 29/30 preregistration, request, payload, data/model/device operation, trace, UI, server, or browser run is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8186,7 +8244,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loop 26 research complete / experiment Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 28 strict zero-shot research complete / experiment Not Started | Loop 29 portability research complete / experiment Not Started | Loops 30-44 Not Started | all 20 execution flags false | source: registries/next_20_loops.v0.json</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-30 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 29 portability research complete | Loop 30 target-free replay research complete | all 20 execution flags false | no Loop 30 trace or runtime</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8599,7 +8657,7 @@
 https://brainflow.readthedocs.io/en/stable/DataFormatDesc.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="138" customHeight="1">
+    <x:row r="10" ht="176" customHeight="1">
       <x:c r="A10" s="126" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -8616,49 +8674,62 @@
         <x:v>Can a user inspect incremental hypotheses, revisions, timing, provenance, and refusals locally without confusing replay with live decoding?</x:v>
       </x:c>
       <x:c r="F10" s="114" t="str">
-        <x:v>A trustworthy interaction surface exposes latency and uncertainty instead of hiding them behind a final sentence.</x:v>
+        <x:v>A trustworthy interaction surface must expose revision, finalization, latency, uncertainty, and proof posture. Loop 23 showed that a stable zero-revision partial can still be wrong, while Brain2Qwerty v2 remains whole-sentence and noncausal.</x:v>
       </x:c>
       <x:c r="G10" s="114" t="str">
-        <x:v>Build: Loopback-only replay UI with partial hypotheses, revision trace, stage clocks, resource telemetry, warnings, and local artifact loading.
-Research: Interaction contract for partial output, abstention, revision, privacy, and replay/live labels.</x:v>
+        <x:v>Build: Future loopback-only target-free replay inspector with explicit partial hypotheses, revisions, finalization, nine clock domains, six latency levels, resources, warnings, hashes, proof posture, and browser QA.
+Research: Completed four-source-mode taxonomy, 30-field target-free trace, fixed localhost/file/network/accessibility contract, 18 future gates, and 30 refusals.</x:v>
       </x:c>
       <x:c r="H10" s="114" t="str">
-        <x:v>Data: Existing synthetic artifacts and aggregate-only real scorecards; no raw real signal, cloud call, socket, or hardware source.
+        <x:v>Data: Planning research used public primary sources and committed aggregate/mechanics documentation only. A future run may create one new target-free synthetic trace after separate authorization; consumed Loop 23/24 artifacts, S7/S21, targets, models, sockets, streams, and hardware remain closed.
 Controls:
-- Replay badge and source identity visible in every view.
-- No-signal comparator shown beside predictive outputs.
-- Cold start, steady state, scheduling delay, compute delay, and render delay separated.</x:v>
+- Source, proof posture, producer/decoder causality, unavailable confidence, and no-signal comparator remain visible.
+- Explicit revision and finalization; stability is not correctness or confidence.
+- Nine clock origins; no unmapped cross-clock subtraction.
+- Fixed 127.0.0.1, share/analytics/monitoring/upload off, one thread/worker, zero non-loopback traffic.
+- Status/log semantics, keyboard access, stable focus, no forced scroll, reduced motion.</x:v>
       </x:c>
       <x:c r="I10" s="114" t="str">
-        <x:v>- first-token and finalization latency by stage
-- revision count and prefix stability
-- event-loop responsiveness
+        <x:v>- first partial, first committed token, and finalization by available clock domain
+- revision count, edit overhead, committed prefix, and stable duration
+- browser long tasks, Event Timing support, console and render QA
 - runtime, peak RSS, input and output bytes
-- network, raw, cache, model, and training counters</x:v>
+- network, WebSocket, raw, cache, consumed, target, model, training, calibration, stream, SDK, and hardware counters
+- source/config/trace/payload hashes and unavailable fields</x:v>
       </x:c>
       <x:c r="J10" s="114" t="str">
-        <x:v>Acceptance: Pass only as a local replay interface when all source, causality, latency, unavailable-confidence, and proof labels remain visible and browser QA passes.
-Stop: Park any interface that implies live hardware, real-time text, confidence, or neural success that the loaded artifact does not prove.</x:v>
+        <x:v>Acceptance: Future execution passes only when all 18 gates and 30 refusals pass, all labels and clock origins remain visible, browser QA records zero non-loopback traffic and zero 50-ms long tasks, and all resource/access caps pass.
+Stop: Park on target or consumed-artifact contribution, inferred finalization, fabricated confidence, cross-clock subtraction, external bind/request/WebSocket, file exposure, accessibility failure, missing label/counter/hash/warning, cap failure, or any implication of live neural or end-to-end real-time decoding.</x:v>
       </x:c>
       <x:c r="K10" s="114" t="str">
         <x:v>Loops: 25
 External: none</x:v>
       </x:c>
       <x:c r="L10" s="114" t="str">
-        <x:v>Planning only. UI implementation and replay execution require a separate bounded Loop 30 authorization; live sources remain outside scope.</x:v>
+        <x:v>Planning research only. No seed, trace, fixture, UI, server, browser run, model, real/consumed data read, socket, stream, SDK, device, or hardware operation is authorized. A future Loop 30 decision can cover only the bounded synthetic replay inspector and cannot authorize RW3 or a live source.</x:v>
       </x:c>
       <x:c r="M10" s="114" t="str">
-        <x:v>Loopback only, one thread, one worker, 32 MiB temporary artifacts, 1 GiB peak RSS, and no network dependency.</x:v>
+        <x:v>Current research: one thread/worker, zero payload/server/browser operations, 8 MiB planning cap. Future: loopback only, one thread/worker, 32 MiB generated artifacts, 1 GiB peak RSS, zero external network dependency.</x:v>
       </x:c>
       <x:c r="N10" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; target_free_replay_only</x:v>
       </x:c>
       <x:c r="O10" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P10" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://labstreaminglayer.readthedocs.io/info/time_synchronization.html</x:v>
+https://labstreaminglayer.readthedocs.io/info/time_synchronization.html
+https://www.gradio.app/main/docs/gradio/blocks
+https://www.gradio.app/main/guides/file-access
+https://docs.python.org/3.12/library/time.html#time.perf_counter_ns
+https://www.w3.org/TR/2026/WD-hr-time-3-20260225/
+https://www.w3.org/TR/longtasks-1/
+https://www.w3.org/TR/2026/WD-event-timing-20260223/
+https://www.w3.org/WAI/WCAG22/Understanding/status-messages
+https://playwright.dev/docs/network
+https://arxiv.org/abs/2006.01416
+https://arxiv.org/abs/2302.12049</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="138" customHeight="1">
@@ -9560,7 +9631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc461626999b4404d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a6a06ec2f8c4eab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8cff6c16b882478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R911e0908f2664062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rb2a4ba2d9c664fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra342cdde757e4b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra61d4fd75e5a4975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re0524869250349a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R22a9a3983ba44d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R962fbf2e3cd64d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R7c13bb034f8942a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc5965ba8188f4a7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R26f55c33fed34576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R838582372f434d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9a76da59872f43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R51613701d6ee46a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R179801f0993a430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R17bb993a549a48c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R245673e5627b4582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R040dd650ad454343"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b2a18c6a001408b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6bda3e2d1804dd0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1012,7 +1012,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1029,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I37"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1047,7 +1047,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -1358,12 +1358,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="225" customHeight="1">
+    <x:row r="10" ht="250" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, 29, and 30 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls under a capacity-only 5-10 GB envelope. Loop 30 defines a loopback-only target-free replay inspector with four source modes, a 30-field trace, nine clock domains, six latency levels, 18 future gates, 30 refusals, and 30 false authorization flags. No Loop 30 seed, trace, UI, server, browser run, model, stream, live source, or hardware operation exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, 29, 30, and 31 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 31 defines a 10-condition encoder attribution matrix, a contingent 5-condition LLM/Neuro Token matrix, exact six-row intersection-union inference, 18 future gates, 24 refusals, and 19 false authorization flags. Its maximum future local claim is sensor-signal dependence; brain-specific attribution remains blocked on Loop 35. No Loop 31 cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R708f3fce435a439c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7719ab952284e9d"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9e5b9ee15d54859"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428e15b765634b05"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4222,16 +4222,34 @@
         <x:v>Planning only. 4 source modes; 30 event fields; 9 clocks; 6 latency levels; 18 gates; 30 refusals; 30 authorization flags false. No seed, trace, UI, server, browser, consumed data, model, stream, live source, or hardware operation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="37"/>
-      <x:c r="B45" s="12"/>
-      <x:c r="C45" s="12"/>
-      <x:c r="D45" s="12"/>
-      <x:c r="E45" s="12"/>
-      <x:c r="F45" s="12"/>
-      <x:c r="G45" s="12"/>
-      <x:c r="H45" s="12"/>
-      <x:c r="I45" s="12"/>
+    <x:row r="45" ht="126" customHeight="1">
+      <x:c r="A45" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B45" s="12" t="str">
+        <x:v>31-R1</x:v>
+      </x:c>
+      <x:c r="C45" s="12" t="str">
+        <x:v>Separate sensor dependence, language gain, and neural origin; hold execution</x:v>
+      </x:c>
+      <x:c r="D45" s="12" t="str">
+        <x:v>The real S21 MEG and S7 EEG paths both lose to no-signal priors. Freeze encoder, timing, context, language, Neuro Token, exact inference, target-blind access, and claim ceilings before any validation or model operation. Sensor-signal dependence is the maximum local claim; Loop 35 is required for brain-specific attribution.</x:v>
+      </x:c>
+      <x:c r="E45" s="12" t="str">
+        <x:v>docs/LOOP_31_PRIMARY_SOURCE_RESEARCH.md; registries/loop31_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F45" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G45" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H45" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 31 remains blocked on an actual Loop 26 result and separate authorization</x:v>
+      </x:c>
+      <x:c r="I45" s="12" t="str">
+        <x:v>Planning only. 10 encoder conditions; 5 contingent LLM conditions; 6 claim classes; 18 gates; 24 refusals; 19 authorization flags false. No protected input, model, training, validation, LLM, Neuro Token, S20/S25, stream, device, or hardware operation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37"/>
@@ -5958,7 +5976,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aa4c18b29743be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07be51e645f94b61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7019,6 +7037,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I36" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="116" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>R36</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Scientific attribution</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Language regularity, timing, prompt/sentence context, broken signal-target correspondence, peripheral artifacts, or a missing control is credited to brain-specific neural information.</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Require the 10-condition encoder matrix, contingent 5-condition LLM matrix, target-blind prediction freeze, exact intersection-union gate, per-condition ledgers/hashes, and a Loop 35 ceiling before brain-specific wording.</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>A no-signal, timing, context, or corrupted-signal control matches full signal; language gain is called neural gain; a Neuro Token drop is called total neural contribution; or sensor dependence is called brain-specific before Loop 35.</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7051,7 +7098,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bf7bdab5f9f4680"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8a36cc6e97a4592"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7575,13 +7622,13 @@
     </x:row>
     <x:row r="37" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A37" s="12" t="str">
-        <x:v>Loop28-Research</x:v>
+        <x:v>Loop31-Research</x:v>
       </x:c>
       <x:c r="B37" s="12" t="str">
-        <x:v>Review Strict Zero-Shot Transfer Rule</x:v>
+        <x:v>Review Neural-Attribution Firewall Without Executing It</x:v>
       </x:c>
       <x:c r="C37" s="12" t="str">
-        <x:v>Read docs/LOOP_28_PRIMARY_SOURCE_RESEARCH.md and registries/loop28_research_boundary.v0.json. Confirm Brain2Qwerty v2 is asynchronous but noncausal, its joint and leave-one-out-plus-finetune results are not strict unseen-person zero-shot, the T0-T3 taxonomy, zero S25 fit/calibration rows, &gt;=48 final rows, &gt;=0.05 macro-CER advantage, 65,535 paired assignments plus observed, four comparators, separate calibrated-transfer design, and 21 false permissions. Loop 28 remains Not Started. Do not hash/open/download S25, inspect a header/signal/target, run a model/control, train, calibrate, score final data, open a backup, or treat this research as authorization.</x:v>
+        <x:v>Loop 31 planning research only; no execution.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="120" customHeight="1">
@@ -7606,10 +7653,21 @@
         <x:v>Read docs/LOOP_30_PRIMARY_SOURCE_RESEARCH.md and registries/loop30_research_boundary.v0.json. Confirm four source modes, a new target-free trace only after authorization, 30 event fields, nine clock domains, six latency levels, explicit revisions/finalization, stability not confidence/correctness, fixed 127.0.0.1 privacy settings, accessible status/log semantics, 18 future gates, 30 refusals, and 30 false permissions. Loop 30 remains Not Started. Do not select a seed, generate a trace, reopen Loop 23/24 or S7/S21 artifacts, launch a UI/server/browser, read targets or models, open a socket/stream, touch a device, or treat replay as live/end-to-end neural decoding.</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" ht="136" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>Loop31-Research</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Review Neural-Attribution Firewall Without Executing It</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Read docs/LOOP_31_PRIMARY_SOURCE_RESEARCH.md and registries/loop31_research_boundary.v0.json. Confirm the 10-condition encoder matrix, contingent 5-condition LLM/Neuro Token matrix, five separate estimands, exact six-row intersection-union math, timing/context allowlist, target-blind prediction freeze, six claim classes, 18 future gates, 24 refusals, and 19 false permissions. Loop 31 remains Not Started. Do not open a cache, target, checkpoint, model, validation row, consumed S7/S21 evidence, S20/S25, LLM, Neuro Token, stream, device, or hardware; do not label sensor-signal dependence as brain-specific before Loop 35.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra457e038d1944212"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra622ebb4e2794e18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8175,7 +8233,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e1f5323d0774f52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05621abc500a452d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8224,7 +8282,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row neural question but no experiment. Loop 27 selected S25 metadata only. Loop 28 defines a strict zero-shot final-only rule. Loop 29 separates local-first scalp EEG, partner/lab OPM-MEG, cryogenic MEG, and non-neural controls under a capacity-only 5-10 GB envelope. Loop 30 planning research defines a target-free local replay inspector; its experiment remains Not Started. No Loop 29/30 preregistration, request, payload, data/model/device operation, trace, UI, server, or browser run is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row predictive question but no experiment. Loop 27 selected S25 metadata only. Loop 28 defines strict zero-shot transfer. Loop 29 separates scalp EEG and partner/lab OPM-MEG. Loop 30 defines target-free local replay. Loop 31 planning research defines a 10-condition encoder and contingent 5-condition LLM attribution firewall; its experiment remains Not Started and brain-specific attribution is blocked on Loop 35. No Loop 31 preregistration, request, protected input, model, training, validation, LLM, Neuro Token, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8244,7 +8302,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-30 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 29 portability research complete | Loop 30 target-free replay research complete | all 20 execution flags false | no Loop 30 trace or runtime</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-31 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 31: 10 encoder + 5 contingent LLM conditions | sensor-signal ceiling / Loop 35 required for brain-specific attribution | all 20 execution flags false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8732,7 +8790,7 @@
 https://arxiv.org/abs/2302.12049</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="138" customHeight="1">
+    <x:row r="11" ht="196" customHeight="1">
       <x:c r="A11" s="126" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -8746,53 +8804,62 @@
         <x:v>P0 / L</x:v>
       </x:c>
       <x:c r="E11" s="114" t="str">
-        <x:v>When a predictive system improves, how much comes from neural signal rather than text priors, timing, sentence lists, or pipeline artifacts?</x:v>
+        <x:v>When a predictive system improves, how much comes from sensor signal rather than language priors, timing, declared context, broken correspondence, or pipeline artifacts?</x:v>
       </x:c>
       <x:c r="F11" s="114" t="str">
-        <x:v>This gate prevents autocomplete, prompt memorization, and event timing from being credited to brain activity.</x:v>
+        <x:v>A fluent prediction is not an attribution result. The consumed S21 MEG and S7 EEG paths both lose to no-signal priors, so any future improvement must survive signal-free, corrupted-signal, timing, context, and language controls before it can be credited to the sensor input.</x:v>
       </x:c>
       <x:c r="G11" s="114" t="str">
-        <x:v>Build: Hash-bound ablation matrix with full signal, no-signal, shuffled-neural, timing-only, text-prior, and optional neurotoken-drop conditions.
-Research: Neural-contribution estimand and claim language for encoder-only and language-model-assisted systems.</x:v>
+        <x:v>Build: Future hash-bound 10-condition encoder matrix plus a separately gated 5-condition LLM/Neuro Token extension.
+Research: Completed estimands, exact six-row intersection-union inference, target-blind freeze order, six claim classes, 18 future gates, 24 refusals, and a Loop 35 ceiling on brain-specific attribution.</x:v>
       </x:c>
       <x:c r="H11" s="114" t="str">
-        <x:v>Data: Future authorized validation data only; no consumed test or target-informed fixture construction.
+        <x:v>Data: Planning research used public primary sources and committed aggregate reports only. Future execution may use one separately authorized source-validation open after target-blind prediction freeze; consumed source test, session 2, S7, S20, and S25 remain closed.
 Controls:
-- No-signal prior and prompt/sentence-list-only baseline.
-- Within-split temporal, channel, and item permutations fixed before evaluation.
-- Encoder-only and language-model-assisted outputs reported separately.
-- Matched access, preprocessing, parameter, and decoding budgets where feasible.</x:v>
+- Full signal; train-only prior; zero signal; item, channel, and time derangements; timing-only; conditional context-only; train-pairing derangement.
+- 2,884-parameter linear signal CTC as a diagnostic.
+- All transforms and predictions frozen before targets.
+- Encoder, language, Neuro Token, total-system, and brain-specific effects separate.
+- Loop 35 required for brain-specific origin.</x:v>
       </x:c>
       <x:c r="I11" s="114" t="str">
-        <x:v>- full-minus-ablation CER and WER deltas
-- paired intervals and effect consistency
-- neural-token drop degradation
-- language-prior gain
-- shortcut-control failure count</x:v>
+        <x:v>- macro sentence control-minus-full CER for every applicable condition
+- exact one-sided paired components and intersection-union decision
+- primary practical margin
+- language-prior and conditional Neuro Token gains
+- per-item edits and wins/ties/losses; WER where valid
+- condition-specific access, model, training, runtime, RSS, bytes, warnings, unavailable fields, and hashes</x:v>
       </x:c>
       <x:c r="J11" s="114" t="str">
-        <x:v>Acceptance: Call a neural contribution only if the preregistered full-signal condition beats every required signal-free or corrupted-signal control with the expected direction and no leakage.
-Stop: If a signal-free or shortcut control matches the full path, withhold the neural claim and return to split, confound, or model diagnosis.</x:v>
+        <x:v>Acceptance: A future result may support sensor-signal dependence only when every applicable condition, exact six-item component, primary margin, target-blind freeze order, ledger, hash, and resource gate passes.
+Stop: Park on a tie or failed/missing control, target-informed transform, hidden timing/context, target open before predictions, restart or threshold change, missing ledger/hash, resource failure, or any promotion to brain-specific attribution before Loop 35.</x:v>
       </x:c>
       <x:c r="K11" s="114" t="str">
         <x:v>Loops: 26
-External: separate_validation_and_model_authorization</x:v>
+External: separate validation/model authorization; Loop 35 for brain-specific claim</x:v>
       </x:c>
       <x:c r="L11" s="114" t="str">
-        <x:v>Planning only. No target, model, validation, or language-model run is authorized.</x:v>
+        <x:v>Planning research only. No cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation is authorized. The experiment remains Not Started.</x:v>
       </x:c>
       <x:c r="M11" s="114" t="str">
-        <x:v>One thread, fixed small model, preregistered condition count, 32 MiB artifacts, and 1 GiB peak RSS.</x:v>
+        <x:v>Current: one thread/worker, zero protected/model downloads, 8 MiB planning cap. Future: one thread/worker, 2,908 parameters, 1,200 sec training, 32 MiB artifacts, 1 GiB RSS, zero new data/model downloads.</x:v>
       </x:c>
       <x:c r="N11" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; sensor_signal_ceiling; loop35_required_for_brain_specific</x:v>
       </x:c>
       <x:c r="O11" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P11" s="150" t="str">
-        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
-https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://github.com/facebookresearch/brain2qwerty/tree/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2
+https://www.jmlr.org/papers/v11/ojala10a.html
+https://arxiv.org/abs/1703.06670
+https://doi.org/10.1016/j.neuroimage.2018.09.074
+https://doi.org/10.1214/ss/1032280304
+https://docs.scipy.org/doc/scipy/reference/generated/scipy.stats.permutation_test.html
+https://pubmed.ncbi.nlm.nih.gov/28655633/</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="138" customHeight="1">
@@ -9631,7 +9698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a6a06ec2f8c4eab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdef9afbb47884f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc5965ba8188f4a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R26f55c33fed34576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R838582372f434d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9a76da59872f43bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R51613701d6ee46a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R179801f0993a430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R17bb993a549a48c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R245673e5627b4582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R040dd650ad454343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1ffe1ff0bcee4916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Ra7e901788ae34754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R7569e246faab4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9ae4555ea6fc43e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R519d19ba2c874e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rc0f6969dba9a4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rd958d047319f4ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc6deb249732540e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R27a6c0a8e2774552"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6bda3e2d1804dd0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbfa3c2e8420b44d6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1012,7 +1012,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1029,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:I37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="RiskRegisterTable" displayName="RiskRegisterTable" ref="A1:I38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I38"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Risk ID"/>
     <x:tableColumn id="2" name="Area"/>
@@ -1047,7 +1047,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PromptBankTable" displayName="PromptBankTable" ref="A1:C38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Loop ID"/>
     <x:tableColumn id="2" name="Loop Name"/>
@@ -1358,12 +1358,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="250" customHeight="1">
+    <x:row r="10" ht="280" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26, 28, 29, 30, and 31 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 31 defines a 10-condition encoder attribution matrix, a contingent 5-condition LLM/Neuro Token matrix, exact six-row intersection-union inference, 18 future gates, 24 refusals, and 19 false authorization flags. Its maximum future local claim is sensor-signal dependence; brain-specific attribution remains blocked on Loop 35. No Loop 31 cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-32 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 32 recommends one causal 32-parameter hidden affine adapter, four zero-shot/unlabeled/label-light/supervised modes, nested 0/2/4/8/16/32 sentence budgets, and physically separate 32/16/48 calibration/selection/final floors. It freezes 20 future gates, 26 refusals, and 22 false authorization flags. No candidate or mode is selected; S25 stays final-only. No Loop 32 participant/cache/signal/label/target/checkpoint/model/adapter/training/evaluation/stream/device/hardware operation exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7719ab952284e9d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f6d8f4e6f44c87"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428e15b765634b05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ade570ac8e4939"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4251,16 +4251,34 @@
         <x:v>Planning only. 10 encoder conditions; 5 contingent LLM conditions; 6 claim classes; 18 gates; 24 refusals; 19 authorization flags false. No protected input, model, training, validation, LLM, Neuro Token, S20/S25, stream, device, or hardware operation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="37"/>
-      <x:c r="B46" s="12"/>
-      <x:c r="C46" s="12"/>
-      <x:c r="D46" s="12"/>
-      <x:c r="E46" s="12"/>
-      <x:c r="F46" s="12"/>
-      <x:c r="G46" s="12"/>
-      <x:c r="H46" s="12"/>
-      <x:c r="I46" s="12"/>
+    <x:row r="46" ht="136" customHeight="1">
+      <x:c r="A46" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="str">
+        <x:v>32-R1</x:v>
+      </x:c>
+      <x:c r="C46" s="12" t="str">
+        <x:v>Count calibration information, not just adapter parameters; hold execution</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="str">
+        <x:v>Recommend one 32-parameter causal adapter and keep strict zero-shot, unlabeled, label-light, and supervised claims separate. Require physical 32/16/48 partitions, pre-calibration zero-shot prediction freeze, one chosen budget, one final-target open, and complete human burden. Keep S25 final-only.</x:v>
+      </x:c>
+      <x:c r="E46" s="12" t="str">
+        <x:v>docs/LOOP_32_PRIMARY_SOURCE_RESEARCH.md; registries/loop32_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F46" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G46" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H46" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 32 remains blocked on Loop 26/31 results and a separately approved fresh-person protocol</x:v>
+      </x:c>
+      <x:c r="I46" s="12" t="str">
+        <x:v>Planning only. 4 modes; 6 budgets; 32 target-trainable values; 32/16/48 floors; 6 conditions; 7 claims; 20 gates; 26 refusals; 22 authorization flags false; no candidate, protected access, model, adapter fit, training, or evaluation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37"/>
@@ -5976,7 +5994,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07be51e645f94b61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref35f65462e14b46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7066,6 +7084,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I37" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="124" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>R37</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Calibration leakage and burden</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Target signal or labels leak across fit, selection, and final evidence; selection supervision is hidden; calibrated performance is called zero-shot; or a tiny adapter is presented as a tiny human burden.</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Require physical 32/16/48 partitions, disjoint row/text hashes, zero-shot predictions frozen before calibration, one mode and budget, final targets opened once, label-inclusive burden, six controls, 20 gates, 26 refusals, and exact access/hash ledgers.</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Final rows influence statistics or selection; unlabeled mode uses target labels; selection labels are omitted; S25 is repurposed; multiple modes are run and only the best is promoted; or one calibrated person is generalized.</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7098,7 +7145,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8a36cc6e97a4592"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d707a956ca4584"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7633,13 +7680,13 @@
     </x:row>
     <x:row r="38" ht="120" customHeight="1">
       <x:c r="A38" s="39" t="str">
-        <x:v>Loop29-Research</x:v>
+        <x:v>Loop32-Research</x:v>
       </x:c>
       <x:c r="B38" s="39" t="str">
-        <x:v>Review Portable Sensing Translation Without Executing It</x:v>
+        <x:v>Review Fresh-Person Calibration Boundary Without Executing It</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
-        <x:v>Read docs/LOOP_29_PRIMARY_SOURCE_RESEARCH.md and registries/loop29_research_boundary.v0.json. Confirm the local-first scalp EEG lane, partner/lab OPM-MEG lane, cryogenic reference, non-neural controls, 15 requirements, four profiles, six qualification levels, 12 packet gates, 24 false permissions, 5,000,000,000-byte preferred and 10,000,000,000-byte absolute capacity limits, and exact 1,106,030,247-byte future S20+S25 allocation. Loop 29 remains Not Started. Storage is not download authorization. Do not open S20/S25 or real headers/signals/targets, run/train a model, select or purchase a device, import an SDK, open a socket/stream, contact a partner, touch hardware, or treat this planning research as portable decoding evidence.</x:v>
+        <x:v>Read docs/LOOP_32_PRIMARY_SOURCE_RESEARCH.md and registries/loop32_research_boundary.v0.json. Confirm four distinct modes, the causal 32-parameter adapter recommendation, nested 0/2/4/8/16/32 sentence budgets, physical 32/16/48 split floors, zero-shot-before-calibration freeze order, six conditions, seven claims, 20 gates, 26 refusals, and 22 false permissions. Loop 32 remains Not Started. Do not select or open a participant, repurpose S25, read signal/labels/targets, run a checkpoint or adapter, train, evaluate, download, stream, or touch a device; do not call calibration zero-shot or one person population evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="126" customHeight="1">
@@ -7664,10 +7711,21 @@
         <x:v>Read docs/LOOP_31_PRIMARY_SOURCE_RESEARCH.md and registries/loop31_research_boundary.v0.json. Confirm the 10-condition encoder matrix, contingent 5-condition LLM/Neuro Token matrix, five separate estimands, exact six-row intersection-union math, timing/context allowlist, target-blind prediction freeze, six claim classes, 18 future gates, 24 refusals, and 19 false permissions. Loop 31 remains Not Started. Do not open a cache, target, checkpoint, model, validation row, consumed S7/S21 evidence, S20/S25, LLM, Neuro Token, stream, device, or hardware; do not label sensor-signal dependence as brain-specific before Loop 35.</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" ht="148" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>Loop32-Research</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Review Fresh-Person Calibration Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Read docs/LOOP_32_PRIMARY_SOURCE_RESEARCH.md and registries/loop32_research_boundary.v0.json. Confirm four distinct modes, the causal 32-parameter adapter recommendation, nested 0/2/4/8/16/32 sentence budgets, physical 32/16/48 split floors, zero-shot-before-calibration freeze order, six conditions, seven claims, 20 gates, 26 refusals, and 22 false permissions. Loop 32 remains Not Started. Do not select or open a participant, repurpose S25, read signal/labels/targets, run a checkpoint or adapter, train, evaluate, download, stream, or touch a device; do not call calibration zero-shot or one person population evidence.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra622ebb4e2794e18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb50f813aca7a4ee9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8233,7 +8291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05621abc500a452d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f84c62375d04053"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8282,7 +8340,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loop 26 planning research defines the six-row predictive question but no experiment. Loop 27 selected S25 metadata only. Loop 28 defines strict zero-shot transfer. Loop 29 separates scalp EEG and partner/lab OPM-MEG. Loop 30 defines target-free local replay. Loop 31 planning research defines a 10-condition encoder and contingent 5-condition LLM attribution firewall; its experiment remains Not Started and brain-specific attribution is blocked on Loop 35. No Loop 31 preregistration, request, protected input, model, training, validation, LLM, Neuro Token, S20/S25, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-32 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 32 defines one causal 32-parameter adapter recommendation, four separate calibration claims, six nested sentence budgets, 32/16/48 physical split floors, a zero-shot-before-calibration freeze order, six final conditions, 20 gates, and 26 refusals. No Loop 32 candidate, preregistration, request, protected input, model, adapter fit, training, evaluation, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8302,7 +8360,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-31 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 31: 10 encoder + 5 contingent LLM conditions | sensor-signal ceiling / Loop 35 required for brain-specific attribution | all 20 execution flags false</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-32 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 32: 32-parameter adapter + 4 modes + 6 budgets + 32/16/48 physical floors | S25 final-only | all 20 execution flags false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -8862,7 +8920,7 @@
 https://pubmed.ncbi.nlm.nih.gov/28655633/</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="138" customHeight="1">
+    <x:row r="12" ht="216" customHeight="1">
       <x:c r="A12" s="126" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -8876,53 +8934,60 @@
         <x:v>P1 / L</x:v>
       </x:c>
       <x:c r="E12" s="114" t="str">
-        <x:v>What is the smallest honest calibration budget that improves a fresh person without training on their final evaluation rows?</x:v>
+        <x:v>What is the smallest honest calibration budget that improves one fresh person without using final rows for fitting, normalization, model selection, stopping, or thresholding?</x:v>
       </x:c>
       <x:c r="F12" s="114" t="str">
-        <x:v>Subject variability is a central barrier, and zero-shot versus calibrated performance must be separated.</x:v>
+        <x:v>Participant variability is central, but calibration information must be counted honestly. Strict zero-shot, unlabeled transductive, label-light, and supervised transfer are different claims; selection labels are supervision, and one calibrated person is not population evidence.</x:v>
       </x:c>
       <x:c r="G12" s="114" t="str">
-        <x:v>Build: Frozen adapter family, calibration-size schedule, train-only normalization, independent selection and final partitions, and time/compute report.
-Research: Calibration protocol covering unlabeled, label-light, and supervised cases with distinct claims.</x:v>
+        <x:v>Build: Future pointwise causal hidden affine adapter with 16 scales plus 16 biases over a frozen 2,908-parameter source model.
+Research: Completed four-mode taxonomy, nested 0/2/4/8/16/32 sentence schedule, physical split and human-burden contracts, zero-shot-before-calibration access order, six conditions, seven claim classes, 20 gates, and 26 refusals.</x:v>
       </x:c>
       <x:c r="H12" s="114" t="str">
-        <x:v>Data: Only a future authorized fresh participant with physically separated calibration, selection, and final partitions.
+        <x:v>Data: Planning used public sources and committed metadata only. A future candidate needs physically distinct, row- and semantic-text-disjoint recordings with at least 32 calibration, 16 selection, and 48 final unique completed sentences. S25 block 2 remains final-only and ineligible.
 Controls:
-- Frozen zero-shot source model.
-- Identity or normalization-only adapter.
-- Same-size signal-free prior and label-permutation control.
-- Multiple registered calibration sizes without final-partition reuse.</x:v>
+- frozen strict zero-shot
+- exact identity adapter
+- selected 32-parameter adapter
+- source-train-only no-signal prior
+- robust normalization-only
+- same-budget label derangement for labeled modes</x:v>
       </x:c>
       <x:c r="I12" s="114" t="str">
-        <x:v>- zero-shot and calibrated CER
-- gain per calibration item and minute
-- calibration compute and wall time
-- no-harm item count
-- selection-to-final generalization</x:v>
+        <x:v>- macro sentence CER gain versus zero-shot and prior
+- gain per item, active second, total minute, and label
+- 65,535 random sign assignments plus observed
+- practical margins and strict control wins
+- no-harm items, wins/ties/losses, selection-to-final generalization
+- burden, runtime, RSS, bytes, updates, warnings, unavailable fields, and hashes</x:v>
       </x:c>
       <x:c r="J12" s="114" t="str">
-        <x:v>Acceptance: Promote a calibrated-person claim only when a preselected adapter improves the one-time final partition against zero-shot and prior controls within the declared budget.
-Stop: Do not call calibration zero-shot, do not pick a budget on final data, and park adapters that help validation but harm the final partition.</x:v>
+        <x:v>Acceptance: Freeze zero-shot final predictions before any target-person calibration access; freeze one mode, adapter, and budget before adapted final predictions; open final targets once; pass recommended 0.05 macro-CER gains versus zero-shot and prior, paired p&lt;=0.05 gates, and strict applicable-control wins.
+Stop: Park on a tie, final harm, split/text/hash/access/privacy/resource failure, hidden labels, multi-mode best-of selection, or any calibrated-as-zero-shot/population/brain-specific overclaim. Margins remain unfrozen until preregistration.</x:v>
       </x:c>
       <x:c r="K12" s="114" t="str">
-        <x:v>Loops: 28, 31
-External: approved_fresh_person_protocol</x:v>
+        <x:v>Loops: 25, 26, 28, 31
+External: approved fresh-person protocol; separate candidate preregistration and exact authorization; Loop 35 for brain-specific wording</x:v>
       </x:c>
       <x:c r="L12" s="114" t="str">
-        <x:v>Planning only. Participant data, labels, calibration, training, and final evaluation remain unauthorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started. No candidate or mode is selected. Participant/cache/signal/label/target access, checkpoint/model/control runs, adapter fitting, parameter updates, training, final evaluation, S20/S25 access, consumed-evidence reopen, downloads, streams, devices, and hardware are unauthorized.</x:v>
       </x:c>
       <x:c r="M12" s="114" t="str">
-        <x:v>One thread, one worker, fixed small adapter family, 32 MiB outputs, and preregistered maximum calibration minutes.</x:v>
+        <x:v>Current: one thread/worker, 6 public network operations, zero protected bytes, 8 MiB planning cap. Future: one thread/worker, 2,908 frozen base plus at most 32 trainable values, 1,200 sec adapter fits, 1 GiB RSS, 32 MiB artifacts, zero new data/model downloads before separate authorization.</x:v>
       </x:c>
       <x:c r="N12" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; four_modes; 32_parameter_ceiling; no_candidate; S25_final_only</x:v>
       </x:c>
       <x:c r="O12" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P12" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://arxiv.org/abs/2404.15319</x:v>
+https://github.com/facebookresearch/brain2qwerty/tree/3bf5a4099ca0d23bbe994b2287905760236e56e0/brain2qwerty_v2
+https://ojs.aaai.org/index.php/AAAI/article/view/10306
+https://pubmed.ncbi.nlm.nih.gov/31034407/
+https://pmc.ncbi.nlm.nih.gov/articles/PMC10790953/
+https://pubmed.ncbi.nlm.nih.gov/27989847/</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="138" customHeight="1">
@@ -9698,7 +9763,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdef9afbb47884f30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4206a4616ad347c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1ffe1ff0bcee4916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Ra7e901788ae34754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R7569e246faab4796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9ae4555ea6fc43e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R519d19ba2c874e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rc0f6969dba9a4049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rd958d047319f4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc6deb249732540e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R27a6c0a8e2774552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R91043209c9244cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R43036eed11ab44ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R3fcfc95b6f2447fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R10576f653d814073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R32f248d3a3124b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R9526d72f1fa143a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rf082dfa417544f26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R62d2c8fe4c244344"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R8edcf127aea44723"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbfa3c2e8420b44d6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6029d1574b144c01"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-32 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 32 recommends one causal 32-parameter hidden affine adapter, four zero-shot/unlabeled/label-light/supervised modes, nested 0/2/4/8/16/32 sentence budgets, and physically separate 32/16/48 calibration/selection/final floors. It freezes 20 future gates, 26 refusals, and 22 false authorization flags. No candidate or mode is selected; S25 stays final-only. No Loop 32 participant/cache/signal/label/target/checkpoint/model/adapter/training/evaluation/stream/device/hardware operation exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-33 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 33 recommends nested 8/16/24/32/44/55 unique-sentence prefixes, at most three optimization seeds and 18 candidate fits, size-matched no-signal priors, and one target-blind shared Loop 26/31/33 validation event. Every prediction must hash-freeze before all six validation targets open once. It freezes 20 gates, 30 refusals, and 23 false authorization flags. Physical-repetition evidence is unavailable, acquisition is not recommended, and no Loop 33 protected/model/training/scoring operation exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f6d8f4e6f44c87"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0516e5438d14daa"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ade570ac8e4939"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6b3249453ae4a6d"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4281,15 +4281,33 @@
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="37"/>
-      <x:c r="B47" s="12"/>
-      <x:c r="C47" s="12"/>
-      <x:c r="D47" s="12"/>
-      <x:c r="E47" s="12"/>
-      <x:c r="F47" s="12"/>
-      <x:c r="G47" s="12"/>
-      <x:c r="H47" s="12"/>
-      <x:c r="I47" s="12"/>
+      <x:c r="A47" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B47" s="12" t="str">
+        <x:v>33-R1</x:v>
+      </x:c>
+      <x:c r="C47" s="12" t="str">
+        <x:v>Spend the shared validation event once; hold execution and acquisition</x:v>
+      </x:c>
+      <x:c r="D47" s="12" t="str">
+        <x:v>Recommend nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 fits, and matched priors. Freeze Loop 33 with Loop 26 before the first validation target opens; otherwise a later curve is exploratory. Duplicated arrays are not physical repeated acquisitions, and no public scaling exponent transfers to this tiny local design.</x:v>
+      </x:c>
+      <x:c r="E47" s="12" t="str">
+        <x:v>docs/LOOP_33_PRIMARY_SOURCE_RESEARCH.md; registries/loop33_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F47" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G47" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H47" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; co-preregister Loop 26 and Loop 33 before any shared validation-target open</x:v>
+      </x:c>
+      <x:c r="I47" s="12" t="str">
+        <x:v>Planning only. 6 prefixes; 3-seed/18-fit ceiling; 4 conditions; 7 outcomes; 7 claims; 20 gates; 30 refusals; 23 authorization flags false. No protected access, model, training, score, physical-repetition study, or acquisition.</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37"/>
@@ -5994,7 +6012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref35f65462e14b46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d6a38ae93b4886"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7113,6 +7131,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I38" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>R38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Scaling and acquisition overclaim</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>A tiny after-the-fact curve, optimizer seeds, duplicated arrays, minutes of signal, or another study's exponent is presented as a prospective scaling law, biological replication, physical repetition, recording hours, or guaranteed acquisition value.</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Freeze Loop 33 before the shared target open; bind six nested prefixes, matched priors, fixed model/data contracts, one target open, 20 gates, and 30 refusals. Report only 8-55 unique sentences, distinguish physical recordings from array reuse, and require a separate acquisition packet.</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Validation targets open before Loop 33 freezes; prefixes or seeds change after scoring; duplicate rows are called recordings; CPU time is called energy; a 90-hour exponent or population conclusion is transferred; or data is acquired without a separate exact packet.</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7145,7 +7192,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d707a956ca4584"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f40f0d4f2c4d5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7722,10 +7769,21 @@
         <x:v>Read docs/LOOP_32_PRIMARY_SOURCE_RESEARCH.md and registries/loop32_research_boundary.v0.json. Confirm four distinct modes, the causal 32-parameter adapter recommendation, nested 0/2/4/8/16/32 sentence budgets, physical 32/16/48 split floors, zero-shot-before-calibration freeze order, six conditions, seven claims, 20 gates, 26 refusals, and 22 false permissions. Loop 32 remains Not Started. Do not select or open a participant, repurpose S25, read signal/labels/targets, run a checkpoint or adapter, train, evaluate, download, stream, or touch a device; do not call calibration zero-shot or one person population evidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>Loop33-Research</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Review Bounded Scaling Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Read docs/LOOP_33_PRIMARY_SOURCE_RESEARCH.md and registries/loop33_research_boundary.v0.json. Confirm nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 fits, matched no-signal priors, the target-blind shared Loop 26/31/33 validation order, four conditions, seven outcomes, seven claims, 20 gates, 30 refusals, and 23 false permissions. Loop 33 remains Not Started. Do not open train/validation payloads or targets, run a model/control, train, score, duplicate rows as physical repetitions, acquire data, transfer a 90-hour exponent, or claim population, energy, real-time, portable, at-home, assistive, diagnostic, or clinical behavior.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb50f813aca7a4ee9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafddda033da34387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8291,7 +8349,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f84c62375d04053"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb95da1dd9d34a7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8340,7 +8398,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-32 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 32 defines one causal 32-parameter adapter recommendation, four separate calibration claims, six nested sentence budgets, 32/16/48 physical split floors, a zero-shot-before-calibration freeze order, six final conditions, 20 gates, and 26 refusals. No Loop 32 candidate, preregistration, request, protected input, model, adapter fit, training, evaluation, S20/S25, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-33 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 33 adds a prospective 8/16/24/32/44/55 unique-sentence curve, one shared target open, and no acquisition now.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8360,7 +8418,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-32 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 32: 32-parameter adapter + 4 modes + 6 budgets + 32/16/48 physical floors | S25 final-only | all 20 execution flags false</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-33 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 33: six prefixes, three-seed/18-fit ceiling, 20 gates, 30 refusals, no physical-repetition lane or acquisition | all execution flags false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -9004,53 +9062,57 @@
         <x:v>P1 / L</x:v>
       </x:c>
       <x:c r="E13" s="114" t="str">
-        <x:v>Do additional hours and additional unique sentences improve the fixed local encoder, and where does the small-data curve stop paying off?</x:v>
+        <x:v>Within the existing 55 source-train sentence instances, does additional unique training data improve one fixed tiny causal encoder, and is its observed upper boundary still improving enough to justify a separate future acquisition decision?</x:v>
       </x:c>
       <x:c r="F13" s="114" t="str">
-        <x:v>Scaling evidence guides acquisition better than guessing whether to collect more repetitions, more sentences, or more people.</x:v>
+        <x:v>A prospective bounded curve can guide whether another metadata-only acquisition packet is worth preparing without guessing, reopening consumed evidence, or transferring Brain2Qwerty v2's 90-hour scaling exponent.</x:v>
       </x:c>
       <x:c r="G13" s="114" t="str">
-        <x:v>Build: Nested train-prefix runner with fixed validation, unique-sentence and repetition controls, multi-seed uncertainty, and compute ledger.
-Research: Local scaling design that avoids extrapolating Brain2Qwerty v2's 90-hour curve to the tiny SpanishBCBL setting.</x:v>
+        <x:v>Build: Future target-blind runner over strictly nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 candidate fits, one fixed 2,908-parameter encoder, matched priors, and complete access/resource/hash ledgers.
+Research: Completed shared-validation access order, unique-versus-physical-repetition firewall, descriptive trend rules, seven outcomes, seven claims, 20 gates, and 30 refusals.</x:v>
       </x:c>
       <x:c r="H13" s="114" t="str">
-        <x:v>Data: Future authorized train and validation partitions only; no fresh test opening and no larger architecture.
+        <x:v>Data: Planning used public primary sources and committed metadata only. Future execution may use separately authorized 55 source-train and six reserved validation rows; source test, session 2, S7, S20, S25, new data, and physical repetitions remain closed.
 Controls:
-- Nested subsets preserve participant and sentence membership.
-- Matched total-trial comparison of repeated versus unique sentences.
-- No-signal baseline at every data size.
-- Fixed architecture, optimizer, stopping rule, and seed list.</x:v>
+- Strict target-blind nested prefixes; 55 is the complete source train.
+- Fixed person/session/device/channels/rate/model/optimizer/stopping/decode/metrics.
+- Size-matched train-only no-signal prior at every prefix.
+- Every Loop 26/31/33 prediction hash-frozen before one six-target open.
+- Distinct recordings required for any physical-repetition claim.</x:v>
       </x:c>
       <x:c r="I13" s="114" t="str">
-        <x:v>- CER versus hours, trials, and unique sentences
-- slope and uncertainty on registered scale
-- neural-minus-prior margin by size
-- training time and energy proxy if available
-- marginal gain per added MiB and minute</x:v>
+        <x:v>- macro sentence CER by item, seed, prefix, and matched prior
+- descriptive slope versus log2 unique sentences and every adjacent delta
+- smallest-band to upper-band and upper-band-over-prior practical gains
+- unique sentences, physical trials, valid seconds/minutes, bytes, runtime, RSS, and artifacts
+- exact access, warning, unavailable-field, and hash ledgers</x:v>
       </x:c>
       <x:c r="J13" s="114" t="str">
-        <x:v>Acceptance: Proceed only if a preregistered monotonic or model-based trend is stable across seeds and remains above the no-signal control; report non-saturation only within observed bounds.
-Stop: Stop the curve when gains disappear, controls fail, or the resource budget is reached; never infer a large-scale law from the bounded local range.</x:v>
+        <x:v>Acceptance: Freeze Loop 33 before any validation target opens; hash-freeze all predictions before one target open; require negative slopes for every registered seed, recommended 0.05 smallest-to-upper and upper-over-prior gains, Loop 31 attribution for sensor wording, and all 20 gates.
+Stop: Park on a lost access order, full-size prior failure, unstable trend, target-informed prefix, fake physical repetition, cap/ledger/hash failure, or post-target restart. Never infer a universal law, saturation beyond 55, acquisition value, population behavior, energy, real-time, portable, at-home, assistive, diagnostic, or clinical performance.</x:v>
       </x:c>
       <x:c r="K13" s="114" t="str">
         <x:v>Loops: 26, 31
-External: separate_bounded_training_authorization</x:v>
+External: shared Loop 26/33 preregistration before validation target open; separate bounded training and one-time validation authorization</x:v>
       </x:c>
       <x:c r="L13" s="114" t="str">
-        <x:v>Planning only. Training prefixes, validation runs, and energy measurements are unauthorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started. No protected cache/signal/target read, checkpoint/model/control run, training, parameter update, prediction, validation score, physical-repetition study, acquisition, download, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M13" s="114" t="str">
-        <x:v>One thread and worker, fixed tiny architecture, at most six train sizes and three seeds if authorized, 32 MiB outputs, and a preregistered CPU-hour cap.</x:v>
+        <x:v>Current: one thread/worker, 6 public web operations, zero protected bytes, 8 MiB planning cap. Future: one thread/worker, 2,908 parameters, at most 18 candidate fits, 1,200 sec total training, 1 GiB RSS, 32 MiB artifacts, zero new downloads, and no energy claim without direct measurement.</x:v>
       </x:c>
       <x:c r="N13" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; planning_research_complete; prefixes=8|16|24|32|44|55; shared_validation_prospective; no_repetition_lane; no_acquisition</x:v>
       </x:c>
       <x:c r="O13" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P13" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://arxiv.org/abs/2404.15319</x:v>
+https://arxiv.org/abs/2501.15322
+https://arxiv.org/abs/2407.07595
+https://pubmed.ncbi.nlm.nih.gov/22336388/
+https://pubmed.ncbi.nlm.nih.gov/28655633/</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="138" customHeight="1">
@@ -9763,7 +9825,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4206a4616ad347c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R699717b72e0c41c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R91043209c9244cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R43036eed11ab44ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R3fcfc95b6f2447fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R10576f653d814073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R32f248d3a3124b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R9526d72f1fa143a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rf082dfa417544f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R62d2c8fe4c244344"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R8edcf127aea44723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdb83a01b6f9c458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R21c930aff0e34ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R36b8427d74fe444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rf61bf2aeecd24872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R2e9a1283bdf44877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd7587698b16b4166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R443c1f83587043e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Reb8d55f952d041a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R93c91127bc154b80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6029d1574b144c01"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8553a034981464e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-33 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 33 recommends nested 8/16/24/32/44/55 unique-sentence prefixes, at most three optimization seeds and 18 candidate fits, size-matched no-signal priors, and one target-blind shared Loop 26/31/33 validation event. Every prediction must hash-freeze before all six validation targets open once. It freezes 20 gates, 30 refusals, and 23 false authorization flags. Physical-repetition evidence is unavailable, acquisition is not recommended, and no Loop 33 protected/model/training/scoring operation exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-34 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable, separates seven confidence semantics and eight score/control roles, and recommends fresh target-free synthetic calibration/selection/final counts of 128/64/256. The six real validation rows remain reserved for Loops 26/31/33 and cannot fit and independently qualify confidence. Loop 34 freezes 20 future gates, 30 refusals, and 26 false authorization flags. No fixture, confidence fit, target open, scoring, product-confidence, or protected-data operation exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0516e5438d14daa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26a48c6f718546ea"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6b3249453ae4a6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c357039deb34bce"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4310,15 +4310,33 @@
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="37"/>
-      <x:c r="B48" s="12"/>
-      <x:c r="C48" s="12"/>
-      <x:c r="D48" s="12"/>
-      <x:c r="E48" s="12"/>
-      <x:c r="F48" s="12"/>
-      <x:c r="G48" s="12"/>
-      <x:c r="H48" s="12"/>
-      <x:c r="I48" s="12"/>
+      <x:c r="A48" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B48" s="12" t="str">
+        <x:v>34-R1</x:v>
+      </x:c>
+      <x:c r="C48" s="12" t="str">
+        <x:v>Keep confidence unavailable until independent evidence exists; hold execution</x:v>
+      </x:c>
+      <x:c r="D48" s="12" t="str">
+        <x:v>Separate raw ranking, calibrated probability, selective policy, conformal bounded risk, revision stability, and product-visible confidence. Reserve the six real validation rows for Loops 26/31/33. Recommend fresh 128/64/256 synthetic partitions and one final open only after every score, mapping, threshold, policy, prediction, and hash freezes.</x:v>
+      </x:c>
+      <x:c r="E48" s="12" t="str">
+        <x:v>docs/LOOP_34_PRIMARY_SOURCE_RESEARCH.md; registries/loop34_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F48" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G48" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H48" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 34 remains blocked on Loop 30/31 execution evidence and a separately authorized fresh synthetic confidence lane</x:v>
+      </x:c>
+      <x:c r="I48" s="12" t="str">
+        <x:v>Planning only. 7 semantics; 8 score/control roles; recommended 128/64/256 partitions; 8 outcomes; 7 claims; 20 gates; 30 refusals; 26 authorization flags false. Confidence unavailable; no fixture, fit, target, scoring, or product-confidence operation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37"/>
@@ -6012,7 +6030,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d6a38ae93b4886"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbc06fe9ce124536"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7160,6 +7178,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I39" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>R39</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Confidence, abstention, and revision overclaim</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>A raw score, entropy, margin, or stable prefix is called a correctness probability; six reused real rows are presented as independent qualification; abstain-all hides error; ECE or AURC stands alone; or a synthetic policy is promoted as real confidence.</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Require fresh disjoint calibration/selection/final groups, seven semantic levels, eight score/control roles, bounded exact-sequence loss, registered useful coverage, full working-point and generalized-risk reporting, frozen mappings and policies before one final open, Loop 30 clock domains, 20 gates, and 30 refusals.</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Calibration, selection, or final groups overlap; a final target changes a threshold or bin; stability is called correctness; raw CER is silently clipped; dependence is omitted; below-floor coverage passes; revision delay is hidden; or synthetic evidence is transferred to real/product confidence.</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7192,7 +7239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f40f0d4f2c4d5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb336f4934aa348c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7780,10 +7827,21 @@
         <x:v>Read docs/LOOP_33_PRIMARY_SOURCE_RESEARCH.md and registries/loop33_research_boundary.v0.json. Confirm nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 fits, matched no-signal priors, the target-blind shared Loop 26/31/33 validation order, four conditions, seven outcomes, seven claims, 20 gates, 30 refusals, and 23 false permissions. Loop 33 remains Not Started. Do not open train/validation payloads or targets, run a model/control, train, score, duplicate rows as physical repetitions, acquire data, transfer a 90-hour exponent, or claim population, energy, real-time, portable, at-home, assistive, diagnostic, or clinical behavior.</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>Loop34-Research</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Review Confidence Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Read docs/LOOP_34_PRIMARY_SOURCE_RESEARCH.md and registries/loop34_research_boundary.v0.json. Confirm seven confidence semantics, eight score/control roles, recommended fresh 128/64/256 synthetic calibration/selection/final partitions, the six-row real-data insufficiency boundary, bounded exact-sequence loss, generalized-risk and revision-delay reporting, eight outcomes, seven claims, 20 gates, 30 refusals, and 26 false permissions. Loop 34 remains Not Started and confidence unavailable. Do not generate a fixture, reuse real/consumed text, compute features, fit a probability map or threshold, open targets, score, expose confidence, access S20/S25, or call stability correctness, raw score probability, or synthetic evidence real confidence.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafddda033da34387"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0cd44ed6c24be8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8349,7 +8407,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb95da1dd9d34a7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159dc329a39b41a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8398,7 +8456,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-33 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 33 adds a prospective 8/16/24/32/44/55 unique-sentence curve, one shared target open, and no acquisition now.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-34 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable and requires fresh three-way evidence rather than reusing six real validation rows.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8418,7 +8476,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-33 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 33: six prefixes, three-seed/18-fit ceiling, 20 gates, 30 refusals, no physical-repetition lane or acquisition | all execution flags false</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-34 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 34: seven semantics, eight scores/controls, 128/64/256 fresh synthetic partitions, 20 gates, 30 refusals, confidence unavailable | all execution flags false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -9129,52 +9187,59 @@
         <x:v>P1 / M</x:v>
       </x:c>
       <x:c r="E14" s="114" t="str">
-        <x:v>Can the system identify when to abstain or delay output without tuning confidence on the final test?</x:v>
+        <x:v>Can a target-blind score rank sequence errors, support a preregistered abstention rule on an independent partition, and keep revision stability separate from calibrated correctness?</x:v>
       </x:c>
       <x:c r="F14" s="114" t="str">
-        <x:v>A decoder that knows when it is unreliable is more useful and safer than one that always emits fluent text.</x:v>
+        <x:v>A decoder that can refuse usefully is safer than one that always emits fluent text, but raw scores, probability calibration, selective risk, revision stability, and product-visible confidence are different claims.</x:v>
       </x:c>
       <x:c r="G14" s="114" t="str">
-        <x:v>Build: Validation-fit confidence contract, risk-coverage report, abstention and revision policy, calibration diagnostics, and user-visible unavailable state.
-Research: Selective-prediction and conformal-risk review mapped to tiny correlated sequence data.</x:v>
+        <x:v>Build: Future seven-level confidence contract, eight score/control roles, full working-point and generalized-risk report, abstention/revision policy, probability diagnostics, and explicit unavailable state.
+Research: Completed selective-prediction, conformal-risk, calibration, ECE, generalized-risk, small-sample, leakage, and latency boundary with eight outcomes, seven claims, 20 gates, and 30 refusals.</x:v>
       </x:c>
       <x:c r="H14" s="114" t="str">
-        <x:v>Data: Synthetic first; any real use requires separate calibration and final partitions and cannot reopen consumed evidence.
+        <x:v>Data: Recommend fresh target-free synthetic calibration/selection/final counts of 128/64/256 grouped by generation block and schedule. The six real source-validation rows remain reserved for Loops 26/31/33 and cannot fit and independently qualify confidence.
 Controls:
-- Confidence-free always-predict baseline.
-- Entropy, margin, stability, and prior-only confidence candidates selected on validation only.
-- Coverage levels fixed before final evaluation.
-- Sequence and item clustering respected in uncertainty estimates.</x:v>
+- normalized log score, entropy, margin, and prefix stability candidates
+- train-only prior, fixed-random, always-predict, and unreachable post-hoc oracle roles
+- exactly one score/policy selected on selection only
+- all mappings, thresholds, predictions, and hashes frozen before one final open
+- no real, consumed, or current-item target leakage</x:v>
       </x:c>
       <x:c r="I14" s="114" t="str">
-        <x:v>- risk-coverage curve and area
-- error rate at registered coverage
-- abstention rate
-- expected calibration error where sample size permits
-- revision count and time-to-stability</x:v>
+        <x:v>- exact-sequence 0/1 error as primary bounded loss; raw CER separately
+- full risk-coverage table and accepted/generalized error at registered coverage
+- legacy AURC with limitations plus AUGRC-equivalent area
+- Brier/log loss/reliability only for calibrated probabilities; ECE secondary
+- abstention, revisions, first-output/stability/finalization/added-delay times
+- exact access, warning, unavailable-field, resource, and hash ledgers</x:v>
       </x:c>
       <x:c r="J14" s="114" t="str">
-        <x:v>Acceptance: Expose confidence only if higher declared confidence reliably lowers error on an independent partition and the registered coverage-risk rule passes.
-Stop: If confidence does not rank errors or sample size is insufficient, publish confidence as unavailable rather than inventing a score.</x:v>
+        <x:v>Acceptance: Pass all 20 gates with disjoint groups, target-blind generation, one selected score and policy, one final open, ranking above prior/random controls, useful minimum coverage, bounded conformal loss, named dependence assumptions, and complete ledgers.
+Stop: Publish unavailable on insufficient evidence, leakage, no ranking, below-floor coverage, unbounded loss, omitted dependence, post-final change, resource failure, or synthetic-to-real transfer. Never call stability correctness or raw score probability.</x:v>
       </x:c>
       <x:c r="K14" s="114" t="str">
         <x:v>Loops: 30, 31
-External: separate_calibration_evaluation_authorization</x:v>
+External: separate synthetic confidence preregistration and exact authorization; fresh physical calibration/selection/final evidence for any real claim</x:v>
       </x:c>
       <x:c r="L14" s="114" t="str">
-        <x:v>Planning only. No confidence fitting, model inference, or final-partition opening is authorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started. Confidence unavailable. No fixture generation, confidence feature, mapping or threshold fit, model inference, target open, scoring, product-visible confidence, real/consumed data access, download, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M14" s="114" t="str">
-        <x:v>Dependency-free metrics where possible, one thread, 16 MiB artifacts, and no additional model training.</x:v>
+        <x:v>Current: one thread/worker, 5 public web operations, zero protected bytes, 8 MiB planning cap. Future: one thread/worker, zero decoder training, at most 6 scalar mapping fits, 120 sec runtime, 1 GiB RSS, 16 MiB artifacts, zero downloads, and no energy claim without direct measurement.</x:v>
       </x:c>
       <x:c r="N14" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning_research_complete_no_confidence_fit_or_result_unauthorized; confidence_unavailable; semantics=7; score_controls=8; partitions=128|64|256; no_existing_real_confidence_partition</x:v>
       </x:c>
       <x:c r="O14" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P14" s="150" t="str">
-        <x:v>https://arxiv.org/abs/1705.08500</x:v>
+        <x:v>https://papers.neurips.cc/paper_files/paper/2017/hash/4a8423d5e91fda00bb7e46540e2b0cf1-Abstract.html
+https://research.google/pubs/conformal-risk-control/
+https://arxiv.org/abs/2202.13415
+https://proceedings.mlr.press/v70/guo17a.html
+https://arxiv.org/abs/1904.01685
+https://arxiv.org/abs/2407.01032</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="138" customHeight="1">
@@ -9825,7 +9890,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R699717b72e0c41c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re701abc426774c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdb83a01b6f9c458b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R21c930aff0e34ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R36b8427d74fe444f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rf61bf2aeecd24872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R2e9a1283bdf44877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd7587698b16b4166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R443c1f83587043e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Reb8d55f952d041a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R93c91127bc154b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R9240e0bce632432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rc91a65904b0c48c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R108c126c15c94b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8abc04ad2f0e4db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rf868902445ab480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rf9d52067b7834243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R2d3481f477684f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R3a554e75643d4f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R3b8802b0235247c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8553a034981464e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R786ee668b0d44c95"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-34 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable, separates seven confidence semantics and eight score/control roles, and recommends fresh target-free synthetic calibration/selection/final counts of 128/64/256. The six real validation rows remain reserved for Loops 26/31/33 and cannot fit and independently qualify confidence. Loop 34 freezes 20 future gates, 30 refusals, and 26 false authorization flags. No fixture, confidence fit, target open, scoring, product-confidence, or protected-data operation exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-35 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable and reserves the six real validation rows for Loops 26/31/33. Loop 35 freezes 10 confound classes, 9 future synchronized stream classes, 13 conditions, 3 independently authorized stages, 24 gates, 32 refusals, and 31 false authorization flags. Current S21/S7 evidence lacks a fresh complete peripheral-control set. Its maximum future local claim is incremental brain-sensor information beyond recorded controls, not absolute brain origin. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26a48c6f718546ea"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96116260641a492f"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c357039deb34bce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc02b225451e44e21"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4338,15 +4338,31 @@
         <x:v>Planning only. 7 semantics; 8 score/control roles; recommended 128/64/256 partitions; 8 outcomes; 7 claims; 20 gates; 30 refusals; 26 authorization flags false. Confidence unavailable; no fixture, fit, target, scoring, or product-confidence operation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="37"/>
-      <x:c r="B49" s="12"/>
-      <x:c r="C49" s="12"/>
-      <x:c r="D49" s="12"/>
-      <x:c r="E49" s="12"/>
-      <x:c r="F49" s="12"/>
-      <x:c r="G49" s="12"/>
-      <x:c r="H49" s="12"/>
+    <x:row r="49" ht="198" hidden="0" customHeight="1">
+      <x:c r="A49" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B49" s="12" t="str">
+        <x:v>35-R1</x:v>
+      </x:c>
+      <x:c r="C49" s="12" t="str">
+        <x:v>Require recorded peripheral controls before bounded neural attribution; hold execution</x:v>
+      </x:c>
+      <x:c r="D49" s="12" t="str">
+        <x:v>Freeze 10 confound classes, 9 future synchronized streams, 13 conditions, 3 separate stages, 24 gates, and 32 refusals. Missing controls remain unavailable. Current S21/S7 evidence cannot close the firewall; a future local pass can claim only incremental brain-sensor information beyond recorded controls, not absolute brain origin.</x:v>
+      </x:c>
+      <x:c r="E49" s="12" t="str">
+        <x:v>docs/LOOP_35_PRIMARY_SOURCE_RESEARCH.md; registries/loop35_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F49" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G49" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H49" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 35 remains blocked on an actual Loop 31 result and separately authorized fresh synchronized multimodal evidence</x:v>
+      </x:c>
       <x:c r="I49" s="12"/>
     </x:row>
     <x:row r="50">
@@ -6030,7 +6046,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbc06fe9ce124536"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6053d6fba41e4925"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7207,6 +7223,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I40" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>R40</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Peripheral confound and neural-origin overclaim</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Key timing, prompt/target leakage, eye activity, distal/proximal muscle, motion, audio/environment, physiology, equipment, or task identity is credited to brain-specific information because a sensor is labeled EEG/MEG or was artifact rejected.</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Require the 10-class registry, 9 synchronized streams, 13 conditions, physical 32/16/48 partitions, strongest-peripheral selection, train-only residualization, one final open, 24 gates, 32 refusals, and fail-closed missing controls. Cap the claim at incremental information beyond recorded controls.</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>A required peripheral stream is absent or imputed; key/prompt content enters features; a nonbrain condition ties or wins; clocks/residualization fail; a final target changes a choice; sensor dependence is called brain origin; or overt typing is generalized to no-keypress/patient use.</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7239,7 +7284,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb336f4934aa348c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b11d099ef294229"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7838,10 +7883,24 @@
         <x:v>Read docs/LOOP_34_PRIMARY_SOURCE_RESEARCH.md and registries/loop34_research_boundary.v0.json. Confirm seven confidence semantics, eight score/control roles, recommended fresh 128/64/256 synthetic calibration/selection/final partitions, the six-row real-data insufficiency boundary, bounded exact-sequence loss, generalized-risk and revision-delay reporting, eight outcomes, seven claims, 20 gates, 30 refusals, and 26 false permissions. Loop 34 remains Not Started and confidence unavailable. Do not generate a fixture, reuse real/consumed text, compute features, fit a probability map or threshold, open targets, score, expose confidence, access S20/S25, or call stability correctness, raw score probability, or synthetic evidence real confidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>Loop35-Research</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Review Peripheral-Confound Firewall Without Executing It</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Read docs/LOOP_35_PRIMARY_SOURCE_RESEARCH.md and registries/loop35_research_boundary.v0.json. Confirm 10 confound classes, 9 future synchronized stream classes, 13 conditions, 3 separately authorized stages, physical 32/16/48 recommendations, the strongest-peripheral and brain-sensor estimands, 65,535 paired assignments plus observed, 8 outcomes, 7 claims, 24 gates, 32 refusals, and 31 false permissions. Loop 35 remains Not Started. Do not generate a fixture, reopen consumed S7/S21 evidence, record EOG/EMG/gaze/motion/audio, open protected data or targets, run a model/control, fit residualization, train, score, download, access S20/S25, stream, touch a device/hardware, impute missing controls, or claim absolute brain origin, no-keypress transfer, patient benefit, real-time behavior, portable hardware, or clinical use.</x:v>
+      </x:c>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec0cd44ed6c24be8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e447b1c4bd24dbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8407,7 +8466,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159dc329a39b41a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6970f005c3a44da6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9242,7 +9301,7 @@
 https://arxiv.org/abs/2407.01032</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="138" customHeight="1">
+    <x:row r="15" ht="108" hidden="0" customHeight="1">
       <x:c r="A15" s="126" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -9256,54 +9315,61 @@
         <x:v>P0 / L</x:v>
       </x:c>
       <x:c r="E15" s="114" t="str">
-        <x:v>Is apparent decoding driven by brain signal, or by keystroke timing, muscle, eye, motion, audio, or prompt leakage?</x:v>
+        <x:v>Does a candidate add predictive information beyond every recorded timing and peripheral control, or can leakage, ocular activity, muscle, motion, audio/environment, physiology, equipment, or task identity explain it?</x:v>
       </x:c>
       <x:c r="F15" s="114" t="str">
-        <x:v>Prompted typing strongly recruits motor systems, so a positive score is not enough to establish neural specificity.</x:v>
+        <x:v>Overt prompted typing couples brain sensors to key timing, gaze, muscle, motion, audio/visual context, and behavior. A positive EEG/MEG score or artifact-rejected channel does not establish physical origin.</x:v>
       </x:c>
       <x:c r="G15" s="114" t="str">
-        <x:v>Build: Confound registry, synchronized brain-only/peripheral-only/combined protocol, shortcut audits, and claim-blocking report fields.
-Research: Primary-source confound taxonomy for prompted typing and future no-keypress translation.</x:v>
+        <x:v>Build: Future 10-class confound registry, 9-stream synchronization contract, 13-condition matrix, train-only residualization, and fail-closed unavailable fields.
+Research: Completed v1/v2 task audit, eye/EMG/MEG artifact review, three-stage evidence plan, eight outcomes, seven claims, 24 gates, and 32 refusals.</x:v>
       </x:c>
       <x:c r="H15" s="114" t="str">
-        <x:v>Data: Protocol and synthetic timing fixtures first; real multimodal collection requires separate consent, retention, device, and acquisition authorization.
+        <x:v>Data: Current S21 has 102 magnetometers and timing but no synchronized EOG/EMG/gaze/motion/audio in the committed cache; consumed S7 named 3 EOG channels but its 61-channel cache contains none.
 Controls:
-- Keystroke timing and key identity without neural samples.
-- Peripheral-only channels including EOG, EMG, motion, microphone, or hand tracking when actually recorded.
-- Brain-only channels with synchronized event structure.
-- Time-shift, channel-drop, and event-jitter controls.</x:v>
+- no-signal and timing-only baselines
+- key-identity and prompt/target leak sentinels that invalidate rather than compete
+- ocular, distal muscle, proximal muscle, motion, and audio/environment conditions
+- strongest combined peripheral comparator
+- brain-sensor-only, train-only residualized, and all-stream conditions
+- missing controls remain unavailable, never imputed clean/zero/synthetic</x:v>
       </x:c>
       <x:c r="I15" s="114" t="str">
-        <x:v>- brain-only, peripheral-only, combined, and timing-only performance
-- incremental neural contribution
-- shortcut detection rate
-- clock and event alignment residuals
-- unavailable modality count</x:v>
+        <x:v>- primary: strongest-peripheral minus all-stream macro sentence CER
+- secondary: strongest-nonbrain minus brain-sensor-only macro sentence CER
+- residualized repeat with train-only nuisance fit
+- recommended 0.05 practical margins and 65,535 paired sign assignments plus observed
+- synchronization residuals, anomalies, unavailable streams, bytes, runtime, RSS, and exact access/hash ledgers</x:v>
       </x:c>
       <x:c r="J15" s="114" t="str">
-        <x:v>Acceptance: A brain-specific claim requires brain-only performance above all preregistered non-brain controls and a positive incremental contribution over the strongest peripheral condition.
-Stop: If peripheral or timing controls explain the result, relabel it as task/peripheral decoding and block a neural claim.</x:v>
+        <x:v>Acceptance: After Loop 31, use physical 32/16/48 calibration/selection/final floors, select the strongest peripheral and one brain candidate on selection only, hash-freeze all predictions, then open final targets once. All registered required components must pass; ties fail.
+Stop: Relabel as task/peripheral decoding on leakage, a nonbrain tie/win, missing required streams, synchronization/residualization failure, cap/ledger/hash failure, or post-final restart. Never claim absolute brain origin, language intent, no-keypress/patient transfer, population, real-time, portable, at-home, assistive, diagnostic, or clinical behavior.</x:v>
       </x:c>
       <x:c r="K15" s="114" t="str">
-        <x:v>Loops: 31
-External: separate_multimodal_ethics_and_acquisition_authorization</x:v>
+        <x:v>Loops: 30, 31
+External: separate Stage A synthetic authorization; new consent/ethics/retention/device/file/byte packet for Stage B; separate task/population program for Stage C</x:v>
       </x:c>
       <x:c r="L15" s="114" t="str">
-        <x:v>Planning only. No peripheral recording, device access, real signal read, or model run is authorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started. No synthetic fixture, EOG/EMG/gaze/motion/audio recording, protected cache/signal/target read, model/control run, residualization fit, training, scoring, no-keypress study, download, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M15" s="114" t="str">
-        <x:v>Zero collection now; future packet must set exact files, bytes, retention, one-thread analysis, and 32 MiB derived-artifact cap.</x:v>
+        <x:v>Current: one thread/worker, 6 public web operations, zero protected bytes, 8 MiB planning cap. Future Stage A: 120 sec, 1 GiB RSS, 16 MiB artifacts. Future Stage B analysis: 1,200 sec, 1 GiB RSS, 32 MiB artifacts; acquisition byte cap remains unavailable until a separate packet. No energy claim without direct measurement.</x:v>
       </x:c>
       <x:c r="N15" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning_research_complete_no_confound_fixture_acquisition_or_brain_specific_result_unauthorized; confounds=10; streams=9; conditions=13; stages=3; missing_controls_fail_closed; maximum_future_local_claim=incremental_brain_sensor_information_beyond_recorded_controls</x:v>
       </x:c>
       <x:c r="O15" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P15" s="150" t="str">
-        <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
-https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf</x:v>
-      </x:c>
+        <x:v>https://www.nature.com/articles/s41593-026-02303-2
+https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://pubmed.ncbi.nlm.nih.gov/30310862/
+https://pmc.ncbi.nlm.nih.gov/articles/PMC8747566/
+https://www.frontiersin.org/journals/neuroscience/articles/10.3389/fnins.2021.682419/full
+https://pubmed.ncbi.nlm.nih.gov/32746290/</x:v>
+      </x:c>
+      <x:c r="Q15"/>
     </x:row>
     <x:row r="16" ht="138" customHeight="1">
       <x:c r="A16" s="126" t="n">
@@ -9890,7 +9956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re701abc426774c63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce0fab0ea2f476f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R9240e0bce632432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rc91a65904b0c48c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R108c126c15c94b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8abc04ad2f0e4db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rf868902445ab480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rf9d52067b7834243"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R2d3481f477684f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R3a554e75643d4f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R3b8802b0235247c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5f9394d12fa54835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R2692f40cfe824f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4884df995f844781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R5f7317161d764daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R36b146c0c2d44627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R56e57cd2a47f472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R0a24438ddc064e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R5efc7f99cfde4007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R54293dc0a0c041ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R786ee668b0d44c95"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R372acd61140a4c79"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-35 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable and reserves the six real validation rows for Loops 26/31/33. Loop 35 freezes 10 confound classes, 9 future synchronized stream classes, 13 conditions, 3 independently authorized stages, 24 gates, 32 refusals, and 31 false authorization flags. Current S21/S7 evidence lacks a fresh complete peripheral-control set. Its maximum future local claim is incremental brain-sensor information beyond recorded controls, not absolute brain origin. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-36 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable, and Loop 35 caps any future local attribution at incremental brain-sensor information beyond recorded controls. Loop 36 freezes 6 representation layers, 5 modality profiles, 24 channel fields, 12 operation classes, 16 fixture families, 22 gates, 30 refusals, and 29 false authorization flags. A future real-header result can establish at most declared metadata compatibility, not numerical/model/device equivalence. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96116260641a492f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd160023b81f14cba"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc02b225451e44e21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81e76986baa84101"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4365,15 +4365,31 @@
       </x:c>
       <x:c r="I49" s="12"/>
     </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="37"/>
-      <x:c r="B50" s="12"/>
-      <x:c r="C50" s="12"/>
-      <x:c r="D50" s="12"/>
-      <x:c r="E50" s="12"/>
-      <x:c r="F50" s="12"/>
-      <x:c r="G50" s="12"/>
-      <x:c r="H50" s="12"/>
+    <x:row r="50" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A50" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B50" s="12" t="str">
+        <x:v>36-R1</x:v>
+      </x:c>
+      <x:c r="C50" s="12" t="str">
+        <x:v>Treat harmonization as an explicit operator, not hidden equivalence; hold execution</x:v>
+      </x:c>
+      <x:c r="D50" s="12" t="str">
+        <x:v>Freeze 6 representation layers, 5 modality profiles, 24 channel fields, 12 operation classes, 16 fixtures, 22 gates, and 30 refusals. Only explicit aliases, unit factors, and named right-handed transforms can preserve metadata identity. Signal scaling, rereference, compensation, and interpolation remain separately authorized data-changing operations.</x:v>
+      </x:c>
+      <x:c r="E50" s="12" t="str">
+        <x:v>docs/LOOP_36_PRIMARY_SOURCE_RESEARCH.md; registries/loop36_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F50" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G50" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H50" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 36 Stage A remains separately preregistered and authorized, with real headers and signal transforms behind later packets</x:v>
+      </x:c>
       <x:c r="I50" s="12"/>
     </x:row>
     <x:row r="51">
@@ -6046,7 +6062,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6053d6fba41e4925"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra122cf01902a40a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7252,6 +7268,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I41" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>R41</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Geometry, reference, and device-equivalence overclaim</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>A shared channel name/count, standard montage, integer frame code, inferred unit, identity transform, hidden rereference/interpolation, or accuracy-selected mapping is presented as sensor, numerical, model, or device equivalence.</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>Require 6 representation layers, explicit bijective aliases, separate signal/coordinate units, named directional right-handed transforms, orientation and reference/compensation state, preserved missingness, 16 fixture families, 22 gates, 30 refusals, hashes, and staged authorization.</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>An alias collides; a unit is magnitude-inferred; a frame/direction/reference is unknown; a reflection or template substitution passes; interpolation loses missingness; final accuracy selects a map; or metadata compatibility is promoted to transfer/device equivalence.</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7284,7 +7329,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b11d099ef294229"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187f8f1d21274c3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7897,10 +7942,24 @@
       <x:c r="E44"/>
       <x:c r="F44"/>
     </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>Loop36-Research</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Review Geometry/Reference Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Read docs/LOOP_36_PRIMARY_SOURCE_RESEARCH.md and registries/loop36_research_boundary.v0.json. Confirm 6 representation layers, 5 modality profiles, 24 channel fields, 12 operation classes, 16 fixture families, explicit alias/unit/rigid-transform/reference/interpolation policies, 8 outcomes, 7 claims, 22 gates, 30 refusals, and 29 false permissions. Loop 36 remains Not Started. Do not generate a fixture, inspect a real header, reopen S7/S21, access S20/S25, read signal/targets, fit or apply aliases/transforms, convert units, rereference, compensate, interpolate, localize sources, run a model, train, download, stream, touch a device/hardware, infer units/frames, substitute a template montage, select a map by accuracy, or claim numerical/model/device equivalence.</x:v>
+      </x:c>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e447b1c4bd24dbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb7c557e11ec46b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8466,7 +8525,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6970f005c3a44da6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3acb4750871d4f1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9371,7 +9430,7 @@
       </x:c>
       <x:c r="Q15"/>
     </x:row>
-    <x:row r="16" ht="138" customHeight="1">
+    <x:row r="16" ht="129.60000610351562" hidden="0" customHeight="1">
       <x:c r="A16" s="126" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -9385,53 +9444,65 @@
         <x:v>P1 / M</x:v>
       </x:c>
       <x:c r="E16" s="114" t="str">
-        <x:v>Can channel geometry, names, units, reference, and missing sensors be normalized across sessions and devices without erasing provenance?</x:v>
+        <x:v>Can source/channel identities, signal and coordinate units, sensor/electrode geometry, directional transforms, reference state, compensation, interpolation, and missingness be preserved without guessing or accuracy-selected mapping?</x:v>
       </x:c>
       <x:c r="F16" s="114" t="str">
-        <x:v>Cross-session and cross-device failures can come from coordinate or reference mismatch rather than model capacity.</x:v>
+        <x:v>A shared name, channel count, or visual layout can hide different sensors, frames, references, and derived signals. Hidden harmonization can manufacture transfer; exact-name refusal alone can block legitimate declared comparisons.</x:v>
       </x:c>
       <x:c r="G16" s="114" t="str">
-        <x:v>Build: Versioned channel ontology, geometry transform ledger, reference/unit converter, missing-channel mask, and roundtrip validation.
-Research: Modality-specific coordinate-frame and referencing requirements with explicit non-equivalence rules.</x:v>
+        <x:v>Build: Future 6-layer identity/unit/geometry/frame/reference ledger with 5 modality profiles, a 24-field channel record, 12 operation classes, transform hashes, and missingness masks.
+Research: Completed BIDS/MNE channel, coordinate, unit, montage, reference, compensation, interpolation, and claim boundary with 8 outcomes, 7 claims, 22 gates, and 30 refusals.</x:v>
       </x:c>
       <x:c r="H16" s="114" t="str">
-        <x:v>Data: Synthetic geometry fixtures and metadata sidecars first; real headers only after separate authorization and without opening signal arrays.
+        <x:v>Data: Planning used public standards plus committed code/aggregate metadata only. S21 exposes names, types, positions, integer frame/unit codes, and coil types but lacks a complete exchange-frame/orientation/transform/compensation ledger; consumed S7 lacks qualified measured electrode/reference evidence.
 Controls:
-- Permutation, missing-channel, mirrored-coordinate, wrong-unit, and wrong-reference fixtures.
-- Original and harmonized metadata retained side by side.
-- No accuracy-based channel mapping on evaluation data.</x:v>
+- exact identity and safe explicit reorder
+- versioned bijective aliases with collision refusal
+- separate coordinate and signal unit conversions
+- directional right-handed rigid transforms and reflection refusal
+- unknown frame/orientation/reference/compensation refusal
+- interpolation and zero-fill retain missingness and never equal identity
+- no mapping selected by evaluation accuracy</x:v>
       </x:c>
       <x:c r="I16" s="114" t="str">
-        <x:v>- matched, missing, duplicate, and ambiguous channel counts
-- coordinate transform residual
-- unit and reference conversion identity
-- geometry availability fraction
-- roundtrip and provenance hashes</x:v>
+        <x:v>- matched, missing, duplicate, ambiguous, and unavailable channel counts
+- rotation orthogonality and determinant; inverse roundtrip residual
+- unit conversion identity and dimensional compatibility
+- geometry, orientation, reference, and compensation availability
+- exact refusal, warning, access, resource, and source/config/transform/payload hash ledgers</x:v>
       </x:c>
       <x:c r="J16" s="114" t="str">
-        <x:v>Acceptance: Proceed only when transforms are deterministic, reversible where promised, hash-bound, and refuse ambiguous geometry or reference instead of guessing.
-Stop: Keep geometry unavailable if source coordinates or frames cannot be proven; do not infer device equivalence from channel names alone.</x:v>
+        <x:v>Acceptance: Future Stage A passes all 22 gates and 30 refusals with unique identities, explicit aliases, declared units, named frames, directional 4x4 transforms, determinant +1, &lt;=1e-9 m synthetic roundtrip residual, orientation-without-translation, complete reference/missingness/operator provenance, one thread, caps, and hashes.
+Stop: Publish unavailable/incompatible on ambiguity, unknown unit/frame/reference/orientation, reflection, failed roundtrip, template substitution, hidden rereference/interpolation, accuracy-selected mapping, cap/hash failure, or overclaim. Never infer numerical/model/device/neural equivalence from metadata.</x:v>
       </x:c>
       <x:c r="K16" s="114" t="str">
-        <x:v>Loops: 29
-External: none</x:v>
+        <x:v>Loops: 29, 30, 35
+External: separate Stage A synthetic metadata preregistration/authorization; separate real-header file/byte/privacy packet; separate signal-transform authorization</x:v>
       </x:c>
       <x:c r="L16" s="114" t="str">
-        <x:v>Planning only. Synthetic fixture work or real-header inspection requires a separately scoped Loop 36 authorization.</x:v>
+        <x:v>Planning research only. Experiment Not Started. No fixture, metadata adapter, real header/signal/target read, alias/transform fit or apply, unit conversion, rereference, compensation, interpolation, source localization, model, training, download, stream, device, hardware, or equivalence claim is authorized.</x:v>
       </x:c>
       <x:c r="M16" s="114" t="str">
-        <x:v>Dependency-free core, optional MNE only inside adapters, one thread, 16 MiB artifacts, and zero signal-array reads for metadata mode.</x:v>
+        <x:v>Current: one thread/worker, 3 public web operations, zero protected bytes, 8 MiB planning cap. Future Stage A: one thread/worker, 120 sec, 1 GiB RSS, 16 MiB artifacts, zero downloads, optional MNE only inside adapters. Real-header and signal-transform byte caps remain unavailable until exact packets; CPU time is not energy.</x:v>
       </x:c>
       <x:c r="N16" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning_research_complete_no_geometry_fixture_header_signal_transform_or_result_unauthorized; layers=6; modalities=5; fields=24; operations=12; fixtures=16; maximum_future_real_metadata_claim=declared_metadata_compatibility</x:v>
       </x:c>
       <x:c r="O16" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P16" s="150" t="str">
-        <x:v>https://mne.tools/stable/generated/mne.filter.resample.html
-https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html</x:v>
-      </x:c>
+        <x:v>https://bids-specification.readthedocs.io/en/stable/appendices/coordinate-systems.html
+https://bids-specification.readthedocs.io/en/stable/modality-specific-files/magnetoencephalography.html
+https://bids-specification.readthedocs.io/en/stable/modality-specific-files/electroencephalography.html
+https://bids-specification.readthedocs.io/en/stable/appendices/units.html
+https://mne.tools/1.8/auto_tutorials/forward/20_source_alignment.html
+https://mne.tools/stable/generated/mne.transforms.Transform.html
+https://mne.tools/stable/generated/mne.channels.DigMontage.html
+https://mne.tools/stable/generated/mne.set_eeg_reference.html
+https://mne.tools/stable/auto_examples/preprocessing/interpolate_bad_channels.html</x:v>
+      </x:c>
+      <x:c r="Q16"/>
     </x:row>
     <x:row r="17" ht="138" customHeight="1">
       <x:c r="A17" s="126" t="n">
@@ -9956,7 +10027,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce0fab0ea2f476f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radff2aac71ac481d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5f9394d12fa54835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R2692f40cfe824f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4884df995f844781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R5f7317161d764daa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R36b146c0c2d44627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R56e57cd2a47f472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R0a24438ddc064e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R5efc7f99cfde4007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R54293dc0a0c041ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb5ca5ba764384c05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rb15b7ad61f9342ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R92b596b181f342d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R26f9ce0ec17e447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R96b4f20918df4c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R8a34305b0f0a4038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Re4110dbedbc441fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rad131dd7facf4749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rc65c6f0041fa47fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R372acd61140a4c79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ff941f43a614ef1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-36 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable, and Loop 35 caps any future local attribution at incremental brain-sensor information beyond recorded controls. Loop 36 freezes 6 representation layers, 5 modality profiles, 24 channel fields, 12 operation classes, 16 fixture families, 22 gates, 30 refusals, and 29 false authorization flags. A future real-header result can establish at most declared metadata compatibility, not numerical/model/device equivalence. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-37 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 freezes 6 export layers, 5 artifact profiles, 15 stable BIDS mappings, 16 NeuroDecodeKit extension fields, 20 fixture families, 4 stages, 24 gates, 32 refusals, and 29 false authorization flags. Custom payloads remain non-standard and no derivative tree exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd160023b81f14cba"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e87d78a5e6e4b44"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81e76986baa84101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7a0219a7b514786"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4392,15 +4392,31 @@
       </x:c>
       <x:c r="I50" s="12"/>
     </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="37"/>
-      <x:c r="B51" s="12"/>
-      <x:c r="C51" s="12"/>
-      <x:c r="D51" s="12"/>
-      <x:c r="E51" s="12"/>
-      <x:c r="F51" s="12"/>
-      <x:c r="G51" s="12"/>
-      <x:c r="H51" s="12"/>
+    <x:row r="51" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A51" s="37" t="n">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="B51" s="12" t="str">
+        <x:v>37-R1</x:v>
+      </x:c>
+      <x:c r="C51" s="12" t="str">
+        <x:v>Separate the stable BIDS envelope from non-standard NeuroDecodeKit payloads; hold execution</x:v>
+      </x:c>
+      <x:c r="D51" s="12" t="str">
+        <x:v>Freeze 6 export layers, 5 artifact profiles, 15 stable mappings, 16 NDK extension fields, 20 fixtures, 4 stages, 24 gates, and 32 refusals. Use truthful BIDS URIs or unavailable fields, redact local identity, forbid raw copies and target text, and cap validator claims at the standard envelope.</x:v>
+      </x:c>
+      <x:c r="E51" s="12" t="str">
+        <x:v>docs/LOOP_37_PRIMARY_SOURCE_RESEARCH.md; registries/loop37_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F51" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G51" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H51" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; Loop 37 Stage A remains separately preregistered and authorized, with privacy/license/reproducibility/release behind Loops 38/39/44</x:v>
+      </x:c>
       <x:c r="I51" s="12"/>
     </x:row>
     <x:row r="52">
@@ -6062,7 +6078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra122cf01902a40a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra594a9aaad054751"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7297,6 +7313,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I42" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>R42</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>BIDS envelope, provenance, privacy, and raw-copy overclaim</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>A standard-looking directory, passing validator, local path, invented source URI, reused subject label, non-standard NPZ/report payload, raw duplicate, or unclear license is presented as BIDS-compliant, portable, privacy-safe, reproducible, or shareable.</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Require 6 export layers, explicit standardization status, truthful BIDS URIs, portable identifiers, complete hashes, allowlisted payloads, zero raw copies/aliases, target/free-text refusal, privacy/license dependencies, 20 fixtures, 24 gates, 32 refusals, and staged authorization.</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>A local path or identifier leaks; DatasetLinks cannot resolve Sources; raw bytes/inodes duplicate; validator ignores a custom file; target/free text appears; license/privacy is unknown; or envelope validation is promoted to payload/scientific/release proof.</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7329,7 +7374,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187f8f1d21274c3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96ed288ce004e3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7956,10 +8001,24 @@
       <x:c r="E45"/>
       <x:c r="F45"/>
     </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>Loop37-Research</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Review BIDS Derivative/Provenance Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Read docs/LOOP_37_PRIMARY_SOURCE_RESEARCH.md and registries/loop37_research_boundary.v0.json. Confirm 6 export layers, 5 artifact profiles, 15 stable BIDS mappings, 16 explicit NDK extension fields, 20 fixture families, 4 separately authorized stages, 8 outcomes, 6 claims, 24 gates, 32 refusals, and 29 false permissions. Loop 37 remains Not Started and unauthorized. Do not generate a fixture or derivative tree, install/run a validator, open any artifact or protected payload, hash real files, map real subjects, copy raw data, write outside a new bounded root, release/upload, run a model, train, download, stream, touch a device/hardware, invent BIDS metadata, leak local paths/targets/free text, or call non-standard payloads BIDS-compliant, privacy-safe, reproducible, or shareable.</x:v>
+      </x:c>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb7c557e11ec46b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R517ef65d2ff540e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8525,7 +8584,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3acb4750871d4f1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3290b76a63c54cbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9504,7 +9563,7 @@
       </x:c>
       <x:c r="Q16"/>
     </x:row>
-    <x:row r="17" ht="138" customHeight="1">
+    <x:row r="17" ht="129.60000610351562" hidden="0" customHeight="1">
       <x:c r="A17" s="126" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -9518,53 +9577,64 @@
         <x:v>P1 / M</x:v>
       </x:c>
       <x:c r="E17" s="114" t="str">
-        <x:v>Can caches, tokens, reports, and split metadata be exported as inspectable derivatives without copying raw data or losing source identity?</x:v>
+        <x:v>Can caches, NeuroTokens, reports, and split metadata become portable source-bound derivative bundles without copying raw recordings, exposing local identifiers, inventing BIDS metadata, or relabeling custom payloads as standard?</x:v>
       </x:c>
       <x:c r="F17" s="114" t="str">
-        <x:v>A standards-aware derivative makes external reproduction easier while preserving the local-first raw-data boundary.</x:v>
+        <x:v>A standard envelope can lower reproduction friction, but local paths, unknown source URIs, subject collisions, raw copies, hidden targets, incompatible licenses, and validator overclaim can make an apparently portable bundle unsafe or scientifically misleading.</x:v>
       </x:c>
       <x:c r="G17" s="114" t="str">
-        <x:v>Build: BIDS-derivative export plan, dataset description, GeneratedBy and SourceDatasets provenance, sidecars, path validator, and no-raw-copy audit.
-Research: BIDS derivative and electrophysiology mapping note identifying standard fields, extension fields, and unsupported claims.</x:v>
+        <x:v>Build: Future 6-layer target-free synthetic BIDS-organized envelope with 5 artifact profiles, 15 stable-field mappings, 16 explicit NeuroDecodeKit extension fields, portable identity, full hashes, and no-raw-copy/release ledgers.
+Research: Completed stable BIDS 1.11.1 derivative, dataset-description, file Sources/BIDS URI, naming, non-standard file, validator 2.4.1, privacy/license, and claim mapping with 20 fixtures, 4 stages, 8 outcomes, 6 claims, 24 gates, and 32 refusals.</x:v>
       </x:c>
       <x:c r="H17" s="114" t="str">
-        <x:v>Data: Tiny synthetic caches and reports only for the interface proof; no real raw file is copied, packaged, or redistributed.
+        <x:v>Data: Planning used public standards, official validator/example repositories, committed source code, and tracked-file metadata only; tracked neural/model binary candidates=0 and bytes=0. No artifact payload opened.
 Controls:
-- Source, configuration, split, payload, and code hashes retained.
-- Path traversal, subject collision, overwrite, and raw-copy refusals.
-- Roundtrip validation from derivative metadata back to source artifact identity.</x:v>
+- standard envelope fields separate from non-standard NDK payload fields
+- truthful BIDS URIs/DatasetLinks or unavailable plus opaque hash
+- no absolute paths, usernames, traversal, case/identity collisions, overwrite, symlink/hardlink/inode aliases
+- no raw filenames/extensions/content duplicates
+- no targets, prompts, responses, sentence/free text
+- unknown payload/license/privacy status refuses
+- validator success cannot upgrade custom payload or scientific claims</x:v>
       </x:c>
       <x:c r="I17" s="114" t="str">
-        <x:v>- required and unavailable field counts
-- source-to-derivative hash coverage
-- roundtrip identity
-- input, output, and duplicated bytes
-- raw-data copy count</x:v>
+        <x:v>- standard/non-standard/required/propagated/omitted/unavailable field counts
+- BIDS URI and DatasetLinks resolution; source/split/config/payload/code/manifest/bundle hash coverage
+- path, subject/session/item, manifest, and two-clean-root roundtrip identity
+- input/output/duplicate/raw-copy/generated bytes and file count
+- validator errors/warnings/ignored files; runtime/RSS/threads/workers/network/access counters</x:v>
       </x:c>
       <x:c r="J17" s="114" t="str">
-        <x:v>Acceptance: Pass as a synthetic derivative interface only when provenance is complete, extension fields are namespaced, no raw payload is copied, and all generated files remain under cap.
-Stop: Do not claim BIDS compliance for unsupported fields or invent source metadata; export an explicit warning or refuse.</x:v>
+        <x:v>Acceptance: Future Stage A passes all 24 gates and 32 refusals with exact dataset envelope, portable paths, collision-free identity, target-free allowlist, complete hashes, two clean roots, zero raw copies/duplicates/aliases, one thread, and caps. Stage B additionally preserves every issue from pinned offline validator 2.4.1 and can claim only a validator-assessed standard envelope with explicitly non-standard payloads.
+Stop: Publish invalid/unavailable/non-standard/blocked on any URI, metadata, path, collision, raw-copy, target, hash, privacy, license, validator, resource, access, or claim failure. Never invent metadata, auto-repair, hide issues, weaken gates, or call custom payloads BIDS-compliant.</x:v>
       </x:c>
       <x:c r="K17" s="114" t="str">
-        <x:v>Loops: 36
-External: none</x:v>
+        <x:v>Loops: 36; Loop 38 before real/public metadata; Loop 39 before cross-machine reproducibility; Loop 44 before release wording
+External: separate Stage A synthetic metadata authorization; separate Stage B payload/validator authorization; separate Stage C real-derived metadata packet; separate Stage D release decision</x:v>
       </x:c>
       <x:c r="L17" s="114" t="str">
-        <x:v>Planning only. Export implementation and generated fixtures require a separate Loop 37 authorization.</x:v>
+        <x:v>Planning research only. Experiment Not Started and unauthorized. No fixture, exporter, derivative tree, validator install/run, real header/cache/signal/target read, payload hash, subject mapping, raw copy, external write, release/upload, network, model, training, stream, device, hardware, or BIDS-compliant NeuroToken claim is authorized.</x:v>
       </x:c>
       <x:c r="M17" s="114" t="str">
-        <x:v>One thread, one worker, dependency-free metadata core, 16 MiB generated derivative tree, and zero real-data bytes.</x:v>
+        <x:v>Current: one thread/worker, 7 public web operations including 2 official GitHub reads, zero protected/generated payload bytes, 8 MiB planning cap. Future Stage A: one thread/worker, 120 sec, 1 GiB RSS, 16 MiB, 128 files, zero network/download bytes, zero raw-copy bytes, no base dependency. Real/public byte caps remain unavailable until exact privacy/license packets.</x:v>
       </x:c>
       <x:c r="N17" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning_research_complete_experiment_not_started; layers=6; artifact_profiles=5; standard_fields=15; ndk_extension_fields=16; fixtures=20; stages=4; gates=24; refusals=32; maximum_future_stage_b_claim=validator_assessed_standard_envelope_with_nonstandard_payloads</x:v>
       </x:c>
       <x:c r="O17" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P17" s="150" t="str">
         <x:v>https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html
+https://bids-specification.readthedocs.io/en/stable/modality-agnostic-files/dataset-description.html
+https://bids-specification.readthedocs.io/en/stable/derivatives/common-data-types.html
+https://bids-specification.readthedocs.io/en/stable/common-principles.html
+https://bids-specification.readthedocs.io/en/stable/extensions.html
+https://github.com/bids-standard/bids-validator
+https://github.com/bids-standard/bids-examples
 https://arxiv.org/abs/1803.09010</x:v>
       </x:c>
+      <x:c r="Q17"/>
     </x:row>
     <x:row r="18" ht="138" customHeight="1">
       <x:c r="A18" s="126" t="n">
@@ -10027,7 +10097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radff2aac71ac481d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc4fbaecba9c4942"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb5ca5ba764384c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rb15b7ad61f9342ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R92b596b181f342d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R26f9ce0ec17e447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R96b4f20918df4c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R8a34305b0f0a4038"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Re4110dbedbc441fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rad131dd7facf4749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rc65c6f0041fa47fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3ffcac7279d44c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rad5f21b16142406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R480978071ec34251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R4945f1dc455d43b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra45d3d19ffec46eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R16f9e77f4df94298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R99662263630945bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R1ff901e040b04e4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9e465bc293904301"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ff941f43a614ef1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra78de5f8d97443fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-37 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 freezes 6 export layers, 5 artifact profiles, 15 stable BIDS mappings, 16 NeuroDecodeKit extension fields, 20 fixture families, 4 stages, 24 gates, 32 refusals, and 29 false authorization flags. Custom payloads remain non-standard and no derivative tree exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-38 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 keeps custom payloads non-standard. Loop 38 freezes 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive-field classes, 5 deletion-receipt levels, 24 fixtures, 26 gates, 36 refusals, and 32 false authorization flags. Unknown copies remain unresolved; no scanner or deletion exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e87d78a5e6e4b44"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc82e618da5a94d17"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7a0219a7b514786"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9454a1d84a7f46f2"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4419,15 +4419,31 @@
       </x:c>
       <x:c r="I51" s="12"/>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="37"/>
-      <x:c r="B52" s="12"/>
-      <x:c r="C52" s="12"/>
-      <x:c r="D52" s="12"/>
-      <x:c r="E52" s="12"/>
-      <x:c r="F52" s="12"/>
-      <x:c r="G52" s="12"/>
-      <x:c r="H52" s="12"/>
+    <x:row r="52" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A52" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B52" s="12" t="str">
+        <x:v>38-R1</x:v>
+      </x:c>
+      <x:c r="C52" s="12" t="str">
+        <x:v>Separate redaction, de-identification, deletion receipts, media sanitization, consent, license, and sharing; hold execution</x:v>
+      </x:c>
+      <x:c r="D52" s="12" t="str">
+        <x:v>Freeze 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive fields, 12 threats, 5 receipt levels, 24 fixtures, 4 stages, 26 gates, and 36 refusals. Keep unknown copies unresolved and forbid broad cleanup or privacy overclaim.</x:v>
+      </x:c>
+      <x:c r="E52" s="12" t="str">
+        <x:v>docs/LOOP_38_PRIMARY_SOURCE_RESEARCH.md; registries/loop38_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F52" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G52" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H52" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; any Loop 38 Stage A requires separate preregistration and authorization, with cross-machine/device/release claims behind Loops 39/42/44</x:v>
+      </x:c>
       <x:c r="I52" s="12"/>
     </x:row>
     <x:row r="53">
@@ -6078,7 +6094,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra594a9aaad054751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5219e9dcef924353"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7342,6 +7358,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I43" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>R43</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Neural-data lifecycle, identity linkage, deletion, and sharing overclaim</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Ignored or redacted neural-derived data, stable hashes, a clean worktree, or a local path receipt is presented as anonymous, privacy-safe, securely deleted, consented, license-cleared, or shareable while backups, clones, CI, remote, or media copies remain unresolved.</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>Require 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive fields, 5 receipt levels, exact ownership/retention/redaction/sharing fields, unresolved-copy counts, consent/license separation, 24 fixtures, 26 gates, 36 refusals, and staged authorization.</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>A sensitive field survives; a hash links releases; temp/backup/Git/clone/CI copies are unknown; broad cleanup crosses scope; a path receipt is promoted to sanitization; or technical redaction is promoted to consent/release authority.</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7374,7 +7419,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96ed288ce004e3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref4900616a024b78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8015,10 +8060,24 @@
       <x:c r="E46"/>
       <x:c r="F46"/>
     </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>Loop38-Research</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Review Neural-Data Privacy/Lifecycle Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Read docs/LOOP_38_PRIMARY_SOURCE_RESEARCH.md and registries/loop38_research_boundary.v0.json. Confirm 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive-field classes, 12 threats, 5 deletion-receipt levels, 24 fixture families, 4 separately authorized stages, 8 outcomes, 6 claims, 26 gates, 36 refusals, and 32 false permissions. Loop 38 remains Not Started and unauthorized. Do not create a fixture or scanner, inspect protected roots, open neural/embedding/target/consent payloads, delete files, follow links, rewrite history, clean backups/remotes/clones/CI, run an identity attack, make consent/license determinations, release/upload, run a model, train, download, stream, touch a device/hardware, or call path absence anonymous, privacy-safe, securely deleted, or shareable. Unknown copies remain unresolved.</x:v>
+      </x:c>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R517ef65d2ff540e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d51fe62ffe422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8584,7 +8643,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3290b76a63c54cbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0859784dd026449e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9636,7 +9695,7 @@
       </x:c>
       <x:c r="Q17"/>
     </x:row>
-    <x:row r="18" ht="138" customHeight="1">
+    <x:row r="18" ht="108" hidden="0" customHeight="1">
       <x:c r="A18" s="126" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -9650,54 +9709,65 @@
         <x:v>P0 / M</x:v>
       </x:c>
       <x:c r="E18" s="114" t="str">
-        <x:v>Can the project prove where sensitive recordings and embeddings live, who can access them, and how they are retained or deleted?</x:v>
+        <x:v>Can the project prove where sensitive recordings, derived caches, embeddings, reports, logs, temporary files, backups, Git/CI copies, and releases live, who owns them, and what a deletion receipt actually establishes?</x:v>
       </x:c>
       <x:c r="F18" s="114" t="str">
-        <x:v>Neural signals and embeddings can carry identity information; local-first behavior needs verifiable lifecycle controls, not just a promise.</x:v>
+        <x:v>A positive fresh-person result is not responsibly shareable without exact lifecycle evidence. Neural derivatives and stable hashes can remain linkable; ignored paths, local deletion, Git cleanup, media sanitization, consent, license, and release authority are different claims.</x:v>
       </x:c>
       <x:c r="G18" s="114" t="str">
-        <x:v>Build: Data inventory, sensitivity labels, local path policy, retention and deletion receipts, redaction scanner, and privacy threat model.
-Research: NIST-aligned privacy risk map plus EEG identity-risk review and contributor guidance.</x:v>
+        <x:v>Build: Future target-free synthetic inventory, redaction scanner, copy-surface report, retention policy, and narrow deletion-receipt interface.
+Research: Completed NIST PF 1.0, NISTIR 8062, PRAM, SP 800-88 Rev. 2, Git-history, Open Brain Consent, EEG identity-risk, and OECD stewardship mapping with 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive-field classes, 12 threats, 5 receipt levels, 24 fixtures, 4 stages, 8 outcomes, 6 claims, 26 gates, and 36 refusals.</x:v>
       </x:c>
       <x:c r="H18" s="114" t="str">
-        <x:v>Data: Repository metadata and synthetic fixtures only; no identity attack, real embedding export, or participant re-identification experiment.
+        <x:v>Data: Public sources, repository metadata, current tracked names, and all-ref history names only. Current/history neural-model candidate paths=0; no payload opened.
 Controls:
-- Tracked-history and staged-secret scans.
-- Raw, derived, report, log, temporary, and backup lifecycle paths tested separately.
-- Absolute paths, participant aliases, timestamps, and device serials redacted by default.
-- Deletion receipt verifies expected paths without destructive broad cleanup.</x:v>
+- sensitivity inherits from the highest source
+- pseudonyms and hashes remain potentially linkable
+- local/temp/log/backup/Git/remote/CI/release surfaces stay separate
+- consent, license, de-identification, redaction, deletion, and release authority stay separate
+- unknown copies remain unresolved
+- dry-run, exact-root, manifest-bound deletion only
+- no identity attack or protected-root scan</x:v>
       </x:c>
       <x:c r="I18" s="114" t="str">
-        <x:v>- sensitive path and field coverage
-- redaction recall on generated fixtures
-- retention-policy violations
-- tracked neural payload bytes
-- verified deletion and unresolved copy counts</x:v>
+        <x:v>- artifact and lifecycle coverage by checked/blocked/unavailable/unresolved
+- sensitive-field recall and public-fixture precision
+- policy violations and prohibited survivor bytes
+- current/all-ref tracked neural paths and bytes
+- receipt level; deleted/skipped/failed/unresolved copies
+- runtime/RSS/bytes/files/threads/workers/network/mutation counters</x:v>
       </x:c>
       <x:c r="J18" s="114" t="str">
-        <x:v>Acceptance: Pass when every artifact class has an owner, location, retention rule, redaction behavior, and verifiable local deletion path, with zero tracked neural payloads.
-Stop: Block data-sharing or release claims when lifecycle ownership, consent, license, or deletion cannot be proven.</x:v>
+        <x:v>Acceptance: Future Stage A passes all 26 gates and 36 refusals with exact synthetic fixtures, zero prohibited survivors, zero tracked neural payload, deterministic receipts, and every copy surface explicitly classified. Unknown copies stay unresolved.
+Stop: Block anonymity, privacy-safe, secure-deletion, sharing, and release claims when owner, consent, license, redaction, copy inventory, receipt level, media evidence, resource, or authorization is incomplete. Never delete unrelated work or infer remotes clean from local state.</x:v>
       </x:c>
       <x:c r="K18" s="114" t="str">
-        <x:v>Loops: 37
-External: none</x:v>
+        <x:v>Loops: 37; Loop 39 before cross-machine copy claims; Loop 42 before device lifecycle; Loop 44 plus external governance before release
+External: separate Stage A synthetic authorization; separate Stage B read-only local metadata authorization; separate Stage C named real-derived packet; separate Stage D public-release decision</x:v>
       </x:c>
       <x:c r="L18" s="114" t="str">
-        <x:v>Planning only. No real identity analysis or destructive cleanup is authorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started and unauthorized. No fixture, scanner, deletion, protected-root scan, identity attack, consent/legal determination, Git history rewrite, remote cleanup, release/upload, network, model, training, stream, device, hardware, anonymous-data, privacy-safe, or secure-sanitization claim is authorized.</x:v>
       </x:c>
       <x:c r="M18" s="114" t="str">
-        <x:v>Standard-library scanners where possible, one thread, one worker, 8 MiB reports, no real signal reads, and no network upload.</x:v>
+        <x:v>Current: one thread/worker, 6 public web operations and 8 primary page opens, zero protected/generated payload bytes, 8 MiB planning cap. Future Stage A: standard-library-first, one thread/worker, 120 sec, 512 MiB RSS, 8 MiB reports, 128 files, zero network/download/upload bytes, zero real signal reads, zero nonfixture destructive mutations.</x:v>
       </x:c>
       <x:c r="N18" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning_research_complete_experiment_not_started; sensitivity_levels=5; artifact_classes=8; lifecycle_surfaces=10; sensitive_fields=12; threats=12; deletion_receipts=5; fixtures=24; stages=4; gates=26; refusals=36; unknown_copies=unresolved</x:v>
       </x:c>
       <x:c r="O18" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P18" s="150" t="str">
-        <x:v>https://arxiv.org/abs/2412.09854
-https://www.nist.gov/privacy-framework/privacy-framework</x:v>
-      </x:c>
+        <x:v>https://www.nist.gov/privacy-framework
+https://doi.org/10.6028/NIST.IR.8062
+https://www.nist.gov/privacy-framework/nist-pram
+https://doi.org/10.6028/NIST.SP.800-88r2
+https://docs.github.com/en/authentication/keeping-your-account-and-data-secure/removing-sensitive-data-from-a-repository
+https://doi.org/10.1002/hbm.25351
+https://arxiv.org/abs/2412.09854
+https://www.oecd.org/en/topics/responsible-innovation.html</x:v>
+      </x:c>
+      <x:c r="Q18"/>
     </x:row>
     <x:row r="19" ht="138" customHeight="1">
       <x:c r="A19" s="126" t="n">
@@ -10097,7 +10167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc4fbaecba9c4942"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R102339faccbe42f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3ffcac7279d44c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rad5f21b16142406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R480978071ec34251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R4945f1dc455d43b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra45d3d19ffec46eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R16f9e77f4df94298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R99662263630945bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R1ff901e040b04e4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9e465bc293904301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R43ba69200ff84acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rd320fc41a4b34368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc5bb9534a4584c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re33175bd1953475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rfe0c96c41ea44908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd2781aff0a6542e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R5d968562eac143d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R598c3022b20e41d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R62c9d41d5f964ea1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra78de5f8d97443fc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25acd1eaa27f46a0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-38 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 keeps custom payloads non-standard. Loop 38 freezes 5 sensitivity levels, 8 artifact classes, 10 lifecycle surfaces, 12 sensitive-field classes, 5 deletion-receipt levels, 24 fixtures, 26 gates, 36 refusals, and 32 false authorization flags. Unknown copies remain unresolved; no scanner or deletion exists. All 20 execution flags remain false.</x:v>
+        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-39 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 keeps custom payloads non-standard. Loop 38 keeps unknown copies unresolved. Loop 39 freezes 7 qualification levels, 18 environment fields, 8 output classes, 6 comparison classes, 6 future matrix cells, 20 fixtures, 28 gates, 38 refusals, and 36 false authorization flags. No matrix cell or cross-machine reproduction exists. All 20 execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc82e618da5a94d17"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b00721eda84322"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9454a1d84a7f46f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rded22743bfa24036"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4447,14 +4447,30 @@
       <x:c r="I52" s="12"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="37"/>
-      <x:c r="B53" s="12"/>
-      <x:c r="C53" s="12"/>
-      <x:c r="D53" s="12"/>
-      <x:c r="E53" s="12"/>
-      <x:c r="F53" s="12"/>
-      <x:c r="G53" s="12"/>
-      <x:c r="H53" s="12"/>
+      <x:c r="A53" s="37" t="n">
+        <x:v>46216.5</x:v>
+      </x:c>
+      <x:c r="B53" s="12" t="str">
+        <x:v>39-R1</x:v>
+      </x:c>
+      <x:c r="C53" s="12" t="str">
+        <x:v>Separate replay, exact identity, numerical compatibility, reproduction, independent reproduction, and replication; hold execution</x:v>
+      </x:c>
+      <x:c r="D53" s="12" t="str">
+        <x:v>Freeze 7 qualification levels, 18 environment fields, 8 output classes, 6 comparison classes, 6 future matrix cells, 20 fixtures, 4 stages, 28 gates, and 38 refusals. Keep all 36 permissions false and treat the current support audit as a gap map, not reproduction proof.</x:v>
+      </x:c>
+      <x:c r="E53" s="12" t="str">
+        <x:v>docs/LOOP_39_PRIMARY_SOURCE_RESEARCH.md; registries/loop39_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F53" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G53" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H53" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision; any Loop 39 Stage A requires separate preregistration and authorization, with edge/independent/device/release claims behind Loops 40/43/42/44</x:v>
+      </x:c>
       <x:c r="I53" s="12"/>
     </x:row>
     <x:row r="54">
@@ -6094,7 +6110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5219e9dcef924353"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raabcc9edacbc4af3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7387,6 +7403,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I44" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>R44</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Cross-machine reproducibility and tolerance overclaim</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>A one-host replay, passing floating tolerance, unspecified latest runner, unlocked dependency set, or same-team rerun is presented as bitwise identity, supported-platform reproduction, independent reproduction, or scientific replication.</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Require 7 qualification levels, 18 environment fields, 8 output classes, 6 comparison classes, an explicit 6-cell future matrix, exact canonical/semantic comparisons, frozen numerical tolerances, unsupported-cell reasons, 20 fixtures, 28 gates, 38 refusals, and staged authorization.</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>A tolerance is widened after results; OS/architecture/dependency identity is missing; latest runners drift silently; package and behavioral hashes are conflated; a single host or same team is called independent reproduction; or compatibility is promoted to replication/scientific proof.</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7419,7 +7464,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref4900616a024b78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a5d204fb5b4013"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8074,10 +8119,21 @@
       <x:c r="E47"/>
       <x:c r="F47"/>
     </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>Loop39-Research</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Review Cross-Machine Reproducibility Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Read docs/LOOP_39_PRIMARY_SOURCE_RESEARCH.md and registries/loop39_research_boundary.v0.json. Confirm 7 qualification levels, 18 environment identity fields, 8 output classes, 6 comparison classes, 6 future matrix cells, 20 fixture families, 4 separately authorized stages, 8 outcomes, 7 claims, 28 gates, 38 refusals, and 36 false permissions. Loop 39 remains Not Started and unauthorized. Do not create a fixture or environment manifest, install or lock dependencies, mutate CI, build packages, open protected payloads, run a model, train, download, upload artifacts, recruit an independent reproducer, package an edge runtime, stream, touch a device/hardware, widen tolerances after results, or call one-host replay cross-machine reproduction, same-team work independent reproduction, compatibility replication, or any result neural advantage, decoding, real-time, edge, device, or hardware proof.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d51fe62ffe422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25eeceebfa224e92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8643,7 +8699,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0859784dd026449e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd073c49f8a74474d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9783,53 +9839,53 @@
         <x:v>P0 / M</x:v>
       </x:c>
       <x:c r="E19" s="114" t="str">
-        <x:v>Which outputs are bitwise stable across supported Python and operating-system combinations, and which require explicit numerical tolerances?</x:v>
+        <x:v>Which outputs can be claimed bitwise identical, semantically identical, or numerically compatible across declared Python, operating-system, architecture, and optional-dependency cells?</x:v>
       </x:c>
       <x:c r="F19" s="114" t="str">
-        <x:v>Open-source users need to know whether a mismatch is a bug, a backend difference, or an unsupported environment.</x:v>
+        <x:v>Open-source contributors need a fail-closed way to distinguish a deterministic replay bug, a backend-specific numerical difference, an unsupported environment, same-team reproduction, and genuinely independent reproduction.</x:v>
       </x:c>
       <x:c r="G19" s="114" t="str">
-        <x:v>Build: CI matrix, environment manifest, golden semantic hashes, tolerance registry, failure diagnostics, and artifact reproducibility report.
-Research: Reproducibility policy distinguishing semantic identity, numerical compatibility, timing comparison, and environment-specific evidence.</x:v>
+        <x:v>Build: Future environment manifest, six-cell base/neuro matrix, output-class comparison engine, canonical semantic hashes, tolerance registry, diagnostics, and bounded reproduction report.
+Research: Completed ACM, Reproducible Builds, Python, PyPA, NumPy, PyTorch, GitHub Actions, MNE, and Scientific Python support audit with 7 qualification levels, 18 environment fields, 8 output classes, 6 comparisons, 20 fixtures, 4 stages, 8 outcomes, 7 claims, 28 gates, and 38 refusals.</x:v>
       </x:c>
       <x:c r="H19" s="114" t="str">
-        <x:v>Data: Dependency-free tests and authorized synthetic fixtures only; no real or consumed cache, target, or model training access.
+        <x:v>Data: Planning used public primary sources plus committed code, CI, package metadata, and local diagnostics only. No fixture or payload opened.
 Controls:
-- At least macOS and Linux where CI capacity permits.
-- Base and optional-neuro environments kept separate.
-- Bitwise semantic fields tested separately from floating payload tolerances.
-- Tolerance changes require a recorded failing environment and explicit decision.</x:v>
+- separate base and optional-neuro profiles
+- explicit Ubuntu 24.04 x64 and macOS 15 arm64 cells
+- Python 3.10/3.11/3.12 base cells plus Python 3.12 neuro cells
+- exact canonical-byte and semantic comparisons separate from preregistered float tolerance
+- NaN, infinity, dtype, shape, timestamps, masks, warnings, and claim fields fail closed
+- same-team and independent reproduction remain separate</x:v>
       </x:c>
       <x:c r="I19" s="114" t="str">
-        <x:v>- matrix pass rate
-- semantic hash agreement
-- maximum numerical drift
-- runtime and peak RSS by environment
-- artifact and dependency size</x:v>
+        <x:v>- no protected payload, target, participant, local path, secret, or credential enters a future artifact
+- environment identity and dependency manifests are target-free
+- public synthetic fixtures only until separate authorization
+- no artifact upload or release from this planning result
+- independent-reproducer identity and access remain unavailable</x:v>
       </x:c>
       <x:c r="J19" s="114" t="str">
-        <x:v>Acceptance: Pass when every supported cell either reproduces the registered contract or fails with an explicit unsupported reason; no tolerance is widened after hidden evaluation access.
-Stop: Do not claim cross-machine reproducibility from one host; quarantine platform-specific drift until diagnosed and documented.</x:v>
+        <x:v>Acceptance: A future staged run must satisfy all 28 gates and 38 refusals, bind every supported cell to the same revision/contract/fixture hashes, compare each output by its declared class, preserve exact semantic identity, keep numerical drift within frozen tolerances, report unsupported cells explicitly, and pass resource/access ledgers.
+Stop: Do not claim cross-machine reproduction from one host, widen tolerance after seeing hidden evaluation, collapse same-team into independent reproduction, call package-hash mismatch behavioral failure, or promote compatibility to replication, neural advantage, decoding, real-time, edge, device, or hardware proof.</x:v>
       </x:c>
       <x:c r="K19" s="114" t="str">
-        <x:v>Loops: 37
-External: ci_capacity_and_optional_environment_review</x:v>
+        <x:v>Loops 25, 37, 38; Loop 40 packaging and Loop 43 independent reproduction remain later separate gates</x:v>
       </x:c>
       <x:c r="L19" s="114" t="str">
-        <x:v>Planning only. New matrix jobs, fixtures, and optional installs require a separate bounded Loop 39 change.</x:v>
+        <x:v>Planning research only. Experiment Not Started. All 36 authorized_now fields are false. No fixture, environment manifest, dependency lock, matrix job, package build, protected payload, model, training, independent reproducer, edge runtime, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M19" s="114" t="str">
-        <x:v>One thread per job, no large cache, 32 MiB job artifacts, and existing CI time limits.</x:v>
+        <x:v>Future only: &lt;=2 parallel jobs; 1 thread/worker; &lt;=20 min and &lt;=1 GiB peak RSS per cell; &lt;=4 MiB generated artifacts per cell; &lt;=24 MiB total; network only for separately authorized dependency setup; protected/model/target/training/download counters remain zero.</x:v>
       </x:c>
       <x:c r="N19" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>Planning research complete; experiment Not Started; no cross-machine reproduction or independent reproduction exists.</x:v>
       </x:c>
       <x:c r="O19" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P19" s="150" t="str">
-        <x:v>https://arxiv.org/abs/2404.15319
-https://arxiv.org/abs/1810.03993</x:v>
+        <x:v>docs/LOOP_39_PRIMARY_SOURCE_RESEARCH.md; registries/loop39_research_boundary.v0.json; https://www.acm.org/publications/policies/artifact-review-and-badging-current; https://reproducible-builds.org/docs/definition/; https://docs.github.com/en/actions/reference/runners/github-hosted-runners</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="138" customHeight="1">
@@ -10167,7 +10223,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R102339faccbe42f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5f02093dee4cc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R43ba69200ff84acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rd320fc41a4b34368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rc5bb9534a4584c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re33175bd1953475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rfe0c96c41ea44908"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd2781aff0a6542e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R5d968562eac143d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R598c3022b20e41d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R62c9d41d5f964ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5d1a9718806a490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R7e7760243cb6443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R18992b3c600445b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9569b14db57145b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R718e032ddff24c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re9ec5bcf72124432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R13ef222941a44694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rd4e80a7a99424d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R7fccb2f7068341c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25acd1eaa27f46a0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905befbe2f8143ab"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>The 20-loop KPI counts the original roadmap; Loop 25 remains the active numbered decision. Loops 26 and 28-39 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable; Loop 35 caps future local attribution at incremental brain-sensor information; Loop 36 caps a future real-header result at declared metadata compatibility. Loop 37 keeps custom payloads non-standard. Loop 38 keeps unknown copies unresolved. Loop 39 freezes 7 qualification levels, 18 environment fields, 8 output classes, 6 comparison classes, 6 future matrix cells, 20 fixtures, 28 gates, 38 refusals, and 36 false authorization flags. No matrix cell or cross-machine reproduction exists. All 20 execution flags remain false.</x:v>
+        <x:v>Loop 40 planning research complete; edge-package experiment Not Started and unauthorized. ExecuTorch/XNNPACK is a research lead only; Loop 39 matrix and named target remain missing.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b00721eda84322"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26b21fe5594c4b32"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rded22743bfa24036"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcf8a42d97cb4b69"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4474,12 +4474,24 @@
       <x:c r="I53" s="12"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="37"/>
-      <x:c r="B54" s="12"/>
-      <x:c r="C54" s="12"/>
-      <x:c r="D54" s="12"/>
-      <x:c r="E54" s="12"/>
-      <x:c r="F54" s="12"/>
+      <x:c r="A54" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B54" s="12" t="str">
+        <x:v>40-R1</x:v>
+      </x:c>
+      <x:c r="C54" s="12" t="str">
+        <x:v>Keep every edge backend unselected until a named target and relevant Loop 39 matrix pass exist; treat ExecuTorch/XNNPACK only as the leading research candidate.</x:v>
+      </x:c>
+      <x:c r="D54" s="12" t="str">
+        <x:v>Prevents a PyTorch export demo, small model file, or simulator run from being mislabeled deployment benefit, portable hardware, or science.</x:v>
+      </x:c>
+      <x:c r="E54" s="12" t="str">
+        <x:v>docs/LOOP_40_PRIMARY_SOURCE_RESEARCH.md; registries/loop40_research_boundary.v0.json</x:v>
+      </x:c>
+      <x:c r="F54" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
       <x:c r="G54" s="12"/>
       <x:c r="H54" s="12"/>
       <x:c r="I54" s="12"/>
@@ -6110,7 +6122,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raabcc9edacbc4af3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54dd5b160f834e30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7432,6 +7444,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I45" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>R45</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Edge export hides host-state drift or fallback</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>A graph package can preserve logits while changing normalization, causal state, timestamps, frame schedule, decoder behavior, total bytes, or runtime partitioning.</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Freeze six package layers, 20 identity fields, exact state/timestamp/provenance checks, full fallback/operator accounting, and complete package/runtime/app resource measures before adoption.</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>An export passes graph comparison while host-state identity, fallback counts, runtime/kernel/app bytes, or named-target evidence is missing.</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7464,7 +7505,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a5d204fb5b4013"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2659c7846f0b4916"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8130,10 +8171,21 @@
         <x:v>Read docs/LOOP_39_PRIMARY_SOURCE_RESEARCH.md and registries/loop39_research_boundary.v0.json. Confirm 7 qualification levels, 18 environment identity fields, 8 output classes, 6 comparison classes, 6 future matrix cells, 20 fixture families, 4 separately authorized stages, 8 outcomes, 7 claims, 28 gates, 38 refusals, and 36 false permissions. Loop 39 remains Not Started and unauthorized. Do not create a fixture or environment manifest, install or lock dependencies, mutate CI, build packages, open protected payloads, run a model, train, download, upload artifacts, recruit an independent reproducer, package an edge runtime, stream, touch a device/hardware, widen tolerances after results, or call one-host replay cross-machine reproduction, same-team work independent reproduction, compatibility replication, or any result neural advantage, decoding, real-time, edge, device, or hardware proof.</x:v>
       </x:c>
     </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>Loop40-Research</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Review Edge Runtime Packaging Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Read docs/LOOP_40_PRIMARY_SOURCE_RESEARCH.md and registries/loop40_research_boundary.v0.json. Confirm 7 qualification levels, 6 package layers, 4 unselected backend profiles, 20 identity fields, 8 output classes, 6 comparison classes, 24 fixtures, 4 stages, 30 gates, 40 refusals, and 40 false permissions. Loop 40 remains Not Started and unauthorized. Do not select a target/backend, install, export, convert, package, infer, profile, run a memory planner/delegate/simulator/app, open protected data, train, touch a device/hardware, hide fallback, change float32, or call packaging neural, decoding, capture-to-text latency, or portable-hardware proof.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25eeceebfa224e92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6feb5ace8ecc4034"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8699,7 +8751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd073c49f8a74474d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434b359e5ec84112"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9902,52 +9954,53 @@
         <x:v>P2 / L</x:v>
       </x:c>
       <x:c r="E20" s="114" t="str">
-        <x:v>Can one already qualified frozen pipeline be packaged for an edge runtime while preserving outputs, state, timestamps, and measured resource behavior?</x:v>
+        <x:v>Can one qualified frozen path preserve graph outputs, host causal state, timestamps, provenance, visible fallback, and complete deployment cost on one named edge target?</x:v>
       </x:c>
       <x:c r="F20" s="114" t="str">
-        <x:v>Packaging is meaningful only after correctness and local runtime gates; it can then reveal startup, delegate, memory-planning, and operator support constraints.</x:v>
+        <x:v>Packaging can matter only after the reference and target are qualified; otherwise a converted graph is deployment theater.</x:v>
       </x:c>
       <x:c r="G20" s="114" t="str">
-        <x:v>Build: Single-backend export contract, operator audit, packaged artifact validator, reference comparison, and startup/runtime/RSS report.
-Research: ExecuTorch or alternative edge-runtime decision note based on supported operators and target platform, not trend appeal.</x:v>
+        <x:v>Build: Future separately authorized named-target contract, operator audit, package validator, eager comparator, host-state adapter, and complete resource report.
+Research: Official comparison of ExecuTorch/XNNPACK, ONNX Runtime Mobile, LiteRT, and Core ML; no backend selected.</x:v>
       </x:c>
       <x:c r="H20" s="114" t="str">
-        <x:v>Data: Frozen target-free synthetic fixture only; no real data, consumed targets, retraining, or architecture changes.
+        <x:v>Data: Repository source and recorded Loop 24/39 evidence only now; future frozen target-free synthetic fixture only.
 Controls:
-- Reference eager path retained.
-- Exact frame, timestamp, decoder trace, and state comparison.
-- Fallback and undelegated operator counts reported.
-- Package size, load time, steady-state time, and peak memory separated.</x:v>
+- retain the 1,130-parameter/5,210-byte float32 reference
+- separate six package layers
+- exact state/timestamp/provenance checks
+- visible fallback and unsupported operators
+- complete package/runtime/kernel/app bytes</x:v>
       </x:c>
       <x:c r="I20" s="114" t="str">
-        <x:v>- behavioral identity and numerical drift
-- package and tensor bytes
-- startup, producer, decoder, and full-pipeline latency
-- peak RSS and planned memory
-- delegated, fallback, and unsupported operator counts</x:v>
+        <x:v>- exact semantic, state, timestamp, and provenance identity
+- field-specific numerical drift
+- delegated, undelegated, fallback, and unsupported operators
+- graph, payload, runtime, kernel, app, temporary, and total bytes
+- startup, load, warmup, steady, teardown, RSS, and planned memory</x:v>
       </x:c>
       <x:c r="J20" s="114" t="str">
-        <x:v>Acceptance: Adopt a package only if a previously qualified reference behavior is preserved, unsupported fallback is zero or explicitly accepted, and a preregistered deployment benefit passes.
-Stop: Park packaging if it requires retraining, architecture changes, hidden fallback, or more resources without a measured benefit; do not call desktop packaging portable hardware.</x:v>
+        <x:v>Acceptance: Adopt only after relevant Loop 39 cells, named target/backend, semantic parity, resource caps, and preregistered complete deployment benefit pass.
+Stop: Park on unsupported export, hidden fallback, dtype drift, post-hoc tolerance, retraining, architecture/checkpoint change, resource overflow, or no complete benefit.</x:v>
       </x:c>
       <x:c r="K20" s="114" t="str">
-        <x:v>Loops: 39
-External: explicit_loop24_result_or_hold, separate_edge_runtime_authorization</x:v>
+        <x:v>Loops: 39 execution; recorded Loop 24 hold
+External: named target before backend selection; separate Stage A-D authorizations; Loop 42 before device qualification; Loop 44 before release</x:v>
       </x:c>
       <x:c r="L20" s="114" t="str">
-        <x:v>Planning only. No export, conversion, optional edge dependency, inference, profiler, or package generation is authorized.</x:v>
+        <x:v>Planning research only. Experiment Not Started. All 40 authorized_now fields are false. No target/backend selection, fixture, install, export, conversion, package, inference, profiler, memory planner, delegate, simulator, app, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M20" s="114" t="str">
-        <x:v>One backend, one thread, one worker, 32 MiB generated package and reports, 60 seconds per measurement worker, and 1 GiB peak RSS.</x:v>
+        <x:v>Future only: one backend/thread/worker; &lt;=60 s per measurement worker; &lt;=1 GiB RSS; &lt;=32 MiB generated package/report bytes; install bytes separately capped; protected/model/target/training counters remain zero.</x:v>
       </x:c>
       <x:c r="N20" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>Planning research complete; experiment Not Started; ExecuTorch/XNNPACK is a research lead only; no edge package or portable-hardware result exists.</x:v>
       </x:c>
       <x:c r="O20" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P20" s="150" t="str">
-        <x:v>https://docs.pytorch.org/executorch/stable/index.html</x:v>
+        <x:v>docs/LOOP_40_PRIMARY_SOURCE_RESEARCH.md; registries/loop40_research_boundary.v0.json; https://docs.pytorch.org/executorch/stable/getting-started.html; https://onnxruntime.ai/docs/tutorials/mobile/; https://developers.google.com/edge/litert/conversion/pytorch/overview; https://apple.github.io/coremltools/docs-guides/source/target-conversion-formats.html</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="138" customHeight="1">
@@ -10223,7 +10276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5f02093dee4cc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c3af451485447b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5d1a9718806a490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R7e7760243cb6443a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R18992b3c600445b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R9569b14db57145b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R718e032ddff24c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Re9ec5bcf72124432"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R13ef222941a44694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rd4e80a7a99424d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R7fccb2f7068341c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rec06eeab957e4758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8fc57ee0db9e460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R77d97c9dd6e54b67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra23a6da1326046bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rf5c89b3397e94da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R66db53b2d7864d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rf86c553f01aa4b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R8569a09b29454ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rf260feef78d642c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905befbe2f8143ab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1668f25ea2b246aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 40 planning research complete; edge-package experiment Not Started and unauthorized. ExecuTorch/XNNPACK is a research lead only; Loop 39 matrix and named target remain missing.</x:v>
+        <x:v>Loop 41 planning research complete; stream-to-NeuroToken experiment Not Started and unauthorized. Loop 25, Loop 37, Loop 39, and RW3 Stage A execution closeouts remain unsatisfied.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26b21fe5594c4b32"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb054410f504d486c"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcf8a42d97cb4b69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6142bffe2b5746f0"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4497,14 +4497,30 @@
       <x:c r="I54" s="12"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="37"/>
-      <x:c r="B55" s="12"/>
-      <x:c r="C55" s="12"/>
-      <x:c r="D55" s="12"/>
-      <x:c r="E55" s="12"/>
-      <x:c r="F55" s="12"/>
-      <x:c r="G55" s="12"/>
-      <x:c r="H55" s="12"/>
+      <x:c r="A55" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="str">
+        <x:v>41-R1</x:v>
+      </x:c>
+      <x:c r="C55" s="12" t="str">
+        <x:v>Preserve every clock and anomaly across the stream-to-token join; hold execution</x:v>
+      </x:c>
+      <x:c r="D55" s="12" t="str">
+        <x:v>Freeze 6 integration layers, 7 clock views, 8 anomaly classes, 5 schedules, 5 resume cuts, 18 hash bindings, 28 fixtures, 32 gates, and 42 refusals. Source time remains immutable; corrected time is derived; replay capture-to-text latency stays unavailable. All four execution dependencies remain unsatisfied.</x:v>
+      </x:c>
+      <x:c r="E55" s="12" t="str">
+        <x:v>docs/LOOP_41_PRIMARY_SOURCE_RESEARCH.md; registries/loop41_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+      </x:c>
+      <x:c r="F55" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G55" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H55" s="12" t="str">
+        <x:v>Make the exact Loop 25 decision separately; Loop 41 remains blocked on compatible Loop 25/37/39 and RW3 Stage A closeouts plus its own preregistration and authorization</x:v>
+      </x:c>
       <x:c r="I55" s="12"/>
     </x:row>
     <x:row r="56">
@@ -6122,7 +6138,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54dd5b160f834e30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778576cc378c4661"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7475,6 +7491,36 @@
       <x:c r="I46" t="str">
         <x:v>Active</x:v>
       </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>R46</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Stream-to-token clock, anomaly, state, and latency overclaim</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Source, corrected, arrival, preprocessing-ready, token-available, decoder, or render clocks are collapsed; gaps or reorder are silently repaired; resume state changes tokens; or replay scheduling is called capture-to-text latency.</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Require 7 distinct clock views, reversible correction ledgers, 8 anomaly classes, 5 schedules, 5 resume cuts, bounded hash-bound state, 18 provenance bindings, 32 gates, 42 refusals, and fail-closed unavailable latency fields.</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>A source timestamp is overwritten; clocks without a mapping are subtracted; a gap is interpolated; duplicate/reorder is hidden; a token spans a reset; resume hashes drift; or replay is called live, real-time, decoding, neural, device, or hardware proof.</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J47"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="8">
@@ -7505,7 +7551,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2659c7846f0b4916"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R648914ecc29743fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8182,10 +8228,21 @@
         <x:v>Read docs/LOOP_40_PRIMARY_SOURCE_RESEARCH.md and registries/loop40_research_boundary.v0.json. Confirm 7 qualification levels, 6 package layers, 4 unselected backend profiles, 20 identity fields, 8 output classes, 6 comparison classes, 24 fixtures, 4 stages, 30 gates, 40 refusals, and 40 false permissions. Loop 40 remains Not Started and unauthorized. Do not select a target/backend, install, export, convert, package, infer, profile, run a memory planner/delegate/simulator/app, open protected data, train, touch a device/hardware, hide fallback, change float32, or call packaging neural, decoding, capture-to-text latency, or portable-hardware proof.</x:v>
       </x:c>
     </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>Loop41-Research</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>Review Stream-To-NeuroToken Integration Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Read docs/LOOP_41_PRIMARY_SOURCE_RESEARCH.md and registries/loop41_research_boundary.v0.json. Confirm 6 integration layers, 7 clock views, 8 anomaly classes, 5 inherited schedules, 5 resume cuts, 18 hash bindings, 28 fixture families, 4 stages, 32 gates, 42 refusals, and 42 false permissions. Loop 41 remains Not Started and unauthorized. Do not create a fixture, seed, source chunk, correction, preprocessing output, adapter, state, NeuroToken payload, run a schedule/resume matrix, open protected data/targets/models, train, decode, use an LLM, launch a server/browser/socket/stream, import an SDK, touch a device/hardware, collapse clocks, repair anomalies silently, or call replay capture-to-text latency, decoding, neural information, live behavior, or portable hardware.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6feb5ace8ecc4034"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R165adb32c1744844"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8751,7 +8808,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434b359e5ec84112"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8528affd7e8549d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8800,7 +8857,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26 and 28-34 have completed planning research while their experiments remain Not Started; Loop 27 selected S25 metadata only. Loop 34 keeps confidence unavailable and requires fresh three-way evidence rather than reusing six real validation rows.</x:v>
+        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26-41 planning research is complete while every experiment remains Not Started and unauthorized.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -8820,7 +8877,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26 and 28-34 planning research complete / experiments Not Started | Loop 27 S25 metadata selected / preregistration blocked | Loop 34: seven semantics, eight scores/controls, 128/64/256 fresh synthetic partitions, 20 gates, 30 refusals, confidence unavailable | all execution flags false</x:v>
+        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26-41 planning research complete | Loops 42-44 Not Started | Every execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -10023,47 +10080,40 @@
         <x:v>This joins the acquisition contract to the model interface while keeping replay mechanics separate from hardware and decoding claims.</x:v>
       </x:c>
       <x:c r="G21" s="114" t="str">
-        <x:v>Build: Source-chunk to preprocessing to NeuroToken adapter, resume state, gap propagation, schedule matrix, and end-to-end provenance hashes.
-Research: Clock-domain and latency ledger mapping source, corrected, arrival, preprocessing, token, decoder, and render times.</x:v>
+        <x:v>Future build only: compose RW3 source chunks, authorized Loop 25 causal preprocessing, a causal NeuroToken producer, bounded resume state, anomaly propagation, all schedules, and complete provenance. Research complete: 6 layers, 7 clocks, 8 anomalies, 5 schedules, 5 resume cuts, 18 hash bindings, 28 fixtures, 32 gates, and 42 refusals.</x:v>
       </x:c>
       <x:c r="H21" s="114" t="str">
-        <x:v>Data: Only future authorized target-free RW3 synthetic replay; no BrainFlow, LSL, PyXDF, socket, live source, hardware, or real recording unless separately staged later.
-Controls:
-- Canonical offline path and every authorized chunk schedule.
-- Gap, duplicate, reorder, reconnect, and reset fixtures.
-- Raw, corrected, and arrival clocks kept distinct.
-- Resume from serialized state compared with uninterrupted replay.</x:v>
+        <x:v>Planning used official timing, streaming, and provenance sources plus committed contracts only. Future data is one separately authorized target-free synthetic replay. Preserve gaps, duplicates, reorder, reset, reconnect, source/corrected/arrival clocks, and uninterrupted versus resumed execution. No labels or target text.</x:v>
       </x:c>
       <x:c r="I21" s="114" t="str">
-        <x:v>- source, preprocessing, and token semantic hash agreement
-- timestamp and valid-length identity
-- gap and anomaly propagation
+        <x:v>- source/preprocessing/token/complete semantic hashes
+- timestamp, interval, length, mask, padding, and identity checks
+- anomaly and segment propagation
 - state bytes and resume identity
-- stage runtime, scheduling delay, peak RSS, and output bytes</x:v>
+- scheduling delay versus stage compute runtime
+- RSS, input/output/report bytes, warnings, unavailable fields, and access counters</x:v>
       </x:c>
       <x:c r="J21" s="114" t="str">
-        <x:v>Acceptance: Pass only when every authorized schedule and resume path preserves canonical tokens and provenance, and anomalies remain explicit rather than repaired silently.
-Stop: Any timestamp collapse, silent interpolation, lost anomaly, schedule-dependent token, or state mismatch parks integration before live or device work.</x:v>
+        <x:v>Acceptance: only after Loop 25/37/39 and RW3 Stage A close compatibly, plus separate Loop 41 preregistration and authorization. Every schedule, anomaly, and resume path must preserve registered source, preprocessing, token, state, and provenance semantics. Stop on silent repair, clock collapse, cross-gap token, schedule/resume drift, hidden latency, or cap failure.</x:v>
       </x:c>
       <x:c r="K21" s="114" t="str">
-        <x:v>Loops: 25, 37, 39
-External: explicit_rw3_stage_a_authorization_and_closeout, separate_loop41_authorization</x:v>
+        <x:v>Loops: compatible 25, 37, and 39 execution closeouts
+External: explicit RW3 Stage A authorization and closeout; separate Loop 41 preregistration and authorization</x:v>
       </x:c>
       <x:c r="L21" s="114" t="str">
-        <x:v>Planning only. This roadmap does not authorize RW3 Stage A or any adapter, fixture, source-chunk, stream, or token runtime.</x:v>
+        <x:v>Planning research only. Experiment Not Started. All 42 authorized_now fields are false. No seed, fixture, source chunk, correction, preprocessing, adapter, state, token runtime, payload, protected read, target, model, training, decoder, language model, server, browser, socket, stream, SDK, device, hardware, or latency claim is authorized.</x:v>
       </x:c>
       <x:c r="M21" s="114" t="str">
-        <x:v>One thread and worker, 32 MiB generated target-free artifacts, 60 seconds per worker, and 1 GiB peak RSS.</x:v>
+        <x:v>Current generated experiment bytes and execution operations: 0. Future only: 1 thread, 1 worker, &lt;=60 s/worker, &lt;=1 GiB RSS, &lt;=4 KiB RW3 state, &lt;=64 KiB complete state, &lt;=32 MiB fixtures/states/caches/reports, zero network/protected/target/model/training operations.</x:v>
       </x:c>
       <x:c r="N21" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>Planning research complete; experiment Not Started; no stream-to-NeuroToken runtime, replay-equivalence result, live source, end-to-end latency, decoding, neural, device, or portable-hardware claim.</x:v>
       </x:c>
       <x:c r="O21" s="147" t="str">
         <x:v>Not Started</x:v>
       </x:c>
       <x:c r="P21" s="150" t="str">
-        <x:v>https://labstreaminglayer.readthedocs.io/info/time_synchronization.html
-https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html</x:v>
+        <x:v>docs/LOOP_41_PRIMARY_SOURCE_RESEARCH.md; registries/loop41_research_boundary.v0.json; https://labstreaminglayer.readthedocs.io/info/time_synchronization.html; https://www.w3.org/TR/hr-time-3/; https://bids-specification.readthedocs.io/en/stable/derivatives/introduction.html</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="138" customHeight="1">
@@ -10276,7 +10326,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c3af451485447b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc8035c1280040e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rec06eeab957e4758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R8fc57ee0db9e460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R77d97c9dd6e54b67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Ra23a6da1326046bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rf5c89b3397e94da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R66db53b2d7864d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rf86c553f01aa4b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R8569a09b29454ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Rf260feef78d642c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1033cd2830e44551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R084509b2650c4f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4644f094f2174992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0f26726094fb473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R265166eacbbc4ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R13bcaefb0fc944d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R86717e1ef7f84663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R0f7412e5012c4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9e4fc00bde884bef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1668f25ea2b246aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbb142de681e432b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 41 planning research complete; stream-to-NeuroToken experiment Not Started and unauthorized. Loop 25, Loop 37, Loop 39, and RW3 Stage A execution closeouts remain unsatisfied.</x:v>
+        <x:v>Loop 42 planning research complete: OpenBCI Cyton base 8-channel USB-radio selected at Q0 for future mechanics only; experiment Not Started and unauthorized.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb054410f504d486c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d2e28f7545a4f9d"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6142bffe2b5746f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd833dddc2d1a490e"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4524,15 +4524,32 @@
       <x:c r="I55" s="12"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="37"/>
-      <x:c r="B56" s="12"/>
-      <x:c r="C56" s="12"/>
-      <x:c r="D56" s="12"/>
-      <x:c r="E56" s="12"/>
-      <x:c r="F56" s="12"/>
-      <x:c r="G56" s="12"/>
-      <x:c r="H56" s="12"/>
+      <x:c r="A56" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B56" s="12" t="str">
+        <x:v>42-R1</x:v>
+      </x:c>
+      <x:c r="C56" s="12" t="str">
+        <x:v>Select OpenBCI Cyton base 8-channel USB-radio as the future mechanics candidate at Q0 only.</x:v>
+      </x:c>
+      <x:c r="D56" s="12" t="str">
+        <x:v>Official packet, firmware, reference, local-file, and BrainFlow paths are inspectable; selection is not purchase, qualification, or decoding evidence.</x:v>
+      </x:c>
+      <x:c r="E56" s="12" t="str">
+        <x:v>No device/SDK/participant/runtime; Daisy, Wi-Fi, cloud, targets, models, and capture-latency inference excluded.</x:v>
+      </x:c>
+      <x:c r="F56" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G56" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H56" s="12" t="str">
+        <x:v>Keep Loop 42 unauthorized until Loops 38/41, RW3 Stage A, consent/retention, a preregistration, and an exact stage-only authorization are independently satisfied.</x:v>
+      </x:c>
       <x:c r="I56" s="12"/>
+      <x:c r="J56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37"/>
@@ -6138,7 +6155,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778576cc378c4661"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551ea2034b744e43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7521,6 +7538,35 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>R47</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Device qualification, clock, privacy, and safety overclaim</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Device specification or connectivity is promoted into EEG quality, capture latency, privacy, home usability, or text-decoding evidence.</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>Freeze Q0-Q5 levels, exact candidate identity, separate clocks, network-off audit, battery-only safety, four stage authorizations, 34 gates, and 46 refusals.</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>A device is called qualified before packet/accounting gates pass; adapter time is called physical capture time; ExG is called EEG without montage/reference; or local storage is called privacy proof.</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>Active</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="8">
@@ -7551,7 +7597,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R648914ecc29743fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8418dcd3834516"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8239,10 +8285,21 @@
         <x:v>Read docs/LOOP_41_PRIMARY_SOURCE_RESEARCH.md and registries/loop41_research_boundary.v0.json. Confirm 6 integration layers, 7 clock views, 8 anomaly classes, 5 inherited schedules, 5 resume cuts, 18 hash bindings, 28 fixture families, 4 stages, 32 gates, 42 refusals, and 42 false permissions. Loop 41 remains Not Started and unauthorized. Do not create a fixture, seed, source chunk, correction, preprocessing output, adapter, state, NeuroToken payload, run a schedule/resume matrix, open protected data/targets/models, train, decode, use an LLM, launch a server/browser/socket/stream, import an SDK, touch a device/hardware, collapse clocks, repair anomalies silently, or call replay capture-to-text latency, decoding, neural information, live behavior, or portable hardware.</x:v>
       </x:c>
     </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>Loop42-Research</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Review One-Device Qualification Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>Read docs/LOOP_42_PRIMARY_SOURCE_RESEARCH.md and registries/loop42_research_boundary.v0.json. Confirm 28 identity fields, 16 packet fields, 7 timing observables, 10 anomalies, 10 privacy surfaces, 10 safety requirements, 6 qualification levels, 4 stages, 30 fixtures, 34 gates, 46 refusals, and 45 false permissions. Loop 42 remains Not Started and unauthorized. Do not import an SDK, create a fixture, run playback, discover or connect a device, open a socket or stream, collect participant data, access targets/models, train, decode, use Daisy/Wi-Fi/cloud, infer physical capture time from adapter timestamps, or call specification review connectivity, EEG quality, privacy, real-time behavior, portable hardware, or decoding proof.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R165adb32c1744844"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f44d9f617d433c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8808,7 +8865,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8528affd7e8549d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb280da40e044dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10130,53 +10187,48 @@
         <x:v>P2 / L</x:v>
       </x:c>
       <x:c r="E22" s="114" t="str">
-        <x:v>Can one named device preserve declared channels, units, clocks, packets, and privacy from recorded replay through a bounded local session?</x:v>
+        <x:v>Can one exact OpenBCI Cyton 8-channel USB-radio path preserve declared configuration, packets, clocks, locality, and safety boundaries?</x:v>
       </x:c>
       <x:c r="F22" s="114" t="str">
-        <x:v>One measured device is more credible than broad compatibility claims based on SDK imports or vendor tables.</x:v>
+        <x:v>Q0 planning packet: 28 identity fields, 16 packet fields, 7 timing observables, 10 anomalies, 4 stages, 34 gates, 46 refusals.</x:v>
       </x:c>
       <x:c r="G22" s="114" t="str">
-        <x:v>Build: Device descriptor, consent and locality checklist, recorded-versus-live equivalence packet, loss/reconnect stress report, and compatibility-level decision.
-Research: Device-specific timestamp, unit, reference, geometry, firmware, and data-retention review.</x:v>
+        <x:v>Current: official-specification candidate only. Future: exact device/firmware/dongle/adapter/host stage gates; no connectivity-to-signal or latency promotion.</x:v>
       </x:c>
       <x:c r="H22" s="114" t="str">
-        <x:v>Data: One separately approved board or headset, one local synthetic or consented non-sensitive qualification session, and no decoding target unless separately approved.
-Controls:
-- SDK synthetic or playback source before physical hardware.
-- Recorded and live paths compared under the same source-chunk contract.
-- Packet loss, reconnect, clock reset, and buffer-drain stress cases.
-- Network-off and local-storage audit.</x:v>
+        <x:v>No current data. Future target-free synthetic/playback, no-contact bench, then separately consented scalp mechanics with frozen controls.</x:v>
       </x:c>
       <x:c r="I22" s="114" t="str">
-        <x:v>- channel, unit, rate, and packet identity
-- clock offset, jitter, gaps, duplicates, and reorder counts
-- capture-to-arrival timing boundary
-- runtime, peak RSS, bytes, and dropped samples
-- privacy and retention violations</x:v>
+        <x:v>Packet integrity, loss/reorder/duplicate/wrap, timestamp provenance, observed latency levels, locality, raw/derived bytes, RSS, warnings.</x:v>
       </x:c>
       <x:c r="J22" s="114" t="str">
-        <x:v>Acceptance: Qualify only the named device, firmware, transport, host, and tested compatibility level; connectivity alone cannot qualify signal quality or decoding.
-Stop: Park physical qualification on ambiguous consent, cloud dependence, hidden timestamps, unstable identity, unsafe retention, or failed replay equivalence.</x:v>
+        <x:v>Acceptance: qualify only the exact device/firmware/dongle/adapter/host/stage whose gates pass. Stop on unsafe power, hidden cloud/network retention, ambiguous identity, clock inference, or failed packet/accounting gates.</x:v>
       </x:c>
       <x:c r="K22" s="114" t="str">
-        <x:v>Loops: 29, 38, 41
-External: explicit_device_stage_authorization, ethics_consent_and_retention_approval</x:v>
+        <x:v>Loops: 29, 38, 41; External: explicit stage authorization plus ethics, consent, and retention approval before any participant-contact stage.</x:v>
       </x:c>
       <x:c r="L22" s="114" t="str">
-        <x:v>Planning only. No SDK import, device discovery, socket, stream, board, hardware, or recording session is authorized.</x:v>
+        <x:v>Planning only. No SDK import, fixture, runtime, device discovery, socket, stream, board, participant, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M22" s="114" t="str">
-        <x:v>One device, one host, one thread for analysis, exact session and byte cap in a future packet, 32 MiB derived artifacts, and no cloud upload.</x:v>
+        <x:v>One candidate/device/host/thread/worker; future stage caps 60/60/300/600 s; 1 GiB RSS; 64 MiB raw plus 32 MiB derived; zero network/cloud.</x:v>
       </x:c>
       <x:c r="N22" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>researched_not_authorized</x:v>
       </x:c>
       <x:c r="O22" s="147" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete</x:v>
       </x:c>
       <x:c r="P22" s="150" t="str">
-        <x:v>https://labstreaminglayer.readthedocs.io/info/time_synchronization.html
-https://www.nist.gov/privacy-framework/privacy-framework</x:v>
+        <x:v>https://docs.openbci.com/Cyton/CytonDataFormat/
+https://docs.openbci.com/Cyton/CytonSDK/
+https://docs.openbci.com/Cyton/CytonSpecs/
+https://docs.openbci.com/GettingStarted/Biosensing-Setups/EEGSetup/
+https://docs.openbci.com/Software/OpenBCISoftware/GUIDocs/
+https://docs.openbci.com/FAQ/PrivacyNotice/
+https://brainflow.readthedocs.io/en/stable/SupportedBoards.html
+https://brainflow.readthedocs.io/en/stable/DataFormatDesc.html
+https://github.com/brainflow-dev/brainflow/blob/master/LICENSE</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="138" customHeight="1">
@@ -10326,7 +10378,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc8035c1280040e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e81c224c1840a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1033cd2830e44551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R084509b2650c4f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4644f094f2174992"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R0f26726094fb473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R265166eacbbc4ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R13bcaefb0fc944d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R86717e1ef7f84663"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R0f7412e5012c4d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9e4fc00bde884bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R34809ed74286405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R64e076736c7a408c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Ra942bc5eceb24bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re6c9d1d6748e4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R2c0aba6ea04d4525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R3919954e666743df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R3f2a31d04eb74ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4ea2a3e3110b414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R85e44514ec7e424d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbb142de681e432b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea1a2f1d35654a7c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,7 +1363,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 42 planning research complete: OpenBCI Cyton base 8-channel USB-radio selected at Q0 for future mechanics only; experiment Not Started and unauthorized.</x:v>
+        <x:v>Loop 43 planning research complete: challenge Not Started and unauthorized; local validator incident recorded (136 cache JSON, 11 known session-2 files, no tuning/scoring).</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1500,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d2e28f7545a4f9d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fa38db491794da4"/>
 </x:worksheet>
 </file>
 
@@ -2914,7 +2914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd833dddc2d1a490e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7e42db2fa3415f"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -4552,15 +4552,32 @@
       <x:c r="J56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="37"/>
-      <x:c r="B57" s="12"/>
-      <x:c r="C57" s="12"/>
-      <x:c r="D57" s="12"/>
-      <x:c r="E57" s="12"/>
-      <x:c r="F57" s="12"/>
-      <x:c r="G57" s="12"/>
-      <x:c r="H57" s="12"/>
+      <x:c r="A57" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B57" s="12" t="str">
+        <x:v>43-R1</x:v>
+      </x:c>
+      <x:c r="C57" s="12" t="str">
+        <x:v>Separate independent artifact reproduction from scientific replication and freeze a target-free commit-reveal challenge boundary.</x:v>
+      </x:c>
+      <x:c r="D57" s="12" t="str">
+        <x:v>A maintainer rerun is repeatability; author-artifact reproduction by an eligible external environment is narrower than independent scientific implementation.</x:v>
+      </x:c>
+      <x:c r="E57" s="12" t="str">
+        <x:v>No packet/oracle/contributor/runtime; validator incident read 136 cache JSON and 11 known session-2 files with no tuning/scoring; no raw neural payload or privileged untrusted CI.</x:v>
+      </x:c>
+      <x:c r="F57" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G57" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H57" s="12" t="str">
+        <x:v>Keep Loop 43 unauthorized until compatible Loops 37-39 close and each A-D stage receives its own hash-bound authorization and green CI.</x:v>
+      </x:c>
       <x:c r="I57" s="12"/>
+      <x:c r="J57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37"/>
@@ -6155,7 +6172,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551ea2034b744e43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ef332725ec4886"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7565,6 +7582,35 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="I48" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>R48</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Independent reproduction and scientific replication overclaim</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>A maintainer rerun, assisted contributor, author-artifact reproduction, or one environment is promoted into scientific replication or generalization.</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>Freeze independence identities, commit-reveal order, public communication, registered comparisons, discrepancy ledger, unprivileged CI, four stage authorizations, 36 gates, and 48 refusals.</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>Private guidance, author/checker edits, early oracle reveal, hidden negative outcome, privileged fork execution, or population/platform/device claim from one artifact run.</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -7597,7 +7643,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8418dcd3834516"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d481221d154729"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8296,10 +8342,21 @@
         <x:v>Read docs/LOOP_42_PRIMARY_SOURCE_RESEARCH.md and registries/loop42_research_boundary.v0.json. Confirm 28 identity fields, 16 packet fields, 7 timing observables, 10 anomalies, 10 privacy surfaces, 10 safety requirements, 6 qualification levels, 4 stages, 30 fixtures, 34 gates, 46 refusals, and 45 false permissions. Loop 42 remains Not Started and unauthorized. Do not import an SDK, create a fixture, run playback, discover or connect a device, open a socket or stream, collect participant data, access targets/models, train, decode, use Daisy/Wi-Fi/cloud, infer physical capture time from adapter timestamps, or call specification review connectivity, EEG quality, privacy, real-time behavior, portable hardware, or decoding proof.</x:v>
       </x:c>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>Loop43-Research</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Review Independent Reproduction Boundary Without Executing It</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>Read docs/LOOP_43_PRIMARY_SOURCE_RESEARCH.md and registries/loop43_research_boundary.v0.json. Confirm 7 qualification levels, 16 independence fields, 28 packet fields, 34 submission fields, 8 comparisons, 12 discrepancies, 4 stages, 32 fixtures, 36 gates, 48 refusals, and 48 false permissions. Confirm the validator incident: 136 cache JSON files, 11 known consumed session-2 files, zero raw arrays/FIF/MAT/model/tuning/scoring, and the zero-consumed-read claim withdrawn. Loop 43 remains Not Started and unauthorized. Do not create a packet, oracle, fixture, issue, workflow, outreach, contributor submission, adjudication, archive, DOI, badge, release, protected payload, model, stream, device, or runtime. Do not call repeatability independent, author-artifact reproduction scientific replication, or one environment population/platform/device generalization.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f44d9f617d433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c00e9943d54503"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8865,7 +8922,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb280da40e044dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4285a31178b647b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10245,54 +10302,48 @@
         <x:v>P1 / M</x:v>
       </x:c>
       <x:c r="E23" s="114" t="str">
-        <x:v>Can an independent contributor reproduce a bounded claim from documented inputs without private guidance or sharing neural recordings?</x:v>
+        <x:v>Can one eligible external environment reproduce a frozen target-free software artifact without private guidance or protected neural data?</x:v>
       </x:c>
       <x:c r="F23" s="114" t="str">
-        <x:v>Independent reproduction tests the developer experience, evidence contracts, and contribution path more honestly than another maintainer-run demo.</x:v>
+        <x:v>Planning packet: 7 qualification levels, 16 independence fields, 28 packet fields, 34 submission fields, 8 comparisons, 12 discrepancies, 4 stages, 36 gates, 48 refusals.</x:v>
       </x:c>
       <x:c r="G23" s="114" t="str">
-        <x:v>Build: Challenge packet, fixture manifest, expected semantic checks, environment capture, blinded result card, and discrepancy triage workflow.
-Research: Reproduction protocol distinguishing exact replication, computational reproduction, and extension on contributor-owned data.</x:v>
+        <x:v>Current: Q0 unavailable and artifact ineligible. Future: commit-reveal target-free NeuroToken causal-replay artifact reproduction; not scientific replication.</x:v>
       </x:c>
       <x:c r="H23" s="114" t="str">
-        <x:v>Data: Public code plus tiny synthetic fixtures by default; contributors keep any owned EEG local and submit metadata/aggregate reports only.
-Controls:
-- Maintainer and contributor environments recorded independently.
-- Expected results hidden where needed until submission hash freezes.
-- No private recording, secret, absolute path, or participant identifier in the submission.
-- Negative and failed reproductions retained.</x:v>
+        <x:v>Incident: local validator parsed 136 cache JSON files, including 11 known consumed session-2 reports/metadata; no tuning, scoring, inference, or claim selection. Future public target-free synthetic artifact only.</x:v>
       </x:c>
       <x:c r="I23" s="114" t="str">
-        <x:v>- semantic and numerical reproduction rate
-- setup time and command count
-- environment and warning completeness
-- discrepancy classes
-- contributor artifact bytes and privacy findings</x:v>
+        <x:v>Semantic/discrete identity, registered floating tolerances, environment and command ledger, runtime/RSS/bytes, warnings, discrepancies, privacy/security findings.</x:v>
       </x:c>
       <x:c r="J23" s="114" t="str">
-        <x:v>Acceptance: Pass when at least one independent environment reproduces the registered artifact contract and a discrepancy, if any, is resolved or documented without moving the claim boundary.
-Stop: Do not promote a result that depends on undocumented maintainer state, private hand edits, leaked data, or an unreviewed tolerance change.</x:v>
+        <x:v>Acceptance: one eligible commit-reveal submission may establish only independent reproduction of the exact artifact contract. Stop on missing independence, commitment order, semantic identity, privacy/security, resource, credit, or release gates.</x:v>
       </x:c>
       <x:c r="K23" s="114" t="str">
-        <x:v>Loops: 37, 38, 39
-External: community_participant_and_challenge_review</x:v>
+        <x:v>Loops: 37, 38, 39; External: separate A-D authorizations, community participant/review, and Loop 44 claim review.</x:v>
       </x:c>
       <x:c r="L23" s="114" t="str">
-        <x:v>Planning only. No outreach, external data exchange, or challenge execution is authorized by the roadmap file.</x:v>
+        <x:v>Planning only. No packet, oracle, fixture, issue, workflow, outreach, contributor, submission, adjudication, archive, badge, DOI, release, or runtime is authorized. Zero-consumed-read claim withdrawn after recorded validator incident.</x:v>
       </x:c>
       <x:c r="M23" s="114" t="str">
-        <x:v>Tiny public fixtures only, one-thread reference commands, 32 MiB submission cap, and no neural recording upload.</x:v>
+        <x:v>One CPU thread/worker; 300 s A/B, 900 s C/D; 1 GiB RSS; 16 MiB packet, 32 MiB submission, 16 MiB archive, 64 MiB total; zero neural payload.</x:v>
       </x:c>
       <x:c r="N23" s="141" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>researched_not_authorized</x:v>
       </x:c>
       <x:c r="O23" s="147" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete</x:v>
       </x:c>
       <x:c r="P23" s="150" t="str">
-        <x:v>https://arxiv.org/abs/2404.15319
-https://arxiv.org/abs/1810.03993
-https://arxiv.org/abs/1803.09010</x:v>
+        <x:v>https://www.acm.org/publications/policies/artifact-review-and-badging-current
+https://codecheck.org.uk/
+https://codecheck.org.uk/project/
+https://resciencec.readthedocs.io/en/latest/submitting.html
+https://rescience.github.io/faq/
+https://www.jmlr.org/papers/v22/20-303.html
+https://doi.org/10.15497/RDA00068
+https://docs.github.com/en/actions/reference/security/secure-use
+https://docs.github.com/en/actions/reference/security/securely-using-pull_request_target</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="138" customHeight="1">
@@ -10378,7 +10429,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e81c224c1840a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf3c72fa9bb4caa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R34809ed74286405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R64e076736c7a408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Ra942bc5eceb24bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re6c9d1d6748e4459"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R2c0aba6ea04d4525"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R3919954e666743df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R3f2a31d04eb74ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4ea2a3e3110b414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R85e44514ec7e424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb5f1ba03791040f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re1abda9233304cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rbe76bd6579a948c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R49d1cab30e6b4895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Re1096d2738904967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R84638497a18943d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rdf1ead6837314b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R2f6d3b5084ed4b9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R98a24ba74e5549be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R2efd4f9d28de48e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +28,7 @@
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -139,8 +140,26 @@
       <x:color rgb="FF245C8A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF6D4C00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF16324F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF234A60"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="24">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -257,8 +276,43 @@
         <x:fgColor rgb="FFFFF4D6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF16324F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEAF3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF276A73"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDECEC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="13">
     <x:border/>
     <x:border/>
     <x:border>
@@ -328,11 +382,41 @@
         <x:color rgb="FFD9E1E5"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1B76B"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="153">
+  <x:cellXfs count="217">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -717,6 +801,176 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -974,7 +1228,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea1a2f1d35654a7c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb6668e7d5db4a65"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1091,6 +1345,31 @@
     <x:tableColumn id="11" name="Dependencies"/>
     <x:tableColumn id="12" name="Authorization boundary"/>
     <x:tableColumn id="13" name="Resource cap"/>
+    <x:tableColumn id="14" name="Proof posture"/>
+    <x:tableColumn id="15" name="Status"/>
+    <x:tableColumn id="16" name="Primary source URLs"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="ScientificLoopsTable" displayName="ScientificLoopsTable" ref="A4:P24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:P24"/>
+  <x:tableColumns count="16">
+    <x:tableColumn id="1" name="Loop"/>
+    <x:tableColumn id="2" name="Phase"/>
+    <x:tableColumn id="3" name="Work order"/>
+    <x:tableColumn id="4" name="Priority"/>
+    <x:tableColumn id="5" name="Core question"/>
+    <x:tableColumn id="6" name="Scientific claim target"/>
+    <x:tableColumn id="7" name="Build deliverable"/>
+    <x:tableColumn id="8" name="Data scope + controls"/>
+    <x:tableColumn id="9" name="Primary metrics"/>
+    <x:tableColumn id="10" name="Acceptance + kill/park"/>
+    <x:tableColumn id="11" name="Dependencies"/>
+    <x:tableColumn id="12" name="Authorization boundary"/>
+    <x:tableColumn id="13" name="Future resource cap"/>
     <x:tableColumn id="14" name="Proof posture"/>
     <x:tableColumn id="15" name="Status"/>
     <x:tableColumn id="16" name="Primary source URLs"/>
@@ -1259,7 +1538,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="21" t="str">
-        <x:v>NeuroDecodeKit Roadmap Tracker: Original 20 + Current Gate + Next 20</x:v>
+        <x:v>NeuroDecodeKit Roadmap Tracker: Original 20 + Evidence 25-44 + Scientific 45-64</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -1341,7 +1620,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 25 amended v1; authorization pending</x:v>
+        <x:v>Loop 25 v1 authorization decision pending</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1358,12 +1637,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="280" customHeight="1">
+    <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 43 planning research complete: challenge Not Started and unauthorized; local validator incident recorded (136 cache JSON, 11 known session-2 files, no tuning/scoring).</x:v>
+        <x:v>Loop 44 artifact review complete: engineering release held and scientific release parked. Loops 45-64 target a real neural-effect verdict, strict unseen-person test, fresh EEG, causal local use, and independent evidence. Every execution flag is false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1500,7 +1779,1498 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fa38db491794da4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f757ce1d9a44800"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="43" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="35" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="156" t="str">
+        <x:v>NeuroDecodeKit Scientific Evidence Roadmap: Loops 45-64</x:v>
+      </x:c>
+      <x:c r="B1" s="156"/>
+      <x:c r="C1" s="156"/>
+      <x:c r="D1" s="156"/>
+      <x:c r="E1" s="156"/>
+      <x:c r="F1" s="156"/>
+      <x:c r="G1" s="156"/>
+      <x:c r="H1" s="156"/>
+      <x:c r="I1" s="156"/>
+      <x:c r="J1" s="156"/>
+      <x:c r="K1" s="156"/>
+      <x:c r="L1" s="156"/>
+      <x:c r="M1" s="156"/>
+      <x:c r="N1" s="156"/>
+      <x:c r="O1" s="156"/>
+      <x:c r="P1" s="156"/>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="161" t="str">
+        <x:v>North star: prove one target-blind real neural effect against no-signal and corrupted-signal controls, then test the frozen effect on one unseen person. EEG, streaming, home, and release claims remain downstream and separate.</x:v>
+      </x:c>
+      <x:c r="B2" s="161"/>
+      <x:c r="C2" s="161"/>
+      <x:c r="D2" s="161"/>
+      <x:c r="E2" s="161"/>
+      <x:c r="F2" s="161"/>
+      <x:c r="G2" s="161"/>
+      <x:c r="H2" s="161"/>
+      <x:c r="I2" s="161"/>
+      <x:c r="J2" s="161"/>
+      <x:c r="K2" s="161"/>
+      <x:c r="L2" s="161"/>
+      <x:c r="M2" s="161"/>
+      <x:c r="N2" s="161"/>
+      <x:c r="O2" s="161"/>
+      <x:c r="P2" s="161"/>
+    </x:row>
+    <x:row r="3" ht="48" customHeight="1">
+      <x:c r="A3" s="173" t="str">
+        <x:v>Planning only | 20 loops | 5 phases | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
+      </x:c>
+      <x:c r="B3" s="174"/>
+      <x:c r="C3" s="174"/>
+      <x:c r="D3" s="174"/>
+      <x:c r="E3" s="174"/>
+      <x:c r="F3" s="174"/>
+      <x:c r="G3" s="174"/>
+      <x:c r="H3" s="174"/>
+      <x:c r="I3" s="174"/>
+      <x:c r="J3" s="174"/>
+      <x:c r="K3" s="174"/>
+      <x:c r="L3" s="174"/>
+      <x:c r="M3" s="174"/>
+      <x:c r="N3" s="174"/>
+      <x:c r="O3" s="174"/>
+      <x:c r="P3" s="175"/>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="180" t="str">
+        <x:v>Loop</x:v>
+      </x:c>
+      <x:c r="B4" s="180" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="C4" s="180" t="str">
+        <x:v>Work order</x:v>
+      </x:c>
+      <x:c r="D4" s="180" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="E4" s="180" t="str">
+        <x:v>Core question</x:v>
+      </x:c>
+      <x:c r="F4" s="180" t="str">
+        <x:v>Scientific claim target</x:v>
+      </x:c>
+      <x:c r="G4" s="180" t="str">
+        <x:v>Build deliverable</x:v>
+      </x:c>
+      <x:c r="H4" s="180" t="str">
+        <x:v>Data scope + controls</x:v>
+      </x:c>
+      <x:c r="I4" s="180" t="str">
+        <x:v>Primary metrics</x:v>
+      </x:c>
+      <x:c r="J4" s="180" t="str">
+        <x:v>Acceptance + kill/park</x:v>
+      </x:c>
+      <x:c r="K4" s="180" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="L4" s="180" t="str">
+        <x:v>Authorization boundary</x:v>
+      </x:c>
+      <x:c r="M4" s="180" t="str">
+        <x:v>Future resource cap</x:v>
+      </x:c>
+      <x:c r="N4" s="180" t="str">
+        <x:v>Proof posture</x:v>
+      </x:c>
+      <x:c r="O4" s="180" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="P4" s="180" t="str">
+        <x:v>Primary source URLs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="174" customHeight="1">
+      <x:c r="A5" s="190" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B5" s="128" t="str">
+        <x:v>P6 - Real Signal Truth</x:v>
+      </x:c>
+      <x:c r="C5" s="193" t="str">
+        <x:v>Causal Source-Path Qualification</x:v>
+      </x:c>
+      <x:c r="D5" s="134" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E5" s="113" t="str">
+        <x:v>Can the amended Loop 25 v1 preprocessing path pass its static anti-alias and exact causal replay gates before any real training row opens?</x:v>
+      </x:c>
+      <x:c r="F5" s="199" t="str">
+        <x:v>mechanics prerequisite only</x:v>
+      </x:c>
+      <x:c r="G5" s="113" t="str">
+        <x:v>Execute the already frozen v1 filter-design, response, alias, schedule, resume, state, timestamp, and mutation gates under its own authorization sequence.</x:v>
+      </x:c>
+      <x:c r="H5" s="113" t="str">
+        <x:v>Data: Fresh target-free synthetic seeds 2501 then conditional 2502 only; no S21, S7, S20, or S25 payload.
+Controls:
+- 65,537-point response grid
+- 23 alias probes
+- 7 schedules
+- 10 resume cuts
+- 3 future-mutation cuts
+- noncausal reference reported separately</x:v>
+      </x:c>
+      <x:c r="I5" s="113" t="str">
+        <x:v>- folding-band attenuation
+- alias destination error
+- sample and timestamp identity
+- right-context samples
+- runtime
+- peak RSS
+- artifact bytes</x:v>
+      </x:c>
+      <x:c r="J5" s="113" t="str">
+        <x:v>Accept: The static anti-alias gate passes before seed 2501 opens and every causal replay invariant passes within the frozen v1 tolerances and resource caps.
+Kill/Park: Park the exact transform with both seeds unopened if the static gate fails; do not alter schedules, tolerances, or filters after protected access.</x:v>
+      </x:c>
+      <x:c r="K5" s="113" t="str">
+        <x:v>Loops: 25</x:v>
+      </x:c>
+      <x:c r="L5" s="113" t="str">
+        <x:v>Requires the exact separate Loop 25 v1 authorization-only commit and green CI; this roadmap does not supply it.</x:v>
+      </x:c>
+      <x:c r="M5" s="113" t="str">
+        <x:v>one thread; one worker; 45 seconds internal; 1 GiB RSS; 8 MiB generated</x:v>
+      </x:c>
+      <x:c r="N5" s="205" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O5" s="214" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P5" s="113" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="174" customHeight="1">
+      <x:c r="A6" s="191" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B6" s="129" t="str">
+        <x:v>P6 - Real Signal Truth</x:v>
+      </x:c>
+      <x:c r="C6" s="194" t="str">
+        <x:v>Reserved S21 Neural-Effect Gate</x:v>
+      </x:c>
+      <x:c r="D6" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E6" s="114" t="str">
+        <x:v>Does one fixed 2,908-parameter causal encoder beat the train-only no-signal prior on all six reserved S21 source-validation sentences?</x:v>
+      </x:c>
+      <x:c r="F6" s="200" t="str">
+        <x:v>bounded one-person one-session neural advantage on source validation</x:v>
+      </x:c>
+      <x:c r="G6" s="114" t="str">
+        <x:v>Preregister, train on 55 source-train rows, hash-freeze six predictions, open six validation targets once, and report exact paired inference.</x:v>
+      </x:c>
+      <x:c r="H6" s="114" t="str">
+        <x:v>Data: S21 session-1 source train and six reserved validation rows only; five source-test rows and session 2 remain closed.
+Controls:
+- train-only no-signal prior
+- zero-signal inference
+- semantic-ID target derangement
+- time displacement
+- channel-name-hash derangement
+- 2,884-parameter linear signal comparator</x:v>
+      </x:c>
+      <x:c r="I6" s="114" t="str">
+        <x:v>- macro sentence CER
+- corpus CER
+- 64 exact sign assignments
+- margin over every control
+- wins ties losses
+- blank fraction
+- runtime and RSS</x:v>
+      </x:c>
+      <x:c r="J6" s="114" t="str">
+        <x:v>Accept: Candidate improves macro sentence CER over the prior by at least 0.05, p &lt;= 0.05 under the frozen exact paired rule, and strictly beats every signal-free and corrupted-signal control.
+Kill/Park: If any primary or control gate fails, park real-model scaling and move to Loop 48 failure localization; never open source test or increase model size.</x:v>
+      </x:c>
+      <x:c r="K6" s="114" t="str">
+        <x:v>Loops: 45, 26</x:v>
+      </x:c>
+      <x:c r="L6" s="114" t="str">
+        <x:v>Needs a new hash-bound preregistration and a separate authorization for exact cache members, targets, training, and validation opening.</x:v>
+      </x:c>
+      <x:c r="M6" s="114" t="str">
+        <x:v>one thread; one worker; &lt;=2,908 trainable parameters; &lt;=20 CPU minutes; &lt;=1 GiB RSS; &lt;=32 MiB generated</x:v>
+      </x:c>
+      <x:c r="N6" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O6" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P6" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="174" customHeight="1">
+      <x:c r="A7" s="191" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B7" s="129" t="str">
+        <x:v>P6 - Real Signal Truth</x:v>
+      </x:c>
+      <x:c r="C7" s="194" t="str">
+        <x:v>Neural Signal Attribution Matrix</x:v>
+      </x:c>
+      <x:c r="D7" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E7" s="114" t="str">
+        <x:v>If Loop 46 passes, does the advantage require intact sensor signal rather than timing, labels, padding, or a language prior?</x:v>
+      </x:c>
+      <x:c r="F7" s="200" t="str">
+        <x:v>sensor-signal dependence for the exact S21 source slice</x:v>
+      </x:c>
+      <x:c r="G7" s="114" t="str">
+        <x:v>Execute the frozen Loop 31 ten-condition encoder matrix with intersection-union logic and prediction commitments before target opening.</x:v>
+      </x:c>
+      <x:c r="H7" s="114" t="str">
+        <x:v>Data: Exactly the authorized Loop 46 train/validation members and frozen predictions; no source test, session 2, S7, S20, or S25.
+Controls:
+- no-signal prior
+- zero signal
+- channel derangement
+- time displacement
+- train-target derangement
+- padding-only
+- timestamp-only
+- linear signal comparator
+- candidate encoder
+- frozen positive control</x:v>
+      </x:c>
+      <x:c r="I7" s="114" t="str">
+        <x:v>- macro CER deltas
+- all six paired differences
+- intersection-union pass
+- control ordering
+- prediction hashes
+- access counters</x:v>
+      </x:c>
+      <x:c r="J7" s="114" t="str">
+        <x:v>Accept: The intact-signal candidate strictly beats every registered signal-free and corrupted-signal condition under the frozen paired rule.
+Kill/Park: Any shortcut win blocks a neural-contribution claim and sends the exact discrepancy to Loop 48 or the Loop 35 peripheral firewall.</x:v>
+      </x:c>
+      <x:c r="K7" s="114" t="str">
+        <x:v>Loops: 46, 31</x:v>
+      </x:c>
+      <x:c r="L7" s="114" t="str">
+        <x:v>Contingent on a passing Loop 46 and a separate matrix authorization; language-model and NeuroToken extensions remain separately gated.</x:v>
+      </x:c>
+      <x:c r="M7" s="114" t="str">
+        <x:v>one thread; one worker; no new architecture; &lt;=10 inference conditions; &lt;=15 CPU minutes; &lt;=32 MiB generated</x:v>
+      </x:c>
+      <x:c r="N7" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O7" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P7" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="174" customHeight="1">
+      <x:c r="A8" s="191" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B8" s="129" t="str">
+        <x:v>P6 - Real Signal Truth</x:v>
+      </x:c>
+      <x:c r="C8" s="194" t="str">
+        <x:v>Negative-Result Failure Localization</x:v>
+      </x:c>
+      <x:c r="D8" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E8" s="114" t="str">
+        <x:v>If the real effect gate fails, is the limiting factor target identity, causal preprocessing, signal quality, temporal resolution, model fit, or no-signal prior strength?</x:v>
+      </x:c>
+      <x:c r="F8" s="200" t="str">
+        <x:v>diagnostic boundary, not decoding performance</x:v>
+      </x:c>
+      <x:c r="G8" s="114" t="str">
+        <x:v>A preregistered artifact-only discrepancy tree with mutually exclusive failure classes and no post-hoc model search.</x:v>
+      </x:c>
+      <x:c r="H8" s="114" t="str">
+        <x:v>Data: Closed Loop 46/47 aggregate reports and permitted train-only diagnostics; no new target opening or consumed cohort access.
+Controls:
+- target identity audit
+- train-only learning curve
+- signal-quality summaries
+- prediction entropy
+- blank dominance
+- prior-strength decomposition
+- no target-conditioned feature search</x:v>
+      </x:c>
+      <x:c r="I8" s="114" t="str">
+        <x:v>- failure class
+- evidence completeness
+- unavailable fields
+- diagnostic runtime
+- new protected reads
+- recommended proceed park or kill branch</x:v>
+      </x:c>
+      <x:c r="J8" s="114" t="str">
+        <x:v>Accept: Exactly one primary failure class or an explicit unresolved set is recorded without using validation targets to select a new architecture.
+Kill/Park: If diagnosis requires target-conditioned search or a larger model, park and design a fresh development cohort instead.</x:v>
+      </x:c>
+      <x:c r="K8" s="114" t="str">
+        <x:v>Loops: 46, 47</x:v>
+      </x:c>
+      <x:c r="L8" s="114" t="str">
+        <x:v>Artifact-only planning may proceed; any train-array diagnostic or target read requires its own exact authorization.</x:v>
+      </x:c>
+      <x:c r="M8" s="114" t="str">
+        <x:v>artifact-only by default; one thread; &lt;=5 CPU minutes; &lt;=8 MiB generated</x:v>
+      </x:c>
+      <x:c r="N8" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O8" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P8" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="174" customHeight="1">
+      <x:c r="A9" s="191" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B9" s="129" t="str">
+        <x:v>P7 - Unseen-Person Verdict</x:v>
+      </x:c>
+      <x:c r="C9" s="194" t="str">
+        <x:v>Fresh Development-Person Intake</x:v>
+      </x:c>
+      <x:c r="D9" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E9" s="114" t="str">
+        <x:v>Can one non-S25 participant provide a development-only transfer cohort without consuming the final unseen-person test?</x:v>
+      </x:c>
+      <x:c r="F9" s="200" t="str">
+        <x:v>development cohort qualification only</x:v>
+      </x:c>
+      <x:c r="G9" s="114" t="str">
+        <x:v>Metadata selector, exact byte plan, task/license/identity audit, preregistration, and bounded acquisition request for one nonfinal MEG participant.</x:v>
+      </x:c>
+      <x:c r="H9" s="114" t="str">
+        <x:v>Data: Public metadata first; future two-file single-FIF/log bundle preferred under 1.25 GiB; S25 remains physically final-only.
+Controls:
+- exclude S21 S7 S20 S25
+- single complete FIF/log pair
+- task and modality match
+- subject exclusion audit
+- dry-run exact bytes
+- no backup substitution</x:v>
+      </x:c>
+      <x:c r="I9" s="114" t="str">
+        <x:v>- eligible candidates
+- files
+- bytes
+- sessions
+- trial floor
+- license
+- identity overlap
+- unavailable fields</x:v>
+      </x:c>
+      <x:c r="J9" s="114" t="str">
+        <x:v>Accept: One eligible development participant has exact identities, &gt;=48 usable trials, compatible task/modality, explicit license, and total planned bytes within cap.
+Kill/Park: If no candidate qualifies, do not repurpose S25; return to public-data search or multi-session S21 mechanics without a generalization claim.</x:v>
+      </x:c>
+      <x:c r="K9" s="114" t="str">
+        <x:v>Loops: 47</x:v>
+      </x:c>
+      <x:c r="L9" s="114" t="str">
+        <x:v>Candidate selection and storage capacity are not download permission; exact acquisition needs a separate dry-run and --execute authorization.</x:v>
+      </x:c>
+      <x:c r="M9" s="114" t="str">
+        <x:v>metadata planning zero download; future preferred &lt;=1.25 GiB; absolute cumulative user envelope remains 10 GB</x:v>
+      </x:c>
+      <x:c r="N9" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O9" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P9" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="174" customHeight="1">
+      <x:c r="A10" s="191" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B10" s="129" t="str">
+        <x:v>P7 - Unseen-Person Verdict</x:v>
+      </x:c>
+      <x:c r="C10" s="194" t="str">
+        <x:v>Multi-Source Frozen Encoder</x:v>
+      </x:c>
+      <x:c r="D10" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E10" s="114" t="str">
+        <x:v>Can a tiny causal model learn from S21 plus one development participant without participant leakage or participant-specific target shortcuts?</x:v>
+      </x:c>
+      <x:c r="F10" s="200" t="str">
+        <x:v>multi-source development evidence only</x:v>
+      </x:c>
+      <x:c r="G10" s="114" t="str">
+        <x:v>Participant-grouped train/selection protocol, fixed architecture, source-balanced losses, no-signal priors, and identity/corruption controls.</x:v>
+      </x:c>
+      <x:c r="H10" s="114" t="str">
+        <x:v>Data: Authorized train and selection partitions from S21 plus the Loop 49 development participant; S25 remains unopened.
+Controls:
+- participant-grouped splits
+- participant-balanced sampling
+- source-only prior
+- pooled prior
+- zero signal
+- participant-ID-only
+- channel and time derangements</x:v>
+      </x:c>
+      <x:c r="I10" s="114" t="str">
+        <x:v>- per-person macro CER
+- worst-person CER
+- pooled CER
+- prior margins
+- control margins
+- parameter count
+- training cost</x:v>
+      </x:c>
+      <x:c r="J10" s="114" t="str">
+        <x:v>Accept: A single frozen candidate beats matched priors and corruptions on every development person without participant-conditioned architecture changes.
+Kill/Park: If pooled gain hides a person-level loss or participant identity predicts targets, park transfer and do not open S25.</x:v>
+      </x:c>
+      <x:c r="K10" s="114" t="str">
+        <x:v>Loops: 49</x:v>
+      </x:c>
+      <x:c r="L10" s="114" t="str">
+        <x:v>Requires exact participant/split authorization and a frozen target-blind model-selection protocol.</x:v>
+      </x:c>
+      <x:c r="M10" s="114" t="str">
+        <x:v>one thread; one worker; &lt;=10,000 parameters; &lt;=60 CPU minutes; &lt;=2 GiB RSS; &lt;=64 MiB generated</x:v>
+      </x:c>
+      <x:c r="N10" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O10" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P10" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="174" customHeight="1">
+      <x:c r="A11" s="191" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B11" s="129" t="str">
+        <x:v>P7 - Unseen-Person Verdict</x:v>
+      </x:c>
+      <x:c r="C11" s="194" t="str">
+        <x:v>S25 Final-Only Freeze Packet</x:v>
+      </x:c>
+      <x:c r="D11" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E11" s="114" t="str">
+        <x:v>Is every model, transform, comparator, threshold, prediction format, and decision rule frozen before any S25 payload or target opens?</x:v>
+      </x:c>
+      <x:c r="F11" s="200" t="str">
+        <x:v>preregistration and target-isolation proof only</x:v>
+      </x:c>
+      <x:c r="G11" s="114" t="str">
+        <x:v>Hash-bound model/checkpoint, source code, environment, exact S25 files/bytes, target isolation, control predictions, statistical rule, and one-time opening order.</x:v>
+      </x:c>
+      <x:c r="H11" s="114" t="str">
+        <x:v>Data: Metadata and frozen source artifacts only; S25 FIF/MAT payload remains unopened during packet preparation.
+Controls:
+- zero candidate fit rows
+- zero calibration rows
+- &gt;=48 final rows
+- 65,535 assignments plus observed
+- no-signal prior
+- zero signal
+- channel derangement
+- time displacement</x:v>
+      </x:c>
+      <x:c r="I11" s="114" t="str">
+        <x:v>- commitment hashes
+- unfrozen fields
+- planned bytes
+- predicted row count
+- decision completeness
+- authorization flags</x:v>
+      </x:c>
+      <x:c r="J11" s="114" t="str">
+        <x:v>Accept: All execution inputs and claim rules are immutable, every target-free prediction path is ready, and independent review finds zero target-dependent choice.
+Kill/Park: Any unfrozen model or target-dependent field keeps S25 sealed and returns the packet for versioned amendment.</x:v>
+      </x:c>
+      <x:c r="K11" s="114" t="str">
+        <x:v>Loops: 50, 27, 28</x:v>
+      </x:c>
+      <x:c r="L11" s="114" t="str">
+        <x:v>Packet preparation cannot authorize download, payload hashing, header read, prediction, target access, or final scoring.</x:v>
+      </x:c>
+      <x:c r="M11" s="114" t="str">
+        <x:v>artifact-only; one thread; &lt;=10 minutes; &lt;=16 MiB generated; future S25 bundle exactly 1,009,939,983 bytes</x:v>
+      </x:c>
+      <x:c r="N11" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O11" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P11" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="174" customHeight="1">
+      <x:c r="A12" s="191" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B12" s="129" t="str">
+        <x:v>P7 - Unseen-Person Verdict</x:v>
+      </x:c>
+      <x:c r="C12" s="194" t="str">
+        <x:v>S25 Strict Zero-Shot Verdict</x:v>
+      </x:c>
+      <x:c r="D12" s="135" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E12" s="114" t="str">
+        <x:v>Does the frozen source-trained model show a qualifying neural advantage on one genuinely unseen person with zero target-person fitting?</x:v>
+      </x:c>
+      <x:c r="F12" s="200" t="str">
+        <x:v>strict T2 unseen-person zero-shot neural advantage or an equally durable negative result</x:v>
+      </x:c>
+      <x:c r="G12" s="114" t="str">
+        <x:v>Execute the Loop 51 order once, retain every prediction and control commitment, open final targets once, and publish the exact pass/fail verdict.</x:v>
+      </x:c>
+      <x:c r="H12" s="114" t="str">
+        <x:v>Data: Pinned S25 session 2 block 2 final-only pair; zero fit/calibration/selection rows.
+Controls:
+- frozen source-train-only prior
+- zero signal
+- channel derangement
+- time displacement
+- target-free access ledger
+- no rerun or threshold change</x:v>
+      </x:c>
+      <x:c r="I12" s="114" t="str">
+        <x:v>- macro sentence CER
+- corpus CER
+- absolute prior margin
+- 65,535 paired assignments plus observed
+- control margins
+- wins ties losses
+- runtime RSS bytes</x:v>
+      </x:c>
+      <x:c r="J12" s="114" t="str">
+        <x:v>Accept: &gt;=48 unique final rows, &gt;=0.05 absolute macro-CER improvement over prior, p &lt;=0.05, and strict wins over zero-signal, channel-deranged, and time-displaced controls.
+Kill/Park: Any failed gate records a negative zero-shot result; S25 becomes consumed and can never become calibration or development data.</x:v>
+      </x:c>
+      <x:c r="K12" s="114" t="str">
+        <x:v>Loops: 51</x:v>
+      </x:c>
+      <x:c r="L12" s="114" t="str">
+        <x:v>Requires separate acquisition and final-opening authorizations after a green freeze packet; this roadmap authorizes neither.</x:v>
+      </x:c>
+      <x:c r="M12" s="114" t="str">
+        <x:v>one thread; one worker; exact 1,009,939,983-byte acquisition cap; &lt;=30 inference minutes; &lt;=2 GiB RSS; &lt;=64 MiB generated</x:v>
+      </x:c>
+      <x:c r="N12" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O12" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P12" s="114" t="str">
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
+https://arxiv.org/abs/1606.05201
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="174" customHeight="1">
+      <x:c r="A13" s="191" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B13" s="129" t="str">
+        <x:v>P8 - Accessible EEG Evidence</x:v>
+      </x:c>
+      <x:c r="C13" s="194" t="str">
+        <x:v>Fresh S20 EEG Acquisition Gate</x:v>
+      </x:c>
+      <x:c r="D13" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E13" s="114" t="str">
+        <x:v>Can the selected S20 EEG bundle be acquired and validated as a fresh accessible-modality cohort under strict byte and license caps?</x:v>
+      </x:c>
+      <x:c r="F13" s="200" t="str">
+        <x:v>fresh EEG mechanics only</x:v>
+      </x:c>
+      <x:c r="G13" s="114" t="str">
+        <x:v>Exact metadata, dry-run, checksum, complete BrainVision triplet/log acquisition, header audit, and no-target-open cache plan.</x:v>
+      </x:c>
+      <x:c r="H13" s="114" t="str">
+        <x:v>Data: Previously selected S20 EEG bundle, approximately 96 MB within the combined S20 plus S25 1,106,030,247-byte plan.
+Controls:
+- complete triplet
+- single participant
+- task match
+- license boundary
+- exact bytes
+- no S7 reuse
+- no signal or target read before authorization</x:v>
+      </x:c>
+      <x:c r="I13" s="114" t="str">
+        <x:v>- files
+- bytes
+- checksums
+- channels
+- sampling rate
+- events planned
+- license
+- access counters</x:v>
+      </x:c>
+      <x:c r="J13" s="114" t="str">
+        <x:v>Accept: Exact files and checksums match the preregistration, the complete bundle stays within cap, and no unauthorized target or signal access occurs.
+Kill/Park: Any missing companion, identity ambiguity, or byte/license mismatch parks acquisition without substituting S7 or another person.</x:v>
+      </x:c>
+      <x:c r="K13" s="114" t="str">
+        <x:v>Loops: 29</x:v>
+      </x:c>
+      <x:c r="L13" s="114" t="str">
+        <x:v>The user's storage allowance is not execute permission; acquisition needs exact --execute authorization.</x:v>
+      </x:c>
+      <x:c r="M13" s="114" t="str">
+        <x:v>preferred exact selected bundle; cumulative new data &lt;=5 GB preferred and &lt;=10 GB absolute; one worker</x:v>
+      </x:c>
+      <x:c r="N13" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O13" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P13" s="114" t="str">
+        <x:v>https://arxiv.org/abs/2502.17480
+https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="174" customHeight="1">
+      <x:c r="A14" s="191" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B14" s="129" t="str">
+        <x:v>P8 - Accessible EEG Evidence</x:v>
+      </x:c>
+      <x:c r="C14" s="194" t="str">
+        <x:v>EEG Trial Geometry And Confound Ledger</x:v>
+      </x:c>
+      <x:c r="D14" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E14" s="114" t="str">
+        <x:v>Does fresh S20 EEG have exact trial identity, geometry/reference metadata, and enough peripheral-control evidence for a bounded classifier claim?</x:v>
+      </x:c>
+      <x:c r="F14" s="200" t="str">
+        <x:v>EEG identity and confound qualification</x:v>
+      </x:c>
+      <x:c r="G14" s="114" t="str">
+        <x:v>Trial map, channel/geometry/reference ledger, event timing, quality summaries, EOG/EMG/motion availability, and fail-closed claim ceiling.</x:v>
+      </x:c>
+      <x:c r="H14" s="114" t="str">
+        <x:v>Data: Authorized S20 headers and then signal/target members in a separately ordered pass; no S7 reopening.
+Controls:
+- event-log identity
+- channel units
+- reference state
+- bad/missing channels
+- EOG and EMG availability
+- keypress timing
+- target isolation</x:v>
+      </x:c>
+      <x:c r="I14" s="114" t="str">
+        <x:v>- trials reconciled
+- channels qualified
+- geometry coverage
+- reference known
+- peripheral streams available
+- quality flags
+- usable-row floor</x:v>
+      </x:c>
+      <x:c r="J14" s="114" t="str">
+        <x:v>Accept: &gt;=48 unique trials have exact identity and every geometry/reference/confound field is known or explicitly unavailable with a bounded claim ceiling.
+Kill/Park: Missing peripheral controls block brain-specific attribution but may allow a narrower sensor-signal dependence test if preregistered.</x:v>
+      </x:c>
+      <x:c r="K14" s="114" t="str">
+        <x:v>Loops: 53, 35, 36</x:v>
+      </x:c>
+      <x:c r="L14" s="114" t="str">
+        <x:v>Header, signal, and target stages remain separate authorizations.</x:v>
+      </x:c>
+      <x:c r="M14" s="114" t="str">
+        <x:v>one thread; one worker; no new download; &lt;=1 GiB RSS; &lt;=32 MiB generated</x:v>
+      </x:c>
+      <x:c r="N14" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O14" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P14" s="114" t="str">
+        <x:v>https://arxiv.org/abs/2502.17480
+https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="174" customHeight="1">
+      <x:c r="A15" s="191" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B15" s="129" t="str">
+        <x:v>P8 - Accessible EEG Evidence</x:v>
+      </x:c>
+      <x:c r="C15" s="194" t="str">
+        <x:v>Fresh EEG Neural-Effect Gate</x:v>
+      </x:c>
+      <x:c r="D15" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E15" s="114" t="str">
+        <x:v>Can a tiny EEG model beat train-only priors and task-locked artifact controls on fresh S20 without borrowing a MEG claim?</x:v>
+      </x:c>
+      <x:c r="F15" s="200" t="str">
+        <x:v>bounded within-person EEG sensor-signal advantage</x:v>
+      </x:c>
+      <x:c r="G15" s="114" t="str">
+        <x:v>Participant-local split, tiny causal and linear models, no-signal priors, peripheral/corruption controls, exact uncertainty, and immutable report.</x:v>
+      </x:c>
+      <x:c r="H15" s="114" t="str">
+        <x:v>Data: Fresh S20 only under the Loop 54 claim ceiling; S7 stays consumed and excluded from selection.
+Controls:
+- train-only prior
+- zero signal
+- time displacement
+- channel derangement
+- keypress timing only
+- available EOG/EMG controls
+- linear comparator</x:v>
+      </x:c>
+      <x:c r="I15" s="114" t="str">
+        <x:v>- macro CER or exact key accuracy
+- prior margin
+- control margins
+- paired inference
+- worst-class recall
+- runtime and RSS</x:v>
+      </x:c>
+      <x:c r="J15" s="114" t="str">
+        <x:v>Accept: The frozen neural model beats the no-signal prior and every available task-locked/peripheral control under a preregistered paired rule.
+Kill/Park: If unavailable peripheral controls could explain the effect, cap the claim at sensor dependence and do not call it brain-specific or home-ready.</x:v>
+      </x:c>
+      <x:c r="K15" s="114" t="str">
+        <x:v>Loops: 54</x:v>
+      </x:c>
+      <x:c r="L15" s="114" t="str">
+        <x:v>Requires a fresh preregistration and exact training/target authorization; no EEG model run is authorized now.</x:v>
+      </x:c>
+      <x:c r="M15" s="114" t="str">
+        <x:v>one thread; one worker; &lt;=10,000 parameters; &lt;=45 CPU minutes; &lt;=1 GiB RSS; &lt;=64 MiB generated</x:v>
+      </x:c>
+      <x:c r="N15" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O15" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P15" s="114" t="str">
+        <x:v>https://arxiv.org/abs/2502.17480
+https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="174" customHeight="1">
+      <x:c r="A16" s="191" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B16" s="129" t="str">
+        <x:v>P8 - Accessible EEG Evidence</x:v>
+      </x:c>
+      <x:c r="C16" s="194" t="str">
+        <x:v>Cross-Modality Accessibility Verdict</x:v>
+      </x:c>
+      <x:c r="D16" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E16" s="114" t="str">
+        <x:v>What capability survives from cryogenic MEG to scalp EEG, and what must remain modality-specific?</x:v>
+      </x:c>
+      <x:c r="F16" s="200" t="str">
+        <x:v>qualified cross-modality boundary, not equivalence</x:v>
+      </x:c>
+      <x:c r="G16" s="114" t="str">
+        <x:v>Matched requirement matrix for identity, timing, geometry, preprocessing, signal effect, controls, resources, and user burden.</x:v>
+      </x:c>
+      <x:c r="H16" s="114" t="str">
+        <x:v>Data: Closed aggregate Loop 46-55 reports only; no pooled MEG/EEG training or new payload access.
+Controls:
+- same claim vocabulary
+- modality-specific baselines
+- no score pooling
+- no channel equivalence
+- no device extrapolation
+- negative result retention</x:v>
+      </x:c>
+      <x:c r="I16" s="114" t="str">
+        <x:v>- requirements passed per modality
+- claim overlap
+- unavailable fields
+- resource ratio
+- candidate home prerequisites</x:v>
+      </x:c>
+      <x:c r="J16" s="114" t="str">
+        <x:v>Accept: Every cross-modality statement identifies the exact shared interface and the nontransferable acquisition/scientific assumptions.
+Kill/Park: If only mechanics transfer, publish mechanics only and keep decoding/home claims unavailable.</x:v>
+      </x:c>
+      <x:c r="K16" s="114" t="str">
+        <x:v>Loops: 55</x:v>
+      </x:c>
+      <x:c r="L16" s="114" t="str">
+        <x:v>No new data, model, device, or home-use operation is authorized.</x:v>
+      </x:c>
+      <x:c r="M16" s="114" t="str">
+        <x:v>artifact-only; one thread; &lt;=10 minutes; &lt;=16 MiB generated</x:v>
+      </x:c>
+      <x:c r="N16" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O16" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P16" s="114" t="str">
+        <x:v>https://arxiv.org/abs/2502.17480
+https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://arxiv.org/abs/1803.09010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="174" customHeight="1">
+      <x:c r="A17" s="191" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B17" s="129" t="str">
+        <x:v>P9 - Causal Local Use</x:v>
+      </x:c>
+      <x:c r="C17" s="194" t="str">
+        <x:v>Train-Stream Causal Parity</x:v>
+      </x:c>
+      <x:c r="D17" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E17" s="114" t="str">
+        <x:v>Does the exact trained preprocessing and encoder path produce semantically identical frames offline and incrementally?</x:v>
+      </x:c>
+      <x:c r="F17" s="200" t="str">
+        <x:v>causal implementation parity only</x:v>
+      </x:c>
+      <x:c r="G17" s="114" t="str">
+        <x:v>Join qualified Loop 45 preprocessing, frozen encoder, NeuroToken state, decoder state, schedules, resumes, timestamps, and anomaly records.</x:v>
+      </x:c>
+      <x:c r="H17" s="114" t="str">
+        <x:v>Data: Target-free fixtures first; later authorized source-validation replay only, never S25 or consumed cohorts.
+Controls:
+- whole item
+- single sample
+- boundary splits
+- seeded irregular
+- resume cuts
+- future mutation
+- state hash
+- zero right context</x:v>
+      </x:c>
+      <x:c r="I17" s="114" t="str">
+        <x:v>- frame identity
+- timestamp identity
+- decoder state identity
+- revision trace
+- right context
+- runtime RSS bytes</x:v>
+      </x:c>
+      <x:c r="J17" s="114" t="str">
+        <x:v>Accept: All registered schedules and resumes preserve semantic identity and declared causality within caps.
+Kill/Park: Any hidden future context or state mismatch blocks streaming claims and returns to the smallest failed layer.</x:v>
+      </x:c>
+      <x:c r="K17" s="114" t="str">
+        <x:v>Loops: 45, 47, 41</x:v>
+      </x:c>
+      <x:c r="L17" s="114" t="str">
+        <x:v>Each fixture, model, replay cache, and integration stage requires separate authorization.</x:v>
+      </x:c>
+      <x:c r="M17" s="114" t="str">
+        <x:v>one thread; one worker; &lt;=64 MiB generated; target-free first</x:v>
+      </x:c>
+      <x:c r="N17" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O17" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P17" s="114" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://doi.org/10.6028/NIST.AI.100-1
+https://arxiv.org/abs/1810.03993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="174" customHeight="1">
+      <x:c r="A18" s="191" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B18" s="129" t="str">
+        <x:v>P9 - Causal Local Use</x:v>
+      </x:c>
+      <x:c r="C18" s="194" t="str">
+        <x:v>Local Capture And Device Mechanics</x:v>
+      </x:c>
+      <x:c r="D18" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E18" s="114" t="str">
+        <x:v>Can one named local EEG device path preserve packets, clocks, channels, locality, anomalies, and privacy without claiming useful neural decoding?</x:v>
+      </x:c>
+      <x:c r="F18" s="200" t="str">
+        <x:v>device mechanics only</x:v>
+      </x:c>
+      <x:c r="G18" s="114" t="str">
+        <x:v>Execute staged OpenBCI Cyton synthetic/playback, no-contact bench, and only later separately consented scalp mechanics under Loop 42/RW3 contracts.</x:v>
+      </x:c>
+      <x:c r="H18" s="114" t="str">
+        <x:v>Data: Synthetic and playback first; no-contact battery bench second; participant stage separate and optional.
+Controls:
+- packet counter
+- host timestamp separation
+- network-off audit
+- battery-only body stage
+- no Daisy or Wi-Fi substitution
+- raw/derived lifecycle inventory</x:v>
+      </x:c>
+      <x:c r="I18" s="114" t="str">
+        <x:v>- packet loss and reorder
+- clock observables
+- channel identity
+- anomalies
+- local writes
+- network endpoints
+- resource use</x:v>
+      </x:c>
+      <x:c r="J18" s="114" t="str">
+        <x:v>Accept: The exact named stage passes identity, timing, locality, privacy, safety, and resource gates; claims stop at that stage.
+Kill/Park: A failed stage parks the exact device/transport configuration without substitution or promotion to EEG quality or decoding.</x:v>
+      </x:c>
+      <x:c r="K18" s="114" t="str">
+        <x:v>Loops: 42, 38, 41</x:v>
+      </x:c>
+      <x:c r="L18" s="114" t="str">
+        <x:v>No purchase, SDK, serial, board, participant, recording, or hardware operation is authorized by this roadmap.</x:v>
+      </x:c>
+      <x:c r="M18" s="114" t="str">
+        <x:v>one device maximum; battery-only participant stage; zero cloud; &lt;=64 MiB generated excluding separately governed raw capture</x:v>
+      </x:c>
+      <x:c r="N18" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O18" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P18" s="114" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://doi.org/10.6028/NIST.AI.100-1
+https://arxiv.org/abs/1810.03993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="174" customHeight="1">
+      <x:c r="A19" s="191" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B19" s="129" t="str">
+        <x:v>P9 - Causal Local Use</x:v>
+      </x:c>
+      <x:c r="C19" s="194" t="str">
+        <x:v>End-To-End Latency And Stability Gate</x:v>
+      </x:c>
+      <x:c r="D19" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E19" s="114" t="str">
+        <x:v>What latency, revision, stability, and abstention behavior is measured from an instrumented source event to final text?</x:v>
+      </x:c>
+      <x:c r="F19" s="200" t="str">
+        <x:v>bounded system latency and stability, separate from accuracy</x:v>
+      </x:c>
+      <x:c r="G19" s="114" t="str">
+        <x:v>Common-clock markers, source-arrival/preprocess/frame/decode/render timestamps, partial hypotheses, finalization, abstention, and anomaly trace.</x:v>
+      </x:c>
+      <x:c r="H19" s="114" t="str">
+        <x:v>Data: Target-free replay first; any neural replay/live stage uses only separately authorized nonfinal data and frozen models.
+Controls:
+- common-clock event
+- replay-vs-live label
+- cold and warm runs
+- stall/drop/reorder fixtures
+- no confidence when unavailable
+- no network</x:v>
+      </x:c>
+      <x:c r="I19" s="114" t="str">
+        <x:v>- capture-to-arrival
+- arrival-to-frame
+- frame-to-decode
+- decode-to-render
+- end-to-end
+- revision count
+- finalization delay
+- abstention coverage</x:v>
+      </x:c>
+      <x:c r="J19" s="114" t="str">
+        <x:v>Accept: Every latency claim has a named clock domain and measured endpoints; p50/p95/max and failure traces meet preregistered local caps.
+Kill/Park: Replay scheduling cannot substitute for capture latency; unavailable clock links keep end-to-end latency unavailable.</x:v>
+      </x:c>
+      <x:c r="K19" s="114" t="str">
+        <x:v>Loops: 57, 58, 34</x:v>
+      </x:c>
+      <x:c r="L19" s="114" t="str">
+        <x:v>UI, server, browser, stream, device, neural model, and participant stages remain separately authorized.</x:v>
+      </x:c>
+      <x:c r="M19" s="114" t="str">
+        <x:v>loopback-only by default; one thread; one worker; &lt;=64 MiB generated; no cloud</x:v>
+      </x:c>
+      <x:c r="N19" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O19" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P19" s="114" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://doi.org/10.6028/NIST.AI.100-1
+https://arxiv.org/abs/1810.03993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="174" customHeight="1">
+      <x:c r="A20" s="191" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B20" s="129" t="str">
+        <x:v>P9 - Causal Local Use</x:v>
+      </x:c>
+      <x:c r="C20" s="194" t="str">
+        <x:v>At-Home EEG Feasibility Pilot</x:v>
+      </x:c>
+      <x:c r="D20" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E20" s="114" t="str">
+        <x:v>Can one consented person complete a battery-only, local-only, repeatable EEG mechanics session at home with acceptable setup burden and signal quality?</x:v>
+      </x:c>
+      <x:c r="F20" s="200" t="str">
+        <x:v>at-home acquisition feasibility only, never home text decoding by default</x:v>
+      </x:c>
+      <x:c r="G20" s="114" t="str">
+        <x:v>Consent/safety protocol, setup checklist, impedance/reference/geometry record, local privacy inventory, repeated short sessions, and usability burden report.</x:v>
+      </x:c>
+      <x:c r="H20" s="114" t="str">
+        <x:v>Data: One separately consented participant, minimal nonlinguistic calibration tasks first; no arbitrary thought or clinical task.
+Controls:
+- battery-only
+- no charging or mains contact
+- network off
+- local encrypted storage
+- EOG/EMG/motion controls
+- stop criteria
+- no target text upload</x:v>
+      </x:c>
+      <x:c r="I20" s="114" t="str">
+        <x:v>- setup time
+- successful channel fraction
+- artifact burden
+- repeat-session identity
+- participant burden
+- local bytes
+- privacy findings
+- adverse events</x:v>
+      </x:c>
+      <x:c r="J20" s="114" t="str">
+        <x:v>Accept: The exact acquisition protocol is safe, repeatable, local, privacy-audited, and meets preregistered quality/usability floors.
+Kill/Park: Any safety, consent, privacy, setup, or quality failure stops the pilot; acquisition feasibility cannot be relabeled decoding.</x:v>
+      </x:c>
+      <x:c r="K20" s="114" t="str">
+        <x:v>Loops: 56, 58, 35, 36, 38</x:v>
+      </x:c>
+      <x:c r="L20" s="114" t="str">
+        <x:v>Requires explicit participant, consent, safety, device, recording, retention, and deletion authorization; none exists now.</x:v>
+      </x:c>
+      <x:c r="M20" s="114" t="str">
+        <x:v>one participant; one named device; battery-only; no cloud; bounded local retention; no new device purchase without separate decision</x:v>
+      </x:c>
+      <x:c r="N20" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O20" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P20" s="114" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/17169606/
+https://doi.org/10.6028/NIST.AI.100-1
+https://arxiv.org/abs/1810.03993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="174" customHeight="1">
+      <x:c r="A21" s="191" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B21" s="129" t="str">
+        <x:v>P10 - Independent Evidence And Release</x:v>
+      </x:c>
+      <x:c r="C21" s="194" t="str">
+        <x:v>Versioned Reproducible Artifact</x:v>
+      </x:c>
+      <x:c r="D21" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E21" s="114" t="str">
+        <x:v>Can the supported target-free and aggregate-evidence surfaces become one exact, privacy-qualified, cross-machine release candidate?</x:v>
+      </x:c>
+      <x:c r="F21" s="200" t="str">
+        <x:v>versioned software reproducibility</x:v>
+      </x:c>
+      <x:c r="G21" s="114" t="str">
+        <x:v>Execute Loop 37-39 gates, freeze package/environment/manifests, run supported OS/Python matrix, and produce a no-payload release candidate.</x:v>
+      </x:c>
+      <x:c r="H21" s="114" t="str">
+        <x:v>Data: Public source, target-free fixtures, aggregate reports, and nonstandard payload labels only; no participant payload or prediction rows.
+Controls:
+- tracked-history scan
+- secret scan
+- privacy lifecycle
+- semantic manifests
+- field-specific tolerances
+- built-package install
+- cross-machine matrix</x:v>
+      </x:c>
+      <x:c r="I21" s="114" t="str">
+        <x:v>- matrix cells passed
+- semantic identity
+- numerical tolerance
+- install success
+- tests
+- runtime RSS bytes
+- privacy/license blockers</x:v>
+      </x:c>
+      <x:c r="J21" s="114" t="str">
+        <x:v>Accept: Every required matrix cell, privacy/license gate, and exact candidate check passes with zero protected payload.
+Kill/Park: Any unresolved privacy, license, semantic, or supported-environment mismatch holds the candidate.</x:v>
+      </x:c>
+      <x:c r="K21" s="114" t="str">
+        <x:v>Loops: 37, 38, 39, 56, 59</x:v>
+      </x:c>
+      <x:c r="L21" s="114" t="str">
+        <x:v>Package, CI expansion, public artifact, tag, archive, and release each require a separate authorization decision.</x:v>
+      </x:c>
+      <x:c r="M21" s="114" t="str">
+        <x:v>public fixtures only; &lt;=128 MiB release candidate; bounded CI matrix; no protected payload</x:v>
+      </x:c>
+      <x:c r="N21" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O21" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P21" s="114" t="str">
+        <x:v>https://doi.org/10.15497/RDA00068
+https://www.acm.org/publications/policies/artifact-review-and-badging-current
+https://arxiv.org/abs/1810.03993
+https://doi.org/10.6028/NIST.AI.100-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="174" customHeight="1">
+      <x:c r="A22" s="191" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B22" s="129" t="str">
+        <x:v>P10 - Independent Evidence And Release</x:v>
+      </x:c>
+      <x:c r="C22" s="194" t="str">
+        <x:v>Independent Artifact Reproduction</x:v>
+      </x:c>
+      <x:c r="D22" s="135" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E22" s="114" t="str">
+        <x:v>Can one independent contributor reproduce the exact released target-free artifact without private maintainer state?</x:v>
+      </x:c>
+      <x:c r="F22" s="200" t="str">
+        <x:v>independent author-artifact reproduction only</x:v>
+      </x:c>
+      <x:c r="G22" s="114" t="str">
+        <x:v>Execute Loop 43 commit-reveal packet, public communication, frozen submission, oracle reveal, discrepancy adjudication, and credit record.</x:v>
+      </x:c>
+      <x:c r="H22" s="114" t="str">
+        <x:v>Data: Target-free public release artifact only; no contributor neural recording or protected data.
+Controls:
+- independence disclosure
+- public-only help
+- unprivileged fork
+- no secrets
+- submission freeze before oracle
+- record dont fix
+- negative outcomes retained</x:v>
+      </x:c>
+      <x:c r="I22" s="114" t="str">
+        <x:v>- outcome class
+- semantic comparisons
+- numerical comparisons
+- manual steps
+- runtime RSS bytes
+- discrepancies
+- independence fields</x:v>
+      </x:c>
+      <x:c r="J22" s="114" t="str">
+        <x:v>Accept: One eligible external submission passes registered identity/comparison gates and independent adjudication.
+Kill/Park: Private guidance, order violation, security/privacy failure, or mutable repair invalidates the run but preserves the record.</x:v>
+      </x:c>
+      <x:c r="K22" s="114" t="str">
+        <x:v>Loops: 61, 43</x:v>
+      </x:c>
+      <x:c r="L22" s="114" t="str">
+        <x:v>Outreach, contributor contact, artifact exchange, adjudication, credit, and publication require separate authorization.</x:v>
+      </x:c>
+      <x:c r="M22" s="114" t="str">
+        <x:v>public artifact &lt;=128 MiB; no protected data; no privileged CI; one external submission</x:v>
+      </x:c>
+      <x:c r="N22" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O22" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P22" s="114" t="str">
+        <x:v>https://doi.org/10.15497/RDA00068
+https://www.acm.org/publications/policies/artifact-review-and-badging-current
+https://arxiv.org/abs/1810.03993
+https://doi.org/10.6028/NIST.AI.100-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="174" customHeight="1">
+      <x:c r="A23" s="191" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B23" s="129" t="str">
+        <x:v>P10 - Independent Evidence And Release</x:v>
+      </x:c>
+      <x:c r="C23" s="194" t="str">
+        <x:v>Independent Scientific Replication Packet</x:v>
+      </x:c>
+      <x:c r="D23" s="135" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="E23" s="114" t="str">
+        <x:v>Can a genuinely independent team test the neural-effect protocol with independently implemented analysis and qualifying new data?</x:v>
+      </x:c>
+      <x:c r="F23" s="200" t="str">
+        <x:v>independent scientific replication</x:v>
+      </x:c>
+      <x:c r="G23" s="114" t="str">
+        <x:v>Public protocol, minimal sufficient aggregate evidence, independent implementation boundary, new-data requirements, preregistered comparators, and discrepancy taxonomy.</x:v>
+      </x:c>
+      <x:c r="H23" s="114" t="str">
+        <x:v>Data: No local protected payload transfer; future partner uses independently governed qualifying data or separately licensed public data.
+Controls:
+- independent implementation
+- new participant evidence
+- no hidden oracle sharing
+- same no-signal controls
+- peripheral controls
+- negative result publication
+- credit and governance</x:v>
+      </x:c>
+      <x:c r="I23" s="114" t="str">
+        <x:v>- independence qualification
+- protocol fidelity
+- effect direction and magnitude
+- paired uncertainty
+- control results
+- deviations
+- data governance</x:v>
+      </x:c>
+      <x:c r="J23" s="114" t="str">
+        <x:v>Accept: An external protocol is sufficiently independent, powered, governed, and comparator-complete to test the same bounded scientific claim.
+Kill/Park: Author-artifact reruns, shared participants, undisclosed assistance, or missing controls remain reproduction or assistance, not replication.</x:v>
+      </x:c>
+      <x:c r="K23" s="114" t="str">
+        <x:v>Loops: 52, 55, 62</x:v>
+      </x:c>
+      <x:c r="L23" s="114" t="str">
+        <x:v>Partner outreach, protocol publication, data exchange, and execution each require separate governance and authorization.</x:v>
+      </x:c>
+      <x:c r="M23" s="114" t="str">
+        <x:v>planning artifacts &lt;=16 MiB locally; external resources separately governed; zero participant payload exchange by default</x:v>
+      </x:c>
+      <x:c r="N23" s="206" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O23" s="215" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P23" s="114" t="str">
+        <x:v>https://doi.org/10.15497/RDA00068
+https://www.acm.org/publications/policies/artifact-review-and-badging-current
+https://arxiv.org/abs/1810.03993
+https://doi.org/10.6028/NIST.AI.100-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="174" customHeight="1">
+      <x:c r="A24" s="192" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B24" s="130" t="str">
+        <x:v>P10 - Independent Evidence And Release</x:v>
+      </x:c>
+      <x:c r="C24" s="195" t="str">
+        <x:v>Scientific Claim Promotion And Release v1</x:v>
+      </x:c>
+      <x:c r="D24" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E24" s="115" t="str">
+        <x:v>Which engineering, neural-effect, transfer, EEG, streaming, home, reproduction, and replication claims have actually earned promotion?</x:v>
+      </x:c>
+      <x:c r="F24" s="201" t="str">
+        <x:v>evidence-limited public release decision</x:v>
+      </x:c>
+      <x:c r="G24" s="115" t="str">
+        <x:v>Versioned successor to the Loop 44 matrix, model/dataset cards, claim diff, risk register, release notes, archive decision, and proceed/park/kill ledger.</x:v>
+      </x:c>
+      <x:c r="H24" s="115" t="str">
+        <x:v>Data: Closed aggregate and artifact evidence from authorized Loops 45-63 only; no new experiment.
+Controls:
+- claim-to-evidence binding
+- negative results visible
+- engineering/science separate
+- cohort and modality ceilings
+- privacy and license
+- independent evidence labels
+- clinical claims prohibited without clinical evidence</x:v>
+      </x:c>
+      <x:c r="I24" s="115" t="str">
+        <x:v>- claims promoted parked prohibited unavailable
+- evidence completeness
+- release gates
+- risk status
+- tests and CI
+- archive identity</x:v>
+      </x:c>
+      <x:c r="J24" s="115" t="str">
+        <x:v>Accept: Release only exact claims whose evidence, comparators, uncertainty, privacy, license, reproducibility, and governance gates pass.
+Kill/Park: Hold the release rather than soften a failed scientific or governance gate.</x:v>
+      </x:c>
+      <x:c r="K24" s="115" t="str">
+        <x:v>Loops: 61, 62, 63</x:v>
+      </x:c>
+      <x:c r="L24" s="115" t="str">
+        <x:v>Claim review cannot retroactively authorize experiments; tag, release, archive, DOI, and public claims require a separate maintainer decision.</x:v>
+      </x:c>
+      <x:c r="M24" s="115" t="str">
+        <x:v>artifact-only; one thread; &lt;=32 MiB generated; zero new data/model/device operations</x:v>
+      </x:c>
+      <x:c r="N24" s="207" t="str">
+        <x:v>planned_not_authorized</x:v>
+      </x:c>
+      <x:c r="O24" s="216" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="P24" s="115" t="str">
+        <x:v>https://doi.org/10.15497/RDA00068
+https://www.acm.org/publications/policies/artifact-review-and-badging-current
+https://arxiv.org/abs/1810.03993
+https://doi.org/10.6028/NIST.AI.100-1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:P2"/>
+    <x:mergeCell ref="A3:P3"/>
+  </x:mergeCells>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="O5:O24">
+      <x:formula1>"Not Started,In Progress,Review,Blocked,Done,Parked"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D5:D24">
+      <x:formula1>"P0,P1,P2,P3"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a1503f457764a49"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -2914,7 +4684,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7e42db2fa3415f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9f567f6478e4aff"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6172,7 +7942,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ef332725ec4886"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8b7549a6394373"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7643,7 +9413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d481221d154729"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfab33dfbaa224a80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8356,7 +10126,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c00e9943d54503"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf542c67347034a1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8922,7 +10692,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4285a31178b647b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68dd37bfac94f2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8951,7 +10721,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="81" t="str">
-        <x:v>NeuroDecodeKit Next 20 Loops: 25-44</x:v>
+        <x:v>NeuroDecodeKit Evidence Roadmap: Loops 25-44</x:v>
       </x:c>
       <x:c r="B1" s="81"/>
       <x:c r="C1" s="81"/>
@@ -8971,7 +10741,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Current gate: Loop 25 amended v1 still awaits its exact decision. Loops 26-41 planning research is complete while every experiment remains Not Started and unauthorized.</x:v>
+        <x:v>Loop 44 artifact-only claim review is complete. Engineering release is held; scientific performance is parked. No experiment, tag, release, DOI, protected payload, model, stream, or device action is authorized by this sheet.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -10399,10 +12169,10 @@
         <x:v>Artifact-only review, one thread, one worker, 16 MiB generated reports, zero data/model/training/device access, and complete link/test checks.</x:v>
       </x:c>
       <x:c r="N24" s="142" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>artifact_only_claim_review_release_held</x:v>
       </x:c>
       <x:c r="O24" s="148" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete</x:v>
       </x:c>
       <x:c r="P24" s="151" t="str">
         <x:v>https://arxiv.org/abs/1810.03993
@@ -10429,7 +12199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf3c72fa9bb4caa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500c007b3c484c5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb5f1ba03791040f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Re1abda9233304cd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="Rbe76bd6579a948c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R49d1cab30e6b4895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Re1096d2738904967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R84638497a18943d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rdf1ead6837314b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R2f6d3b5084ed4b9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R98a24ba74e5549be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R2efd4f9d28de48e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R047e85a8acec4405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rec2ef2acf87e4e2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R47bc6d88994344a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8be315dad5b84d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R1d91ebeefef64d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rcb622c12fa5a417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R7571022a98b3438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R27563c3bb52b4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R426830c00bea4be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rcba2cfbce2264a0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,7 +28,7 @@
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="23">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -158,8 +158,19 @@
       <x:color rgb="FF234A60"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF1B5E20"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF1B5E20"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="33">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -311,6 +322,16 @@
         <x:fgColor rgb="FFFDECEC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F5E9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9F2E3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="13">
     <x:border/>
@@ -416,7 +437,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="217">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -970,6 +991,18 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="18" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="32" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="32" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1228,7 +1261,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb6668e7d5db4a65"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e60b2bf77914e86"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1620,7 +1653,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 25 v1 authorization decision pending</x:v>
+        <x:v>Loop 26 preregistration decision next</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1642,7 +1675,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 44 artifact review complete: engineering release held and scientific release parked. Loops 45-64 target a real neural-effect verdict, strict unseen-person test, fresh EEG, causal local use, and independent evidence. Every execution flag is false.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 target-free causal mechanics passed once: 24/24 items, 168 schedules, 240 resumes, 72 mutation controls, zero protected reads, 788,967 generated bytes, and 136,806,400-byte maximum RSS. No rerun is authorized. Loop 26 / 46 is the next separate decision; all current execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1779,7 +1812,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f757ce1d9a44800"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R542644b7e38548d0"/>
 </x:worksheet>
 </file>
 
@@ -1847,7 +1880,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Planning only | 20 loops | 5 phases | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46-64 Not Started | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all current execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -1935,45 +1968,45 @@
         <x:v>mechanics prerequisite only</x:v>
       </x:c>
       <x:c r="G5" s="113" t="str">
-        <x:v>Execute the already frozen v1 filter-design, response, alias, schedule, resume, state, timestamp, and mutation gates under its own authorization sequence.</x:v>
+        <x:v>Completed the exact v1 filter-design, response, alias, schedule, resume, state, timestamp, padding, access, mutation, and resource gates under the separate green authorization and implementation sequence.</x:v>
       </x:c>
       <x:c r="H5" s="113" t="str">
-        <x:v>Data: Fresh target-free synthetic seeds 2501 then conditional 2502 only; no S21, S7, S20, or S25 payload.
-Controls:
+        <x:v>Data: 24 target-free synthetic items only; no S21, S7, S20, or S25 payload.
+Controls passed:
 - 65,537-point response grid
 - 23 alias probes
-- 7 schedules
-- 10 resume cuts
-- 3 future-mutation cuts
-- noncausal reference reported separately</x:v>
+- 168 schedule checks
+- 240 resume checks
+- 72 future-mutation checks
+- zero protected reads</x:v>
       </x:c>
       <x:c r="I5" s="113" t="str">
-        <x:v>- folding-band attenuation
-- alias destination error
-- sample and timestamp identity
-- right-context samples
-- runtime
-- peak RSS
-- artifact bytes</x:v>
+        <x:v>- 24/24 items passed
+- folding-band maximum -67.503786 dB
+- exact sample/timestamp identity
+- zero right context
+- 5.542175 sec static + complete internal
+- 136,806,400-byte maximum RSS
+- 788,967 generated bytes</x:v>
       </x:c>
       <x:c r="J5" s="113" t="str">
-        <x:v>Accept: The static anti-alias gate passes before seed 2501 opens and every causal replay invariant passes within the frozen v1 tolerances and resource caps.
-Kill/Park: Park the exact transform with both seeds unopened if the static gate fails; do not alter schedules, tolerances, or filters after protected access.</x:v>
+        <x:v>Passed once: static anti-alias qualification preceded seed access, development froze before conditional qualification, and every causal replay and resource invariant passed.
+No rerun is authorized. Retained neural information and end-to-end latency remain unmeasured.</x:v>
       </x:c>
       <x:c r="K5" s="113" t="str">
-        <x:v>Loops: 25</x:v>
+        <x:v>Loops: 25 (satisfied)</x:v>
       </x:c>
       <x:c r="L5" s="113" t="str">
-        <x:v>Requires the exact separate Loop 25 v1 authorization-only commit and green CI; this roadmap does not supply it.</x:v>
+        <x:v>Completed once through green authorization 1e7296a and implementation 439f151. Current execution authorization is false; Loop 46 remains a separate hash-bound preregistration and authorization decision.</x:v>
       </x:c>
       <x:c r="M5" s="113" t="str">
-        <x:v>one thread; one worker; 45 seconds internal; 1 GiB RSS; 8 MiB generated</x:v>
-      </x:c>
-      <x:c r="N5" s="205" t="str">
-        <x:v>planned_not_authorized</x:v>
-      </x:c>
-      <x:c r="O5" s="214" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Measured: one thread; one worker; 5.542175 sec static + complete internal; 136,806,400-byte maximum RSS; 788,967 generated bytes</x:v>
+      </x:c>
+      <x:c r="N5" s="218" t="str">
+        <x:v>target_free_synthetic_mechanics_only</x:v>
+      </x:c>
+      <x:c r="O5" s="220" t="str">
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="P5" s="113" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -3259,17 +3292,20 @@
     <x:mergeCell ref="A2:P2"/>
     <x:mergeCell ref="A3:P3"/>
   </x:mergeCells>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="O5:O24">
       <x:formula1>"Not Started,In Progress,Review,Blocked,Done,Parked"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="D5:D24">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="O5">
+      <x:formula1>"Not Started,In Progress,Review,Blocked,Complete,Parked"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a1503f457764a49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb1f83e80827483e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4684,7 +4720,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9f567f6478e4aff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22299958fa7f4882"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6349,16 +6385,34 @@
       <x:c r="I57" s="12"/>
       <x:c r="J57"/>
     </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="37"/>
-      <x:c r="B58" s="12"/>
-      <x:c r="C58" s="12"/>
-      <x:c r="D58" s="12"/>
-      <x:c r="E58" s="12"/>
-      <x:c r="F58" s="12"/>
-      <x:c r="G58" s="12"/>
-      <x:c r="H58" s="12"/>
-      <x:c r="I58" s="12"/>
+    <x:row r="58" ht="96" customHeight="1">
+      <x:c r="A58" s="37" t="n">
+        <x:v>46216.5</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="str">
+        <x:v>25-R1</x:v>
+      </x:c>
+      <x:c r="C58" s="12" t="str">
+        <x:v>Accept Loop 25 causal mechanics; keep science closed and prohibit rerun</x:v>
+      </x:c>
+      <x:c r="D58" s="12" t="str">
+        <x:v>Static qualification passed before seed access; development froze before one conditional qualification open; all 24 items, 168 schedules, 240 resumes, and 72 mutation controls passed with zero protected reads and all resource caps satisfied.</x:v>
+      </x:c>
+      <x:c r="E58" s="12" t="str">
+        <x:v>docs/LOOP_25_CAUSAL_PREPROCESSING_RESULT.md; registries/loop25_causal_preprocessing_result.v1.json; commits 1e7296a and 439f151</x:v>
+      </x:c>
+      <x:c r="F58" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G58" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H58" s="12" t="str">
+        <x:v>Loop 25 and roadmap Loop 45 are complete. Loop 26/46 requires a new preregistration and separate authorization; no real cache, target, model, training, RW3, device, or rerun is opened.</x:v>
+      </x:c>
+      <x:c r="I58" s="12" t="str">
+        <x:v>Engineering mechanics only; no retained neural information, decoding, latency, transfer, device, home-use, or clinical claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37"/>
@@ -7942,7 +7996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8b7549a6394373"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d46a62f2f0b4325"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9413,7 +9467,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfab33dfbaa224a80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f757e5d9ccb4729"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9904,24 +9958,24 @@
     </x:row>
     <x:row r="34" ht="126" hidden="0" customHeight="1">
       <x:c r="A34" s="14" t="str">
-        <x:v>Loop25-Decision</x:v>
+        <x:v>Loop25-Result-Audit</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Decide Amended Causal Preprocessing Gate v1</x:v>
+        <x:v>Audit Completed Causal Mechanics Without Rerun</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>Review docs/LOOP_25_AUTHORIZATION_PACKET_V1.md and registries/loop25_authorization_request.v1.json. Confirm green amendment b6b92d8, contract SHA-256 ecec99a7cc505ec0256c01c3c1e8aeaa05323ab54a71528323fa6d32bd289141, the dedicated anti-alias stage, 65,537 response points, 23 alias probes, seeds 2501/2502, seven schedules, ten resume cuts, three future-mutation cuts, 45 refusals, 23 counters, and 8 MiB/45-second caps. Decide explicitly to authorize only v1, amend again, or hold. General continuation is not authorization. Do not implement, generate coefficients or fixtures, open either seed, read data/caches/targets, run models, train, touch RW3, streams, devices, or hardware from this prompt.</x:v>
+        <x:v>Read docs/LOOP_25_CAUSAL_PREPROCESSING_RESULT.md and registries/loop25_causal_preprocessing_result.v1.json. Verify the immutable request, separate green authorization 1e7296a, green implementation 439f151, static-first access order, 24/24 items, 168/240/72 replay checks, zero protected counters, measured caps, and no-rerun boundary. Do not regenerate fixtures, reopen seeds 2501/2502, rerun the gate, or promote a scientific claim.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="135" customHeight="1">
       <x:c r="A35" s="12" t="str">
-        <x:v>Loop26-Research</x:v>
+        <x:v>Loop26-Preregister</x:v>
       </x:c>
       <x:c r="B35" s="12" t="str">
-        <x:v>Review Validation Identifiability Before Preregistration</x:v>
+        <x:v>Preregister Reserved S21 Neural-Effect Gate Without Executing</x:v>
       </x:c>
       <x:c r="C35" s="12" t="str">
-        <x:v>Read docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md and registries/loop26_research_boundary.v0.json. Confirm 55/6/5 source membership, one person/session, 64 paired assignments, the unfrozen 2,908-parameter causal candidate and 2,884-parameter linear comparator, six control families, and 14 false authorization flags. Loop 25 must close first. Do not read caches or targets, run or train a model, open validation, reopen source test or session 2, create an experiment contract, or treat this research packet as authorization.</x:v>
+        <x:v>Read docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md and registries/loop26_research_boundary.v0.json. Freeze the 55/6/5 split, 2,908-parameter causal candidate, 2,884-parameter linear comparator, six controls, all 64 paired assignments, target-blind prediction hashes, exact access order, one-thread caps, and source-test/session-2 exclusions. Produce a hash-bound preregistration and decision packet only. Do not read caches or targets, train or run a model, open validation, or treat this prompt as authorization.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="144" customHeight="1">
@@ -10126,7 +10180,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf542c67347034a1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a7d4d2b40cb4c49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10692,7 +10746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68dd37bfac94f2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ee4b58ba324d62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10761,7 +10815,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 v1 decision pending | Loops 26-41 planning research complete | Loops 42-44 Not Started | Every execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loop 26 decision next | Loops 26-43 execution Not Started | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -10849,44 +10903,49 @@
         <x:v>A causal model is not causal if filtering, resampling, padding, or normalization leaks future context; this gate protects every later streaming claim.</x:v>
       </x:c>
       <x:c r="G5" s="113" t="str">
-        <x:v>Build: Versioned stateful preprocessing contract with a dedicated causal anti-alias SOS stage, phase-locked decimator, replay harness, transform provenance, and fail-closed refusals.
-Research: Pinned Brain2Qwerty-to-NeuralSet-to-MNE source trace plus filter delay, full folding-band, alias-map, resampling jitter, padding, and train-only normalization analysis.</x:v>
+        <x:v>Built: Versioned stateful 1000-to-100 Hz preprocessing with dedicated causal anti-alias SOS, phase-locked decimation, frozen normalization, exact snapshots, deterministic resume, fail-closed validation, four CLI commands, and audit-hashed reports.
+Result: Static, development, and conditional qualification gates passed once.</x:v>
       </x:c>
       <x:c r="H5" s="113" t="str">
-        <x:v>Data: Target-free synthetic signals first; any later S21 use is restricted to separately authorized source-train rows and may not open source-test or session-2 evidence.
-Controls:
-- Seven frozen chunk schedules including whole-item, single-sample, decimation-boundary, frame-boundary, powers-of-two, and seeded-irregular splits.
-- Six target-free signal families, ten resume cuts, and three future-mutation cuts across physically separate seeds 2501 and 2502.
-- A 65,537-point 0-500 Hz response grid, 23 exact alias source probes, and complete 50-500 Hz folding-band attenuation before any fixture array opens.
-- Offline noncausal reference reported separately and never substituted for the causal path.</x:v>
+        <x:v>Data: 24 target-free synthetic items from physically separate seeds 2501 and 2502; no S21, S7, S20, or S25 payload.
+Controls passed:
+- 65,537-point response grid and 23 alias probes before partition access
+- 7 schedules per item
+- 10 resume cuts per item
+- 3 future-mutation cuts per item
+- metadata inspection opened zero signal arrays
+- all protected and forbidden counters were zero</x:v>
       </x:c>
       <x:c r="I5" s="113" t="str">
-        <x:v>- right-context samples and milliseconds
-- valid-sample and timestamp identity
-- maximum offline-stream payload error
-- schedule hash agreement
-- dedicated and complete-chain folding-band attenuation plus alias destination correctness
-- runtime, peak RSS, input bytes, output bytes, and access counts</x:v>
+        <x:v>- 24/24 items passed
+- 168/168 schedule checks
+- 240/240 resume checks
+- 72/72 future-mutation controls
+- folding-band maximum -67.503786 dB
+- zero right-context samples
+- 1,971,744 input bytes; 212,328 output bytes
+- 5.542175 sec static + complete internal
+- 136,806,400-byte maximum RSS</x:v>
       </x:c>
       <x:c r="J5" s="113" t="str">
-        <x:v>Acceptance: Proceed only if the dedicated anti-alias and complete chain pass the full 50-500 Hz folding-band gate before seed access, declared right context is zero, every schedule preserves samples, timestamps, and state, all forbidden counters are zero, and resource caps pass.
-Stop: Park with both seeds unopened if the static filter gate fails; otherwise park any transform that needs future samples or cannot preserve timing, and never widen tolerances after observing a protected row.</x:v>
+        <x:v>Passed once: the static filter gate preceded every partition open; development passed and froze before qualification opened; every replay, timestamp, padding, access, and resource gate passed.
+No rerun, post-result tuning, tolerance widening, seed reuse, or protected access is authorized.</x:v>
       </x:c>
       <x:c r="K5" s="113" t="str">
         <x:v>Loops: none
-External: explicit_loop25_authorization_decision</x:v>
+External: satisfied by green authorization commit 1e7296a and green implementation commit 439f151</x:v>
       </x:c>
       <x:c r="L5" s="113" t="str">
-        <x:v>Amended at green commit b6b92d8 after the v0 anti-alias scope was superseded before authorization. Await a separate exact decision through docs/LOOP_25_AUTHORIZATION_PACKET_V1.md; the v1 request is false, seeds 2501/2502 are unopened, and coefficients, fixtures, runtime, data/cache/target/model/training access, RW3, streams, devices, and hardware remain unauthorized.</x:v>
+        <x:v>Completed once after a separate hash-bound authorization and green CI. Current execution authorization is false because no rerun is open. Real/consumed data, targets, models, training, RW3, streams, devices, and hardware were not used and remain separately gated. Loop 26 requires a new preregistration and authorization.</x:v>
       </x:c>
       <x:c r="M5" s="113" t="str">
-        <x:v>One thread, one worker, 4 MiB fixtures, 16 MiB working arrays, 8 MiB total generated artifacts, 45 seconds internal runtime, 4 KiB mutable state, and 1 GiB peak RSS.</x:v>
-      </x:c>
-      <x:c r="N5" s="140" t="str">
-        <x:v>amended_preregistered_no_implementation_or_execution</x:v>
-      </x:c>
-      <x:c r="O5" s="146" t="str">
-        <x:v>Review</x:v>
+        <x:v>Measured: one thread, one worker, 788,967 total generated bytes, 985,872-byte maximum partition array, 720-byte state, 5.542175 sec static + complete internal, 136,806,400-byte maximum RSS. All frozen 8 MiB / 16 MiB / 45 sec per-gate / 1 GiB caps passed.</x:v>
+      </x:c>
+      <x:c r="N5" s="218" t="str">
+        <x:v>target_free_synthetic_causal_preprocessing_mechanics_passed</x:v>
+      </x:c>
+      <x:c r="O5" s="220" t="str">
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="P5" s="149" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -10936,15 +10995,14 @@
 - raw, cache, target, model, and training access counts</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Acceptance: A future preregistration may proceed only after Loop 25 closes. A future experiment may proceed only if its frozen primary neural-versus-prior margin and every required control pass on exactly six validation rows with no access violation; this cannot authorize source-test opening.
-Stop: If the neural path does not beat the registered controls, park real-model scaling and move to failure analysis without touching test or increasing model size.</x:v>
+        <x:v>Loop 25 mechanics is satisfied. A future experiment may proceed only after a new hash-bound preregistration and separate authorization freeze the model, controls, predictions, access order, statistics, and resources. If the neural path misses any registered control, park scaling and keep source test/session 2 closed.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
         <x:v>Loops: 25
 External: separate_real_cache_and_training_authorization</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Planning research is complete, but no experiment preregistration or authorization sentence exists. Real-cache reads, target access, training, validation opening, model runs, test/session-2 access, and Loop 25 execution are unauthorized now.</x:v>
+        <x:v>Planning research is complete, but no Loop 26 experiment preregistration or authorization exists. Loop 25 mechanics is complete; real-cache reads, targets, training, validation opening, model runs, source test, and session 2 remain unauthorized.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
         <x:v>One thread, one worker, at most 2,908 trainable parameters, 32 MiB generated artifacts, 20 minutes total future CPU time across candidate and controls, and 1 GiB peak RSS.</x:v>
@@ -12192,14 +12250,17 @@
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Blocked"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Not Started"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="O5:O24">
       <x:formula1>'Lists'!$A$2:$A$7</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O5">
+      <x:formula1>"Not Started,In Progress,Review,Blocked,Complete,Parked"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500c007b3c484c5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaa2ab541ef442e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R047e85a8acec4405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rec2ef2acf87e4e2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R47bc6d88994344a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R8be315dad5b84d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R1d91ebeefef64d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rcb622c12fa5a417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R7571022a98b3438e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R27563c3bb52b4c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R426830c00bea4be7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rcba2cfbce2264a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbaed766ffe4e4ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rfd08684946d240f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R8b90e7e6353c4d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R17b0955df64e4cc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R53d6191b606f4c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R3b87953c08164615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8137f2334b104054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4d45a9507a604a39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R39c7206a8b6c451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rf93bfb48336b484e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -170,7 +170,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -332,6 +332,11 @@
         <x:fgColor rgb="FFD9F2E3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="13">
     <x:border/>
@@ -437,7 +442,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="221">
+  <x:cellXfs count="223">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1003,6 +1008,12 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="32" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="33" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="33" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1261,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e60b2bf77914e86"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9171fb31122f4639"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1653,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 26 preregistration decision next</x:v>
+        <x:v>Loop 26 authorization decision next</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1675,7 +1686,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 25 / scientific Loop 45 target-free causal mechanics passed once: 24/24 items, 168 schedules, 240 resumes, 72 mutation controls, zero protected reads, 788,967 generated bytes, and 136,806,400-byte maximum RSS. No rerun is authorized. Loop 26 / 46 is the next separate decision; all current execution flags remain false.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 target-free mechanics passed once with no rerun. Loop 26/31/33 and scientific Loop 46 are preregistered at green commit 881145d: 21 fits, 24 target-blind inferences, 6 priors, 31 prediction sets, and one post-freeze six-target delivery. The request remains unauthorized; no cache value, target delivery, model run, training run, prediction, or score exists. All current execution flags remain false.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1812,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R542644b7e38548d0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f302d482c784849"/>
 </x:worksheet>
 </file>
 
@@ -1860,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: prove one target-blind real neural effect against no-signal and corrupted-signal controls, then test the frozen effect on one unseen person. EEG, streaming, home, and release claims remain downstream and separate.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loop 46 is preregistered at 881145d; exact authorization is pending and every execution flag remains false.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1880,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loops 46-64 Not Started | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all current execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
+        <x:v>Loop 45 mechanics complete | Loop 46 preregistered, authorization pending | Loops 47-64 execution Not Started | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all current execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2034,45 +2045,38 @@
         <x:v>bounded one-person one-session neural advantage on source validation</x:v>
       </x:c>
       <x:c r="G6" s="114" t="str">
-        <x:v>Preregister, train on 55 source-train rows, hash-freeze six predictions, open six validation targets once, and report exact paired inference.</x:v>
+        <x:v>Green shared Loop 26/31/33 contract freezes 55 train rows, 21 fits, 24 target-blind inferences, 6 priors, 31 six-row prediction sets, one green prediction freeze, and one six-target scoring delivery. Implementation and execution await the exact sentence.</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
-        <x:v>Data: S21 session-1 source train and six reserved validation rows only; five source-test rows and session 2 remain closed.
-Controls:
-- train-only no-signal prior
-- zero-signal inference
-- semantic-ID target derangement
-- time displacement
-- channel-name-hash derangement
-- 2,884-parameter linear signal comparator</x:v>
+        <x:v>Data: S21 session-1 source train and six validation rows only after authorization; five source-test rows and session 2 remain closed.
+Controls: prior, zero signal, row/channel/time derangements, timing-only, train-pairing derangement, and 2,884-parameter linear comparator.</x:v>
       </x:c>
       <x:c r="I6" s="114" t="str">
-        <x:v>- macro sentence CER
-- corpus CER
-- 64 exact sign assignments
-- margin over every control
-- wins ties losses
-- blank fraction
-- runtime and RSS</x:v>
+        <x:v>- macro sentence and corpus CER
+- all 6 paired differences and 64 sign assignments
+- 6 strict wins
+- every attribution control
+- linear comparator
+- bounded scaling outcomes
+- runtime, RSS, bytes, hashes, and access counts</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Accept: Candidate improves macro sentence CER over the prior by at least 0.05, p &lt;= 0.05 under the frozen exact paired rule, and strictly beats every signal-free and corrupted-signal control.
-Kill/Park: If any primary or control gate fails, park real-model scaling and move to Loop 48 failure localization; never open source test or increase model size.</x:v>
+        <x:v>Accept only with &gt;=0.05 macro sentence-CER gain over prior, 6 strict sentence wins, one-sided exact p &lt;=0.05, every registered control component, a strict win over the linear comparator, and all resource/access/hash gates. Any failure parks scaling and keeps source test/session 2 closed.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops: 45, 26</x:v>
+        <x:v>Loops: 45, 26, 31, 33</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Needs a new hash-bound preregistration and a separate authorization for exact cache members, targets, training, and validation opening.</x:v>
+        <x:v>Preregistered at green commit 881145d and CI 29282661766. The exact separate authorization sentence has not been received; cache values, targets, training, inference, prediction freezing, and scoring remain unauthorized.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
-        <x:v>one thread; one worker; &lt;=2,908 trainable parameters; &lt;=20 CPU minutes; &lt;=1 GiB RSS; &lt;=32 MiB generated</x:v>
+        <x:v>1 thread; 1 worker; &lt;=2,908 parameters; &lt;=1,500 sec end to end; &lt;=1 GiB RSS; &lt;=32 MiB generated; 0 downloads</x:v>
       </x:c>
       <x:c r="N6" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
-      </x:c>
-      <x:c r="O6" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>green_preregistration_no_protected_execution</x:v>
+      </x:c>
+      <x:c r="O6" s="222" t="str">
+        <x:v>Preregistered; Authorization Pending</x:v>
       </x:c>
       <x:c r="P6" s="114" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -2094,51 +2098,39 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E7" s="114" t="str">
-        <x:v>If Loop 46 passes, does the advantage require intact sensor signal rather than timing, labels, padding, or a language prior?</x:v>
+        <x:v>Does the same shared event show that any primary advantage requires intact sensor structure rather than timing, labels, or corruption artifacts?</x:v>
       </x:c>
       <x:c r="F7" s="200" t="str">
         <x:v>sensor-signal dependence for the exact S21 source slice</x:v>
       </x:c>
       <x:c r="G7" s="114" t="str">
-        <x:v>Execute the frozen Loop 31 ten-condition encoder matrix with intersection-union logic and prediction commitments before target opening.</x:v>
+        <x:v>Freeze and score the Loop 31 ten-condition encoder matrix inside the same Loop 46 prediction-freeze and target-delivery event; no post-score matrix execution is allowed.</x:v>
       </x:c>
       <x:c r="H7" s="114" t="str">
-        <x:v>Data: Exactly the authorized Loop 46 train/validation members and frozen predictions; no source test, session 2, S7, S20, or S25.
-Controls:
-- no-signal prior
-- zero signal
-- channel derangement
-- time displacement
-- train-target derangement
-- padding-only
-- timestamp-only
-- linear signal comparator
-- candidate encoder
-- frozen positive control</x:v>
+        <x:v>Data: Exactly the authorized Loop 46 train/validation members. Controls: full signal, prior, zero signal, validation-row/channel/time derangements, timing-only, train-target pairing derangement, and linear comparator. LLM/Neuro Token remains separate.</x:v>
       </x:c>
       <x:c r="I7" s="114" t="str">
         <x:v>- macro CER deltas
-- all six paired differences
-- intersection-union pass
+- all 6 paired differences
+- intersection-union components
 - control ordering
-- prediction hashes
-- access counters</x:v>
+- prediction/config/transform hashes
+- access and resource ledgers</x:v>
       </x:c>
       <x:c r="J7" s="114" t="str">
-        <x:v>Accept: The intact-signal candidate strictly beats every registered signal-free and corrupted-signal condition under the frozen paired rule.
-Kill/Park: Any shortcut win blocks a neural-contribution claim and sends the exact discrepancy to Loop 48 or the Loop 35 peripheral firewall.</x:v>
+        <x:v>Accept sensor-signal dependence only if every registered encoder condition passes in the one shared scoring event. Any missing, tied, or failed component parks attribution and routes failure localization to Loop 48 or peripheral controls to Loop 35.</x:v>
       </x:c>
       <x:c r="K7" s="114" t="str">
         <x:v>Loops: 46, 31</x:v>
       </x:c>
       <x:c r="L7" s="114" t="str">
-        <x:v>Contingent on a passing Loop 46 and a separate matrix authorization; language-model and NeuroToken extensions remain separately gated.</x:v>
+        <x:v>Prediction and scoring operations are bound to the shared Loop 26 authorization sequence; no separate post-Loop-46 target open or matrix run exists. The LLM/Neuro Token extension remains separately gated.</x:v>
       </x:c>
       <x:c r="M7" s="114" t="str">
-        <x:v>one thread; one worker; no new architecture; &lt;=10 inference conditions; &lt;=15 CPU minutes; &lt;=32 MiB generated</x:v>
+        <x:v>Included inside the Loop 46 caps; no new architecture, target delivery, or artifact allowance</x:v>
       </x:c>
       <x:c r="N7" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>matrix_bound_to_loop46_shared_event_no_execution</x:v>
       </x:c>
       <x:c r="O7" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -3305,7 +3297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb1f83e80827483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0ce3965ea445ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4720,7 +4712,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22299958fa7f4882"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff2e5871df264fce"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6415,15 +6407,33 @@
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="37"/>
-      <x:c r="B59" s="12"/>
-      <x:c r="C59" s="12"/>
-      <x:c r="D59" s="12"/>
-      <x:c r="E59" s="12"/>
-      <x:c r="F59" s="12"/>
-      <x:c r="G59" s="12"/>
-      <x:c r="H59" s="12"/>
-      <x:c r="I59" s="12"/>
+      <x:c r="A59" s="37" t="n">
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="B59" s="12" t="str">
+        <x:v>26/31/33-R1</x:v>
+      </x:c>
+      <x:c r="C59" s="12" t="str">
+        <x:v>Share the six S21 validation targets; preregister and hold execution</x:v>
+      </x:c>
+      <x:c r="D59" s="12" t="str">
+        <x:v>Freeze the primary model, 10 encoder conditions, six-size scaling curve, and 31 prediction sets before one six-target scoring delivery. Withdraw physical-never-opened wording because the legacy deflated NPZ loader materialized complete arrays; preserve the narrower unused-for-fit/selection/scoring claim.</x:v>
+      </x:c>
+      <x:c r="E59" s="12" t="str">
+        <x:v>docs/LOOP_26_SHARED_VALIDATION_PREREGISTRATION.md; registries/loop26_shared_validation_contract.v0.json; commit 881145d; CI 29282661766</x:v>
+      </x:c>
+      <x:c r="F59" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G59" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H59" s="12" t="str">
+        <x:v>Exact authorization sentence or hold</x:v>
+      </x:c>
+      <x:c r="I59" s="12" t="str">
+        <x:v>No implementation or protected execution. Maximum future pass: bounded same-person/session predictive advantage and sensor-signal dependence; no brain-specific, transfer, real-time, device, home, or clinical claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37"/>
@@ -7996,7 +8006,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d46a62f2f0b4325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a111b0a14b46bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9467,7 +9477,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f757e5d9ccb4729"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459e4be7fc5a44f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10180,7 +10190,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a7d4d2b40cb4c49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf595e5a7d46b445d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10746,7 +10756,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ee4b58ba324d62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2869d8bee6d45aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10795,7 +10805,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Loop 44 artifact-only claim review is complete. Engineering release is held; scientific performance is parked. No experiment, tag, release, DOI, protected payload, model, stream, or device action is authorized by this sheet.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 mechanics passed once. Loop 26/31/33 shared preregistration is green at 881145d; exact authorization is pending and every execution flag is false.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -10974,44 +10984,46 @@
         <x:v>The project has strong mechanics but no real neural advantage; this is the first gate that can justify continuing the predictive branch.</x:v>
       </x:c>
       <x:c r="G6" s="114" t="str">
-        <x:v>Build: Preregistered tiny architecture, train-only fit path, six-row validation report, uncertainty, control parity, and immutable access ledger.
-Research: Completed planning-only power and identifiability note: six paired rows yield 64 exact sign assignments, one-person inference only, and no source-test or transfer claim.
-Packet: docs/LOOP_26_PRIMARY_SOURCE_RESEARCH.md</x:v>
+        <x:v>Build: Green shared preregistration freezes the 2,908-parameter causal candidate, 2,884-parameter linear comparator, bounded row-streaming isolation, 21 parameter-update runs, 24 target-blind inferences, 6 train-only priors, 31 prediction sets, and one post-freeze scorer.
+Research: Complete 64-assignment inference, 10-condition encoder matrix, bounded 8/16/24/32/44/55 curve, archive-access correction, and 40 refusals.
+Packets: docs/LOOP_26_SHARED_VALIDATION_PREREGISTRATION.md; docs/LOOP_26_AUTHORIZATION_PACKET.md</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
-        <x:v>Data: Only separately authorized S21 source-train and source-validation members; five source-test rows and all session-2 rows stay closed.
+        <x:v>Data: Existing S21 session-1 cache only after exact authorization; 55 train rows and 6 target-free validation-signal rows before scoring. Five source-test rows and session 2 stay closed. Validation targets reach one isolated scorer only after a green hash-only prediction freeze.
 Controls:
-- Same-split train-only no-signal sentence prior and zero-signal inference.
-- Semantic-ID-derived train-target derangement frozen before targets open.
-- Nonwrapping zero-filled time displacement and channel-name-hash derangements frozen before signal arrays open.
-- A 2,884-parameter linear signal CTC matched against the recommended 2,908-parameter causal candidate.</x:v>
+- train-only prior and zero signal
+- validation-row, channel, and time derangements
+- timing-only and train-target-pairing fits
+- 2,884-parameter linear signal CTC
+- no language model or prompt context</x:v>
       </x:c>
       <x:c r="I6" s="114" t="str">
-        <x:v>- macro per-sentence CER and corpus CER
-- all six paired item differences and complete 64-assignment exact null
-- exact-sequence accuracy, WER, blank fraction, and wins/ties/losses
-- margin over every signal-free and corrupted-signal control
-- parameter count, runtime, peak RSS, and artifact bytes
-- raw, cache, target, model, and training access counts</x:v>
+        <x:v>- macro per-sentence and corpus CER
+- all 6 paired differences and all 64 sign assignments
+- 6 strict sentence wins
+- exact-sequence accuracy, WER, blank fraction
+- every attribution control and linear comparator
+- bounded scaling deltas and per-seed slopes
+- runtime, RSS, bytes, hashes, warnings, and complete access counts</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Loop 25 mechanics is satisfied. A future experiment may proceed only after a new hash-bound preregistration and separate authorization freeze the model, controls, predictions, access order, statistics, and resources. If the neural path misses any registered control, park scaling and keep source test/session 2 closed.</x:v>
+        <x:v>Accept only if candidate-minus-prior macro CER gain is &gt;=0.05, all 6 sentences are strict wins, one-sided exact p &lt;=0.05, every required control component passes, the candidate beats the linear comparator, the scaling rules pass, and all hash/access/resource gates pass. Park without restart, retuning, source-test/session-2/S25 open, or larger model on any failure.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops: 25
-External: separate_real_cache_and_training_authorization</x:v>
+        <x:v>Loops: 25, 31, 33; scientific 46
+External: exact Loop 26 shared authorization sentence; green authorization record; green implementation and synthetic isolation tests; green prediction-freeze record before target delivery</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Planning research is complete, but no Loop 26 experiment preregistration or authorization exists. Loop 25 mechanics is complete; real-cache reads, targets, training, validation opening, model runs, source test, and session 2 remain unauthorized.</x:v>
+        <x:v>Green preregistration commit 881145d and CI 29282661766 establish design only. The request is prepared but unauthorized. Historical whole-array loading means physical-never-opened target wording is withdrawn; the six validation targets remain unused for fit, selection, threshold choice, or predictive scoring. No real-cache value, target delivery, model, training, prediction, or score is authorized now.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
-        <x:v>One thread, one worker, at most 2,908 trainable parameters, 32 MiB generated artifacts, 20 minutes total future CPU time across candidate and controls, and 1 GiB peak RSS.</x:v>
+        <x:v>1 CPU thread; 1 worker; 2,908 candidate parameters; 1,200 sec parameter updates; 1,500 sec end to end; 1 GiB RSS; 128 MiB working arrays; 4 MiB checkpoints; 2 MiB predictions; 32 MiB generated artifacts; 0 download bytes</x:v>
       </x:c>
       <x:c r="N6" s="141" t="str">
-        <x:v>planned_not_authorized; planning_research_complete</x:v>
-      </x:c>
-      <x:c r="O6" s="147" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>green_hash_bound_shared_validation_preregistration; authorization_pending; no_protected_execution; upstream_cache_noncausal; model_only_causal</x:v>
+      </x:c>
+      <x:c r="O6" s="222" t="str">
+        <x:v>Preregistered; Authorization Pending</x:v>
       </x:c>
       <x:c r="P6" s="150" t="str">
         <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
@@ -11327,45 +11339,40 @@
         <x:v>A fluent prediction is not an attribution result. The consumed S21 MEG and S7 EEG paths both lose to no-signal priors, so any future improvement must survive signal-free, corrupted-signal, timing, context, and language controls before it can be credited to the sensor input.</x:v>
       </x:c>
       <x:c r="G11" s="114" t="str">
-        <x:v>Build: Future hash-bound 10-condition encoder matrix plus a separately gated 5-condition LLM/Neuro Token extension.
-Research: Completed estimands, exact six-row intersection-union inference, target-blind freeze order, six claim classes, 18 future gates, 24 refusals, and a Loop 35 ceiling on brain-specific attribution.</x:v>
+        <x:v>Build: The 10-condition encoder matrix is frozen inside the green Loop 26 shared contract.
+Research: Exact six-row intersection-union inference, target-blind transforms, and the Loop 35 ceiling remain binding.
+Separate: the 5-condition LLM/Neuro Token extension is not preregistered.</x:v>
       </x:c>
       <x:c r="H11" s="114" t="str">
-        <x:v>Data: Planning research used public primary sources and committed aggregate reports only. Future execution may use one separately authorized source-validation open after target-blind prediction freeze; consumed source test, session 2, S7, S20, and S25 remain closed.
-Controls:
-- Full signal; train-only prior; zero signal; item, channel, and time derangements; timing-only; conditional context-only; train-pairing derangement.
-- 2,884-parameter linear signal CTC as a diagnostic.
-- All transforms and predictions frozen before targets.
-- Encoder, language, Neuro Token, total-system, and brain-specific effects separate.
-- Loop 35 required for brain-specific origin.</x:v>
+        <x:v>Data: Same authorized Loop 26 train/validation membership only; all 31 prediction sets freeze before one target delivery. Source test, session 2, S7, S20, and S25 stay closed.
+Controls: full signal, prior, zero signal, row/channel/time derangement, timing-only, train-pairing derangement, and linear comparator. No context-only condition is available in this event.</x:v>
       </x:c>
       <x:c r="I11" s="114" t="str">
-        <x:v>- macro sentence control-minus-full CER for every applicable condition
+        <x:v>- macro sentence control-minus-full CER
 - exact one-sided paired components and intersection-union decision
-- primary practical margin
-- language-prior and conditional Neuro Token gains
-- per-item edits and wins/ties/losses; WER where valid
-- condition-specific access, model, training, runtime, RSS, bytes, warnings, unavailable fields, and hashes</x:v>
+- per-item edits and wins/ties/losses
+- exact sequences and WER where valid
+- per-condition hashes, access, runtime, RSS, bytes, warnings, and unavailable fields</x:v>
       </x:c>
       <x:c r="J11" s="114" t="str">
-        <x:v>Acceptance: A future result may support sensor-signal dependence only when every applicable condition, exact six-item component, primary margin, target-blind freeze order, ledger, hash, and resource gate passes.
-Stop: Park on a tie or failed/missing control, target-informed transform, hidden timing/context, target open before predictions, restart or threshold change, missing ledger/hash, resource failure, or any promotion to brain-specific attribution before Loop 35.</x:v>
+        <x:v>Accept sensor-signal dependence only when every registered encoder condition and exact six-item component passes with the 0.05 primary margin, six strict primary wins, target-blind freeze order, complete ledgers, and resource gates. Brain-specific origin remains unavailable before Loop 35. A missing or tied control parks the claim.</x:v>
       </x:c>
       <x:c r="K11" s="114" t="str">
-        <x:v>Loops: 26
-External: separate validation/model authorization; Loop 35 for brain-specific claim</x:v>
+        <x:v>Loops: 26, 33
+External: exact shared authorization; Loop 35 for brain-specific claim
+LLM/Neuro Token extension remains a separate future gate</x:v>
       </x:c>
       <x:c r="L11" s="114" t="str">
-        <x:v>Planning research only. No cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation is authorized. The experiment remains Not Started.</x:v>
+        <x:v>Encoder matrix is bound to green shared contract 881145d, but the exact authorization sentence is absent. No cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M11" s="114" t="str">
-        <x:v>Current: one thread/worker, zero protected/model downloads, 8 MiB planning cap. Future: one thread/worker, 2,908 parameters, 1,200 sec training, 32 MiB artifacts, 1 GiB RSS, zero new data/model downloads.</x:v>
+        <x:v>Shared cap: 1 thread/worker, 2,908 parameters, 1,200 sec parameter updates, 1,500 sec end to end, 1 GiB RSS, 32 MiB artifacts, zero downloads</x:v>
       </x:c>
       <x:c r="N11" s="141" t="str">
-        <x:v>planned_not_authorized; planning_research_complete; sensor_signal_ceiling; loop35_required_for_brain_specific</x:v>
-      </x:c>
-      <x:c r="O11" s="147" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>encoder_matrix_preregistered_with_loop26; language_extension_unpreregistered; no_execution; sensor_signal_ceiling; loop35_required_for_brain_specific</x:v>
+      </x:c>
+      <x:c r="O11" s="222" t="str">
+        <x:v>Shared Encoder Preregistration; Authorization Pending</x:v>
       </x:c>
       <x:c r="P11" s="150" t="str">
         <x:v>https://www.nature.com/articles/s41593-026-02303-2
@@ -11469,44 +11476,38 @@
         <x:v>A prospective bounded curve can guide whether another metadata-only acquisition packet is worth preparing without guessing, reopening consumed evidence, or transferring Brain2Qwerty v2's 90-hour scaling exponent.</x:v>
       </x:c>
       <x:c r="G13" s="114" t="str">
-        <x:v>Build: Future target-blind runner over strictly nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 candidate fits, one fixed 2,908-parameter encoder, matched priors, and complete access/resource/hash ledgers.
-Research: Completed shared-validation access order, unique-versus-physical-repetition firewall, descriptive trend rules, seven outcomes, seven claims, 20 gates, and 30 refusals.</x:v>
+        <x:v>Build: Green shared contract freezes strictly nested 8/16/24/32/44/55 unique-sentence prefixes, 3 fixed seeds, 18 candidate fits, 6 matched priors, one fixed 2,908-parameter model, and complete prediction/access/resource hashes.
+Research: Unique-versus-physical-repetition firewall and bounded descriptive outcome rules remain binding.</x:v>
       </x:c>
       <x:c r="H13" s="114" t="str">
-        <x:v>Data: Planning used public primary sources and committed metadata only. Future execution may use separately authorized 55 source-train and six reserved validation rows; source test, session 2, S7, S20, S25, new data, and physical repetitions remain closed.
-Controls:
-- Strict target-blind nested prefixes; 55 is the complete source train.
-- Fixed person/session/device/channels/rate/model/optimizer/stopping/decode/metrics.
-- Size-matched train-only no-signal prior at every prefix.
-- Every Loop 26/31/33 prediction hash-frozen before one six-target open.
-- Distinct recordings required for any physical-repetition claim.</x:v>
+        <x:v>Data: Same authorized 55 train and 6 validation rows as Loop 26; all prefix and control predictions freeze before the one shared target delivery. Source test, session 2, S7, S20, S25, new data, and physical repetitions stay closed. Prefix order is target-blind and the 55-row endpoint equals all train rows.</x:v>
       </x:c>
       <x:c r="I13" s="114" t="str">
         <x:v>- macro sentence CER by item, seed, prefix, and matched prior
-- descriptive slope versus log2 unique sentences and every adjacent delta
-- smallest-band to upper-band and upper-band-over-prior practical gains
-- unique sentences, physical trials, valid seconds/minutes, bytes, runtime, RSS, and artifacts
-- exact access, warning, unavailable-field, and hash ledgers</x:v>
+- median-seed curve versus log2 unique sentences
+- smallest-band to upper-band gain
+- size-55 gain over matched prior
+- per-seed ordinary least-squares slope
+- unique rows, valid seconds, runtime, RSS, bytes, access, warnings, and hashes</x:v>
       </x:c>
       <x:c r="J13" s="114" t="str">
-        <x:v>Acceptance: Freeze Loop 33 before any validation target opens; hash-freeze all predictions before one target open; require negative slopes for every registered seed, recommended 0.05 smallest-to-upper and upper-over-prior gains, Loop 31 attribution for sensor wording, and all 20 gates.
-Stop: Park on a lost access order, full-size prior failure, unstable trend, target-informed prefix, fake physical repetition, cap/ledger/hash failure, or post-target restart. Never infer a universal law, saturation beyond 55, acquisition value, population behavior, energy, real-time, portable, at-home, assistive, diagnostic, or clinical performance.</x:v>
+        <x:v>Require &gt;=0.05 smallest-band-to-upper-band gain, &gt;=0.05 size-55-over-prior gain, a negative slope for every seed, and the Loop 31 attribution gate before sensor wording. Park on any target-informed prefix, missing fit/prior, access/hash/cap failure, or post-target restart. No universal law or acquisition permission is available.</x:v>
       </x:c>
       <x:c r="K13" s="114" t="str">
         <x:v>Loops: 26, 31
-External: shared Loop 26/33 preregistration before validation target open; separate bounded training and one-time validation authorization</x:v>
+External: exact shared authorization and the same green prediction-freeze-before-target sequence</x:v>
       </x:c>
       <x:c r="L13" s="114" t="str">
-        <x:v>Planning research only. Experiment Not Started. No protected cache/signal/target read, checkpoint/model/control run, training, parameter update, prediction, validation score, physical-repetition study, acquisition, download, S20/S25, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>The bounded curve is frozen inside green shared contract 881145d, but exact authorization is absent. No protected cache/signal/target read, model/control run, training, prediction, score, physical-repetition study, acquisition, S20/S25, stream, device, or hardware operation is authorized.</x:v>
       </x:c>
       <x:c r="M13" s="114" t="str">
-        <x:v>Current: one thread/worker, 6 public web operations, zero protected bytes, 8 MiB planning cap. Future: one thread/worker, 2,908 parameters, at most 18 candidate fits, 1,200 sec total training, 1 GiB RSS, 32 MiB artifacts, zero new downloads, and no energy claim without direct measurement.</x:v>
+        <x:v>Shared cap: 1 thread/worker, 2,908 parameters, 18 candidate fits, 1,200 sec parameter updates, 1,500 sec end to end, 1 GiB RSS, 32 MiB artifacts, zero downloads</x:v>
       </x:c>
       <x:c r="N13" s="141" t="str">
-        <x:v>planned_not_authorized; planning_research_complete; prefixes=8|16|24|32|44|55; shared_validation_prospective; no_repetition_lane; no_acquisition</x:v>
-      </x:c>
-      <x:c r="O13" s="147" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>bounded_scaling_preregistered_with_loop26; prefixes=8|16|24|32|44|55; no_protected_execution; no_repetition_lane; no_acquisition_permission</x:v>
+      </x:c>
+      <x:c r="O13" s="222" t="str">
+        <x:v>Shared Preregistration; Authorization Pending</x:v>
       </x:c>
       <x:c r="P13" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -12260,7 +12261,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaa2ab541ef442e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae871baa0c5c4969"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbaed766ffe4e4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rfd08684946d240f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R8b90e7e6353c4d70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R17b0955df64e4cc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R53d6191b606f4c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R3b87953c08164615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R8137f2334b104054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R4d45a9507a604a39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R39c7206a8b6c451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rf93bfb48336b484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdfa077f71e1d4510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R392dcb032e1a48a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R9569287305914e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rce4a8bcb3e264cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R9d06ddceb6504a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R63833487345c4c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R54e817ab05ba4345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R9b8d8946c4bc4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Ra34d04a419a34a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R32a9e1a114fc4982"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9171fb31122f4639"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc652ffb8dff04c42"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1664,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 26 authorization decision next</x:v>
+        <x:v>Loop 48 failure localization next</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1681,12 +1681,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="108" customHeight="1">
+    <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 25 / scientific Loop 45 target-free mechanics passed once with no rerun. Loop 26/31/33 and scientific Loop 46 are preregistered at green commit 881145d: 21 fits, 24 target-blind inferences, 6 priors, 31 prediction sets, and one post-freeze six-target delivery. The request remains unauthorized; no cache value, target delivery, model run, training run, prediction, or score exists. All current execution flags remain false.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 mechanics passed once with no rerun. Loop 26/31/33 and scientific Loops 46/47 were preregistered at 881145d, authorized at 1c0e52c, and consumed once after remote-green prediction freeze 54bdca9. Candidate macro CER 0.938177 was worse than prior 0.751235 by 0.186942; primary, attribution, and scaling gates failed. Source test and session 2 stayed closed. No rerun is authorized; Loop 48 is Not Started and separately gated.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f302d482c784849"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ed0949d94264fb1"/>
 </x:worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: one target-blind real neural-effect event at a time. Loop 46 is preregistered at 881145d; exact authorization is pending and every execution flag remains false.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked after the registered S21 gate failed; Loop 48 artifact-first failure localization is next but separately gated.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1891,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loop 46 preregistered, authorization pending | Loops 47-64 execution Not Started | one-thread default | S21 session 2 and S7 stay consumed | S25 stays final-only | all current execution_authorized=false | source: registries/next_scientific_loops.v0.json</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46/47 parked after one consumed negative result | Loop 48 Not Started | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2045,38 +2045,37 @@
         <x:v>bounded one-person one-session neural advantage on source validation</x:v>
       </x:c>
       <x:c r="G6" s="114" t="str">
-        <x:v>Green shared Loop 26/31/33 contract freezes 55 train rows, 21 fits, 24 target-blind inferences, 6 priors, 31 six-row prediction sets, one green prediction freeze, and one six-target scoring delivery. Implementation and execution await the exact sentence.</x:v>
+        <x:v>Completed the shared 55-row train path, 21 fits, 24 target-blind inferences, 6 priors, 31-set prediction freeze, remote-green target firewall, and one six-target score.</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
-        <x:v>Data: S21 session-1 source train and six validation rows only after authorization; five source-test rows and session 2 remain closed.
-Controls: prior, zero signal, row/channel/time derangements, timing-only, train-pairing derangement, and 2,884-parameter linear comparator.</x:v>
+        <x:v>S21 session-1 source train and six validation rows only. Five source-test rows and session 2 remained closed. Prior, zero, row/channel/time derangements, timing-only, train-pairing, and linear controls were retained.</x:v>
       </x:c>
       <x:c r="I6" s="114" t="str">
-        <x:v>- macro sentence and corpus CER
-- all 6 paired differences and 64 sign assignments
-- 6 strict wins
-- every attribution control
-- linear comparator
-- bounded scaling outcomes
-- runtime, RSS, bytes, hashes, and access counts</x:v>
+        <x:v>- candidate/prior macro CER 0.938177 / 0.751235
+- margin -0.186942
+- 0 wins, 1 tie, 5 losses
+- one-sided p=1.0
+- blank fraction 0.993477
+- runtime 184.046922 sec target-blind + 0.017592 sec score
+- max RSS 532,955,136 bytes</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Accept only with &gt;=0.05 macro sentence-CER gain over prior, 6 strict sentence wins, one-sided exact p &lt;=0.05, every registered control component, a strict win over the linear comparator, and all resource/access/hash gates. Any failure parks scaling and keeps source test/session 2 closed.</x:v>
+        <x:v>Failed: candidate did not improve by &gt;=0.05 and did not win all six items; complete control conjunction failed. Park scaling and do not open source test or session 2.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops: 45, 26, 31, 33</x:v>
+        <x:v>Loops 45, 26, 31, 33. Next diagnostic work order: Loop 48.</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Preregistered at green commit 881145d and CI 29282661766. The exact separate authorization sentence has not been received; cache values, targets, training, inference, prediction freezing, and scoring remain unauthorized.</x:v>
+        <x:v>Preregistered at 881145d, authorized at 1c0e52c, and frozen at remote-green 54bdca9 before one target delivery. Event consumed; no rerun, larger model, or tuning authorized.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
-        <x:v>1 thread; 1 worker; &lt;=2,908 parameters; &lt;=1,500 sec end to end; &lt;=1 GiB RSS; &lt;=32 MiB generated; 0 downloads</x:v>
+        <x:v>Measured: 1 thread; 1 worker; 2,908 parameters; 184.046922 sec target-blind end to end; 532,955,136-byte max RSS; 10,148,673 generated bytes; all caps passed</x:v>
       </x:c>
       <x:c r="N6" s="206" t="str">
-        <x:v>green_preregistration_no_protected_execution</x:v>
+        <x:v>consumed_registered_negative_result_no_rerun</x:v>
       </x:c>
       <x:c r="O6" s="222" t="str">
-        <x:v>Preregistered; Authorization Pending</x:v>
+        <x:v>Parked; Registered Gate Failed</x:v>
       </x:c>
       <x:c r="P6" s="114" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -2104,36 +2103,33 @@
         <x:v>sensor-signal dependence for the exact S21 source slice</x:v>
       </x:c>
       <x:c r="G7" s="114" t="str">
-        <x:v>Freeze and score the Loop 31 ten-condition encoder matrix inside the same Loop 46 prediction-freeze and target-delivery event; no post-score matrix execution is allowed.</x:v>
+        <x:v>Completed the frozen ten-condition Loop 31 encoder matrix inside the same consumed Loop 46 event. No post-score matrix run occurred.</x:v>
       </x:c>
       <x:c r="H7" s="114" t="str">
-        <x:v>Data: Exactly the authorized Loop 46 train/validation members. Controls: full signal, prior, zero signal, validation-row/channel/time derangements, timing-only, train-target pairing derangement, and linear comparator. LLM/Neuro Token remains separate.</x:v>
+        <x:v>Same consumed Loop 46 members. Zero/timing controls passed individually; prior and required corruption conjunction did not. LLM/Neuro Token remained closed.</x:v>
       </x:c>
       <x:c r="I7" s="114" t="str">
-        <x:v>- macro CER deltas
-- all 6 paired differences
-- intersection-union components
-- control ordering
-- prediction/config/transform hashes
-- access and resource ledgers</x:v>
+        <x:v>- zero signal and timing-only: 6/6 wins, p=0.015625
+- prior: 0/1/5, p=1.0
+- row/channel/time/target components did not form a passing conjunction</x:v>
       </x:c>
       <x:c r="J7" s="114" t="str">
-        <x:v>Accept sensor-signal dependence only if every registered encoder condition passes in the one shared scoring event. Any missing, tied, or failed component parks attribution and routes failure localization to Loop 48 or peripheral controls to Loop 35.</x:v>
+        <x:v>Failed: the intact candidate did not beat every registered signal-free and corrupted-signal condition. No sensor-signal-dependence or brain-origin claim.</x:v>
       </x:c>
       <x:c r="K7" s="114" t="str">
-        <x:v>Loops: 46, 31</x:v>
+        <x:v>Loops 46 and 31. Route aggregate discrepancy to Loop 48 only.</x:v>
       </x:c>
       <x:c r="L7" s="114" t="str">
-        <x:v>Prediction and scoring operations are bound to the shared Loop 26 authorization sequence; no separate post-Loop-46 target open or matrix run exists. The LLM/Neuro Token extension remains separately gated.</x:v>
+        <x:v>Shared event consumed. No post-Loop-46 target open, matrix rerun, LLM/Neuro Token extension, or protected operation is authorized.</x:v>
       </x:c>
       <x:c r="M7" s="114" t="str">
-        <x:v>Included inside the Loop 46 caps; no new architecture, target delivery, or artifact allowance</x:v>
+        <x:v>Included in Loop 46 measured resource envelope; no new target delivery or artifact allowance</x:v>
       </x:c>
       <x:c r="N7" s="206" t="str">
-        <x:v>matrix_bound_to_loop46_shared_event_no_execution</x:v>
+        <x:v>consumed_shared_attribution_gate_failed</x:v>
       </x:c>
       <x:c r="O7" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Parked; Shared Attribution Gate Failed</x:v>
       </x:c>
       <x:c r="P7" s="114" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -2190,13 +2186,13 @@
         <x:v>Loops: 46, 47</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Artifact-only planning may proceed; any train-array diagnostic or target read requires its own exact authorization.</x:v>
+        <x:v>Artifact-only planning may use committed aggregate reports. Any train-array diagnostic, cache member, target, model run, or implementation requires its own exact authorization. Source test and session 2 remain closed.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
         <x:v>artifact-only by default; one thread; &lt;=5 CPU minutes; &lt;=8 MiB generated</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planned_not_authorized; next_numbered_work_order</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -3297,7 +3293,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0ce3965ea445ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3497e8e9a89f4270"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff2e5871df264fce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a64f65b22c4a83"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6436,15 +6432,33 @@
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="37"/>
-      <x:c r="B60" s="12"/>
-      <x:c r="C60" s="12"/>
-      <x:c r="D60" s="12"/>
-      <x:c r="E60" s="12"/>
-      <x:c r="F60" s="12"/>
-      <x:c r="G60" s="12"/>
-      <x:c r="H60" s="12"/>
-      <x:c r="I60" s="12"/>
+      <x:c r="A60" s="37" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="str">
+        <x:v>26/31/33-R2</x:v>
+      </x:c>
+      <x:c r="C60" s="12" t="str">
+        <x:v>Park the consumed shared S21 validation, attribution, and scaling gates; prohibit rerun</x:v>
+      </x:c>
+      <x:c r="D60" s="12" t="str">
+        <x:v>The fixed candidate reached macro CER 0.938177 versus 0.751235 for the train-only prior, a -0.186942 margin. The primary, complete attribution, and scaling gates failed even though engineering and access-order gates passed.</x:v>
+      </x:c>
+      <x:c r="E60" s="12" t="str">
+        <x:v>docs/LOOP_26_SHARED_VALIDATION_RESULT.md; registries/loop26_shared_validation_result.v0.json; freeze 54bdca9</x:v>
+      </x:c>
+      <x:c r="F60" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G60" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H60" s="12" t="str">
+        <x:v>Loop 48 artifact-first failure localization under a separate exact authorization</x:v>
+      </x:c>
+      <x:c r="I60" s="12" t="str">
+        <x:v>Six validation targets consumed once; zero source-test/session-2 rows; zero post-target changes; no neural advantage, sensor-signal, transfer, real-time, device, or clinical claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37"/>
@@ -8006,7 +8020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a111b0a14b46bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da8150d97ca4fb0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9477,7 +9491,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459e4be7fc5a44f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b21942df7974c74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10190,7 +10204,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf595e5a7d46b445d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91c202ea380048ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10756,7 +10770,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2869d8bee6d45aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R485e6df436c747dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10805,7 +10819,7 @@
     </x:row>
     <x:row r="2" ht="61.5" customHeight="1">
       <x:c r="A2" s="86" t="str">
-        <x:v>Loop 25 / scientific Loop 45 mechanics passed once. Loop 26/31/33 shared preregistration is green at 881145d; exact authorization is pending and every execution flag is false.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 mechanics passed once. Loop 26/31/33 shared validation is consumed and parked: candidate macro CER 0.938177 versus prior 0.751235 after remote-green freeze 54bdca9; no rerun.</x:v>
       </x:c>
       <x:c r="B2" s="86"/>
       <x:c r="C2" s="86"/>
@@ -10825,7 +10839,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 complete once | Loop 26 decision next | Loops 26-43 execution Not Started | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 next but Not Started | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -10984,46 +10998,42 @@
         <x:v>The project has strong mechanics but no real neural advantage; this is the first gate that can justify continuing the predictive branch.</x:v>
       </x:c>
       <x:c r="G6" s="114" t="str">
-        <x:v>Build: Green shared preregistration freezes the 2,908-parameter causal candidate, 2,884-parameter linear comparator, bounded row-streaming isolation, 21 parameter-update runs, 24 target-blind inferences, 6 train-only priors, 31 prediction sets, and one post-freeze scorer.
-Research: Complete 64-assignment inference, 10-condition encoder matrix, bounded 8/16/24/32/44/55 curve, archive-access correction, and 40 refusals.
-Packets: docs/LOOP_26_SHARED_VALIDATION_PREREGISTRATION.md; docs/LOOP_26_AUTHORIZATION_PACKET.md</x:v>
+        <x:v>Built and executed: bounded row streaming, isolated 55-train/6-validation derivatives, 2,908-parameter candidate, 2,884-parameter comparator, 21 fits, 24 target-blind inferences, 6 priors, 31 frozen prediction sets, remote-green target firewall, and one score.
+Result: candidate macro CER 0.938177; prior 0.751235; margin -0.186942; primary gate failed.
+Evidence: docs/LOOP_26_SHARED_VALIDATION_RESULT.md</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
-        <x:v>Data: Existing S21 session-1 cache only after exact authorization; 55 train rows and 6 target-free validation-signal rows before scoring. Five source-test rows and session 2 stay closed. Validation targets reach one isolated scorer only after a green hash-only prediction freeze.
-Controls:
-- train-only prior and zero signal
-- validation-row, channel, and time derangements
-- timing-only and train-target-pairing fits
-- 2,884-parameter linear signal CTC
-- no language model or prompt context</x:v>
+        <x:v>Consumed S21 session-1 shared event only: 55 train signals/targets, 6 validation signals, then the same 6 validation targets after green freeze. Five source-test rows and session 2 stayed closed. No raw FIF/MAT, download, language model, RW3, stream, device, or hardware operation.</x:v>
       </x:c>
       <x:c r="I6" s="114" t="str">
-        <x:v>- macro per-sentence and corpus CER
-- all 6 paired differences and all 64 sign assignments
-- 6 strict sentence wins
-- exact-sequence accuracy, WER, blank fraction
-- every attribution control and linear comparator
-- bounded scaling deltas and per-seed slopes
-- runtime, RSS, bytes, hashes, warnings, and complete access counts</x:v>
+        <x:v>- candidate/prior macro CER 0.938177 / 0.751235
+- corpus CER 0.938547 / 0.748603
+- WER 0.966667 / 0.833333
+- 0 wins, 1 tie, 5 losses; one-sided p=1.0
+- blank fraction 0.993477
+- 21 fits; 5,040 steps; 24 inferences; 31 frozen sets
+- 184.046922 sec target-blind end to end
+- 532,955,136-byte maximum measured RSS
+- 10,148,673 generated bytes</x:v>
       </x:c>
       <x:c r="J6" s="114" t="str">
-        <x:v>Accept only if candidate-minus-prior macro CER gain is &gt;=0.05, all 6 sentences are strict wins, one-sided exact p &lt;=0.05, every required control component passes, the candidate beats the linear comparator, the scaling rules pass, and all hash/access/resource gates pass. Park without restart, retuning, source-test/session-2/S25 open, or larger model on any failure.</x:v>
+        <x:v>Failed and parked: candidate was 0.186942 worse than the train-only prior, not &gt;=0.05 better. The complete attribution and scaling conjunctions also failed. No restart, retuning, larger model, source-test/session-2/S25 open, or rerun is authorized.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops: 25, 31, 33; scientific 46
-External: exact Loop 26 shared authorization sentence; green authorization record; green implementation and synthetic isolation tests; green prediction-freeze record before target delivery</x:v>
+        <x:v>Loops 25, 31, 33 and scientific 45-47.
+Next: Loop 48 artifact-first failure localization, separately authorized.</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
-        <x:v>Green preregistration commit 881145d and CI 29282661766 establish design only. The request is prepared but unauthorized. Historical whole-array loading means physical-never-opened target wording is withdrawn; the six validation targets remain unused for fit, selection, threshold choice, or predictive scoring. No real-cache value, target delivery, model, training, prediction, or score is authorized now.</x:v>
+        <x:v>Authorized once at 1c0e52c. Implementation 91409bd and ledger correction 4015677 were remotely green. Prediction-freeze 54bdca9 was remotely green before one target delivery and score. Event consumed; no rerun or post-target tuning.</x:v>
       </x:c>
       <x:c r="M6" s="114" t="str">
-        <x:v>1 CPU thread; 1 worker; 2,908 candidate parameters; 1,200 sec parameter updates; 1,500 sec end to end; 1 GiB RSS; 128 MiB working arrays; 4 MiB checkpoints; 2 MiB predictions; 32 MiB generated artifacts; 0 download bytes</x:v>
+        <x:v>Measured: 1 thread/worker; 2,908/2,884 parameters; 184.046922 sec target-blind end to end; 0.017592 sec score; 532,955,136-byte maximum RSS; 10,148,673 generated bytes. All 20 min / 1 GiB / 32 MiB caps passed.</x:v>
       </x:c>
       <x:c r="N6" s="141" t="str">
-        <x:v>green_hash_bound_shared_validation_preregistration; authorization_pending; no_protected_execution; upstream_cache_noncausal; model_only_causal</x:v>
+        <x:v>consumed_same_person_same_session_validation; primary_gate_failed; no_rerun; upstream_cache_noncausal; source_test_session2_closed</x:v>
       </x:c>
       <x:c r="O6" s="222" t="str">
-        <x:v>Preregistered; Authorization Pending</x:v>
+        <x:v>Parked; Registered Gate Failed</x:v>
       </x:c>
       <x:c r="P6" s="150" t="str">
         <x:v>https://www.nature.com/articles/s41593-026-02303-2.pdf
@@ -11339,40 +11349,37 @@
         <x:v>A fluent prediction is not an attribution result. The consumed S21 MEG and S7 EEG paths both lose to no-signal priors, so any future improvement must survive signal-free, corrupted-signal, timing, context, and language controls before it can be credited to the sensor input.</x:v>
       </x:c>
       <x:c r="G11" s="114" t="str">
-        <x:v>Build: The 10-condition encoder matrix is frozen inside the green Loop 26 shared contract.
-Research: Exact six-row intersection-union inference, target-blind transforms, and the Loop 35 ceiling remain binding.
-Separate: the 5-condition LLM/Neuro Token extension is not preregistered.</x:v>
+        <x:v>Executed inside the consumed shared event: 10-condition encoder matrix with exact six-item comparisons. The 5-condition LLM/Neuro Token extension remained closed.</x:v>
       </x:c>
       <x:c r="H11" s="114" t="str">
-        <x:v>Data: Same authorized Loop 26 train/validation membership only; all 31 prediction sets freeze before one target delivery. Source test, session 2, S7, S20, and S25 stay closed.
-Controls: full signal, prior, zero signal, row/channel/time derangement, timing-only, train-pairing derangement, and linear comparator. No context-only condition is available in this event.</x:v>
+        <x:v>Same consumed Loop 26 train/validation membership only. No source test, session 2, S7, S20, S25, LLM, Neuro Token, stream, device, or hardware access.</x:v>
       </x:c>
       <x:c r="I11" s="114" t="str">
-        <x:v>- macro sentence control-minus-full CER
-- exact one-sided paired components and intersection-union decision
-- per-item edits and wins/ties/losses
-- exact sequences and WER where valid
-- per-condition hashes, access, runtime, RSS, bytes, warnings, and unavailable fields</x:v>
+        <x:v>- zero-signal: 6/6 wins, p=0.015625
+- timing-only: 6/6 wins, p=0.015625
+- prior: 0/1/5, p=1.0
+- row derangement: p=0.5
+- channel derangement: p=0.71875
+- time displacement: p=0.25
+- target derangement: p=0.0625</x:v>
       </x:c>
       <x:c r="J11" s="114" t="str">
-        <x:v>Accept sensor-signal dependence only when every registered encoder condition and exact six-item component passes with the 0.05 primary margin, six strict primary wins, target-blind freeze order, complete ledgers, and resource gates. Brain-specific origin remains unavailable before Loop 35. A missing or tied control parks the claim.</x:v>
+        <x:v>Failed and parked: the complete registered intersection-union conjunction did not pass. Individual zero/timing wins are diagnostic only and do not establish sensor-signal dependence or brain-specific origin.</x:v>
       </x:c>
       <x:c r="K11" s="114" t="str">
-        <x:v>Loops: 26, 33
-External: exact shared authorization; Loop 35 for brain-specific claim
-LLM/Neuro Token extension remains a separate future gate</x:v>
+        <x:v>Shared consumed Loop 26 event; Loop 35 remains required for any future brain-specific claim.</x:v>
       </x:c>
       <x:c r="L11" s="114" t="str">
-        <x:v>Encoder matrix is bound to green shared contract 881145d, but the exact authorization sentence is absent. No cache, target, checkpoint, model, training, validation, LLM, Neuro Token, S20, S25, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>The encoder matrix scored once inside the authorized shared event. Targets are consumed; no matrix rerun, post-target target open, LLM/Neuro Token extension, or new protected operation is authorized.</x:v>
       </x:c>
       <x:c r="M11" s="114" t="str">
-        <x:v>Shared cap: 1 thread/worker, 2,908 parameters, 1,200 sec parameter updates, 1,500 sec end to end, 1 GiB RSS, 32 MiB artifacts, zero downloads</x:v>
+        <x:v>Shared measured cap: 1 thread/worker; included in 184.046922 sec and 10,148,673 generated bytes; all caps passed.</x:v>
       </x:c>
       <x:c r="N11" s="141" t="str">
-        <x:v>encoder_matrix_preregistered_with_loop26; language_extension_unpreregistered; no_execution; sensor_signal_ceiling; loop35_required_for_brain_specific</x:v>
+        <x:v>consumed_encoder_matrix; complete_conjunction_failed; no_sensor_signal_claim; language_extension_closed</x:v>
       </x:c>
       <x:c r="O11" s="222" t="str">
-        <x:v>Shared Encoder Preregistration; Authorization Pending</x:v>
+        <x:v>Parked; Shared Attribution Gate Failed</x:v>
       </x:c>
       <x:c r="P11" s="150" t="str">
         <x:v>https://www.nature.com/articles/s41593-026-02303-2
@@ -11476,38 +11483,37 @@
         <x:v>A prospective bounded curve can guide whether another metadata-only acquisition packet is worth preparing without guessing, reopening consumed evidence, or transferring Brain2Qwerty v2's 90-hour scaling exponent.</x:v>
       </x:c>
       <x:c r="G13" s="114" t="str">
-        <x:v>Build: Green shared contract freezes strictly nested 8/16/24/32/44/55 unique-sentence prefixes, 3 fixed seeds, 18 candidate fits, 6 matched priors, one fixed 2,908-parameter model, and complete prediction/access/resource hashes.
-Research: Unique-versus-physical-repetition firewall and bounded descriptive outcome rules remain binding.</x:v>
+        <x:v>Executed inside the consumed shared event: nested 8/16/24/32/44/55 unique-sentence prefixes, 3 seeds, 18 candidate fits, 6 matched priors, and one shared target open.</x:v>
       </x:c>
       <x:c r="H13" s="114" t="str">
-        <x:v>Data: Same authorized 55 train and 6 validation rows as Loop 26; all prefix and control predictions freeze before the one shared target delivery. Source test, session 2, S7, S20, S25, new data, and physical repetitions stay closed. Prefix order is target-blind and the 55-row endpoint equals all train rows.</x:v>
+        <x:v>Same 55 train and 6 validation rows as Loop 26. Source test, session 2, new data, and physical repetitions stayed closed.</x:v>
       </x:c>
       <x:c r="I13" s="114" t="str">
-        <x:v>- macro sentence CER by item, seed, prefix, and matched prior
-- median-seed curve versus log2 unique sentences
-- smallest-band to upper-band gain
-- size-55 gain over matched prior
-- per-seed ordinary least-squares slope
-- unique rows, valid seconds, runtime, RSS, bytes, access, warnings, and hashes</x:v>
+        <x:v>- median macro CER 8: 1.514517
+- 16: 0.944502; 24: 0.928779
+- 32: 0.982745; 44: 0.942438
+- 55: 0.938177
+- all 3 seed slopes negative
+- 8-to-55 gain 0.289202
+- 55-vs-prior gain -0.186942</x:v>
       </x:c>
       <x:c r="J13" s="114" t="str">
-        <x:v>Require &gt;=0.05 smallest-band-to-upper-band gain, &gt;=0.05 size-55-over-prior gain, a negative slope for every seed, and the Loop 31 attribution gate before sensor wording. Park on any target-informed prefix, missing fit/prior, access/hash/cap failure, or post-target restart. No universal law or acquisition permission is available.</x:v>
+        <x:v>Failed and parked: descriptive improvement and negative slopes passed subrules, but the 55-row candidate remained 0.186942 worse than its matched prior. No scaling law, saturation, repetition, acquisition, or larger-model claim.</x:v>
       </x:c>
       <x:c r="K13" s="114" t="str">
-        <x:v>Loops: 26, 31
-External: exact shared authorization and the same green prediction-freeze-before-target sequence</x:v>
+        <x:v>Shared consumed Loops 26 and 31 event. Loop 31 conjunction also failed.</x:v>
       </x:c>
       <x:c r="L13" s="114" t="str">
-        <x:v>The bounded curve is frozen inside green shared contract 881145d, but exact authorization is absent. No protected cache/signal/target read, model/control run, training, prediction, score, physical-repetition study, acquisition, S20/S25, stream, device, or hardware operation is authorized.</x:v>
+        <x:v>The curve trained and scored once under authorization 1c0e52c and freeze 54bdca9. No rerun, post-target restart, acquisition, or protected cohort substitution is authorized.</x:v>
       </x:c>
       <x:c r="M13" s="114" t="str">
-        <x:v>Shared cap: 1 thread/worker, 2,908 parameters, 18 candidate fits, 1,200 sec parameter updates, 1,500 sec end to end, 1 GiB RSS, 32 MiB artifacts, zero downloads</x:v>
+        <x:v>Shared measured cap: 1 thread/worker; 18 candidate fits; included in 184.046922 sec, 532,955,136-byte maximum RSS, and 10,148,673 generated bytes.</x:v>
       </x:c>
       <x:c r="N13" s="141" t="str">
-        <x:v>bounded_scaling_preregistered_with_loop26; prefixes=8|16|24|32|44|55; no_protected_execution; no_repetition_lane; no_acquisition_permission</x:v>
+        <x:v>consumed_bounded_curve; size55_failed_matched_prior; no_scaling_law; no_acquisition_claim</x:v>
       </x:c>
       <x:c r="O13" s="222" t="str">
-        <x:v>Shared Preregistration; Authorization Pending</x:v>
+        <x:v>Parked; Shared Scaling Gate Failed</x:v>
       </x:c>
       <x:c r="P13" s="150" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -12261,7 +12267,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae871baa0c5c4969"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e3d1b08ee8046ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdfa077f71e1d4510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R392dcb032e1a48a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R9569287305914e6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rce4a8bcb3e264cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R9d06ddceb6504a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R63833487345c4c5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R54e817ab05ba4345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R9b8d8946c4bc4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="Ra34d04a419a34a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R32a9e1a114fc4982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rff9a371e1ac843a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R89cade4494d742aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R127c02136fa945d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Raafea30530154f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R4a65ab58f94b4c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd9bbabc0aec84b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R700024d1ccdf4111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R643f9ea7b89c4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R69cb8c4d65d94c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R0aa633017b9d4d35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc652ffb8dff04c42"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R37ae510e71c3424a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1664,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 48 failure localization next</x:v>
+        <x:v>Loop 48 authorization decision next</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1681,12 +1681,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="96" customHeight="1">
+    <x:row r="10" ht="154" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 25 / scientific Loop 45 mechanics passed once with no rerun. Loop 26/31/33 and scientific Loops 46/47 were preregistered at 881145d, authorized at 1c0e52c, and consumed once after remote-green prediction freeze 54bdca9. Candidate macro CER 0.938177 was worse than prior 0.751235 by 0.186942; primary, attribution, and scaling gates failed. Source test and session 2 stayed closed. No rerun is authorized; Loop 48 is Not Started and separately gated.</x:v>
+        <x:v>Loop 25 / scientific Loop 45 mechanics passed once with no rerun. Loop 26/31/33 and scientific Loops 46/47 were consumed once and parked after the candidate lost to the no-signal prior. Loop 48 now has a hash-bound artifact-only failure-localization contract: F5 output-distribution instability is the leading phenotype, not a proven root cause. Every execution flag remains false; protected data, targets, models, training, S25, streams, devices, and hardware stay closed.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ed0949d94264fb1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra623675d7f994614"/>
 </x:worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked after the registered S21 gate failed; Loop 48 artifact-first failure localization is next but separately gated.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 now freezes an artifact-only failure-localization tree while execution and protected evidence remain closed.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1891,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loops 46/47 parked after one consumed negative result | Loop 48 Not Started | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46/47 parked after one consumed negative result | Loop 48 preregistered; authorization pending | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2157,50 +2157,43 @@
         <x:v>diagnostic boundary, not decoding performance</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>A preregistered artifact-only discrepancy tree with mutually exclusive failure classes and no post-hoc model search.</x:v>
+        <x:v>Prepared a hash-bound post-outcome artifact-only discrepancy tree with 8 ordered classes, 17 unavailable root-cause fields, 30 refusals, and one bounded future Stage A. F5 output-distribution instability is the leading observed phenotype, not a proven cause.</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Data: Closed Loop 46/47 aggregate reports and permitted train-only diagnostics; no new target opening or consumed cohort access.
-Controls:
-- target identity audit
-- train-only learning curve
-- signal-quality summaries
-- prediction entropy
-- blank dominance
-- prior-strength decomposition
-- no target-conditioned feature search</x:v>
+        <x:v>Exactly four committed JSON artifacts totaling 155,545 bytes: consumed Loop 26 result, prediction freeze, shared contract, and Loop 25 mechanics result. No cache, derivative, checkpoint, private prediction, target, raw FIF/MAT, source-test, session 2, S7, S20, or S25 read.</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>- failure class
-- evidence completeness
-- unavailable fields
-- diagnostic runtime
-- new protected reads
-- recommended proceed park or kill branch</x:v>
+        <x:v>- primary blank fraction 0.993477
+- candidate/prior macro CER 0.938177 / 0.751235
+- all-condition blank range 0.997146
+- 6/6 prefix groups have &gt;=0.25 seed range
+- 3/3 size-55 seeds worse than prior
+- 17 unavailable root-cause fields
+- 30 refusals</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Accept: Exactly one primary failure class or an explicit unresolved set is recorded without using validation targets to select a new architecture.
-Kill/Park: If diagnosis requires target-conditioned search or a larger model, park and design a fresh development cohort instead.</x:v>
+        <x:v>Current gate: remotely qualify the exact artifact-only contract, then require a separate authorization for one Stage A. Park if diagnosis needs target-conditioned search, a model run, protected input, threshold change, or architecture escalation.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
-        <x:v>Loops: 46, 47</x:v>
+        <x:v>Loops 46/47 consumed and parked. Future train-only diagnostics require a separate preregistration; fresh-person work remains separate.</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Artifact-only planning may use committed aggregate reports. Any train-array diagnostic, cache member, target, model run, or implementation requires its own exact authorization. Source test and session 2 remain closed.</x:v>
+        <x:v>All authorization fields are false. No implementation, generated diagnostic report, protected read, target read, model inference, training, scoring, new participant, download, S25, language model, RW3, stream, device, or hardware operation exists.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>artifact-only by default; one thread; &lt;=5 CPU minutes; &lt;=8 MiB generated</x:v>
+        <x:v>Current planning: 1 thread, 1 worker, 42,044 generated bytes, zero protected/model/training/network operations. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output, 4 committed JSON inputs only.</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>planned_not_authorized; next_numbered_work_order</x:v>
+        <x:v>post_outcome_artifact_only_preregistration; F5_phenotype_not_root_cause; no_execution; no_scientific_claim_upgrade</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Preregistered; Authorization Pending</x:v>
       </x:c>
       <x:c r="P8" s="114" t="str">
-        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
-https://arxiv.org/abs/1606.05201
-https://www.jmlr.org/papers/v11/ojala10a.html</x:v>
+        <x:v>https://ai.meta.com/research/publications/accurate-decoding-of-natural-sentences-from-non-invasive-brain-recordings/
+https://doi.org/10.1038/s41593-026-02303-2
+https://arxiv.org/abs/2105.14849
+https://distill.pub/2017/ctc/</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="174" customHeight="1">
@@ -3293,7 +3286,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3497e8e9a89f4270"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R046264d0cdf84289"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4708,7 +4701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a64f65b22c4a83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a63fbd517314a07"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6461,15 +6454,33 @@
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="37"/>
-      <x:c r="B61" s="12"/>
-      <x:c r="C61" s="12"/>
-      <x:c r="D61" s="12"/>
-      <x:c r="E61" s="12"/>
-      <x:c r="F61" s="12"/>
-      <x:c r="G61" s="12"/>
-      <x:c r="H61" s="12"/>
-      <x:c r="I61" s="12"/>
+      <x:c r="A61" s="37" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B61" s="12" t="str">
+        <x:v>48-R1</x:v>
+      </x:c>
+      <x:c r="C61" s="12" t="str">
+        <x:v>Preregister artifact-only failure localization; keep execution and protected evidence closed</x:v>
+      </x:c>
+      <x:c r="D61" s="12" t="str">
+        <x:v>The primary checkpoint emitted 99.3477% blank, every fixed-prefix group showed at least 0.25 three-seed blank-fraction dispersion, and all size-55 seeds lost to the prior. Register F5 as an output-instability phenotype, not a causal explanation.</x:v>
+      </x:c>
+      <x:c r="E61" s="12" t="str">
+        <x:v>docs/LOOP_48_PRIMARY_SOURCE_RESEARCH.md; registries/loop48_failure_localization_contract.v0.json; Decision 0077</x:v>
+      </x:c>
+      <x:c r="F61" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G61" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H61" s="12" t="str">
+        <x:v>Commit, push, and remotely qualify the exact contract; then make a separate Stage A authorization decision or hold</x:v>
+      </x:c>
+      <x:c r="I61" s="12" t="str">
+        <x:v>Post-outcome aggregate diagnosis only. No implementation, cache/target/checkpoint/private-prediction read, model, training, scoring, S25, stream, device, hardware, or scientific claim upgrade.</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37"/>
@@ -8020,7 +8031,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da8150d97ca4fb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb06349a05db4432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9491,7 +9502,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b21942df7974c74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806503993b604d8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10204,7 +10215,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91c202ea380048ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra044e48278d34031"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10770,7 +10781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R485e6df436c747dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7656d1bf155d4b12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10839,7 +10850,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 next but Not Started | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 artifact-only contract preregistered; authorization pending | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -12267,7 +12278,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e3d1b08ee8046ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701873903d474a13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rff9a371e1ac843a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R89cade4494d742aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R127c02136fa945d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Raafea30530154f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R4a65ab58f94b4c20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rd9bbabc0aec84b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R700024d1ccdf4111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R643f9ea7b89c4130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R69cb8c4d65d94c10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R0aa633017b9d4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re24812e7e34d498b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rab1d8239a2694ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R9e1af908775b48fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re3c833f788044b94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Raa2e784a2c6d4d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R869cbff0f7544cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Raa3a24f1d5144366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc7a6bb7551a74560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R3a5e3f28dc5f413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Re60b9dd9c0f449ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R37ae510e71c3424a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50b469a4f588491b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1664,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 48 authorization decision next</x:v>
+        <x:v>Loop 48 exact Stage A authorization or hold</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1686,7 +1686,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 25 / scientific Loop 45 mechanics passed once with no rerun. Loop 26/31/33 and scientific Loops 46/47 were consumed once and parked after the candidate lost to the no-signal prior. Loop 48 now has a hash-bound artifact-only failure-localization contract: F5 output-distribution instability is the leading phenotype, not a proven root cause. Every execution flag remains false; protected data, targets, models, training, S25, streams, devices, and hardware stay closed.</x:v>
+        <x:v>Loop 26/31/33 and scientific Loops 46/47 are consumed and parked after the candidate lost to the no-signal prior. Loop 48 contract commit 83309bf is remotely green; its exact four-JSON Stage A authorization request is prepared but every execution field remains false. A separate H1-H5 train-only portfolio improves the hypotheses using shared evidence and sequential one-thread compute, but Stage B is design-only and cannot inherit Stage A permission.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra623675d7f994614"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16bc5409a30e4ad0"/>
 </x:worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 now freezes an artifact-only failure-localization tree while execution and protected evidence remain closed.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 has one exact artifact-only Stage A request plus a separate design-only H1-H5 train-only portfolio.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1891,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loops 46/47 parked after one consumed negative result | Loop 48 preregistered; authorization pending | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46/47 parked | Loop 48 Stage A authorization pending; Stage B design-only | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2157,43 +2157,38 @@
         <x:v>diagnostic boundary, not decoding performance</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>Prepared a hash-bound post-outcome artifact-only discrepancy tree with 8 ordered classes, 17 unavailable root-cause fields, 30 refusals, and one bounded future Stage A. F5 output-distribution instability is the leading observed phenotype, not a proven cause.</x:v>
+        <x:v>Prepared the green hash-bound artifact-only contract, its exact four-JSON Stage A request, and a separate design-only H1-H5 train-only hypothesis portfolio. F5 remains a phenotype, not a root cause; Stage B allows multiple causes to coexist.</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Exactly four committed JSON artifacts totaling 155,545 bytes: consumed Loop 26 result, prediction freeze, shared contract, and Loop 25 mechanics result. No cache, derivative, checkpoint, private prediction, target, raw FIF/MAT, source-test, session 2, S7, S20, or S25 read.</x:v>
+        <x:v>Stage A: only four committed JSON artifacts totaling 155,545 bytes. Stage B design: future disjoint fit/check partitions only inside 55 source-train rows. No validation target, source test, session 2, S7, S20, or S25 contribution.</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>- primary blank fraction 0.993477
-- candidate/prior macro CER 0.938177 / 0.751235
-- all-condition blank range 0.997146
-- 6/6 prefix groups have &gt;=0.25 seed range
-- 3/3 size-55 seeds worse than prior
-- 17 unavailable root-cause fields
-- 30 refusals</x:v>
+        <x:v>Stage A evidence: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior. Stage B hypotheses: H1 CTC fit; H2 signal quality; H3 timing/preprocessing; H4 separability; H5 prior dominance.</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Current gate: remotely qualify the exact artifact-only contract, then require a separate authorization for one Stage A. Park if diagnosis needs target-conditioned search, a model run, protected input, threshold change, or architecture escalation.</x:v>
+        <x:v>Current gate: exact Stage A authorization sentence or hold. Stage B remains unregistered until Stage A closes and a separately authorized static prototype measures overhead; do not force one root-cause winner or use validation targets.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
-        <x:v>Loops 46/47 consumed and parked. Future train-only diagnostics require a separate preregistration; fresh-person work remains separate.</x:v>
+        <x:v>Loops 46/47 consumed and parked. Stage A request is independent. Stage B cannot inherit Stage A authorization and requires frozen train-only split, thresholds, inventory, and caps.</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>All authorization fields are false. No implementation, generated diagnostic report, protected read, target read, model inference, training, scoring, new participant, download, S25, language model, RW3, stream, device, or hardware operation exists.</x:v>
+        <x:v>Every authorization field is false. No analyzer, Stage A run, fixture, Stage B split, train/cache/signal/target read, model, training, score, S25, stream, device, hardware, claim upgrade, or rerun exists.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>Current planning: 1 thread, 1 worker, 42,044 generated bytes, zero protected/model/training/network operations. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output, 4 committed JSON inputs only.</x:v>
+        <x:v>Current artifacts: Stage A request 23,788 bytes; H1-H5 portfolio 20,377 bytes. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output, 1 thread/worker. Stage B runtime/RSS/output/model caps are intentionally unfrozen.</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>post_outcome_artifact_only_preregistration; F5_phenotype_not_root_cause; no_execution; no_scientific_claim_upgrade</x:v>
+        <x:v>stage_a_request_prepared_unauthorized; stage_b_parallel_hypotheses_design_only; sequential_compute; no_scientific_claim_upgrade</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
         <x:v>Preregistered; Authorization Pending</x:v>
       </x:c>
       <x:c r="P8" s="114" t="str">
-        <x:v>https://ai.meta.com/research/publications/accurate-decoding-of-natural-sentences-from-non-invasive-brain-recordings/
-https://doi.org/10.1038/s41593-026-02303-2
-https://arxiv.org/abs/2105.14849
-https://distill.pub/2017/ctc/</x:v>
+        <x:v>https://arxiv.org/abs/2105.14849
+https://www.nature.com/articles/s41593-026-02303-2
+https://www.nature.com/articles/s41467-025-65499-0
+https://www.nature.com/articles/s42003-025-08464-3
+https://pubmed.ncbi.nlm.nih.gov/30127712/</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="174" customHeight="1">
@@ -3286,7 +3281,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R046264d0cdf84289"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd872a93ec36420b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4701,7 +4696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a63fbd517314a07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf226df55c0204a9c"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6483,26 +6478,62 @@
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="37"/>
-      <x:c r="B62" s="12"/>
-      <x:c r="C62" s="12"/>
-      <x:c r="D62" s="12"/>
-      <x:c r="E62" s="12"/>
-      <x:c r="F62" s="12"/>
-      <x:c r="G62" s="12"/>
-      <x:c r="H62" s="12"/>
-      <x:c r="I62" s="12"/>
+      <x:c r="A62" s="37" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="str">
+        <x:v>48-R2</x:v>
+      </x:c>
+      <x:c r="C62" s="12" t="str">
+        <x:v>Prepare one exact four-JSON Stage A request; keep every authorization false</x:v>
+      </x:c>
+      <x:c r="D62" s="12" t="str">
+        <x:v>Bind green contract commit 83309bf and both CI runs. A future authorized Stage A may verify four committed JSON inputs totaling 155,545 bytes, reproduce frozen aggregate arithmetic, apply the eight-class tree, and write one target-free report.</x:v>
+      </x:c>
+      <x:c r="E62" s="12" t="str">
+        <x:v>docs/LOOP_48_AUTHORIZATION_PACKET.md; registries/loop48_authorization_request.v0.json; Decision 0078</x:v>
+      </x:c>
+      <x:c r="F62" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G62" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H62" s="12" t="str">
+        <x:v>Exact Stage A authorization sentence or hold</x:v>
+      </x:c>
+      <x:c r="I62" s="12" t="str">
+        <x:v>No implementation or execution. One thread/worker, 30 sec, 256 MiB RSS, 1 MiB output; zero protected reads, models, training, targets, S25, streams, devices, hardware, claim upgrades, or reruns.</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="37"/>
-      <x:c r="B63" s="12"/>
-      <x:c r="C63" s="12"/>
-      <x:c r="D63" s="12"/>
-      <x:c r="E63" s="12"/>
-      <x:c r="F63" s="12"/>
-      <x:c r="G63" s="12"/>
-      <x:c r="H63" s="12"/>
-      <x:c r="I63" s="12"/>
+      <x:c r="A63" s="37" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B63" s="12" t="str">
+        <x:v>48-R3</x:v>
+      </x:c>
+      <x:c r="C63" s="12" t="str">
+        <x:v>Evaluate five coexisting failure hypotheses from one shared train-only evidence bundle</x:v>
+      </x:c>
+      <x:c r="D63" s="12" t="str">
+        <x:v>Compare CTC fit, sensor quality, timing/preprocessing, representation separability, and prior dominance in parallel scientifically while numerical work remains sequential and one-threaded.</x:v>
+      </x:c>
+      <x:c r="E63" s="12" t="str">
+        <x:v>docs/LOOP_48_TRAIN_ONLY_HYPOTHESIS_PORTFOLIO.md; registries/loop48_hypothesis_portfolio.v0.json; Decision 0079</x:v>
+      </x:c>
+      <x:c r="F63" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G63" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H63" s="12" t="str">
+        <x:v>Stage A decision first; Stage B requires a later exact preregistration and authorization</x:v>
+      </x:c>
+      <x:c r="I63" s="12" t="str">
+        <x:v>Design research only. No split, threshold, seed, model inventory, cap, fixture, train-array read, model, training, score, or protected operation is authorized.</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37"/>
@@ -8031,7 +8062,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb06349a05db4432b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8990df5cec694938"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9502,7 +9533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806503993b604d8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f5a6e5c6ea341a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10215,7 +10246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra044e48278d34031"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30fccff3da224435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10781,7 +10812,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7656d1bf155d4b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1c649bbc6dc45f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10850,7 +10881,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 artifact-only contract preregistered; authorization pending | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 Stage A exact request prepared; H1-H5 Stage B design-only | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -12278,7 +12309,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701873903d474a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199c5ad139ca4280"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re24812e7e34d498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Rab1d8239a2694ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R9e1af908775b48fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Re3c833f788044b94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Raa2e784a2c6d4d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R869cbff0f7544cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Raa3a24f1d5144366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rc7a6bb7551a74560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R3a5e3f28dc5f413a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Re60b9dd9c0f449ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reef93c7c93a24b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R47a1b22996964aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R2ec8b1862ee64b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rfe697187078545d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra0b83dd76c524760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R631e036254d84ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R995229b9371b4b47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rba21fd009fba4599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9bdcf60d77794a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rd71695d67ba04828"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50b469a4f588491b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f85dd07d41042b3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1681,12 +1681,12 @@
       <x:c r="G9" s="29" t="str"/>
       <x:c r="H9" s="29" t="str"/>
     </x:row>
-    <x:row r="10" ht="154" customHeight="1">
+    <x:row r="10" ht="158" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 26/31/33 and scientific Loops 46/47 are consumed and parked after the candidate lost to the no-signal prior. Loop 48 contract commit 83309bf is remotely green; its exact four-JSON Stage A authorization request is prepared but every execution field remains false. A separate H1-H5 train-only portfolio improves the hypotheses using shared evidence and sequential one-thread compute, but Stage B is design-only and cannot inherit Stage A permission.</x:v>
+        <x:v>Loop 26/31/33 and scientific Loops 46/47 are consumed and parked after the candidate lost to the no-signal prior. Loop 48 Stage A remains an exact authorization-or-hold decision; every execution field is false. Additive H1-H6 research separates the fixed CTC recipe, signal quality, timing, representation, prior, and data regime, while T1 routes shortcut risk to Loop 35. Commit 33a14d8 passed push CI 29436731383 and PR CI 29436735374. Stage B is design-only, sequential, one-threaded, and cannot inherit Stage A permission or establish brain-specific origin.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16bc5409a30e4ad0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11ff03dab024171"/>
 </x:worksheet>
 </file>
 
@@ -2157,38 +2157,38 @@
         <x:v>diagnostic boundary, not decoding performance</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>Prepared the green hash-bound artifact-only contract, its exact four-JSON Stage A request, and a separate design-only H1-H5 train-only hypothesis portfolio. F5 remains a phenotype, not a root cause; Stage B allows multiple causes to coexist.</x:v>
+        <x:v>Prepared the green hash-bound artifact-only contract and exact four-JSON Stage A request. The immutable H1-H5 portfolio now has an additive H1-H6 discrimination map: H1 is the fixed recipe, H6 is data quantity/diversity, and T1 is the orthogonal shortcut threat. F5 remains a phenotype, not a root cause.</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Stage A: only four committed JSON artifacts totaling 155,545 bytes. Stage B design: future disjoint fit/check partitions only inside 55 source-train rows. No validation target, source test, session 2, S7, S20, or S25 contribution.</x:v>
+        <x:v>Stage A: only four committed JSON artifacts totaling 155,545 bytes. Stage B design: a future grouped, disjoint fit/check partition only inside 55 source-train rows. No validation target, source test, session 2, S7, S20, or S25 contribution. Current pass consulted five public sources and performed zero protected/model operations.</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>Stage A evidence: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior. Stage B hypotheses: H1 CTC fit; H2 signal quality; H3 timing/preprocessing; H4 separability; H5 prior dominance.</x:v>
+        <x:v>Stage A evidence: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior. Stage B: 6 hypotheses, 5 evidence levels, 6 sequential stages, 1 shortcut threat, and 15 false authorizations. E3 requires practical-margin plus paired-uncertainty gates.</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Current gate: exact Stage A authorization sentence or hold. Stage B remains unregistered until Stage A closes and a separately authorized static prototype measures overhead; do not force one root-cause winner or use validation targets.</x:v>
+        <x:v>Current gate: exact Stage A authorization sentence or hold. Future Stage B can reach at most E3 only after separate preregistration and authorization; its support vector must retain conflicts. Do not force one winner, create predictions after check labels, or reuse consumed validation.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
-        <x:v>Loops 46/47 consumed and parked. Stage A request is independent. Stage B cannot inherit Stage A authorization and requires frozen train-only split, thresholds, inventory, and caps.</x:v>
+        <x:v>Loops 46/47 are consumed and parked. Stage A is independent. Stage B cannot inherit Stage A authorization. E4 and any brain-origin review route to Loop 35. Exact Stage B split, thresholds, inventory, and resource caps remain unfrozen.</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Every authorization field is false. No analyzer, Stage A run, fixture, Stage B split, train/cache/signal/target read, model, training, score, S25, stream, device, hardware, claim upgrade, or rerun exists.</x:v>
+        <x:v>Every authorization field is false. No analyzer, Stage A run, fixture, Stage B split, train/cache/signal/target read, model, training, prediction, checkpoint, scoring, S25, stream, device, hardware, claim upgrade, or rerun exists.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>Current artifacts: Stage A request 23,788 bytes; H1-H5 portfolio 20,377 bytes. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output, 1 thread/worker. Stage B runtime/RSS/output/model caps are intentionally unfrozen.</x:v>
+        <x:v>Current discrimination document plus registry: 24,268 bytes; five public sources; one thread/worker; zero protected/model operations. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output. Stage B runtime/RSS/output/model caps are intentionally unfrozen.</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>stage_a_request_prepared_unauthorized; stage_b_parallel_hypotheses_design_only; sequential_compute; no_scientific_claim_upgrade</x:v>
+        <x:v>stage_a_request_prepared_unauthorized; stage_b_h1_h6_design_only; e3_margin_uncertainty_gate; t1_routes_loop35; sequential_compute; no_scientific_claim_upgrade</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
         <x:v>Preregistered; Authorization Pending</x:v>
       </x:c>
       <x:c r="P8" s="114" t="str">
-        <x:v>https://arxiv.org/abs/2105.14849
+        <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
 https://www.nature.com/articles/s41593-026-02303-2
+https://arxiv.org/abs/2105.14849
 https://www.nature.com/articles/s41467-025-65499-0
-https://www.nature.com/articles/s42003-025-08464-3
-https://pubmed.ncbi.nlm.nih.gov/30127712/</x:v>
+https://arxiv.org/abs/2410.14453</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="174" customHeight="1">
@@ -3281,7 +3281,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd872a93ec36420b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb09829ec07474c01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4696,7 +4696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf226df55c0204a9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199044988de046af"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6535,16 +6535,34 @@
         <x:v>Design research only. No split, threshold, seed, model inventory, cap, fixture, train-array read, model, training, score, or protected operation is authorized.</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="37"/>
-      <x:c r="B64" s="12"/>
-      <x:c r="C64" s="12"/>
-      <x:c r="D64" s="12"/>
-      <x:c r="E64" s="12"/>
-      <x:c r="F64" s="12"/>
-      <x:c r="G64" s="12"/>
-      <x:c r="H64" s="12"/>
-      <x:c r="I64" s="12"/>
+    <x:row r="64" ht="152" customHeight="1">
+      <x:c r="A64" s="37" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B64" s="12" t="str">
+        <x:v>48-R4</x:v>
+      </x:c>
+      <x:c r="C64" s="12" t="str">
+        <x:v>Separate fixed-recipe, data-regime, and shortcut hypotheses; keep execution closed</x:v>
+      </x:c>
+      <x:c r="D64" s="12" t="str">
+        <x:v>Preserve the immutable H1-H5 portfolio. Narrow H1 to the exact fixed tiny CTC recipe, add H6 for data quantity and unique-sentence diversity, and track T1 peripheral/task-locked shortcuts separately. E3 requires a registered practical margin and paired uncertainty against every prior and corruption.</x:v>
+      </x:c>
+      <x:c r="E64" s="12" t="str">
+        <x:v>docs/LOOP_48_HYPOTHESIS_DISCRIMINATION_RESEARCH.md; registries/loop48_hypothesis_discrimination.v0.json; Decision 0080; commit 33a14d8; CI 29436731383/29436735374</x:v>
+      </x:c>
+      <x:c r="F64" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G64" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H64" s="12" t="str">
+        <x:v>Exact Stage A authorization sentence or hold; Stage B still needs separate preregistration and authorization</x:v>
+      </x:c>
+      <x:c r="I64" s="12" t="str">
+        <x:v>Design research only. Five public sources; one thread/worker; 24,268 document/registry bytes; 15 false authorizations; zero protected reads, models, training, predictions, or scoring. E3 is not brain origin; Loop 35 is required.</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37"/>
@@ -8062,7 +8080,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8990df5cec694938"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4131f11ce9f4dbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9533,7 +9551,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f5a6e5c6ea341a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd4c863c66d4f88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10246,7 +10264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30fccff3da224435"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R988952f36d7348e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10812,7 +10830,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1c649bbc6dc45f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be39bf2be8e420f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10881,7 +10899,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 Stage A exact request prepared; H1-H5 Stage B design-only | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 Stage A exact request prepared; additive H1-H6/T1 Stage B design-only | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -12309,7 +12327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199c5ad139ca4280"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc38118f9bd4aa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reef93c7c93a24b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R47a1b22996964aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R2ec8b1862ee64b8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="Rfe697187078545d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Ra0b83dd76c524760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R631e036254d84ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R995229b9371b4b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rba21fd009fba4599"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R9bdcf60d77794a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rd71695d67ba04828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R25a856a80ec948dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Radfb28a0ce434b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R3ea0ae7e2d4f4862"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R384221d0d6ae46ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R909fde647cd1435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rba7702250ef449a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R99302320762e4768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rdaf8ff3655084974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R1edc88c41ff145b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rba050d0bca4242fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f85dd07d41042b3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20d480a0ce6e4116"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1310,7 +1310,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1664,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 48 exact Stage A authorization or hold</x:v>
+        <x:v>Loop 48 Stage A complete; descriptive F5; no rerun</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1686,7 +1686,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loop 26/31/33 and scientific Loops 46/47 are consumed and parked after the candidate lost to the no-signal prior. Loop 48 Stage A remains an exact authorization-or-hold decision; every execution field is false. Additive H1-H6 research separates the fixed CTC recipe, signal quality, timing, representation, prior, and data regime, while T1 routes shortcut risk to Loop 35. Commit 33a14d8 passed push CI 29436731383 and PR CI 29436735374. Stage B is design-only, sequential, one-threaded, and cannot inherit Stage A permission or establish brain-specific origin.</x:v>
+        <x:v>Loops 26/31/33 and scientific Loops 46/47 remain consumed and parked after the candidate lost to the no-signal prior. Loop 48 completed one four-JSON artifact-only Stage A: descriptive F5 output-distribution instability, 0.016568875 sec internal runtime, 23,429,120-byte peak RSS, and 10,643 output bytes. This is not a proven root cause and no rerun is authorized. Additive H1-H6/T1 Stage B research remains design-only, sequential, one-threaded, and unauthorized.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11ff03dab024171"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35d675c5576945b4"/>
 </x:worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 has one exact artifact-only Stage A request plus a separate design-only H1-H5 train-only portfolio.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 completed one artifact-only Stage A while the separate H1-H6/T1 train-only design remains unauthorized.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1891,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loops 46/47 parked | Loop 48 Stage A authorization pending; Stage B design-only | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46/47 parked | Loop 48 artifact-only Stage A complete at descriptive F5; no rerun; Stage B design-only | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2063,7 +2063,7 @@
         <x:v>Failed: candidate did not improve by &gt;=0.05 and did not win all six items; complete control conjunction failed. Park scaling and do not open source test or session 2.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops 45, 26, 31, 33. Next diagnostic work order: Loop 48.</x:v>
+        <x:v>Loops 45, 26, 31, 33. Loop 48 artifact-only follow-up completed; predictive branch remains parked.</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
         <x:v>Preregistered at 881145d, authorized at 1c0e52c, and frozen at remote-green 54bdca9 before one target delivery. Event consumed; no rerun, larger model, or tuning authorized.</x:v>
@@ -2117,7 +2117,7 @@
         <x:v>Failed: the intact candidate did not beat every registered signal-free and corrupted-signal condition. No sensor-signal-dependence or brain-origin claim.</x:v>
       </x:c>
       <x:c r="K7" s="114" t="str">
-        <x:v>Loops 46 and 31. Route aggregate discrepancy to Loop 48 only.</x:v>
+        <x:v>Loops 46 and 31. Aggregate discrepancy routed to consumed Loop 48 Stage A; no rerun.</x:v>
       </x:c>
       <x:c r="L7" s="114" t="str">
         <x:v>Shared event consumed. No post-Loop-46 target open, matrix rerun, LLM/Neuro Token extension, or protected operation is authorized.</x:v>
@@ -2157,31 +2157,31 @@
         <x:v>diagnostic boundary, not decoding performance</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>Prepared the green hash-bound artifact-only contract and exact four-JSON Stage A request. The immutable H1-H5 portfolio now has an additive H1-H6 discrimination map: H1 is the fixed recipe, H6 is data quantity/diversity, and T1 is the orthogonal shortcut threat. F5 remains a phenotype, not a root cause.</x:v>
+        <x:v>Completed the green hash-bound artifact-only contract, dependency-light analyzer, exact authorization sequence, four-input SHA verification, frozen aggregate recomputation, ordered eight-class tree, bounded JSON writer, and one consumed Stage A. The immutable H1-H6/T1 Stage B design remains separate and unauthorized.</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Stage A: only four committed JSON artifacts totaling 155,545 bytes. Stage B design: a future grouped, disjoint fit/check partition only inside 55 source-train rows. No validation target, source test, session 2, S7, S20, or S25 contribution. Current pass consulted five public sources and performed zero protected/model operations.</x:v>
+        <x:v>Stage A read only four committed aggregate JSON artifacts totaling 155,545 bytes. It read no ignored output, cache member, array, target, checkpoint, private prediction, source test, session 2, S7, S20, S25, FIF, or MAT payload. Stage B remains train-only design research with no split or payload access.</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>Stage A evidence: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior. Stage B: 6 hypotheses, 5 evidence levels, 6 sequential stages, 1 shortcut threat, and 15 false authorizations. E3 requires practical-margin plus paired-uncertainty gates.</x:v>
+        <x:v>Stage A: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior; F5 selected; 0.016568875 sec; 23,429,120-byte peak RSS; 10,643 output bytes; zero model, training, target, network, stream, device, or hardware operations.</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Current gate: exact Stage A authorization sentence or hold. Future Stage B can reach at most E3 only after separate preregistration and authorization; its support vector must retain conflicts. Do not force one winner, create predictions after check labels, or reuse consumed validation.</x:v>
+        <x:v>Completed once: all identities and resource gates passed and the frozen tree selected descriptive F5. Root cause remains unresolved. The result is consumed; do not rerun, tune thresholds or seeds, reopen targets, inspect ignored payloads, or escalate the architecture. Stage B requires a new preregistration and authorization.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
-        <x:v>Loops 46/47 are consumed and parked. Stage A is independent. Stage B cannot inherit Stage A authorization. E4 and any brain-origin review route to Loop 35. Exact Stage B split, thresholds, inventory, and resource caps remain unfrozen.</x:v>
+        <x:v>Loops 46/47 are consumed and parked. Stage A is consumed and independent. Stage B cannot inherit Stage A authorization. E4 and any brain-origin review route to Loop 35. Exact Stage B split, thresholds, inventory, stopping rules, and resource caps remain unfrozen.</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Every authorization field is false. No analyzer, Stage A run, fixture, Stage B split, train/cache/signal/target read, model, training, prediction, checkpoint, scoring, S25, stream, device, hardware, claim upgrade, or rerun exists.</x:v>
+        <x:v>Authorized once at 5bae880 and implemented at ca21539; both push and PR CI runs were green before input access. Stage A is consumed with no rerun. Every Stage B authorization remains false. S25, source test, session 2, RW3, streams, devices, hardware, release, and scientific claim upgrades remain closed.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>Current discrimination document plus registry: 24,268 bytes; five public sources; one thread/worker; zero protected/model operations. Future Stage A cap: 30 sec, 256 MiB RSS, 1 MiB output. Stage B runtime/RSS/output/model caps are intentionally unfrozen.</x:v>
+        <x:v>Measured Stage A: 1 thread; 1 worker; 0.016568875 sec internal; 0.38 sec wall; 23,429,120-byte internal and 23,560,192-byte external peak RSS; 155,545 input bytes; 10,643 generated bytes; 30 sec / 256 MiB / 1 MiB caps all passed.</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>stage_a_request_prepared_unauthorized; stage_b_h1_h6_design_only; e3_margin_uncertainty_gate; t1_routes_loop35; sequential_compute; no_scientific_claim_upgrade</x:v>
+        <x:v>completed_artifact_only_descriptive_f5_no_root_cause; consumed_no_rerun; stage_b_h1_h6_design_only; t1_routes_loop35; no_scientific_claim_upgrade</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
-        <x:v>Preregistered; Authorization Pending</x:v>
+        <x:v>Complete; Artifact-Only F5 Phenotype</x:v>
       </x:c>
       <x:c r="P8" s="114" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -3281,7 +3281,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb09829ec07474c01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e7e95c29c6e4a5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4696,7 +4696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199044988de046af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8291c90607e94759"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6064,31 +6064,31 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="n">
-        <x:v>46215</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="B47" s="12" t="str">
-        <x:v>33-R1</x:v>
+        <x:v>48-R5</x:v>
       </x:c>
       <x:c r="C47" s="12" t="str">
-        <x:v>Spend the shared validation event once; hold execution and acquisition</x:v>
+        <x:v>Consume one artifact-only Stage A; retain F5 as a phenotype, not a root cause</x:v>
       </x:c>
       <x:c r="D47" s="12" t="str">
-        <x:v>Recommend nested 8/16/24/32/44/55 unique-sentence prefixes, at most three seeds and 18 fits, and matched priors. Freeze Loop 33 with Loop 26 before the first validation target opens; otherwise a later curve is exploratory. Duplicated arrays are not physical repeated acquisitions, and no public scaling exponent transfers to this tiny local design.</x:v>
+        <x:v>After separate green authorization and implementation milestones, one bounded pass verified four exact committed JSON artifacts and reproduced the frozen aggregate evidence. F5 triggered from 99.3477% primary blank output, six unstable prefix groups, and all three size-55 seeds losing to the prior.</x:v>
       </x:c>
       <x:c r="E47" s="12" t="str">
-        <x:v>docs/LOOP_33_PRIMARY_SOURCE_RESEARCH.md; registries/loop33_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
+        <x:v>docs/LOOP_48_FAILURE_LOCALIZATION_RESULT.md; registries/loop48_failure_localization_result.v0.json; Decision 0081; commits 5bae880/ca21539</x:v>
       </x:c>
       <x:c r="F47" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="G47" s="12" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>Make the exact Loop 25 decision; co-preregister Loop 26 and Loop 33 before any shared validation-target open</x:v>
+        <x:v>Draft a new Stage B preregistration or park; do not rerun Stage A</x:v>
       </x:c>
       <x:c r="I47" s="12" t="str">
-        <x:v>Planning only. 6 prefixes; 3-seed/18-fit ceiling; 4 conditions; 7 outcomes; 7 claims; 20 gates; 30 refusals; 23 authorization flags false. No protected access, model, training, score, physical-repetition study, or acquisition.</x:v>
+        <x:v>One thread/worker; 0.016568875 sec; 23,429,120-byte peak RSS; 10,643-byte report; zero protected/model/training operations. No causal root cause, neural advantage, decoding, transfer, real-time, EEG, device, or clinical claim.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -6564,16 +6564,34 @@
         <x:v>Design research only. Five public sources; one thread/worker; 24,268 document/registry bytes; 15 false authorizations; zero protected reads, models, training, predictions, or scoring. E3 is not brain origin; Loop 35 is required.</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="37"/>
-      <x:c r="B65" s="12"/>
-      <x:c r="C65" s="12"/>
-      <x:c r="D65" s="12"/>
-      <x:c r="E65" s="12"/>
-      <x:c r="F65" s="12"/>
-      <x:c r="G65" s="12"/>
-      <x:c r="H65" s="12"/>
-      <x:c r="I65" s="12"/>
+    <x:row r="65" ht="168" customHeight="1">
+      <x:c r="A65" s="40" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>48-R5</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>Consume one artifact-only Stage A; retain F5 as a phenotype, not a root cause</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>After separate green authorization and implementation milestones, one bounded pass verified four exact committed JSON artifacts and reproduced the frozen aggregate evidence. F5 triggered from 99.3477% primary blank output, six unstable prefix groups, and all three size-55 seeds losing to the prior.</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>docs/LOOP_48_FAILURE_LOCALIZATION_RESULT.md; registries/loop48_failure_localization_result.v0.json; Decision 0081; commits 5bae880/ca21539</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str">
+        <x:v>Draft a new Stage B preregistration or park; do not rerun Stage A</x:v>
+      </x:c>
+      <x:c r="I65" s="14" t="str">
+        <x:v>One thread/worker; 0.016568875 sec; 23,429,120-byte peak RSS; 10,643-byte report; zero protected/model/training operations. No causal root cause, neural advantage, decoding, transfer, real-time, EEG, device, or clinical claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37"/>
@@ -8080,7 +8098,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4131f11ce9f4dbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4b560c426f2406c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9551,7 +9569,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd4c863c66d4f88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0001209ad9204dac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10264,7 +10282,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R988952f36d7348e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126bc59398754e79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10830,7 +10848,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be39bf2be8e420f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62bf399797ff4f81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10899,7 +10917,7 @@
     </x:row>
     <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="98" t="str">
-        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 Stage A exact request prepared; additive H1-H6/T1 Stage B design-only | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
+        <x:v>20 loops | Loop 25 complete once | Loops 26/31/33 parked after registered negative result | Loop 48 artifact-only Stage A complete at descriptive F5 with no rerun; H1-H6/T1 Stage B design-only | Loop 44 artifact review complete | Every current execution_authorized flag remains false</x:v>
       </x:c>
       <x:c r="B3" s="99"/>
       <x:c r="C3" s="99"/>
@@ -11080,8 +11098,8 @@
         <x:v>Failed and parked: candidate was 0.186942 worse than the train-only prior, not &gt;=0.05 better. The complete attribution and scaling conjunctions also failed. No restart, retuning, larger model, source-test/session-2/S25 open, or rerun is authorized.</x:v>
       </x:c>
       <x:c r="K6" s="114" t="str">
-        <x:v>Loops 25, 31, 33 and scientific 45-47.
-Next: Loop 48 artifact-first failure localization, separately authorized.</x:v>
+        <x:v>Loops 25, 31, 33 and scientific 45-48.
+Loop 48 artifact-only Stage A is consumed; no rerun.</x:v>
       </x:c>
       <x:c r="L6" s="114" t="str">
         <x:v>Authorized once at 1c0e52c. Implementation 91409bd and ledger correction 4015677 were remotely green. Prediction-freeze 54bdca9 was remotely green before one target delivery and score. Event consumed; no rerun or post-target tuning.</x:v>
@@ -12327,7 +12345,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc38118f9bd4aa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45a291701b4a44e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
+++ b/docs/NEURODECODEKIT_20_LOOP_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R25a856a80ec948dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="Radfb28a0ce434b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R3ea0ae7e2d4f4862"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R384221d0d6ae46ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="R909fde647cd1435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="Rba7702250ef449a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R99302320762e4768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="Rdaf8ff3655084974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R1edc88c41ff145b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="Rba050d0bca4242fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R17ac8e1a857f45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loop Tracker" sheetId="2" r:id="R560d666da3274628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="3" r:id="R4473c383fb214f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="4" r:id="R85808d5c236349a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Template" sheetId="5" r:id="Rd82e0f74ba1441ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Bank" sheetId="6" r:id="R67c5a80080514f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R3d5e4b12fe07414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice Track" sheetId="8" r:id="R8253afd75f2a44a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 25-44" sheetId="9" r:id="R4acddd0809484244"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loops 45-64" sheetId="10" r:id="R2e4daaa095c64d13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1272,7 +1272,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20d480a0ce6e4116"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff68f25e3eb543e8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1310,7 +1310,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:I48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Loop ID"/>
@@ -1664,7 +1664,7 @@
         <x:v>Current numbered gate</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Loop 48 Stage A complete; descriptive F5; no rerun</x:v>
+        <x:v>Loop 53 acquisition passed; consumed; no rerun</x:v>
       </x:c>
       <x:c r="F8" s="29" t="str"/>
       <x:c r="G8" s="29" t="str"/>
@@ -1686,7 +1686,7 @@
         <x:v>Scope note</x:v>
       </x:c>
       <x:c r="B10" s="39" t="str">
-        <x:v>Loops 26/31/33 and scientific Loops 46/47 remain consumed and parked after the candidate lost to the no-signal prior. Loop 48 completed one four-JSON artifact-only Stage A: descriptive F5 output-distribution instability, 0.016568875 sec internal runtime, 23,429,120-byte peak RSS, and 10,643 output bytes. This is not a proven root cause and no rerun is authorized. Additive H1-H6/T1 Stage B research remains design-only, sequential, one-threaded, and unauthorized.</x:v>
+        <x:v>Loops 26/31/33 and scientific Loops 46/47 remain consumed and parked after the candidate lost to the no-signal prior. Loop 48 Stage A recorded descriptive F5, Stage B supported H4 stable nonseparability, and synthetic Stage C failed its absolute gates; every stage is consumed without rerun. Loop 53 then acquired and opaque-verified exactly four S20 files totaling 96,090,264 bytes in 3.629499 seconds at 63,225,856-byte peak RSS. That proves acquisition mechanics only: the bundle remains uninterpreted, and each Loop 54 content stage needs a separate exact Tier C decision.</x:v>
       </x:c>
       <x:c r="C10" s="39"/>
       <x:c r="D10" s="39"/>
@@ -1823,7 +1823,7 @@
     <x:mergeCell ref="B10:D10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35d675c5576945b4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08a3803428474a41"/>
 </x:worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </x:row>
     <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="161" t="str">
-        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 completed one artifact-only Stage A while the separate H1-H6/T1 train-only design remains unauthorized.</x:v>
+        <x:v>North star: one target-blind real neural-effect event at a time. Loops 46/47 are consumed and parked; Loop 48 A/B/C is consumed; Loop 53 acquisition mechanics passed once while S20 content and every scientific claim remain closed.</x:v>
       </x:c>
       <x:c r="B2" s="161"/>
       <x:c r="C2" s="161"/>
@@ -1891,7 +1891,7 @@
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="173" t="str">
-        <x:v>Loop 45 mechanics complete | Loops 46/47 parked | Loop 48 artifact-only Stage A complete at descriptive F5; no rerun; Stage B design-only | Loops 49-64 Not Started | one-thread default | S21 validation/session 2 and S7 consumed | S25 final-only | all execution_authorized=false</x:v>
+        <x:v>Loop 45 mechanics complete | Loops 46/47 parked | Loop 48 A/B/C consumed; no rerun | Loops 49-52 Not Started | Loop 53 acquisition passed; no rerun | Loops 54-56 planning only | one-thread default | S25 final-only | all future execution_authorized=false</x:v>
       </x:c>
       <x:c r="B3" s="174"/>
       <x:c r="C3" s="174"/>
@@ -2157,31 +2157,62 @@
         <x:v>diagnostic boundary, not decoding performance</x:v>
       </x:c>
       <x:c r="G8" s="114" t="str">
-        <x:v>Completed the green hash-bound artifact-only contract, dependency-light analyzer, exact authorization sequence, four-input SHA verification, frozen aggregate recomputation, ordered eight-class tree, bounded JSON writer, and one consumed Stage A. The immutable H1-H6/T1 Stage B design remains separate and unauthorized.</x:v>
+        <x:v>Completed one hash-bound post-outcome artifact-only Stage A under registries/loop48_failure_localization_contract.v0.json with src/neurodecodekit/experiments/failure_localization.py and registries/loop48_failure_localization_result.v0.json. The four exact committed inputs satisfied descriptive F5 output-distribution instability under the eight-class tree; root cause remained unresolved. The immutable registries/loop48_hypothesis_portfolio.v0.json and registries/loop48_hypothesis_discrimination.v0.json remain the design history. Stage B then completed once under registries/loop48_train_only_discrimination_contract.v0.json with a deterministic 44-fit/11-check split, 20 fits, 35 target-blind inferences, five priors, 41 prediction sets, and one post-freeze 11-target score. Registries/loop48_stage_b_prediction_freeze.v0.json became remotely green before target delivery. Registries/loop48_train_only_discrimination_result.v0.json supports H4 stable nonseparability, records evidence against H3 fixed timing offsets, and keeps H1/H2/H5/H6 unresolved at an E2 ceiling. Stage C research and implementation then froze the R1 temporal-context-starvation hypothesis with one 7,692-parameter 470 ms causal candidate, one 7,568-parameter zero-context ablation, and one 24/8/8 synthetic gate in registries/loop48_stage_c_synthetic_implementation.v0.json after zero-update local qualification. After fail-closed correction commit 2836ecc passed push CI 29467415680 and PR CI 29467416894, the gate ran once. The candidate reached final CER 0.433333 and 1/8 exact versus ablation CER 1.000000. The 0.566667 relative improvement and mechanics gates passed, but the absolute CER and exact-sequence gates failed. Docs/LOOP_48_STAGE_C_SYNTHETIC_RESULT.md and registries/loop48_stage_c_synthetic_result.v0.json record the consumed parked result with no rerun and zero real or protected reads.</x:v>
       </x:c>
       <x:c r="H8" s="114" t="str">
-        <x:v>Stage A read only four committed aggregate JSON artifacts totaling 155,545 bytes. It read no ignored output, cache member, array, target, checkpoint, private prediction, source test, session 2, S7, S20, S25, FIF, or MAT payload. Stage B remains train-only design research with no split or payload access.</x:v>
+        <x:v>Data: Consumed Stage A read and SHA-256 verified only four exact committed aggregate JSON artifacts totaling 155,545 bytes. Consumed Stage B made one SHA-256 pass over the exact 10,632,576-byte S21 session-1 sentence cache, delivered 44 source-train signal/target rows and 11 source-train check signal rows into isolated derivatives, froze predictions before targets, and delivered the same 11 check targets once after both freeze CI workflows were green. Consumed Stage C generated 40 synthetic rows in memory, used a 24/8/8 synthetic split, and performed zero raw-data, real-cache, real-signal, real-target, S24, or S25 operations. Validation, source test, session 2, S7, S20, S24, and S25 remained closed.
+Controls:
+- exact artifact bytes and hashes
+- ordered Stage A class precedence
+- deterministic 44-fit/11-check split
+- prediction-before-target freeze
+- train-only no-signal priors
+- exact-zero and timing-only controls
+- channel and check-row derangements
+- fit-target derangement
+- fixed time displacements
+- linear probes
+- five nested sizes and three fixed seeds
+- 2,048 exact sign assignments
+- no post-check tuning or rerun
+- Stage C candidate versus near-parameter-matched zero-context ablation
+- synthetic-only calibration before any protected contract</x:v>
       </x:c>
       <x:c r="I8" s="114" t="str">
-        <x:v>Stage A: primary blank 0.993477; candidate/prior CER 0.938177/0.751235; all-condition blank range 0.997146; 6/6 prefix groups disperse; 3/3 size-55 seeds lose to prior; F5 selected; 0.016568875 sec; 23,429,120-byte peak RSS; 10,643 output bytes; zero model, training, target, network, stream, device, or hardware operations.</x:v>
+        <x:v>- Stage A F5 phenotype
+- Stage B H1-H6 support vector
+- candidate and prior macro sentence CER
+- blank fraction
+- all-six-probe stability
+- fixed-shift sensitivity
+- nested-size behavior
+- exact paired p-values
+- runtime
+- peak RSS
+- generated bytes
+- protected access counters
+- Stage C receptive field and parameter-gap identity
+- Stage C candidate and ablation final CER and exact sequences
+- synthetic determinism, causality, padding, output-length, mutation, resume, and replay gates</x:v>
       </x:c>
       <x:c r="J8" s="114" t="str">
-        <x:v>Completed once: all identities and resource gates passed and the frozen tree selected descriptive F5. Root cause remains unresolved. The result is consumed; do not rerun, tune thresholds or seeds, reopen targets, inspect ignored payloads, or escalate the architecture. Stage B requires a new preregistration and authorization.</x:v>
+        <x:v>Acceptance: Stage A recorded one descriptive failure class. Stage B recorded one exact H1-H6 support vector after a remotely green prediction freeze without using validation, source test, session 2, S24, or S25 and without changing any rule after the 11 train-check targets opened. Stage C executed one synthetic temporal-context comparison after fresh remote-green correction CI; the relative candidate-ablation gate and mechanics checks passed, while the absolute CER and exact-sequence gates failed.
+Kill/Park: The consumed Stage B supports stable nonseparability, no causal or linear size-44 probe clears its prior, and H6 nonsaturation does not pass. Apply Loop 50 route L50-R05 and park S24 acquisition for this model family. Consumed Stage C failed both absolute synthetic gates, so do not rerun, tune from final outcomes, or escalate this candidate into protected evidence without a separate prospective Tier C decision.</x:v>
       </x:c>
       <x:c r="K8" s="114" t="str">
-        <x:v>Loops 46/47 are consumed and parked. Stage A is consumed and independent. Stage B cannot inherit Stage A authorization. E4 and any brain-origin review route to Loop 35. Exact Stage B split, thresholds, inventory, stopping rules, and resource caps remain unfrozen.</x:v>
+        <x:v>Loops: 46, 47</x:v>
       </x:c>
       <x:c r="L8" s="114" t="str">
-        <x:v>Authorized once at 5bae880 and implemented at ca21539; both push and PR CI runs were green before input access. Stage A is consumed with no rerun. Every Stage B authorization remains false. S25, source test, session 2, RW3, streams, devices, hardware, release, and scientific claim upgrades remain closed.</x:v>
+        <x:v>Stage A authorization commit 5bae880 and implementation commit ca21539 were remotely green before one consumed execution; Stage A has no rerun authorized. Stage B was unable to inherit Stage A authorization and received its own exact decision at commit 8d17342. Implementation commit 1d840e3 passed push CI 29461579009 and PR CI 29461580293 before protected access. Hash-only freeze commit 00215b1 passed push CI 29461934145 and PR CI 29461935560 before the same 11 check targets opened once. Stage B is consumed with no rerun. Stage C research commit 9579be9 passed push and PR CI. Implementation commit 59b30a3 also passed push and PR CI. The first invocation failed closed before spending the calibration. Correction commit 2836ecc then passed push CI 29467415680 and PR CI 29467416894 before one four-fit synthetic calibration ran. Stage C is consumed and parked with no rerun. No S21 cache stat/hash/member/target read, 44-row reuse, 11-row reopen, validation/source-test/session-2/S24/S25 access, real training/inference/scoring, larger model, download, device, hardware, or claim upgrade is authorized. Execution_authorized remains false because no protected or roadmap experiment is open.</x:v>
       </x:c>
       <x:c r="M8" s="114" t="str">
-        <x:v>Measured Stage A: 1 thread; 1 worker; 0.016568875 sec internal; 0.38 sec wall; 23,429,120-byte internal and 23,560,192-byte external peak RSS; 155,545 input bytes; 10,643 generated bytes; 30 sec / 256 MiB / 1 MiB caps all passed.</x:v>
+        <x:v>Consumed Stage A measured 0.016568875 seconds, 23,429,120-byte peak RSS, and 10,643 generated bytes. Consumed Stage B used one thread and worker, 20 fits, 4,800 optimizer steps, 35 target-blind inferences, 41 prediction sets, 185.354233 parameter-update seconds, 190.140486 cumulative execution seconds through freeze, 483,540,992-byte maximum peak RSS, 9,623,773 total generated execution-artifact bytes, one 10,632,576-byte cache hash pass, and zero download bytes. Consumed Stage C used one thread and worker, four fits, 1,680 optimizer steps, eight inference runs, 7.829308 seconds, 310,509,568-byte peak RSS, 83,132 generated bytes, and zero real-data downloads. No Stage C rerun resource is open.</x:v>
       </x:c>
       <x:c r="N8" s="206" t="str">
-        <x:v>completed_artifact_only_descriptive_f5_no_root_cause; consumed_no_rerun; stage_b_h1_h6_design_only; t1_routes_loop35; no_scientific_claim_upgrade</x:v>
+        <x:v>consumed diagnostics; no root-cause or neural claim</x:v>
       </x:c>
       <x:c r="O8" s="215" t="str">
-        <x:v>Complete; Artifact-Only F5 Phenotype</x:v>
+        <x:v>Complete A/B; Stage C Consumed and Parked</x:v>
       </x:c>
       <x:c r="P8" s="114" t="str">
         <x:v>https://facebookresearch.github.io/brain2qwerty/assets/brain2qwerty_v2.pdf
@@ -2211,43 +2242,48 @@
         <x:v>development cohort qualification only</x:v>
       </x:c>
       <x:c r="G9" s="114" t="str">
-        <x:v>Metadata selector, exact byte plan, task/license/identity audit, preregistration, and bounded acquisition request for one nonfinal MEG participant.</x:v>
+        <x:v>Planning research in docs/LOOP_49_PRIMARY_SOURCE_RESEARCH.md and registries/loop49_research_boundary.v0.json selects one exact S24 session-2 block-2 MEG FIF/log bundle from pinned metadata, defines a text-grouped 16-selection/remainder-fit development split, and leaves preregistration, acquisition request, qualification, and execution pending.</x:v>
       </x:c>
       <x:c r="H9" s="114" t="str">
-        <x:v>Data: Public metadata first; future two-file single-FIF/log bundle preferred under 1.25 GiB; S25 remains physically final-only.
+        <x:v>Data: Public metadata only. S24 session 2 block 2 is the preferred permanently development-only candidate: two exact files totaling 1,048,579,727 bytes. No S24 local path or payload was inspected; S25 remains physically final-only.
 Controls:
 - exclude S21 S7 S20 S25
 - single complete FIF/log pair
 - task and modality match
-- subject exclusion audit
+- subject exclusion and alias audit
+- S24 permanently development-only
+- canonical sentence-text grouping across people
+- exclude S21 fit rows matching future S24 selection text
 - dry-run exact bytes
 - no backup substitution</x:v>
       </x:c>
       <x:c r="I9" s="114" t="str">
         <x:v>- eligible candidates
-- files
-- bytes
-- sessions
-- trial floor
+- exact files and hashes
+- exact bytes and cap margin
+- canonical identity
+- usable unique-trial floor
+- fit and selection sentence groups
+- source-text overlap
 - license
-- identity overlap
-- unavailable fields</x:v>
+- unavailable fields
+- protected access counters</x:v>
       </x:c>
       <x:c r="J9" s="114" t="str">
-        <x:v>Accept: One eligible development participant has exact identities, &gt;=48 usable trials, compatible task/modality, explicit license, and total planned bytes within cap.
-Kill/Park: If no candidate qualifies, do not repurpose S25; return to public-data search or multi-session S21 mechanics without a generalization claim.</x:v>
+        <x:v>Acceptance: After separate acquisition and redacted audit, S24 has exact identities, &gt;=48 usable unique trials, compatible task/modality/channels/geometry, explicit license, deterministic text-group split, and total bytes within cap.
+Kill/Park: If S24 fails the &gt;=48 unique-row, identity, hash, channel, geometry, resource, or alignment gate, do not open a backup and do not repurpose S25; park or prepare a versioned amendment without a generalization claim.</x:v>
       </x:c>
       <x:c r="K9" s="114" t="str">
         <x:v>Loops: 47</x:v>
       </x:c>
       <x:c r="L9" s="114" t="str">
-        <x:v>Candidate selection and storage capacity are not download permission; exact acquisition needs a separate dry-run and --execute authorization.</x:v>
+        <x:v>Metadata selection and storage capacity are not download permission. Loop 49 remains Not Started: every authorization is false, Decision 0083 keeps new acquisition after Loop 48 Stage B, and exact acquisition still needs a separately green dry-run/--execute decision. No S24 stat, hash, header, signal, MAT, target, split, model, training, scoring, or backup substitution is authorized.</x:v>
       </x:c>
       <x:c r="M9" s="114" t="str">
-        <x:v>metadata planning zero download; future preferred &lt;=1.25 GiB; absolute cumulative user envelope remains 10 GB</x:v>
+        <x:v>Metadata planning used one thread/worker, 3.51 seconds, 62,685,184-byte peak RSS, and zero payload bytes. The future exact S24 bundle is 1,048,579,727 bytes under a 1.25 GiB cap, 20 GiB free-disk floor, and 10 GB cumulative user envelope.</x:v>
       </x:c>
       <x:c r="N9" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; S24 parked for this model family</x:v>
       </x:c>
       <x:c r="O9" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -2278,43 +2314,47 @@
         <x:v>multi-source development evidence only</x:v>
       </x:c>
       <x:c r="G10" s="114" t="str">
-        <x:v>Participant-grouped train/selection protocol, fixed architecture, source-balanced losses, no-signal priors, and identity/corruption controls.</x:v>
+        <x:v>Primary-source design now freezes a global text-group firewall, five-fold historical S21 out-of-fold diagnostic, 16-group S24 development qualification, equal-person loss, one shared causal candidate family, fixed controls, an exact 20-parameter-update inventory, and a remote-green prediction firewall; exact execution remains future work.</x:v>
       </x:c>
       <x:c r="H10" s="114" t="str">
-        <x:v>Data: Authorized train and selection partitions from S21 plus the Loop 49 development participant; S25 remains unopened.
+        <x:v>Data: Historically used S21 source-train rows plus separately qualified S24 development-fit and selection partitions only; S21 validation/source-test/session 2 stay closed and S25 remains unopened.
 Controls:
-- participant-grouped splits
-- participant-balanced sampling
-- source-only prior
-- pooled prior
+- global canonical sentence-text grouping across people
+- five-fold S21 historical out-of-fold diagnostic
+- participant-balanced 0.5/0.5 loss
+- pooled and per-participant no-signal priors
+- S21-only neural comparator
 - zero signal
 - participant-ID-only
-- channel and time derangements</x:v>
+- channel and time derangements
+- timing-only
+- parameter-matched linear CTC</x:v>
       </x:c>
       <x:c r="I10" s="114" t="str">
-        <x:v>- per-person macro CER
-- worst-person CER
-- pooled CER
-- prior margins
-- control margins
+        <x:v>- S21 historical out-of-fold macro CER
+- S24 development-selection macro CER
+- worst-person CER and no-signal margin
+- pooled CER descriptive only
+- source-only and control margins
+- seed stability
 - parameter count
-- training cost</x:v>
+- runtime RSS bytes</x:v>
       </x:c>
       <x:c r="J10" s="114" t="str">
-        <x:v>Accept: A single frozen candidate beats matched priors and corruptions on every development person without participant-conditioned architecture changes.
-Kill/Park: If pooled gain hides a person-level loss or participant identity predicts targets, park transfer and do not open S25.</x:v>
+        <x:v>Acceptance: Primary seed 5001 beats the strongest no-signal prior by &gt;=0.05 macro CER and strictly beats registered corruptions on both development people; worst-person passes, S24 improves over the S21-only neural comparator, S21 degrades by &lt;=0.02, and stability seeds preserve the S24 no-signal direction without replacing the primary.
+Kill/Park: If Stage B routes to mechanics repair or plateau, compatibility fails, any person-level gate fails, participant identity erases the margin, or pooled gain hides a person-level loss, park Loop 50 and do not prepare or open S25.</x:v>
       </x:c>
       <x:c r="K10" s="114" t="str">
-        <x:v>Loops: 49</x:v>
+        <x:v>Loops: 48, 49</x:v>
       </x:c>
       <x:c r="L10" s="114" t="str">
-        <x:v>Requires exact participant/split authorization and a frozen target-blind model-selection protocol.</x:v>
+        <x:v>Planning is complete but the experiment remains Not Started. Loop 48 Stage B must close or park, S24 needs separately gated acquisition and qualification, and an exact Loop 50 preregistration/authorization/prediction-freeze sequence must be green before fit or selection targets.</x:v>
       </x:c>
       <x:c r="M10" s="114" t="str">
-        <x:v>one thread; one worker; &lt;=10,000 parameters; &lt;=60 CPU minutes; &lt;=2 GiB RSS; &lt;=64 MiB generated</x:v>
+        <x:v>one thread; one worker; 20 planned and &lt;=24 absolute parameter-update runs; &lt;=10,000 parameters; &lt;=60 CPU minutes; &lt;=2 GiB RSS; &lt;=64 MiB generated</x:v>
       </x:c>
       <x:c r="N10" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; same-family route parked</x:v>
       </x:c>
       <x:c r="O10" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -2368,7 +2408,7 @@
 - authorization flags</x:v>
       </x:c>
       <x:c r="J11" s="114" t="str">
-        <x:v>Accept: All execution inputs and claim rules are immutable, every target-free prediction path is ready, and independent review finds zero target-dependent choice.
+        <x:v>Acceptance: All execution inputs and claim rules are immutable, every target-free prediction path is ready, and independent review finds zero target-dependent choice.
 Kill/Park: Any unfrozen model or target-dependent field keeps S25 sealed and returns the packet for versioned amendment.</x:v>
       </x:c>
       <x:c r="K11" s="114" t="str">
@@ -2381,7 +2421,7 @@
         <x:v>artifact-only; one thread; &lt;=10 minutes; &lt;=16 MiB generated; future S25 bundle exactly 1,009,939,983 bytes</x:v>
       </x:c>
       <x:c r="N11" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; S25 sealed and final-only</x:v>
       </x:c>
       <x:c r="O11" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -2434,7 +2474,7 @@
 - runtime RSS bytes</x:v>
       </x:c>
       <x:c r="J12" s="114" t="str">
-        <x:v>Accept: &gt;=48 unique final rows, &gt;=0.05 absolute macro-CER improvement over prior, p &lt;=0.05, and strict wins over zero-signal, channel-deranged, and time-displaced controls.
+        <x:v>Acceptance: &gt;=48 unique final rows, &gt;=0.05 absolute macro-CER improvement over prior, p &lt;=0.05, and strict wins over zero-signal, channel-deranged, and time-displaced controls.
 Kill/Park: Any failed gate records a negative zero-shot result; S25 becomes consumed and can never become calibration or development data.</x:v>
       </x:c>
       <x:c r="K12" s="114" t="str">
@@ -2447,7 +2487,7 @@
         <x:v>one thread; one worker; exact 1,009,939,983-byte acquisition cap; &lt;=30 inference minutes; &lt;=2 GiB RSS; &lt;=64 MiB generated</x:v>
       </x:c>
       <x:c r="N12" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>not started; S25 unopened</x:v>
       </x:c>
       <x:c r="O12" s="215" t="str">
         <x:v>Not Started</x:v>
@@ -2478,47 +2518,50 @@
         <x:v>fresh EEG mechanics only</x:v>
       </x:c>
       <x:c r="G13" s="114" t="str">
-        <x:v>Exact metadata, dry-run, checksum, complete BrainVision triplet/log acquisition, header audit, and no-target-open cache plan.</x:v>
+        <x:v>Consumed registries/loop53_acquisition_result.v0.json: one exact four-file transfer, opaque integrity hashes, isolated complete-bundle promotion, bounded private receipts, all ten gates passed, and no rerun. Header audit and cache planning remain in Loop 54.</x:v>
       </x:c>
       <x:c r="H13" s="114" t="str">
-        <x:v>Data: Previously selected S20 EEG bundle, approximately 96 MB within the combined S20 plus S25 1,106,030,247-byte plan.
+        <x:v>Data: Exact S20 session 2 block 2 BrainVision triplet plus companion MAT log at revision 88f9096c6ce3a3fb17cc7b8e3131ff7f96da5684: four files and 96,090,264 bytes acquired and opaque-verified once; payload interpretation remains closed.
 Controls:
-- complete triplet
+- complete four-file bundle
 - single participant
 - task match
-- license boundary
-- exact bytes
+- CC BY-NC 4.0 metadata boundary
+- exact path size and source identity
+- new isolated destination
 - no S7 reuse
-- no signal or target read before authorization</x:v>
+- opaque hash only
+- no header marker signal MAT target cache split or model operation</x:v>
       </x:c>
       <x:c r="I13" s="114" t="str">
-        <x:v>- files
-- bytes
-- checksums
-- channels
-- sampling rate
-- events planned
-- license
-- access counters</x:v>
+        <x:v>- metadata calls
+- network payload bytes
+- incremental disk peak
+- final files and bytes
+- integrity hashes
+- runtime
+- peak RSS
+- access counters
+- warnings and unavailable fields</x:v>
       </x:c>
       <x:c r="J13" s="114" t="str">
-        <x:v>Accept: Exact files and checksums match the preregistration, the complete bundle stays within cap, and no unauthorized target or signal access occurs.
-Kill/Park: Any missing companion, identity ambiguity, or byte/license mismatch parks acquisition without substituting S7 or another person.</x:v>
+        <x:v>Acceptance: The pinned public revision and license remain exact; exactly four regular files total 96,090,264 bytes and pass source-identity hashes within all caps; every forbidden parse, signal, target, cache, split, model, training, and scoring counter remains zero.
+Kill/Park: Any missing companion, identity/license mismatch, destination collision, cap breach, unauthorized read, partial transfer, or hash failure parks acquisition without substitution or rerun.</x:v>
       </x:c>
       <x:c r="K13" s="114" t="str">
         <x:v>Loops: 29</x:v>
       </x:c>
       <x:c r="L13" s="114" t="str">
-        <x:v>The user's storage allowance is not execute permission; acquisition needs exact --execute authorization.</x:v>
+        <x:v>The exact Tier C decision, green authorization commit 2a47bbc, green implementation commit 8ec5b1b, and one registered invocation are consumed. No Loop 53 rerun or Loop 54 content interpretation is authorized by this pass.</x:v>
       </x:c>
       <x:c r="M13" s="114" t="str">
-        <x:v>preferred exact selected bundle; cumulative new data &lt;=5 GB preferred and &lt;=10 GB absolute; one worker</x:v>
+        <x:v>one thread; one worker; 600 seconds; 512 MiB RSS; 128 MiB network payload; 256 MiB incremental disk peak; 1 MiB receipt; at least 2 GiB free disk</x:v>
       </x:c>
       <x:c r="N13" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>consumed acquisition mechanics only; no content or science</x:v>
       </x:c>
       <x:c r="O13" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Consumed; Acquisition Passed; No Rerun</x:v>
       </x:c>
       <x:c r="P13" s="114" t="str">
         <x:v>https://arxiv.org/abs/2502.17480
@@ -2546,10 +2589,10 @@
         <x:v>EEG identity and confound qualification</x:v>
       </x:c>
       <x:c r="G14" s="114" t="str">
-        <x:v>Trial map, channel/geometry/reference ledger, event timing, quality summaries, EOG/EMG/motion availability, and fail-closed claim ceiling.</x:v>
+        <x:v>Source-backed registries/loop54_eeg_trial_geometry_research.v0.json: strict VHDR-only metadata, target-blind VHDR+EEG quality with all channels retained, isolated target-bearing VMRK+MAT reconciliation, and aggregate closeout. Loop 54 does not create a split, model, or score.</x:v>
       </x:c>
       <x:c r="H14" s="114" t="str">
-        <x:v>Data: Authorized S20 headers and then signal/target members in a separately ordered pass; no S7 reopening.
+        <x:v>Data: Exact S20 session 2 block 2 bundle acquired and opaque-verified by Loop 53; every VHDR, EEG, VMRK, MAT, header, signal, target, geometry, event, and trial interpretation remains closed pending separate staged authorizations; no S7 reopening, and S21/S24/S25 remain forbidden.
 Controls:
 - event-log identity
 - channel units
@@ -2557,7 +2600,10 @@
 - bad/missing channels
 - EOG and EMG availability
 - keypress timing
-- target isolation</x:v>
+- target isolation
+- no hidden marker resolution
+- trial-unit pseudoreplication firewall
+- all-channel preservation</x:v>
       </x:c>
       <x:c r="I14" s="114" t="str">
         <x:v>- trials reconciled
@@ -2569,23 +2615,23 @@
 - usable-row floor</x:v>
       </x:c>
       <x:c r="J14" s="114" t="str">
-        <x:v>Accept: &gt;=48 unique trials have exact identity and every geometry/reference/confound field is known or explicitly unavailable with a bounded claim ceiling.
-Kill/Park: Missing peripheral controls block brain-specific attribution but may allow a narrower sensor-signal dependence test if preregistered.</x:v>
+        <x:v>Acceptance: &gt;=48 unique performed trials have exact identity; VHDR, EEG, and VMRK+MAT access stayed stage-isolated; all channels were retained; and every geometry/reference/confound field is known or explicitly unavailable under a bounded claim ceiling.
+Kill/Park: Any hidden sibling read, plaintext target leak, ambiguous trial identity, &lt;48 unique trials, event-window pseudoreplication, transform before audit, or cap breach parks. Missing peripheral controls block brain-specific attribution but may allow a narrower separately preregistered sensor-signal test.</x:v>
       </x:c>
       <x:c r="K14" s="114" t="str">
         <x:v>Loops: 53, 35, 36</x:v>
       </x:c>
       <x:c r="L14" s="114" t="str">
-        <x:v>Header, signal, and target stages remain separate authorizations.</x:v>
+        <x:v>Planning research only. Loop 53 completed cleanly; VHDR-only, target-blind EEG quality, and isolated VMRK+MAT reconciliation each still require a separate exact Tier C decision after a hash-bound implementation is pushed and remotely green. No S20 content stage, split, model, training, inference, or scoring is authorized now.</x:v>
       </x:c>
       <x:c r="M14" s="114" t="str">
-        <x:v>one thread; one worker; no new download; &lt;=1 GiB RSS; &lt;=32 MiB generated</x:v>
+        <x:v>one thread; one worker per stage; no new download or incremental payload; &lt;=1 GiB RSS; &lt;=32 MiB combined public generated output</x:v>
       </x:c>
       <x:c r="N14" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; real content unauthorized</x:v>
       </x:c>
       <x:c r="O14" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete; Acquisition Passed; Content Stages Unauthorized</x:v>
       </x:c>
       <x:c r="P14" s="114" t="str">
         <x:v>https://arxiv.org/abs/2502.17480
@@ -2610,48 +2656,52 @@
         <x:v>Can a tiny EEG model beat train-only priors and task-locked artifact controls on fresh S20 without borrowing a MEG claim?</x:v>
       </x:c>
       <x:c r="F15" s="200" t="str">
-        <x:v>bounded within-person EEG sensor-signal advantage</x:v>
+        <x:v>prospective bounded within-person causal pre-keypress EEG sensor-signal advantage, separated into performed-hand and performed-key endpoints</x:v>
       </x:c>
       <x:c r="G15" s="114" t="str">
-        <x:v>Participant-local split, tiny causal and linear models, no-signal priors, peripheral/corruption controls, exact uncertainty, and immutable report.</x:v>
+        <x:v>Planning artifact registries/loop55_eeg_neural_effect_research.v0.json freezes an ordered causal hand gate, harder 29-key gate, performed-action target, post-keypress diagnostic, grouped trial-level split recommendation, twelve-condition matched control matrix, exact one-shot scoring order, hypothesis router, claim ceiling, and resource limits. It does not create a split or implement or run a model.</x:v>
       </x:c>
       <x:c r="H15" s="114" t="str">
-        <x:v>Data: Fresh S20 only under the Loop 54 claim ceiling; S7 stays consumed and excluded from selection.
+        <x:v>Data: Future fresh S20 session-2 block-2 only after Loop 54 closes cleanly; Loop 53 acquisition passed but interpretation remains closed, S7 remains consumed, and S21/S24/S25 stay excluded.
 Controls:
-- train-only prior
+- strongest train-only global or position-length prior
 - zero signal
-- time displacement
+- whole-trial row derangement
 - channel derangement
-- keypress timing only
-- available EOG/EMG controls
-- linear comparator</x:v>
+- nonwrapping pre-keypress time displacement
+- keypress count position and timing only
+- train-pairing derangement
+- EOG-only when available
+- linear comparator
+- noncausal centered-window diagnostic</x:v>
       </x:c>
       <x:c r="I15" s="114" t="str">
-        <x:v>- macro CER or exact key accuracy
+        <x:v>- macro trial hand error rate
+- macro trial keypress-aligned CER
 - prior margin
 - control margins
-- paired inference
+- exact paired trial-level inference
 - worst-class recall
 - runtime and RSS</x:v>
       </x:c>
       <x:c r="J15" s="114" t="str">
-        <x:v>Accept: The frozen neural model beats the no-signal prior and every available task-locked/peripheral control under a preregistered paired rule.
-Kill/Park: If unavailable peripheral controls could explain the effect, cap the claim at sensor dependence and do not call it brain-specific or home-ready.</x:v>
+        <x:v>Acceptance: Each prospectively frozen causal endpoint must clear its practical margin over the strongest train-only no-signal prior and strictly beat every applicable task-locked peripheral and corruption control under exact paired trial-level tests. The centered post-keypress diagnostic cannot rescue a causal failure.
+Kill/Park: Any leakage ordering or cap failure invalidates the run. If only hand passes, retain a performed-hand sensor effect only; if only the centered diagnostic passes, report task-aligned or post-keypress information; missing peripheral controls cap every result below brain-specific origin.</x:v>
       </x:c>
       <x:c r="K15" s="114" t="str">
         <x:v>Loops: 54</x:v>
       </x:c>
       <x:c r="L15" s="114" t="str">
-        <x:v>Requires a fresh preregistration and exact training/target authorization; no EEG model run is authorized now.</x:v>
+        <x:v>Planning research only. Loop 53 acquisition passed and Loop 54 must still close; an exact Loop 55 preregistration, separate exact Tier C authorization, green implementation, protected split and target order, and hash-frozen one-shot final score are required. No S20 interpretation, split, target, model, training, inference, or score is authorized now.</x:v>
       </x:c>
       <x:c r="M15" s="114" t="str">
         <x:v>one thread; one worker; &lt;=10,000 parameters; &lt;=45 CPU minutes; &lt;=1 GiB RSS; &lt;=64 MiB generated</x:v>
       </x:c>
       <x:c r="N15" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; neural effect unavailable</x:v>
       </x:c>
       <x:c r="O15" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete; Loop 54 Dependent</x:v>
       </x:c>
       <x:c r="P15" s="114" t="str">
         <x:v>https://arxiv.org/abs/2502.17480
@@ -2679,43 +2729,45 @@
         <x:v>qualified cross-modality boundary, not equivalence</x:v>
       </x:c>
       <x:c r="G16" s="114" t="str">
-        <x:v>Matched requirement matrix for identity, timing, geometry, preprocessing, signal effect, controls, resources, and user burden.</x:v>
+        <x:v>docs/LOOP_56_PRIMARY_SOURCE_RESEARCH.md plus registries/loop56_cross_modality_accessibility_research.v0.json: five verdict classes, a 12-level capability ladder, an 18-dimension matrix, a 16-field claim sentence, an at-home conjunction, and a future artifact-only outcome router.</x:v>
       </x:c>
       <x:c r="H16" s="114" t="str">
         <x:v>Data: Closed aggregate Loop 46-55 reports only; no pooled MEG/EEG training or new payload access.
 Controls:
-- same claim vocabulary
-- modality-specific baselines
-- no score pooling
-- no channel equivalence
-- no device extrapolation
-- negative result retention</x:v>
+- same 16-field claim vocabulary
+- five explicit transfer classes
+- 12 non-skippable capability levels
+- modality-specific baselines and controls
+- no score pooling or inherited threshold
+- no channel, representation, device, causal, latency, home, or clinical equivalence
+- negative and unavailable result retention</x:v>
       </x:c>
       <x:c r="I16" s="114" t="str">
-        <x:v>- requirements passed per modality
-- claim overlap
-- unavailable fields
-- resource ratio
-- candidate home prerequisites</x:v>
+        <x:v>- verdict-class counts by modality and dimension
+- satisfied and unavailable capability levels
+- claim-field completeness
+- warnings and refusals
+- homologous resource ratios or explicit unavailability
+- at-home conjunction completeness</x:v>
       </x:c>
       <x:c r="J16" s="114" t="str">
-        <x:v>Accept: Every cross-modality statement identifies the exact shared interface and the nontransferable acquisition/scientific assumptions.
+        <x:v>Acceptance: All 18 dimensions and 12 capability levels are classified from hash-bound aggregate evidence; every claim carries all 16 fields; external and local evidence remain separate; no pooled score, inherited threshold, channel equivalence, device extrapolation, or continuous-to-causal shortcut is allowed.
 Kill/Park: If only mechanics transfer, publish mechanics only and keep decoding/home claims unavailable.</x:v>
       </x:c>
       <x:c r="K16" s="114" t="str">
         <x:v>Loops: 55</x:v>
       </x:c>
       <x:c r="L16" s="114" t="str">
-        <x:v>No new data, model, device, or home-use operation is authorized.</x:v>
+        <x:v>Planning research only. Final Loop 56 execution waits for a closed Loop 55 result, an exact hash-bound aggregate-only preregistration, and a separate exact Tier C scientific-claim decision committed, pushed, and remotely green. No raw, ignored, protected, cache, target, prediction, checkpoint, model, score recomputation, download, network, stream, device, participant, home, release, or claim operation is authorized now.</x:v>
       </x:c>
       <x:c r="M16" s="114" t="str">
         <x:v>artifact-only; one thread; &lt;=10 minutes; &lt;=16 MiB generated</x:v>
       </x:c>
       <x:c r="N16" s="206" t="str">
-        <x:v>planned_not_authorized</x:v>
+        <x:v>planning only; mechanics/interfaces provisional</x:v>
       </x:c>
       <x:c r="O16" s="215" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planning Research Complete; Loop 55 Result Dependent</x:v>
       </x:c>
       <x:c r="P16" s="114" t="str">
         <x:v>https://arxiv.org/abs/2502.17480
@@ -3281,7 +3333,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e7e95c29c6e4a5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee163656d334de4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4696,7 +4748,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8291c90607e94759"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7237ecc41b8b4304"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6092,33 +6144,15 @@
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="37" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B48" s="12" t="str">
-        <x:v>34-R1</x:v>
-      </x:c>
-      <x:c r="C48" s="12" t="str">
-        <x:v>Keep confidence unavailable until independent evidence exists; hold execution</x:v>
-      </x:c>
-      <x:c r="D48" s="12" t="str">
-        <x:v>Separate raw ranking, calibrated probability, selective policy, conformal bounded risk, revision stability, and product-visible confidence. Reserve the six real validation rows for Loops 26/31/33. Recommend fresh 128/64/256 synthetic partitions and one final open only after every score, mapping, threshold, policy, prediction, and hash freezes.</x:v>
-      </x:c>
-      <x:c r="E48" s="12" t="str">
-        <x:v>docs/LOOP_34_PRIMARY_SOURCE_RESEARCH.md; registries/loop34_research_boundary.v0.json; docs/LOOPS_25_44_ROADMAP.md</x:v>
-      </x:c>
-      <x:c r="F48" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G48" s="12" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
-      <x:c r="H48" s="12" t="str">
-        <x:v>Make the exact Loop 25 decision; Loop 34 remains blocked on Loop 30/31 execution evidence and a separately authorized fresh synthetic confidence lane</x:v>
-      </x:c>
-      <x:c r="I48" s="12" t="str">
-        <x:v>Planning only. 7 semantics; 8 score/control roles; recommended 128/64/256 partitions; 8 outcomes; 7 claims; 20 gates; 30 refusals; 26 authorization flags false. Confidence unavailable; no fixture, fit, target, scoring, or product-confidence operation.</x:v>
-      </x:c>
+      <x:c r="A48" s="37"/>
+      <x:c r="B48" s="12"/>
+      <x:c r="C48" s="12"/>
+      <x:c r="D48" s="12"/>
+      <x:c r="E48" s="12"/>
+      <x:c r="F48" s="12"/>
+      <x:c r="G48" s="12"/>
+      <x:c r="H48" s="12"/>
+      <x:c r="I48" s="12"/>
     </x:row>
     <x:row r="49" ht="198" hidden="0" customHeight="1">
       <x:c r="A49" s="37" t="n">
@@ -6594,15 +6628,33 @@
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="37"/>
-      <x:c r="B66" s="12"/>
-      <x:c r="C66" s="12"/>
-      <x:c r="D66" s="12"/>
-      <x:c r="E66" s="12"/>
-      <x:c r="F66" s="12"/>
-      <x:c r="G66" s="12"/>
-      <x:c r="H66" s="12"/>
-      <x:c r="I66" s="12"/>
+      <x:c r="A66" s="37" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B66" s="12" t="str">
+        <x:v>53-R2</x:v>
+      </x:c>
+      <x:c r="C66" s="12" t="str">
+        <x:v>Consume one exact S20 acquisition-only pass; prohibit rerun and content interpretation</x:v>
+      </x:c>
+      <x:c r="D66" s="12" t="str">
+        <x:v>The pinned four-file bundle passed revision, availability, license, path, exact-size, Git/LFS/Xet, resource, isolation, and receipt gates. Exactly 96,090,264 bytes were acquired and opaque-verified once; every interpretive and model counter remained zero.</x:v>
+      </x:c>
+      <x:c r="E66" s="12" t="str">
+        <x:v>docs/LOOP_53_ACQUISITION_RESULT.md; registries/loop53_acquisition_result.v0.json; commits 2a47bbc and 8ec5b1b</x:v>
+      </x:c>
+      <x:c r="F66" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G66" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H66" s="12" t="str">
+        <x:v>Loop 54 content only after a separate exact Tier C decision and green implementation</x:v>
+      </x:c>
+      <x:c r="I66" s="12" t="str">
+        <x:v>3.629499 sec; 63,225,856-byte peak RSS; 102,035,529-byte peak disk; mechanics only; no EEG signal, target, decoding, neural, real-time, device, home, or clinical claim.</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37"/>
@@ -8098,7 +8150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4b560c426f2406c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e6eac95b3e64201"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9569,7 +9621,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0001209ad9204dac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27ab88671ce7419d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10282,7 +10334,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126bc59398754e79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6084ca64231846dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10506,7 +10558,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="48" t="str">
-        <x:v>Parallel to Loop 24. Its frozen target-free run is now parked after 65.154951 s exceeded the 60 s cap; float32 is retained, seed 2401 is consumed, and seed 2402 stayed unopened. RW3 Stage A remains unauthorized at 163ff2f, and RW4/S20 remains blocked. Real data, targets, training, energy, streams, devices, and hardware are not authorized.</x:v>
+        <x:v>Parallel to Loop 24. Its frozen target-free run remains parked after exceeding the time cap. The older broad RW4/S20 benchmark is superseded and parked; Loop 53 completed one exact acquisition-only pass, but S20 headers, signals, targets, training, streams, devices, and hardware remain unauthorized.</x:v>
       </x:c>
       <x:c r="B2" s="48"/>
       <x:c r="C2" s="48"/>
@@ -10673,22 +10725,22 @@
         <x:v>Does one fresh typing block beat prior and shuffle controls?</x:v>
       </x:c>
       <x:c r="D9" s="69" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Parked</x:v>
       </x:c>
       <x:c r="E9" s="57" t="str">
-        <x:v>One-time S20 event-level aggregate report.</x:v>
+        <x:v>Superseded by the exact Loop 53 acquisition-only result; no event-level report, cache, model, or score was produced.</x:v>
       </x:c>
       <x:c r="F9" s="57" t="str">
-        <x:v>Explicit approval; exactly 4 files/96,090,264 bytes; no CER/WER.</x:v>
+        <x:v>Loop 53 transferred four files and 96,090,264 bytes once with zero interpretive/model counters. Any S20 content stage now belongs to Loop 54 and requires separate authorization.</x:v>
       </x:c>
       <x:c r="G9" s="57" t="str">
-        <x:v>User approval + RW2</x:v>
+        <x:v>Loop 53 consumed; Loop 54 separately gated</x:v>
       </x:c>
       <x:c r="H9" s="57" t="str">
-        <x:v>Within-recording event evidence at most</x:v>
+        <x:v>Acquisition mechanics only; no EEG scientific claim</x:v>
       </x:c>
       <x:c r="I9" s="57" t="str">
-        <x:v>docs/FRESH_EEG_BENCHMARK_S20_APPROVAL_PACKET.md</x:v>
+        <x:v>docs/LOOP_53_ACQUISITION_RESULT.md</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="61.5" customHeight="1">
@@ -10848,7 +10900,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62bf399797ff4f81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf046effdecb44188"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12345,7 +12397,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45a291701b4a44e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16621b026b14bfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>